--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6725,7 +6725,7 @@
         <v>27</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>27</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6719,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>27</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -21193,30 +21193,74 @@
       <c r="C183" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D183" s="52"/>
-      <c r="E183" s="52"/>
-      <c r="F183" s="52"/>
-      <c r="G183" s="53"/>
-      <c r="H183" s="52"/>
-      <c r="I183" s="52"/>
-      <c r="J183" s="52"/>
-      <c r="K183" s="52"/>
-      <c r="L183" s="52"/>
-      <c r="M183" s="53"/>
+      <c r="D183" s="52">
+        <v>16897.53</v>
+      </c>
+      <c r="E183" s="52">
+        <v>5491.7</v>
+      </c>
+      <c r="F183" s="52">
+        <v>11405.829999999998</v>
+      </c>
+      <c r="G183" s="53">
+        <v>0.6749998372543206</v>
+      </c>
+      <c r="H183" s="52">
+        <v>9226.27</v>
+      </c>
+      <c r="I183" s="52">
+        <v>3702.78</v>
+      </c>
+      <c r="J183" s="52">
+        <v>2977.1100000000006</v>
+      </c>
+      <c r="K183" s="52">
+        <v>2335.9700000000003</v>
+      </c>
+      <c r="L183" s="52">
+        <v>641.1400000000003</v>
+      </c>
+      <c r="M183" s="53">
+        <v>0.2153565034546927</v>
+      </c>
       <c r="N183" s="53"/>
-      <c r="O183" s="52"/>
-      <c r="P183" s="52"/>
-      <c r="Q183" s="52"/>
-      <c r="R183" s="53"/>
-      <c r="S183" s="54"/>
-      <c r="T183" s="54"/>
-      <c r="U183" s="54"/>
-      <c r="V183" s="53"/>
+      <c r="O183" s="52">
+        <v>6249.16</v>
+      </c>
+      <c r="P183" s="52">
+        <v>1366.81</v>
+      </c>
+      <c r="Q183" s="52">
+        <v>4882.35</v>
+      </c>
+      <c r="R183" s="53">
+        <v>0.7812810041669601</v>
+      </c>
+      <c r="S183" s="54">
+        <v>125.17</v>
+      </c>
+      <c r="T183" s="54">
+        <v>23.75</v>
+      </c>
+      <c r="U183" s="54">
+        <v>101.42</v>
+      </c>
+      <c r="V183" s="53">
+        <v>0.8102580490532876</v>
+      </c>
       <c r="W183" s="53"/>
-      <c r="X183" s="55"/>
-      <c r="Y183" s="55"/>
-      <c r="Z183" s="53"/>
-      <c r="AA183" s="56"/>
+      <c r="X183" s="55">
+        <v>75.32294736842105</v>
+      </c>
+      <c r="Y183" s="55">
+        <v>61.286703843093385</v>
+      </c>
+      <c r="Z183" s="53">
+        <v>0.3257</v>
+      </c>
+      <c r="AA183" s="56">
+        <v>0.454</v>
+      </c>
       <c r="AB183" s="57"/>
       <c r="AD183" s="35"/>
       <c r="AE183" s="35"/>
@@ -21596,32 +21640,74 @@
       <c r="C190" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D190" s="52"/>
-      <c r="E190" s="52"/>
-      <c r="F190" s="52"/>
-      <c r="G190" s="53"/>
-      <c r="H190" s="52"/>
-      <c r="I190" s="52"/>
-      <c r="J190" s="52"/>
+      <c r="D190" s="52">
+        <v>20992.12</v>
+      </c>
+      <c r="E190" s="52">
+        <v>14169.68</v>
+      </c>
+      <c r="F190" s="52">
+        <v>6822.439999999999</v>
+      </c>
+      <c r="G190" s="53">
+        <v>0.32500004763692275</v>
+      </c>
+      <c r="H190" s="52">
+        <v>16299.09</v>
+      </c>
+      <c r="I190" s="52">
+        <v>9699.51</v>
+      </c>
+      <c r="J190" s="52">
+        <v>9784.33</v>
+      </c>
       <c r="K190" s="52">
-        <v>0</v>
-      </c>
-      <c r="L190" s="52"/>
-      <c r="M190" s="53"/>
+        <v>8137.88</v>
+      </c>
+      <c r="L190" s="52">
+        <v>1646.4499999999998</v>
+      </c>
+      <c r="M190" s="53">
+        <v>0.16827416900288522</v>
+      </c>
       <c r="N190" s="53"/>
-      <c r="O190" s="52"/>
-      <c r="P190" s="52"/>
-      <c r="Q190" s="52"/>
-      <c r="R190" s="53"/>
-      <c r="S190" s="54"/>
-      <c r="T190" s="54"/>
-      <c r="U190" s="54"/>
-      <c r="V190" s="53"/>
+      <c r="O190" s="52">
+        <v>6514.76</v>
+      </c>
+      <c r="P190" s="52">
+        <v>1561.63</v>
+      </c>
+      <c r="Q190" s="52">
+        <v>4953.13</v>
+      </c>
+      <c r="R190" s="53">
+        <v>0.7602935488030257</v>
+      </c>
+      <c r="S190" s="54">
+        <v>130.62</v>
+      </c>
+      <c r="T190" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U190" s="54">
+        <v>95.87</v>
+      </c>
+      <c r="V190" s="53">
+        <v>0.7339611085591793</v>
+      </c>
       <c r="W190" s="53"/>
-      <c r="X190" s="55"/>
-      <c r="Y190" s="55"/>
-      <c r="Z190" s="53"/>
-      <c r="AA190" s="56"/>
+      <c r="X190" s="55">
+        <v>128.6379856115108</v>
+      </c>
+      <c r="Y190" s="55">
+        <v>35.92887828502527</v>
+      </c>
+      <c r="Z190" s="53">
+        <v>0.3155</v>
+      </c>
+      <c r="AA190" s="56">
+        <v>0.2236</v>
+      </c>
       <c r="AB190" s="57"/>
       <c r="AD190" s="35"/>
       <c r="AE190" s="35"/>
@@ -21995,32 +22081,74 @@
       <c r="C197" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D197" s="52"/>
-      <c r="E197" s="52"/>
-      <c r="F197" s="52"/>
-      <c r="G197" s="53"/>
-      <c r="H197" s="52"/>
-      <c r="I197" s="52"/>
-      <c r="J197" s="52"/>
+      <c r="D197" s="52">
+        <v>23770.95</v>
+      </c>
+      <c r="E197" s="52">
+        <v>10204.54</v>
+      </c>
+      <c r="F197" s="52">
+        <v>13566.41</v>
+      </c>
+      <c r="G197" s="53">
+        <v>0.5707138334816235</v>
+      </c>
+      <c r="H197" s="52">
+        <v>14310.96</v>
+      </c>
+      <c r="I197" s="52">
+        <v>6935.96</v>
+      </c>
+      <c r="J197" s="52">
+        <v>7389.339999999999</v>
+      </c>
       <c r="K197" s="52">
-        <v>0</v>
-      </c>
-      <c r="L197" s="52"/>
-      <c r="M197" s="53"/>
+        <v>6605.05</v>
+      </c>
+      <c r="L197" s="52">
+        <v>784.289999999999</v>
+      </c>
+      <c r="M197" s="53">
+        <v>0.1061380312720756</v>
+      </c>
       <c r="N197" s="53"/>
-      <c r="O197" s="52"/>
-      <c r="P197" s="52"/>
-      <c r="Q197" s="52"/>
-      <c r="R197" s="53"/>
-      <c r="S197" s="54"/>
-      <c r="T197" s="54"/>
-      <c r="U197" s="54"/>
-      <c r="V197" s="53"/>
+      <c r="O197" s="52">
+        <v>6921.62</v>
+      </c>
+      <c r="P197" s="52">
+        <v>330.91</v>
+      </c>
+      <c r="Q197" s="52">
+        <v>6590.71</v>
+      </c>
+      <c r="R197" s="53">
+        <v>0.9521918279246766</v>
+      </c>
+      <c r="S197" s="54">
+        <v>140.15</v>
+      </c>
+      <c r="T197" s="54">
+        <v>5.75</v>
+      </c>
+      <c r="U197" s="54">
+        <v>134.4</v>
+      </c>
+      <c r="V197" s="53">
+        <v>0.9589725294327506</v>
+      </c>
       <c r="W197" s="53"/>
-      <c r="X197" s="55"/>
-      <c r="Y197" s="55"/>
-      <c r="Z197" s="53"/>
-      <c r="AA197" s="56"/>
+      <c r="X197" s="55">
+        <v>568.4486956521739</v>
+      </c>
+      <c r="Y197" s="55">
+        <v>67.49902570438813</v>
+      </c>
+      <c r="Z197" s="53">
+        <v>0.32030000000000003</v>
+      </c>
+      <c r="AA197" s="56">
+        <v>0.398</v>
+      </c>
       <c r="AB197" s="57"/>
       <c r="AD197" s="35"/>
       <c r="AE197" s="35"/>
@@ -22968,30 +23096,74 @@
       <c r="C218" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D218" s="52"/>
-      <c r="E218" s="52"/>
-      <c r="F218" s="52"/>
-      <c r="G218" s="53"/>
-      <c r="H218" s="52"/>
-      <c r="I218" s="52"/>
-      <c r="J218" s="52"/>
-      <c r="K218" s="52"/>
-      <c r="L218" s="52"/>
-      <c r="M218" s="53"/>
+      <c r="D218" s="52">
+        <v>137109.56</v>
+      </c>
+      <c r="E218" s="52">
+        <v>30174.75</v>
+      </c>
+      <c r="F218" s="52">
+        <v>106934.81</v>
+      </c>
+      <c r="G218" s="53">
+        <v>0.7799223482301307</v>
+      </c>
+      <c r="H218" s="52">
+        <v>117394.57</v>
+      </c>
+      <c r="I218" s="52">
+        <v>26124</v>
+      </c>
+      <c r="J218" s="52">
+        <v>99479.62000000001</v>
+      </c>
+      <c r="K218" s="52">
+        <v>26124</v>
+      </c>
+      <c r="L218" s="52">
+        <v>73355.62000000001</v>
+      </c>
+      <c r="M218" s="53">
+        <v>0.7373934480248316</v>
+      </c>
       <c r="N218" s="53"/>
-      <c r="O218" s="52"/>
-      <c r="P218" s="52"/>
-      <c r="Q218" s="52"/>
-      <c r="R218" s="53"/>
-      <c r="S218" s="54"/>
-      <c r="T218" s="54"/>
-      <c r="U218" s="54"/>
-      <c r="V218" s="53"/>
+      <c r="O218" s="52">
+        <v>17914.95</v>
+      </c>
+      <c r="P218" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q218" s="52">
+        <v>17914.95</v>
+      </c>
+      <c r="R218" s="53">
+        <v>1</v>
+      </c>
+      <c r="S218" s="54">
+        <v>358.86</v>
+      </c>
+      <c r="T218" s="54">
+        <v>0</v>
+      </c>
+      <c r="U218" s="54">
+        <v>358.86</v>
+      </c>
+      <c r="V218" s="53">
+        <v>1</v>
+      </c>
       <c r="W218" s="53"/>
-      <c r="X218" s="55"/>
-      <c r="Y218" s="55"/>
-      <c r="Z218" s="53"/>
-      <c r="AA218" s="56"/>
+      <c r="X218" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y218" s="55">
+        <v>54.93783457863793</v>
+      </c>
+      <c r="Z218" s="53">
+        <v>0.13419999999999999</v>
+      </c>
+      <c r="AA218" s="56">
+        <v>0.1438</v>
+      </c>
       <c r="AB218" s="57"/>
       <c r="AD218" s="35"/>
       <c r="AE218" s="35"/>
@@ -23369,34 +23541,74 @@
       <c r="C225" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D225" s="52"/>
-      <c r="E225" s="52"/>
-      <c r="F225" s="52"/>
-      <c r="G225" s="53"/>
-      <c r="H225" s="52"/>
-      <c r="I225" s="52"/>
+      <c r="D225" s="52">
+        <v>396453.46</v>
+      </c>
+      <c r="E225" s="52">
+        <v>271388.15</v>
+      </c>
+      <c r="F225" s="52">
+        <v>125065.31</v>
+      </c>
+      <c r="G225" s="53">
+        <v>0.3154602560411504</v>
+      </c>
+      <c r="H225" s="52">
+        <v>295569.99</v>
+      </c>
+      <c r="I225" s="52">
+        <v>234322.81</v>
+      </c>
       <c r="J225" s="52">
-        <v>0</v>
+        <v>178700.37</v>
       </c>
       <c r="K225" s="52">
-        <v>0</v>
-      </c>
-      <c r="L225" s="52"/>
-      <c r="M225" s="53"/>
+        <v>177071.47999999998</v>
+      </c>
+      <c r="L225" s="52">
+        <v>1628.890000000014</v>
+      </c>
+      <c r="M225" s="53">
+        <v>0.009115202167740415</v>
+      </c>
       <c r="N225" s="53"/>
-      <c r="O225" s="52"/>
-      <c r="P225" s="52"/>
-      <c r="Q225" s="52"/>
-      <c r="R225" s="53"/>
-      <c r="S225" s="54"/>
-      <c r="T225" s="54"/>
-      <c r="U225" s="54"/>
-      <c r="V225" s="53"/>
+      <c r="O225" s="52">
+        <v>116869.62</v>
+      </c>
+      <c r="P225" s="52">
+        <v>57251.33</v>
+      </c>
+      <c r="Q225" s="52">
+        <v>59618.28999999999</v>
+      </c>
+      <c r="R225" s="53">
+        <v>0.5101264982293944</v>
+      </c>
+      <c r="S225" s="54">
+        <v>2344.68</v>
+      </c>
+      <c r="T225" s="54">
+        <v>1212</v>
+      </c>
+      <c r="U225" s="54">
+        <v>1132.6799999999998</v>
+      </c>
+      <c r="V225" s="53">
+        <v>0.48308511182762676</v>
+      </c>
       <c r="W225" s="53"/>
-      <c r="X225" s="55"/>
-      <c r="Y225" s="55"/>
-      <c r="Z225" s="53"/>
-      <c r="AA225" s="56"/>
+      <c r="X225" s="55">
+        <v>30.581963696369634</v>
+      </c>
+      <c r="Y225" s="55">
+        <v>43.0265399367206</v>
+      </c>
+      <c r="Z225" s="53">
+        <v>0.1366</v>
+      </c>
+      <c r="AA225" s="56">
+        <v>0.2545</v>
+      </c>
       <c r="AB225" s="57"/>
       <c r="AD225" s="35"/>
       <c r="AE225" s="35"/>
@@ -24013,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24027,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24049,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24097,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24115,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24162,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24179,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24199,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="53">
-        <v>0.2556317756411565</v>
+        <v>0.25548771651006935</v>
       </c>
       <c r="H6" s="53">
         <v>0.239214585617637</v>
@@ -24214,22 +24426,22 @@
         <v>1872.6</v>
       </c>
       <c r="L6" s="53">
-        <v>0.2016787498663849</v>
+        <v>0.20153469073529773</v>
       </c>
       <c r="M6" s="52">
-        <v>6999.8599999999915</v>
+        <v>6994.8599999999915</v>
       </c>
       <c r="N6" s="54">
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
-        <v>-559.9887999999993</v>
+        <v>-559.5887999999993</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24246,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24289,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24306,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24353,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24370,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24418,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24435,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24482,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24499,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24544,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24561,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24611,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24628,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24667,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24684,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24725,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24742,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24779,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -24796,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24841,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -24858,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24901,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -24918,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24961,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -24978,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25025,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25042,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25087,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25104,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25147,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25164,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25205,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25222,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25267,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25284,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25327,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25344,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25381,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25398,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25439,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25456,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25499,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25516,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25558,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25575,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25620,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25637,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25682,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25699,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25710,14 +25922,14 @@
         <v>12937.1</v>
       </c>
       <c r="D56" s="99">
-        <v>4850.19</v>
+        <v>4794.2300000000005</v>
       </c>
       <c r="E56" s="99">
-        <v>8086.910000000001</v>
+        <v>8142.87</v>
       </c>
       <c r="F56" s="99"/>
       <c r="G56" s="100">
-        <v>0.6250944956752287</v>
+        <v>0.6294200400398853</v>
       </c>
       <c r="H56" s="100">
         <v>0.22356150784199</v>
@@ -25732,19 +25944,19 @@
         <v>5400</v>
       </c>
       <c r="L56" s="100">
-        <v>0.20769028607647777</v>
+        <v>0.2120158304411344</v>
       </c>
       <c r="M56" s="99">
-        <v>2686.9100000000008</v>
+        <v>2742.87</v>
       </c>
       <c r="N56" s="98">
         <v>-32.25</v>
       </c>
       <c r="O56" s="60">
-        <v>-120.76000000000003</v>
-      </c>
-    </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>-123.27505617977528</v>
+      </c>
+    </row>
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25761,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -25769,17 +25981,17 @@
         <v>60</v>
       </c>
       <c r="C58" s="99">
-        <v>0</v>
+        <v>10204.54</v>
       </c>
       <c r="D58" s="99">
-        <v>6849.16</v>
+        <v>6605.05</v>
       </c>
       <c r="E58" s="99">
-        <v>-6849.16</v>
+        <v>3599.4900000000007</v>
       </c>
       <c r="F58" s="99"/>
       <c r="G58" s="100">
-        <v>0</v>
+        <v>0.35273417518085093</v>
       </c>
       <c r="H58" s="100"/>
       <c r="I58" s="98"/>
@@ -25788,17 +26000,17 @@
         <v>0</v>
       </c>
       <c r="L58" s="100">
-        <v>0</v>
+        <v>0.35273417518085093</v>
       </c>
       <c r="M58" s="99">
-        <v>-6849.16</v>
+        <v>3599.4900000000007</v>
       </c>
       <c r="N58" s="98"/>
       <c r="O58" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -25815,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -25832,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -25849,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -25870,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -25887,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -25895,17 +26107,17 @@
         <v>62</v>
       </c>
       <c r="C64" s="99">
-        <v>0</v>
+        <v>30174.75</v>
       </c>
       <c r="D64" s="99">
-        <v>1749.8</v>
+        <v>26124</v>
       </c>
       <c r="E64" s="99">
-        <v>-1749.8</v>
+        <v>4050.75</v>
       </c>
       <c r="F64" s="99"/>
       <c r="G64" s="100">
-        <v>0</v>
+        <v>0.13424303432505655</v>
       </c>
       <c r="H64" s="100">
         <v>0.143790046441692</v>
@@ -25918,17 +26130,17 @@
         <v>1750</v>
       </c>
       <c r="L64" s="100">
-        <v>0</v>
+        <v>0.07624752483450567</v>
       </c>
       <c r="M64" s="99">
-        <v>-3499.8</v>
+        <v>2300.75</v>
       </c>
       <c r="N64" s="98"/>
       <c r="O64" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -25945,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -25956,10 +26168,10 @@
         <v>0</v>
       </c>
       <c r="D66" s="99">
-        <v>2584.2399999999907</v>
+        <v>9863.48999999999</v>
       </c>
       <c r="E66" s="99">
-        <v>-2584.2399999999907</v>
+        <v>-9863.48999999999</v>
       </c>
       <c r="F66" s="99"/>
       <c r="G66" s="100">
@@ -25981,16 +26193,16 @@
         <v>0</v>
       </c>
       <c r="M66" s="99">
-        <v>-5784.239999999991</v>
+        <v>-13063.48999999999</v>
       </c>
       <c r="N66" s="98">
         <v>-1014.25</v>
       </c>
       <c r="O66" s="60">
-        <v>6.191319240032102</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>13.982863259298894</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26007,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26024,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26032,25 +26244,25 @@
         <v>122</v>
       </c>
       <c r="C69" s="104">
-        <v>308475.47</v>
+        <v>348854.75999999995</v>
       </c>
       <c r="D69" s="104">
-        <v>345627.75999999995</v>
+        <v>376981.13999999996</v>
       </c>
       <c r="E69" s="105">
-        <v>-37152.289999999986</v>
+        <v>-28126.379999999983</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>123</v>
       </c>
       <c r="G69" s="107">
-        <v>-0.12043839336722621</v>
+        <v>-0.08062489960005129</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>124</v>
       </c>
       <c r="I69" s="109">
-        <v>-0.2884666647886135</v>
+        <v>-0.2292042109444056</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -26059,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26442,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26453,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26474,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26536,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26594,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26628,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26647,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26681,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26700,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26734,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26753,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -26789,7 +27001,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -26808,7 +27020,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -26846,7 +27058,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -26865,7 +27077,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -26903,7 +27115,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -26922,7 +27134,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -26955,7 +27167,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -26974,7 +27186,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27007,7 +27219,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27026,7 +27238,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27057,7 +27269,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27076,7 +27288,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27111,7 +27323,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27130,7 +27342,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27163,7 +27375,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27182,7 +27394,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27213,7 +27425,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27232,7 +27444,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27264,7 +27476,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27283,7 +27495,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27319,7 +27531,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27338,7 +27550,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27367,7 +27579,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27386,7 +27598,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27417,7 +27629,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27436,7 +27648,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27469,7 +27681,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27488,7 +27700,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27524,7 +27736,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27543,7 +27755,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27578,7 +27790,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27597,7 +27809,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27627,7 +27839,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27646,7 +27858,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27686,7 +27898,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27705,7 +27917,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27734,7 +27946,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27753,7 +27965,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27786,7 +27998,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -27805,7 +28017,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -27838,7 +28050,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -27857,7 +28069,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -27893,7 +28105,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -27912,7 +28124,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -27948,7 +28160,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -27967,7 +28179,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28001,7 +28213,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28020,7 +28232,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28055,7 +28267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28074,7 +28286,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28093,7 +28305,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28112,7 +28324,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28133,7 +28345,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28152,7 +28364,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28185,7 +28397,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28204,7 +28416,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28212,13 +28424,13 @@
         <v>63</v>
       </c>
       <c r="C66" s="54">
-        <v>2312.68</v>
+        <v>2344.68</v>
       </c>
       <c r="D66" s="54">
-        <v>1120.5</v>
+        <v>1212</v>
       </c>
       <c r="E66" s="54">
-        <v>1192.1799999999998</v>
+        <v>1132.6799999999998</v>
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="54"/>
@@ -28243,7 +28455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28262,7 +28474,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28281,7 +28493,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28300,7 +28512,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28345,7 +28557,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28384,7 +28596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28413,7 +28625,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28458,7 +28670,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28503,7 +28715,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28522,7 +28734,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28569,7 +28781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28614,7 +28826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28633,7 +28845,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28656,7 +28868,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28679,7 +28891,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28702,7 +28914,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28725,7 +28937,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28748,7 +28960,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28771,7 +28983,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -28794,7 +29006,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -28817,7 +29029,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -28840,7 +29052,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -28863,7 +29075,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -28886,7 +29098,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -28909,7 +29121,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -28930,7 +29142,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -28951,7 +29163,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -28972,7 +29184,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -28993,7 +29205,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29014,7 +29226,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29035,7 +29247,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29056,7 +29268,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29079,7 +29291,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29102,7 +29314,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29125,7 +29337,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29148,7 +29360,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29171,7 +29383,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29194,7 +29406,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29217,7 +29429,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29236,7 +29448,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29255,7 +29467,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29274,7 +29486,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29293,7 +29505,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29367,10 +29579,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29402,7 +29615,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29435,7 +29648,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29468,7 +29681,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29501,7 +29714,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29534,7 +29747,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29567,7 +29780,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29600,7 +29813,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29633,7 +29846,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29664,7 +29877,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29695,7 +29908,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29728,7 +29941,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29761,7 +29974,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -29794,7 +30007,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -29827,7 +30040,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -29860,7 +30073,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -29893,7 +30106,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -29926,7 +30139,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -29959,7 +30172,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -29992,7 +30205,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30025,7 +30238,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30058,7 +30271,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30091,7 +30304,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30124,7 +30337,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30157,7 +30370,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30190,7 +30403,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30223,7 +30436,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30255,7 +30468,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30287,7 +30500,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30319,7 +30532,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30351,7 +30564,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30383,7 +30596,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30413,7 +30626,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30443,7 +30656,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30475,7 +30688,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30507,7 +30720,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30539,7 +30752,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30571,7 +30784,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30603,7 +30816,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30633,7 +30846,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30665,7 +30878,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30697,7 +30910,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30729,7 +30942,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30761,7 +30974,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -30791,7 +31004,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -30821,7 +31034,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -30851,7 +31064,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -30881,7 +31094,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -30913,7 +31126,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -30945,7 +31158,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -30975,7 +31188,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31005,7 +31218,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31035,7 +31248,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31065,7 +31278,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31095,7 +31308,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31190,10 +31403,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31225,7 +31439,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31256,7 +31470,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31287,7 +31501,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31318,7 +31532,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31349,7 +31563,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31380,7 +31594,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31411,7 +31625,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31442,7 +31656,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31473,7 +31687,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31504,7 +31718,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31535,7 +31749,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31566,7 +31780,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31597,7 +31811,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31628,7 +31842,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31659,7 +31873,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31690,7 +31904,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31721,7 +31935,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31752,7 +31966,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31783,7 +31997,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -31814,7 +32028,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -31844,7 +32058,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -31874,7 +32088,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -31904,7 +32118,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -31934,7 +32148,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -31964,7 +32178,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -31994,7 +32208,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32024,7 +32238,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32054,7 +32268,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32084,7 +32298,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32114,7 +32328,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32144,7 +32358,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32174,7 +32388,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32204,7 +32418,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32234,7 +32448,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32264,7 +32478,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32294,7 +32508,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32326,7 +32540,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32358,7 +32572,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32388,7 +32602,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32418,7 +32632,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32448,7 +32662,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32478,7 +32692,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32508,7 +32722,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54251,19 +54465,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54277,7 +54491,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54289,7 +54503,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54300,7 +54514,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54311,7 +54525,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54322,13 +54536,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -24225,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24239,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24261,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24327,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24391,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24458,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24518,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24582,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24647,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24711,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24756,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24773,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24823,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24840,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24954,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -25008,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25053,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -25070,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -25130,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -25190,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25254,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25316,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25376,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25434,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25479,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25496,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25556,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25610,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25668,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25728,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25787,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25849,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25911,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>-123.27505617977528</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25973,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -26027,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -26044,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -26061,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -26082,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -26099,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -26157,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>13.982863259298894</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26219,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26236,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26654,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26665,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26686,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26748,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26859,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26912,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26965,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -27001,7 +27001,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -27020,7 +27020,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -27058,7 +27058,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -27077,7 +27077,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -27134,7 +27134,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -27167,7 +27167,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -27186,7 +27186,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27219,7 +27219,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27238,7 +27238,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27269,7 +27269,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27288,7 +27288,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27323,7 +27323,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27342,7 +27342,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27375,7 +27375,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27394,7 +27394,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27425,7 +27425,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27444,7 +27444,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27476,7 +27476,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27495,7 +27495,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27531,7 +27531,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27550,7 +27550,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27579,7 +27579,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27598,7 +27598,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27629,7 +27629,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27648,7 +27648,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27681,7 +27681,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27700,7 +27700,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27736,7 +27736,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27755,7 +27755,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27790,7 +27790,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27809,7 +27809,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27839,7 +27839,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27858,7 +27858,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27917,7 +27917,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27946,7 +27946,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27965,7 +27965,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27998,7 +27998,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -28017,7 +28017,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -28050,7 +28050,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -28069,7 +28069,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -28105,7 +28105,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -28124,7 +28124,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -28160,7 +28160,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -28179,7 +28179,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28213,7 +28213,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28232,7 +28232,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28267,7 +28267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28286,7 +28286,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28305,7 +28305,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28324,7 +28324,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28345,7 +28345,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28364,7 +28364,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28397,7 +28397,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28416,7 +28416,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28455,7 +28455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28474,7 +28474,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28493,7 +28493,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28512,7 +28512,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28557,7 +28557,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28596,7 +28596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28625,7 +28625,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28670,7 +28670,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28715,7 +28715,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28734,7 +28734,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28781,7 +28781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28826,7 +28826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28845,7 +28845,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28868,7 +28868,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28891,7 +28891,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28914,7 +28914,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28937,7 +28937,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28960,7 +28960,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28983,7 +28983,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -29006,7 +29006,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -29029,7 +29029,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -29052,7 +29052,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -29075,7 +29075,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -29098,7 +29098,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -29121,7 +29121,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -29142,7 +29142,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -29163,7 +29163,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -29184,7 +29184,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -29205,7 +29205,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29226,7 +29226,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29247,7 +29247,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29268,7 +29268,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29291,7 +29291,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29314,7 +29314,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29337,7 +29337,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29360,7 +29360,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29383,7 +29383,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29406,7 +29406,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29429,7 +29429,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29448,7 +29448,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29467,7 +29467,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29486,7 +29486,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29505,7 +29505,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29579,11 +29579,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29615,7 +29614,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29648,7 +29647,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29681,7 +29680,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29714,7 +29713,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29747,7 +29746,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29780,7 +29779,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29813,7 +29812,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29846,7 +29845,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29877,7 +29876,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29908,7 +29907,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29941,7 +29940,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29974,7 +29973,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -30007,7 +30006,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -30040,7 +30039,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -30073,7 +30072,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -30106,7 +30105,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -30139,7 +30138,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -30172,7 +30171,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -30205,7 +30204,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30238,7 +30237,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30271,7 +30270,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30304,7 +30303,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30337,7 +30336,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30370,7 +30369,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30403,7 +30402,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30436,7 +30435,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30468,7 +30467,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30500,7 +30499,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30532,7 +30531,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30564,7 +30563,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30596,7 +30595,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30626,7 +30625,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30656,7 +30655,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30688,7 +30687,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30720,7 +30719,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30752,7 +30751,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30784,7 +30783,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30816,7 +30815,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30846,7 +30845,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30878,7 +30877,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30910,7 +30909,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30942,7 +30941,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30974,7 +30973,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -31004,7 +31003,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -31034,7 +31033,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -31064,7 +31063,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -31094,7 +31093,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -31126,7 +31125,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -31158,7 +31157,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -31188,7 +31187,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31218,7 +31217,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31248,7 +31247,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31278,7 +31277,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31308,7 +31307,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31403,11 +31402,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31439,7 +31437,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31470,7 +31468,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31501,7 +31499,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31532,7 +31530,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31563,7 +31561,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31594,7 +31592,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31625,7 +31623,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31656,7 +31654,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31687,7 +31685,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31718,7 +31716,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31749,7 +31747,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31780,7 +31778,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31811,7 +31809,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31842,7 +31840,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31873,7 +31871,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31904,7 +31902,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31935,7 +31933,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31966,7 +31964,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31997,7 +31995,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -32028,7 +32026,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -32058,7 +32056,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -32088,7 +32086,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -32118,7 +32116,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -32148,7 +32146,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -32178,7 +32176,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -32208,7 +32206,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32238,7 +32236,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32268,7 +32266,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32298,7 +32296,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32328,7 +32326,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32358,7 +32356,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32388,7 +32386,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32418,7 +32416,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32448,7 +32446,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32478,7 +32476,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32508,7 +32506,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32540,7 +32538,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32572,7 +32570,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32602,7 +32600,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32632,7 +32630,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32662,7 +32660,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32692,7 +32690,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32722,7 +32720,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54465,19 +54463,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54491,7 +54489,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54503,7 +54501,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54514,7 +54512,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54525,7 +54523,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54536,13 +54534,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -24225,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24239,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24261,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24327,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24391,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24458,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24518,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24582,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24647,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24711,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24756,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24773,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24823,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24840,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24954,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -25008,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25053,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -25070,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -25130,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -25190,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25254,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25316,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25376,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25434,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25479,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25496,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25556,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25610,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25668,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25728,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25787,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25849,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25911,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>-123.27505617977528</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25973,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -26027,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -26044,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -26061,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -26082,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -26099,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -26157,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>13.982863259298894</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26219,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26236,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26654,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26665,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26686,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26748,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26859,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26912,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26965,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -27001,7 +27001,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -27020,7 +27020,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -27058,7 +27058,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -27077,7 +27077,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -27134,7 +27134,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -27167,7 +27167,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -27186,7 +27186,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27219,7 +27219,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27238,7 +27238,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27269,7 +27269,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27288,7 +27288,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27323,7 +27323,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27342,7 +27342,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27375,7 +27375,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27394,7 +27394,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27425,7 +27425,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27444,7 +27444,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27476,7 +27476,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27495,7 +27495,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27531,7 +27531,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27550,7 +27550,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27579,7 +27579,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27598,7 +27598,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27629,7 +27629,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27648,7 +27648,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27681,7 +27681,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27700,7 +27700,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27736,7 +27736,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27755,7 +27755,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27790,7 +27790,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27809,7 +27809,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27839,7 +27839,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27858,7 +27858,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27917,7 +27917,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27946,7 +27946,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27965,7 +27965,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27998,7 +27998,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -28017,7 +28017,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -28050,7 +28050,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -28069,7 +28069,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -28105,7 +28105,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -28124,7 +28124,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -28160,7 +28160,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -28179,7 +28179,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28213,7 +28213,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28232,7 +28232,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28267,7 +28267,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28286,7 +28286,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28305,7 +28305,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28324,7 +28324,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28345,7 +28345,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28364,7 +28364,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28397,7 +28397,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28416,7 +28416,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28455,7 +28455,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28474,7 +28474,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28493,7 +28493,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28512,7 +28512,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28557,7 +28557,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28596,7 +28596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28625,7 +28625,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28670,7 +28670,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28715,7 +28715,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28734,7 +28734,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28781,7 +28781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28826,7 +28826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28845,7 +28845,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28868,7 +28868,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28891,7 +28891,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28914,7 +28914,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28937,7 +28937,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28960,7 +28960,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28983,7 +28983,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -29006,7 +29006,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -29029,7 +29029,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -29052,7 +29052,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -29075,7 +29075,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -29098,7 +29098,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -29121,7 +29121,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -29142,7 +29142,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -29163,7 +29163,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -29184,7 +29184,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -29205,7 +29205,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29226,7 +29226,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29247,7 +29247,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29268,7 +29268,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29291,7 +29291,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29314,7 +29314,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29337,7 +29337,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29360,7 +29360,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29383,7 +29383,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29406,7 +29406,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29429,7 +29429,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29448,7 +29448,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29467,7 +29467,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29486,7 +29486,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29505,7 +29505,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29579,10 +29579,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29614,7 +29615,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29647,7 +29648,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29680,7 +29681,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29713,7 +29714,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29746,7 +29747,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29779,7 +29780,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29812,7 +29813,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29845,7 +29846,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29876,7 +29877,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29907,7 +29908,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29940,7 +29941,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29973,7 +29974,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -30006,7 +30007,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -30039,7 +30040,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -30072,7 +30073,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -30105,7 +30106,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -30138,7 +30139,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -30171,7 +30172,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -30204,7 +30205,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30237,7 +30238,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30270,7 +30271,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30303,7 +30304,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30336,7 +30337,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30369,7 +30370,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30402,7 +30403,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30435,7 +30436,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30467,7 +30468,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30499,7 +30500,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30531,7 +30532,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30563,7 +30564,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30595,7 +30596,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30625,7 +30626,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30655,7 +30656,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30687,7 +30688,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30719,7 +30720,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30751,7 +30752,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30783,7 +30784,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30815,7 +30816,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30845,7 +30846,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30877,7 +30878,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30909,7 +30910,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30941,7 +30942,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30973,7 +30974,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -31003,7 +31004,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -31033,7 +31034,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -31063,7 +31064,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -31093,7 +31094,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -31125,7 +31126,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -31157,7 +31158,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -31187,7 +31188,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31217,7 +31218,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31247,7 +31248,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31277,7 +31278,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31307,7 +31308,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31402,10 +31403,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31437,7 +31439,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31468,7 +31470,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31499,7 +31501,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31530,7 +31532,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31561,7 +31563,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31592,7 +31594,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31623,7 +31625,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31654,7 +31656,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31685,7 +31687,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31716,7 +31718,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31747,7 +31749,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31778,7 +31780,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31809,7 +31811,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31840,7 +31842,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31871,7 +31873,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31902,7 +31904,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31933,7 +31935,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31964,7 +31966,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31995,7 +31997,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -32026,7 +32028,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -32056,7 +32058,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -32086,7 +32088,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -32116,7 +32118,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -32146,7 +32148,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -32176,7 +32178,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -32206,7 +32208,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32236,7 +32238,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32266,7 +32268,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32296,7 +32298,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32326,7 +32328,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32356,7 +32358,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32386,7 +32388,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32416,7 +32418,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32446,7 +32448,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32476,7 +32478,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32506,7 +32508,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32538,7 +32540,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32570,7 +32572,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32600,7 +32602,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32630,7 +32632,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32660,7 +32662,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32690,7 +32692,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32720,7 +32722,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54463,19 +54465,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54489,7 +54491,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54501,7 +54503,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54512,7 +54514,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54523,7 +54525,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54534,13 +54536,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -18043,7 +18043,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>96</v>
@@ -24225,7 +24225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -24239,7 +24239,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -24261,7 +24261,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>101</v>
       </c>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -24327,7 +24327,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -24374,7 +24374,7 @@
         <v>-726.0072857142857</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -24391,7 +24391,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -24441,7 +24441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -24458,7 +24458,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -24501,7 +24501,7 @@
         <v>-232.53333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -24518,7 +24518,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>-50.95312270389416</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -24582,7 +24582,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -24647,7 +24647,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>-42.80544642857142</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -24711,7 +24711,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -24756,7 +24756,7 @@
         <v>7.380864553314173</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -24773,7 +24773,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -24823,7 +24823,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -24840,7 +24840,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -24896,7 +24896,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -24937,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -24954,7 +24954,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -25008,7 +25008,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25053,7 +25053,7 @@
         <v>0.2554973821989554</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -25070,7 +25070,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>7.589966329966334</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -25130,7 +25130,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -25190,7 +25190,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25237,7 +25237,7 @@
         <v>4.666337611056268</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -25254,7 +25254,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>285.64884004884004</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -25316,7 +25316,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25359,7 +25359,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -25376,7 +25376,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -25434,7 +25434,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25479,7 +25479,7 @@
         <v>561.1049999999996</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -25496,7 +25496,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25539,7 +25539,7 @@
         <v>-9.801274601686979</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -25556,7 +25556,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -25610,7 +25610,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25651,7 +25651,7 @@
         <v>0.05940556088207709</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -25668,7 +25668,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>-179.9832402234637</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -25728,7 +25728,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -25770,7 +25770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -25787,7 +25787,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>-9.106177818515201</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -25849,7 +25849,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>862.1199999999999</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -25911,7 +25911,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -25956,7 +25956,7 @@
         <v>-123.27505617977528</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -25973,7 +25973,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -26027,7 +26027,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -26044,7 +26044,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -26061,7 +26061,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>61</v>
@@ -26082,7 +26082,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -26099,7 +26099,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -26157,7 +26157,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>13.982863259298894</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -26219,7 +26219,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -26236,7 +26236,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>121</v>
       </c>
@@ -26271,7 +26271,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>125</v>
@@ -26654,7 +26654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -26665,7 +26665,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26686,7 +26686,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>126</v>
@@ -26748,7 +26748,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>142</v>
       </c>
@@ -26806,7 +26806,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -26859,7 +26859,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -26912,7 +26912,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -26946,7 +26946,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -26965,7 +26965,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -26994,14 +26994,16 @@
       <c r="N10" s="54">
         <v>80</v>
       </c>
-      <c r="O10" s="54"/>
+      <c r="O10" s="54">
+        <v>0</v>
+      </c>
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -27020,7 +27022,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -27058,7 +27060,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -27077,7 +27079,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -27115,7 +27117,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -27134,7 +27136,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -27167,7 +27169,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -27186,7 +27188,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -27219,7 +27221,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -27238,7 +27240,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -27269,7 +27271,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -27288,7 +27290,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -27323,7 +27325,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -27342,7 +27344,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -27375,7 +27377,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -27394,7 +27396,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -27425,7 +27427,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -27444,7 +27446,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -27476,7 +27478,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -27495,7 +27497,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -27531,7 +27533,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -27550,7 +27552,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -27579,7 +27581,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -27598,7 +27600,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -27629,7 +27631,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -27648,7 +27650,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -27681,7 +27683,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -27700,7 +27702,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -27736,7 +27738,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -27755,7 +27757,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -27790,7 +27792,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -27809,7 +27811,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -27839,7 +27841,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -27858,7 +27860,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -27898,7 +27900,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -27917,7 +27919,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -27946,7 +27948,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -27965,7 +27967,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -27998,7 +28000,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -28017,7 +28019,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -28050,7 +28052,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -28069,7 +28071,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -28105,7 +28107,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -28124,7 +28126,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -28160,7 +28162,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -28179,7 +28181,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -28213,7 +28215,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -28232,7 +28234,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -28267,7 +28269,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -28286,7 +28288,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -28305,7 +28307,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -28324,7 +28326,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>61</v>
@@ -28345,7 +28347,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -28364,7 +28366,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -28397,7 +28399,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -28416,7 +28418,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -28455,7 +28457,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -28474,7 +28476,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -28493,7 +28495,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -28512,7 +28514,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>146</v>
@@ -28557,7 +28559,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>147</v>
@@ -28596,7 +28598,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -28625,7 +28627,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>149</v>
@@ -28670,7 +28672,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>150</v>
@@ -28715,7 +28717,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -28734,7 +28736,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>151</v>
@@ -28781,7 +28783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>153</v>
@@ -28826,7 +28828,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -28845,7 +28847,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>154</v>
@@ -28868,7 +28870,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>156</v>
@@ -28891,7 +28893,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>157</v>
@@ -28914,7 +28916,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -28937,7 +28939,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -28960,7 +28962,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -28983,7 +28985,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -29006,7 +29008,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -29029,7 +29031,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -29052,7 +29054,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -29075,7 +29077,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -29098,7 +29100,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -29121,7 +29123,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -29142,7 +29144,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -29163,7 +29165,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -29184,7 +29186,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -29205,7 +29207,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -29226,7 +29228,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -29247,7 +29249,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -29268,7 +29270,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>167</v>
@@ -29291,7 +29293,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -29314,7 +29316,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -29337,7 +29339,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -29360,7 +29362,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -29383,7 +29385,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -29406,7 +29408,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -29429,7 +29431,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -29448,7 +29450,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -29467,7 +29469,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -29486,7 +29488,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -29505,7 +29507,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>174</v>
@@ -29579,11 +29581,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>175</v>
       </c>
@@ -29615,7 +29616,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>176</v>
       </c>
@@ -29648,7 +29649,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>177</v>
       </c>
@@ -29681,7 +29682,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>178</v>
       </c>
@@ -29714,7 +29715,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>179</v>
       </c>
@@ -29747,7 +29748,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>180</v>
       </c>
@@ -29780,7 +29781,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>181</v>
       </c>
@@ -29813,7 +29814,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>182</v>
       </c>
@@ -29846,7 +29847,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -29877,7 +29878,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -29908,7 +29909,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>183</v>
       </c>
@@ -29941,7 +29942,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>184</v>
       </c>
@@ -29974,7 +29975,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>185</v>
       </c>
@@ -30007,7 +30008,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>186</v>
       </c>
@@ -30040,7 +30041,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>187</v>
       </c>
@@ -30073,7 +30074,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>188</v>
       </c>
@@ -30106,7 +30107,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>189</v>
       </c>
@@ -30139,7 +30140,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>190</v>
       </c>
@@ -30172,7 +30173,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>191</v>
       </c>
@@ -30205,7 +30206,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>192</v>
       </c>
@@ -30238,7 +30239,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>193</v>
       </c>
@@ -30271,7 +30272,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>194</v>
       </c>
@@ -30304,7 +30305,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>195</v>
       </c>
@@ -30337,7 +30338,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>196</v>
       </c>
@@ -30370,7 +30371,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>197</v>
       </c>
@@ -30403,7 +30404,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>198</v>
       </c>
@@ -30436,7 +30437,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>199</v>
       </c>
@@ -30468,7 +30469,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>200</v>
       </c>
@@ -30500,7 +30501,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>201</v>
       </c>
@@ -30532,7 +30533,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>202</v>
       </c>
@@ -30564,7 +30565,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>203</v>
       </c>
@@ -30596,7 +30597,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -30626,7 +30627,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -30656,7 +30657,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>204</v>
       </c>
@@ -30688,7 +30689,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>205</v>
       </c>
@@ -30720,7 +30721,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>206</v>
       </c>
@@ -30752,7 +30753,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>207</v>
       </c>
@@ -30784,7 +30785,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>208</v>
       </c>
@@ -30816,7 +30817,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -30846,7 +30847,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>209</v>
       </c>
@@ -30878,7 +30879,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>210</v>
       </c>
@@ -30910,7 +30911,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>211</v>
       </c>
@@ -30942,7 +30943,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>212</v>
       </c>
@@ -30974,7 +30975,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -31004,7 +31005,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -31034,7 +31035,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -31064,7 +31065,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -31094,7 +31095,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>213</v>
       </c>
@@ -31126,7 +31127,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>214</v>
       </c>
@@ -31158,7 +31159,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -31188,7 +31189,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -31218,7 +31219,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -31248,7 +31249,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -31278,7 +31279,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -31308,7 +31309,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -31403,11 +31404,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>215</v>
       </c>
@@ -31439,7 +31439,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -31470,7 +31470,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -31501,7 +31501,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -31532,7 +31532,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -31563,7 +31563,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -31594,7 +31594,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -31625,7 +31625,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -31656,7 +31656,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -31687,7 +31687,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -31718,7 +31718,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -31749,7 +31749,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -31780,7 +31780,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -31811,7 +31811,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -31842,7 +31842,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -31873,7 +31873,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -31904,7 +31904,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -31935,7 +31935,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -31966,7 +31966,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -31997,7 +31997,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -32028,7 +32028,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -32058,7 +32058,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -32088,7 +32088,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -32118,7 +32118,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -32148,7 +32148,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -32178,7 +32178,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -32208,7 +32208,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -32238,7 +32238,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -32268,7 +32268,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -32298,7 +32298,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -32328,7 +32328,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -32358,7 +32358,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -32388,7 +32388,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -32418,7 +32418,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -32448,7 +32448,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -32478,7 +32478,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -32508,7 +32508,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>213</v>
       </c>
@@ -32540,7 +32540,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>214</v>
       </c>
@@ -32572,7 +32572,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -32602,7 +32602,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -32632,7 +32632,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -32662,7 +32662,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -32692,7 +32692,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -32722,7 +32722,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -54465,19 +54465,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -54491,7 +54491,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>222</v>
       </c>
@@ -54503,7 +54503,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>223</v>
       </c>
@@ -54514,7 +54514,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>224</v>
       </c>
@@ -54525,7 +54525,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>225</v>
       </c>
@@ -54536,13 +54536,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">Major Hornbrook </t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>NA</t>
@@ -6722,7 +6719,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>27</v>
@@ -6752,7 +6749,7 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
@@ -6805,7 +6802,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>42</v>
@@ -6875,7 +6872,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6943,7 +6940,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -7011,7 +7008,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -7079,7 +7076,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7147,7 +7144,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>42</v>
@@ -7229,7 +7226,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>42</v>
@@ -7321,7 +7318,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -7389,7 +7386,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
@@ -7457,7 +7454,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="29" t="s">
         <v>42</v>
@@ -7545,7 +7542,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>42</v>
@@ -7615,7 +7612,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>42</v>
@@ -7705,7 +7702,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>42</v>
@@ -7863,7 +7860,7 @@
     <row r="62" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="27"/>
       <c r="B62" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -7931,7 +7928,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>26</v>
@@ -8001,7 +7998,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>42</v>
@@ -9391,79 +9388,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="E2" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="I2" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="43" t="s">
+      <c r="P2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="43" t="s">
+      <c r="Q2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="R2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="S2" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="T2" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="44" t="s">
+      <c r="U2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="45" t="s">
+      <c r="V2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="W2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="X2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="46" t="s">
+      <c r="Y2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Z2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="AA2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AA2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9501,10 +9498,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AI3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9515,7 +9512,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>215046.91</v>
@@ -9589,7 +9586,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9605,7 +9602,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52">
         <v>233882.27</v>
@@ -9677,7 +9674,7 @@
       </c>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9689,7 +9686,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9725,7 +9722,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52">
         <v>233882.27</v>
@@ -9797,7 +9794,7 @@
       </c>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9809,7 +9806,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52">
         <v>245679.5</v>
@@ -9889,7 +9886,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9966,7 +9963,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="52">
         <v>95023.47</v>
@@ -10040,7 +10037,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -10056,7 +10053,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -10128,7 +10125,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10140,7 +10137,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10176,7 +10173,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="52">
         <v>129074.86</v>
@@ -10248,7 +10245,7 @@
       </c>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10260,7 +10257,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="52">
         <v>129074.86</v>
@@ -10340,7 +10337,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10417,7 +10414,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10491,7 +10488,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10507,7 +10504,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -10535,7 +10532,7 @@
       <c r="AA19" s="56"/>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE19" s="36">
         <v>-5911.24</v>
@@ -10547,7 +10544,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
@@ -10583,7 +10580,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="52">
         <v>27500.32</v>
@@ -10655,7 +10652,7 @@
       </c>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE21" s="36">
         <v>0</v>
@@ -10667,7 +10664,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="52">
         <v>27500.32</v>
@@ -10747,7 +10744,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -10824,7 +10821,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="55">
         <v>150850.82</v>
@@ -10900,7 +10897,7 @@
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE25" s="35">
         <v>-388.25</v>
@@ -10916,7 +10913,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="55">
         <v>150850.82</v>
@@ -10988,7 +10985,7 @@
       </c>
       <c r="AB26" s="57"/>
       <c r="AD26" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE26" s="36">
         <v>-56964.81</v>
@@ -11000,7 +10997,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="55"/>
@@ -11036,7 +11033,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="55">
         <v>150850.82</v>
@@ -11108,7 +11105,7 @@
       </c>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE28" s="36">
         <v>0</v>
@@ -11120,7 +11117,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="55">
         <v>150850.82</v>
@@ -11200,7 +11197,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="55"/>
@@ -11277,7 +11274,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="52">
         <v>389022.03</v>
@@ -11351,7 +11348,7 @@
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE32" s="35">
         <v>-387.5</v>
@@ -11367,7 +11364,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="52">
         <v>396422.03</v>
@@ -11439,7 +11436,7 @@
       </c>
       <c r="AB33" s="57"/>
       <c r="AD33" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE33" s="36">
         <v>-132316.71</v>
@@ -11451,7 +11448,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="52"/>
       <c r="E34" s="52"/>
@@ -11487,7 +11484,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="52">
         <v>396422.03</v>
@@ -11559,7 +11556,7 @@
       </c>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE35" s="36">
         <v>0</v>
@@ -11571,7 +11568,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="52">
         <v>396422.03</v>
@@ -11651,7 +11648,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -11728,7 +11725,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="52">
         <v>128258.5</v>
@@ -11802,7 +11799,7 @@
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE39" s="35">
         <v>-112</v>
@@ -11818,7 +11815,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="52">
         <v>128258.5</v>
@@ -11890,7 +11887,7 @@
       </c>
       <c r="AB40" s="57"/>
       <c r="AD40" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE40" s="36">
         <v>-26847.46</v>
@@ -11902,7 +11899,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" s="52">
         <v>128258.5</v>
@@ -11982,7 +11979,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="52">
         <v>128258.5</v>
@@ -12054,7 +12051,7 @@
       </c>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE42" s="36">
         <v>0</v>
@@ -12066,7 +12063,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="52">
         <v>128258.5</v>
@@ -12146,7 +12143,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -12223,7 +12220,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="52">
         <v>64305.21</v>
@@ -12299,7 +12296,7 @@
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE46" s="35">
         <v>-86.75</v>
@@ -12315,7 +12312,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="52">
         <v>65693.36</v>
@@ -12387,7 +12384,7 @@
       </c>
       <c r="AB47" s="57"/>
       <c r="AD47" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE47" s="36">
         <v>-15639.05</v>
@@ -12399,7 +12396,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="52">
         <v>65693.36</v>
@@ -12479,7 +12476,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="52">
         <v>65693.36</v>
@@ -12551,7 +12548,7 @@
       </c>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE49" s="36">
         <v>0</v>
@@ -12563,7 +12560,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="52">
         <v>65693.36</v>
@@ -12643,7 +12640,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -12720,7 +12717,7 @@
         <v>37</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="52">
         <v>150152.16</v>
@@ -12794,7 +12791,7 @@
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE53" s="35">
         <v>-269</v>
@@ -12810,7 +12807,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="52">
         <v>154527.79</v>
@@ -12882,7 +12879,7 @@
       </c>
       <c r="AB54" s="57"/>
       <c r="AD54" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE54" s="36">
         <v>-66399.88</v>
@@ -12894,7 +12891,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="52">
         <v>154527.79</v>
@@ -12974,7 +12971,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="52">
         <v>154527.79</v>
@@ -13046,7 +13043,7 @@
       </c>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE56" s="36">
         <v>0</v>
@@ -13058,7 +13055,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="52">
         <v>155296.79</v>
@@ -13138,7 +13135,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -13215,7 +13212,7 @@
         <v>38</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="52">
         <v>20420.56</v>
@@ -13289,7 +13286,7 @@
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE60" s="35">
         <v>-26.75</v>
@@ -13305,7 +13302,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D61" s="52">
         <v>20420.56</v>
@@ -13377,7 +13374,7 @@
       </c>
       <c r="AB61" s="57"/>
       <c r="AD61" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE61" s="36">
         <v>-11159.14</v>
@@ -13389,7 +13386,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="52">
         <v>20420.56</v>
@@ -13469,7 +13466,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="52">
         <v>20420.56</v>
@@ -13541,7 +13538,7 @@
       </c>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE63" s="36">
         <v>0</v>
@@ -13553,7 +13550,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="52">
         <v>20420.56</v>
@@ -13633,7 +13630,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -13710,7 +13707,7 @@
         <v>39</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="52">
         <v>46303.5</v>
@@ -13780,7 +13777,7 @@
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE67" s="35"/>
       <c r="AH67" s="19"/>
@@ -13792,7 +13789,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="52">
         <v>46303.5</v>
@@ -13864,7 +13861,7 @@
       </c>
       <c r="AB68" s="57"/>
       <c r="AD68" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE68" s="36">
         <v>-5397.27</v>
@@ -13876,7 +13873,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -13912,7 +13909,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="52">
         <v>46303.5</v>
@@ -13984,7 +13981,7 @@
       </c>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE70" s="36">
         <v>0</v>
@@ -13996,7 +13993,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="52">
         <v>47801.68</v>
@@ -14076,7 +14073,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -14151,31 +14148,31 @@
         <v>40</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="52"/>
       <c r="E74" s="52"/>
       <c r="F74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G74" s="53"/>
       <c r="H74" s="52"/>
       <c r="I74" s="52"/>
       <c r="J74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M74" s="53"/>
       <c r="N74" s="53"/>
       <c r="O74" s="52"/>
       <c r="P74" s="52"/>
       <c r="Q74" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R74" s="53"/>
       <c r="S74" s="54">
@@ -14193,13 +14190,13 @@
       </c>
       <c r="X74" s="55"/>
       <c r="Y74" s="55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z74" s="53"/>
       <c r="AA74" s="56"/>
       <c r="AB74" s="57"/>
       <c r="AD74" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE74" s="35"/>
       <c r="AH74" s="19"/>
@@ -14209,7 +14206,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D75" s="52">
         <v>77166.16</v>
@@ -14281,7 +14278,7 @@
       </c>
       <c r="AB75" s="57"/>
       <c r="AD75" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE75" s="36"/>
       <c r="AH75" s="19"/>
@@ -14291,7 +14288,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="52">
         <v>77166.16</v>
@@ -14371,7 +14368,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77" s="52">
         <v>77166.16</v>
@@ -14443,7 +14440,7 @@
       </c>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE77" s="36">
         <v>0</v>
@@ -14455,7 +14452,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="52">
         <v>77166.16</v>
@@ -14535,7 +14532,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -14608,7 +14605,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" s="52">
         <v>25467.84</v>
@@ -14682,7 +14679,7 @@
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE81" s="35">
         <v>-143.25</v>
@@ -14698,7 +14695,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="52">
         <v>25467.84</v>
@@ -14770,7 +14767,7 @@
       </c>
       <c r="AB82" s="57"/>
       <c r="AD82" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE82" s="36">
         <v>-5569.48</v>
@@ -14782,7 +14779,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -14818,7 +14815,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="52">
         <v>25467.84</v>
@@ -14890,7 +14887,7 @@
       </c>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE84" s="36">
         <v>0</v>
@@ -14902,7 +14899,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" s="52">
         <v>25467.84</v>
@@ -14982,7 +14979,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
@@ -15059,7 +15056,7 @@
         <v>43</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="67">
         <v>37083.03</v>
@@ -15133,7 +15130,7 @@
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE88" s="35">
         <v>-148.5</v>
@@ -15149,7 +15146,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D89" s="67">
         <v>37083.03</v>
@@ -15221,7 +15218,7 @@
       </c>
       <c r="AB89" s="57"/>
       <c r="AD89" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE89" s="36">
         <v>-14143.19</v>
@@ -15233,7 +15230,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="67">
         <v>37083.03</v>
@@ -15313,7 +15310,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="67">
         <v>37083.03</v>
@@ -15385,7 +15382,7 @@
       </c>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE91" s="36">
         <v>0</v>
@@ -15397,7 +15394,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="67">
         <v>37083.03</v>
@@ -15477,7 +15474,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="67"/>
       <c r="E93" s="67"/>
@@ -15554,7 +15551,7 @@
         <v>44</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D95" s="52">
         <v>26186.14</v>
@@ -15628,7 +15625,7 @@
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE95" s="35">
         <v>-5</v>
@@ -15644,7 +15641,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="52"/>
       <c r="E96" s="52"/>
@@ -15672,7 +15669,7 @@
       <c r="AA96" s="56"/>
       <c r="AB96" s="57"/>
       <c r="AD96" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE96" s="36">
         <v>-7679.91</v>
@@ -15684,7 +15681,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="52"/>
@@ -15720,7 +15717,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" s="52">
         <v>26186.14</v>
@@ -15792,7 +15789,7 @@
       </c>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE98" s="36">
         <v>0</v>
@@ -15804,7 +15801,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" s="52">
         <v>26186.14</v>
@@ -15884,7 +15881,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -15961,7 +15958,7 @@
         <v>45</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="52">
         <v>33188.02</v>
@@ -16035,7 +16032,7 @@
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE102" s="35">
         <v>-317.25</v>
@@ -16051,7 +16048,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D103" s="52">
         <v>32473.02</v>
@@ -16123,7 +16120,7 @@
       </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE103" s="36">
         <v>-16562.52</v>
@@ -16135,7 +16132,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="52">
         <v>32473.02</v>
@@ -16215,7 +16212,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105" s="52">
         <v>32473.02</v>
@@ -16287,7 +16284,7 @@
       </c>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE105" s="36">
         <v>0</v>
@@ -16299,7 +16296,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D106" s="52">
         <v>32473.02</v>
@@ -16379,7 +16376,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="67"/>
@@ -16453,10 +16450,10 @@
         <v>8840</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="52">
         <v>56556.55</v>
@@ -16532,7 +16529,7 @@
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE109" s="35">
         <v>-204.75</v>
@@ -16548,7 +16545,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D110" s="52">
         <v>58902.56</v>
@@ -16620,7 +16617,7 @@
       </c>
       <c r="AB110" s="57"/>
       <c r="AD110" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE110" s="36">
         <v>-12155.27</v>
@@ -16632,7 +16629,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="52">
         <v>58902.56</v>
@@ -16712,7 +16709,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="52">
         <v>58902.56</v>
@@ -16784,7 +16781,7 @@
       </c>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE112" s="36">
         <v>0</v>
@@ -16796,7 +16793,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" s="52">
         <v>58902.56</v>
@@ -16876,7 +16873,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D114" s="52"/>
       <c r="E114" s="52"/>
@@ -16950,10 +16947,10 @@
         <v>8769</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="52">
         <v>21404.82</v>
@@ -16977,7 +16974,7 @@
         <v>13229.5</v>
       </c>
       <c r="K116" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L116" s="52">
         <v>13229.5</v>
@@ -17025,7 +17022,7 @@
       </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE116" s="35"/>
       <c r="AH116" s="19"/>
@@ -17035,7 +17032,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="52">
         <v>21404.82</v>
@@ -17107,7 +17104,7 @@
       </c>
       <c r="AB117" s="57"/>
       <c r="AD117" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE117" s="36"/>
       <c r="AH117" s="19"/>
@@ -17117,7 +17114,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="52"/>
       <c r="E118" s="52"/>
@@ -17155,7 +17152,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="52">
         <v>21404.82</v>
@@ -17227,7 +17224,7 @@
       </c>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE119" s="36">
         <v>0</v>
@@ -17239,7 +17236,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D120" s="52">
         <v>21404.82</v>
@@ -17319,7 +17316,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D121" s="52"/>
       <c r="E121" s="52"/>
@@ -17391,10 +17388,10 @@
         <v>7901</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D123" s="52">
         <v>96573.02</v>
@@ -17464,7 +17461,7 @@
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE123" s="35"/>
       <c r="AH123" s="19"/>
@@ -17476,7 +17473,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="52">
         <v>99768.39</v>
@@ -17548,7 +17545,7 @@
       </c>
       <c r="AB124" s="57"/>
       <c r="AD124" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE124" s="36">
         <v>-12186.08</v>
@@ -17560,7 +17557,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D125" s="52">
         <v>99768.39</v>
@@ -17640,7 +17637,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="52">
         <v>100987.51</v>
@@ -17712,7 +17709,7 @@
       </c>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE126" s="36">
         <v>0</v>
@@ -17724,7 +17721,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D127" s="52">
         <v>100987.51</v>
@@ -17804,7 +17801,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="52"/>
       <c r="E128" s="52"/>
@@ -17878,10 +17875,10 @@
         <v>8923</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D130" s="52">
         <v>31802.41</v>
@@ -17955,7 +17952,7 @@
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE130" s="35">
         <v>-2</v>
@@ -17971,7 +17968,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="52"/>
       <c r="E131" s="52"/>
@@ -17999,7 +17996,7 @@
       <c r="AA131" s="56"/>
       <c r="AB131" s="57"/>
       <c r="AD131" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE131" s="36">
         <v>-11154.51</v>
@@ -18011,7 +18008,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="52"/>
       <c r="E132" s="52"/>
@@ -18046,7 +18043,7 @@
     <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="52">
         <v>31802.41</v>
@@ -18118,7 +18115,7 @@
       </c>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE133" s="36">
         <v>0</v>
@@ -18130,7 +18127,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D134" s="52">
         <v>31802.41</v>
@@ -18210,7 +18207,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D135" s="52"/>
       <c r="E135" s="52"/>
@@ -18284,10 +18281,10 @@
         <v>7864</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D137" s="52">
         <v>28626.25</v>
@@ -18361,7 +18358,7 @@
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE137" s="35">
         <v>-266.75</v>
@@ -18377,7 +18374,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D138" s="52">
         <v>28626.25</v>
@@ -18449,7 +18446,7 @@
       </c>
       <c r="AB138" s="57"/>
       <c r="AD138" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE138" s="36">
         <v>-11702.32</v>
@@ -18461,7 +18458,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" s="52">
         <v>30749.24</v>
@@ -18541,7 +18538,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D140" s="52">
         <v>30749.24</v>
@@ -18613,7 +18610,7 @@
       </c>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE140" s="36">
         <v>0</v>
@@ -18625,7 +18622,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D141" s="52">
         <v>30749.24</v>
@@ -18705,7 +18702,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="52"/>
       <c r="E142" s="52"/>
@@ -18779,10 +18776,10 @@
         <v>7912</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D144" s="52">
         <v>268228.26</v>
@@ -18854,7 +18851,7 @@
       </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE144" s="35"/>
       <c r="AH144" s="19"/>
@@ -18864,7 +18861,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D145" s="52">
         <v>268228.26</v>
@@ -18936,7 +18933,7 @@
       </c>
       <c r="AB145" s="57"/>
       <c r="AD145" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE145" s="36"/>
       <c r="AH145" s="19"/>
@@ -18946,7 +18943,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" s="52"/>
       <c r="E146" s="52"/>
@@ -18982,7 +18979,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D147" s="52">
         <v>268228.26</v>
@@ -19054,7 +19051,7 @@
       </c>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE147" s="36">
         <v>0</v>
@@ -19066,7 +19063,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D148" s="52">
         <v>268228.26</v>
@@ -19146,7 +19143,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D149" s="52"/>
       <c r="E149" s="52"/>
@@ -19216,10 +19213,10 @@
         <v>8360</v>
       </c>
       <c r="B151" s="74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="52">
         <v>32773.41</v>
@@ -19228,10 +19225,10 @@
         <v>32773.41</v>
       </c>
       <c r="F151" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G151" s="53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H151" s="52">
         <v>22750.99</v>
@@ -19291,7 +19288,7 @@
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE151" s="35">
         <v>-260.75</v>
@@ -19307,7 +19304,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D152" s="52">
         <v>32773.41</v>
@@ -19379,7 +19376,7 @@
       </c>
       <c r="AB152" s="57"/>
       <c r="AD152" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE152" s="36">
         <v>-9324.41</v>
@@ -19391,7 +19388,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153" s="52"/>
       <c r="E153" s="52"/>
@@ -19427,7 +19424,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D154" s="52">
         <v>32773.41</v>
@@ -19499,7 +19496,7 @@
       </c>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE154" s="36">
         <v>0</v>
@@ -19511,7 +19508,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D155" s="52">
         <v>32773.41</v>
@@ -19591,7 +19588,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -19665,10 +19662,10 @@
         <v>8337</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158" s="52">
         <v>17899.33</v>
@@ -19738,7 +19735,7 @@
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE158" s="35">
         <v>-44.75</v>
@@ -19752,7 +19749,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D159" s="52">
         <v>17899.33</v>
@@ -19824,7 +19821,7 @@
       </c>
       <c r="AB159" s="57"/>
       <c r="AD159" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE159" s="36"/>
       <c r="AH159" s="19"/>
@@ -19834,7 +19831,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -19874,7 +19871,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D161" s="52">
         <v>17899.33</v>
@@ -19946,7 +19943,7 @@
       </c>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE161" s="36">
         <v>0</v>
@@ -19958,7 +19955,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" s="52">
         <v>17899.33</v>
@@ -20038,7 +20035,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -20114,10 +20111,10 @@
         <v>9240</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D165" s="52">
         <v>10827.2</v>
@@ -20137,7 +20134,7 @@
         <v>4388.87</v>
       </c>
       <c r="K165" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L165" s="52">
         <v>4388.87</v>
@@ -20177,7 +20174,7 @@
       </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE165" s="35"/>
       <c r="AH165" s="19"/>
@@ -20187,7 +20184,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D166" s="52"/>
       <c r="E166" s="52"/>
@@ -20215,7 +20212,7 @@
       <c r="AA166" s="56"/>
       <c r="AB166" s="57"/>
       <c r="AD166" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE166" s="36"/>
       <c r="AH166" s="19"/>
@@ -20225,7 +20222,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="52"/>
       <c r="E167" s="52"/>
@@ -20261,7 +20258,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D168" s="52"/>
       <c r="E168" s="52"/>
@@ -20289,7 +20286,7 @@
       <c r="AA168" s="56"/>
       <c r="AB168" s="57"/>
       <c r="AD168" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE168" s="36">
         <v>0</v>
@@ -20301,7 +20298,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
@@ -20337,7 +20334,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
@@ -20407,10 +20404,10 @@
         <v>7428</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="52">
         <v>146237.11</v>
@@ -20482,7 +20479,7 @@
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE172" s="35">
         <v>-304.75</v>
@@ -20496,7 +20493,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="52">
         <v>146237.11</v>
@@ -20568,7 +20565,7 @@
       </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE173" s="36"/>
       <c r="AH173" s="19"/>
@@ -20578,7 +20575,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D174" s="52">
         <v>146237.11</v>
@@ -20658,7 +20655,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D175" s="52">
         <v>146237.11</v>
@@ -20730,7 +20727,7 @@
       </c>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE175" s="36">
         <v>0</v>
@@ -20742,7 +20739,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D176" s="52">
         <v>146237.11</v>
@@ -20822,7 +20819,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="52"/>
       <c r="E177" s="52"/>
@@ -20898,10 +20895,10 @@
         <v>9351</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="52">
         <v>16897.53</v>
@@ -20971,7 +20968,7 @@
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE179" s="35">
         <v>-11.25</v>
@@ -20987,7 +20984,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D180" s="52">
         <v>16897.53</v>
@@ -21059,7 +21056,7 @@
       </c>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE180" s="36">
         <v>-2298.71</v>
@@ -21071,7 +21068,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="52"/>
       <c r="E181" s="52"/>
@@ -21107,7 +21104,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D182" s="52">
         <v>16897.53</v>
@@ -21179,7 +21176,7 @@
       </c>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE182" s="36">
         <v>0</v>
@@ -21191,7 +21188,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D183" s="52">
         <v>16897.53</v>
@@ -21271,7 +21268,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
@@ -21345,10 +21342,10 @@
         <v>7429</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D186" s="52">
         <v>20992.12</v>
@@ -21420,7 +21417,7 @@
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE186" s="35">
         <v>-32.25</v>
@@ -21434,7 +21431,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="52">
         <v>20992.12</v>
@@ -21506,7 +21503,7 @@
       </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE187" s="36"/>
       <c r="AH187" s="19"/>
@@ -21516,7 +21513,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="52"/>
       <c r="E188" s="52"/>
@@ -21554,7 +21551,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D189" s="52">
         <v>20992.12</v>
@@ -21626,7 +21623,7 @@
       </c>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE189" s="36">
         <v>0</v>
@@ -21638,7 +21635,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D190" s="52">
         <v>20992.12</v>
@@ -21718,7 +21715,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D191" s="52"/>
       <c r="E191" s="52"/>
@@ -21792,10 +21789,10 @@
         <v>9508</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D193" s="52">
         <v>23770.95</v>
@@ -21819,7 +21816,7 @@
         <v>7389.339999999999</v>
       </c>
       <c r="K193" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L193" s="52">
         <v>7389.339999999999</v>
@@ -21865,7 +21862,7 @@
       </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE193" s="35"/>
       <c r="AH193" s="19"/>
@@ -21875,7 +21872,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D194" s="52">
         <v>23770.95</v>
@@ -21947,7 +21944,7 @@
       </c>
       <c r="AB194" s="57"/>
       <c r="AD194" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE194" s="36"/>
       <c r="AH194" s="19"/>
@@ -21957,7 +21954,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" s="52"/>
       <c r="E195" s="52"/>
@@ -21995,7 +21992,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D196" s="52">
         <v>23770.95</v>
@@ -22067,7 +22064,7 @@
       </c>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE196" s="36">
         <v>0</v>
@@ -22079,7 +22076,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D197" s="52">
         <v>23770.95</v>
@@ -22159,7 +22156,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D198" s="52"/>
       <c r="E198" s="52"/>
@@ -22230,7 +22227,7 @@
       <c r="A200" s="19"/>
       <c r="B200" s="19"/>
       <c r="C200" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -22278,7 +22275,7 @@
       <c r="AA200" s="56"/>
       <c r="AB200" s="57"/>
       <c r="AD200" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE200" s="35"/>
       <c r="AH200" s="19"/>
@@ -22288,7 +22285,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D201" s="52"/>
       <c r="E201" s="52"/>
@@ -22320,7 +22317,7 @@
       <c r="AA201" s="56"/>
       <c r="AB201" s="57"/>
       <c r="AD201" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE201" s="36"/>
       <c r="AH201" s="19"/>
@@ -22330,7 +22327,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -22370,7 +22367,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -22402,7 +22399,7 @@
       <c r="AA203" s="56"/>
       <c r="AB203" s="57"/>
       <c r="AD203" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE203" s="36">
         <v>0</v>
@@ -22414,7 +22411,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -22454,7 +22451,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -22526,10 +22523,10 @@
     <row r="207" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="19"/>
       <c r="B207" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D207" s="52"/>
       <c r="E207" s="52"/>
@@ -22561,7 +22558,7 @@
       <c r="AA207" s="56"/>
       <c r="AB207" s="57"/>
       <c r="AD207" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE207" s="35"/>
       <c r="AH207" s="19"/>
@@ -22571,7 +22568,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D208" s="52"/>
       <c r="E208" s="52"/>
@@ -22603,7 +22600,7 @@
       <c r="AA208" s="56"/>
       <c r="AB208" s="57"/>
       <c r="AD208" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE208" s="36"/>
       <c r="AH208" s="19"/>
@@ -22613,7 +22610,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -22653,7 +22650,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -22685,7 +22682,7 @@
       <c r="AA210" s="56"/>
       <c r="AB210" s="57"/>
       <c r="AD210" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE210" s="36">
         <v>0</v>
@@ -22697,7 +22694,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -22737,7 +22734,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -22811,10 +22808,10 @@
         <v>8946</v>
       </c>
       <c r="B214" s="77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D214" s="52">
         <v>137109.56</v>
@@ -22838,7 +22835,7 @@
         <v>99479.62000000001</v>
       </c>
       <c r="K214" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L214" s="52">
         <v>99479.62000000001</v>
@@ -22882,7 +22879,7 @@
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE214" s="35"/>
       <c r="AH214" s="19"/>
@@ -22892,7 +22889,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D215" s="52">
         <v>137109.56</v>
@@ -22964,7 +22961,7 @@
       </c>
       <c r="AB215" s="57"/>
       <c r="AD215" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE215" s="36"/>
       <c r="AH215" s="19"/>
@@ -22974,7 +22971,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -23010,7 +23007,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D217" s="52">
         <v>137109.56</v>
@@ -23082,7 +23079,7 @@
       </c>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE217" s="36">
         <v>0</v>
@@ -23094,7 +23091,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D218" s="52">
         <v>137109.56</v>
@@ -23174,7 +23171,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -23244,10 +23241,10 @@
         <v>8308</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D221" s="52">
         <v>389318.35</v>
@@ -23319,7 +23316,7 @@
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE221" s="35">
         <v>-1014.25</v>
@@ -23333,7 +23330,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D222" s="52">
         <v>389318.35</v>
@@ -23405,7 +23402,7 @@
       </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE222" s="36"/>
       <c r="AH222" s="19"/>
@@ -23415,7 +23412,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -23455,7 +23452,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D224" s="52">
         <v>389318.35</v>
@@ -23527,7 +23524,7 @@
       </c>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE224" s="36">
         <v>0</v>
@@ -23539,7 +23536,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D225" s="52">
         <v>396453.46</v>
@@ -23619,7 +23616,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -24263,49 +24260,49 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="C2" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="D2" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="E2" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="F2" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="H2" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="83" t="s">
+      <c r="I2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="J2" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="82" t="s">
+      <c r="K2" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="L2" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="83" t="s">
+      <c r="M2" s="83" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="83" t="s">
+      <c r="N2" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="N2" s="81" t="s">
+      <c r="O2" s="84" t="s">
         <v>114</v>
-      </c>
-      <c r="O2" s="84" t="s">
-        <v>115</v>
       </c>
       <c r="P2" s="35"/>
     </row>
@@ -24438,7 +24435,7 @@
         <v>-559.5887999999993</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -24587,7 +24584,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="52">
         <v>83186.06</v>
@@ -24627,7 +24624,7 @@
         <v>190.44884057971015</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -24820,7 +24817,7 @@
         <v>-29.987619047619066</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -25259,7 +25256,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="52">
         <v>-35454.43</v>
@@ -25321,7 +25318,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="52">
         <v>0</v>
@@ -25381,7 +25378,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="52">
         <v>0</v>
@@ -25439,7 +25436,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="52">
         <v>0</v>
@@ -25501,7 +25498,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="52">
         <v>3554.300000000003</v>
@@ -25561,7 +25558,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="52">
         <v>0</v>
@@ -25615,7 +25612,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="99">
         <v>0</v>
@@ -25673,7 +25670,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="99">
         <v>13424.5</v>
@@ -25733,7 +25730,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="99">
         <v>0</v>
@@ -25767,7 +25764,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -25792,7 +25789,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="99">
         <v>31119.76000000001</v>
@@ -25854,7 +25851,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="99">
         <v>5491.7</v>
@@ -25916,7 +25913,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="99">
         <v>12937.1</v>
@@ -25978,7 +25975,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="99">
         <v>10204.54</v>
@@ -26064,7 +26061,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="99"/>
       <c r="D62" s="99"/>
@@ -26104,7 +26101,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="99">
         <v>30174.75</v>
@@ -26162,7 +26159,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="99">
         <v>0</v>
@@ -26238,10 +26235,10 @@
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="103" t="s">
         <v>121</v>
-      </c>
-      <c r="B69" s="103" t="s">
-        <v>122</v>
       </c>
       <c r="C69" s="104">
         <v>348854.75999999995</v>
@@ -26253,13 +26250,13 @@
         <v>-28126.379999999983</v>
       </c>
       <c r="F69" s="106" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G69" s="107">
         <v>-0.08062489960005129</v>
       </c>
       <c r="H69" s="108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I69" s="109">
         <v>-0.2292042109444056</v>
@@ -26274,7 +26271,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C70" s="99">
         <v>-22865.6</v>
@@ -26290,7 +26287,7 @@
         <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I70" s="114">
         <v>2.685240710936954</v>
@@ -26689,52 +26686,52 @@
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="D2" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="117" t="s">
+      <c r="E2" s="117" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="117" t="s">
+      <c r="F2" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="117" t="s">
+      <c r="G2" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="H2" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="I2" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="J2" s="117" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="K2" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="K2" s="117" t="s">
+      <c r="L2" s="117" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="117" t="s">
+      <c r="M2" s="117" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="117" t="s">
+      <c r="N2" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="N2" s="117" t="s">
+      <c r="O2" s="117" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="117" t="s">
+      <c r="P2" s="117" t="s">
         <v>139</v>
       </c>
-      <c r="P2" s="117" t="s">
+      <c r="Q2" s="118" t="s">
         <v>140</v>
-      </c>
-      <c r="Q2" s="118" t="s">
-        <v>141</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -26750,10 +26747,10 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="123" t="s">
         <v>142</v>
-      </c>
-      <c r="B3" s="123" t="s">
-        <v>143</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -26837,7 +26834,7 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -26890,7 +26887,7 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -26943,7 +26940,7 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27000,7 +26997,7 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27027,7 +27024,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -27057,7 +27054,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27114,7 +27111,7 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -27605,7 +27602,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="54">
         <v>324.19</v>
@@ -27655,7 +27652,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="54">
         <v>84.05</v>
@@ -27707,7 +27704,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="54">
         <v>290.15</v>
@@ -27762,7 +27759,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="54">
         <v>156.69</v>
@@ -27816,7 +27813,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="54">
         <v>200.82</v>
@@ -27865,7 +27862,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="54">
         <v>497.55</v>
@@ -27924,7 +27921,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="54">
         <v>210.6</v>
@@ -27972,7 +27969,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="54">
         <v>110.44</v>
@@ -28024,7 +28021,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="54">
         <v>64.71</v>
@@ -28076,7 +28073,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="54">
         <v>659.73</v>
@@ -28131,7 +28128,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="54">
         <v>125.17</v>
@@ -28186,7 +28183,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="54">
         <v>130.62</v>
@@ -28239,7 +28236,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="54">
         <v>140.15</v>
@@ -28329,7 +28326,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="54"/>
       <c r="D62" s="54"/>
@@ -28371,7 +28368,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="54">
         <v>358.86</v>
@@ -28423,7 +28420,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="54">
         <v>2344.68</v>
@@ -28517,7 +28514,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C70" s="147"/>
       <c r="D70" s="147"/>
@@ -28562,7 +28559,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
@@ -28601,7 +28598,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C72" s="20">
         <v>4490.26</v>
@@ -28630,7 +28627,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
@@ -28675,7 +28672,7 @@
     <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C74" s="152"/>
       <c r="D74" s="152"/>
@@ -28739,10 +28736,10 @@
     <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="157" t="s">
         <v>151</v>
-      </c>
-      <c r="C76" s="157" t="s">
-        <v>152</v>
       </c>
       <c r="D76" s="157"/>
       <c r="E76" s="157"/>
@@ -28786,7 +28783,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C77" s="157"/>
       <c r="D77" s="157"/>
@@ -28850,7 +28847,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C79" s="165"/>
       <c r="D79" s="35"/>
@@ -28862,7 +28859,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="166" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M79" s="166"/>
       <c r="N79" s="35"/>
@@ -28873,7 +28870,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C80" s="168">
         <v>1</v>
@@ -28896,7 +28893,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" s="131">
         <v>1</v>
@@ -28919,7 +28916,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -28942,7 +28939,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -28965,7 +28962,7 @@
     <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -28988,7 +28985,7 @@
     <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C85" s="131">
         <v>0.5</v>
@@ -29011,7 +29008,7 @@
     <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C86" s="131">
         <v>1</v>
@@ -29034,7 +29031,7 @@
     <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -29057,7 +29054,7 @@
     <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -29080,7 +29077,7 @@
     <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C89" s="131">
         <v>0</v>
@@ -29103,7 +29100,7 @@
     <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C90" s="131">
         <v>1</v>
@@ -29273,7 +29270,7 @@
     <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C98" s="131">
         <v>1</v>
@@ -29296,7 +29293,7 @@
     <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -29319,7 +29316,7 @@
     <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -29342,7 +29339,7 @@
     <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -29365,7 +29362,7 @@
     <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -29388,7 +29385,7 @@
     <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -29411,7 +29408,7 @@
     <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -29510,7 +29507,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C109" s="170">
         <v>16.5</v>
@@ -29586,7 +29583,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -29618,7 +29615,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -29651,7 +29648,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -29684,7 +29681,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -29717,7 +29714,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -29750,7 +29747,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -29783,7 +29780,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -29816,7 +29813,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -29911,7 +29908,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -29944,7 +29941,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -29977,7 +29974,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -30010,7 +30007,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -30043,7 +30040,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -30076,7 +30073,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -30109,7 +30106,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -30142,7 +30139,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -30175,7 +30172,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -30208,7 +30205,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -30241,7 +30238,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -30274,7 +30271,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -30307,7 +30304,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -30340,7 +30337,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -30373,7 +30370,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -30406,7 +30403,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -30439,7 +30436,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -30471,7 +30468,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -30503,7 +30500,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -30535,7 +30532,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -30567,7 +30564,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -30659,7 +30656,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -30691,7 +30688,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -30723,7 +30720,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -30755,7 +30752,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -30787,7 +30784,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -30849,7 +30846,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -30881,7 +30878,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -30913,7 +30910,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -30945,7 +30942,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -31097,7 +31094,7 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -31129,7 +31126,7 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -31409,7 +31406,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -32510,7 +32507,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -32542,7 +32539,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -32877,88 +32874,88 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="I2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="P2" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q2" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="R2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="P2" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q2" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="R2" s="43" t="s">
+      <c r="S2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="43" t="s">
+      <c r="T2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="U2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="V2" s="214" t="s">
         <v>79</v>
       </c>
-      <c r="V2" s="214" t="s">
+      <c r="W2" s="214" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="214" t="s">
+      <c r="X2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="X2" s="45" t="s">
+      <c r="Y2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Z2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="AA2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="AA2" s="46" t="s">
+      <c r="AB2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="AB2" s="47" t="s">
+      <c r="AC2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="AC2" s="46" t="s">
+      <c r="AD2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AD2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AG2" s="35"/>
       <c r="AH2" s="35"/>
@@ -32999,10 +32996,10 @@
       <c r="AG3" s="35"/>
       <c r="AH3" s="35"/>
       <c r="AK3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AL3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -33015,7 +33012,7 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>1914143.52</v>
@@ -33111,7 +33108,7 @@
       </c>
       <c r="AE4" s="57"/>
       <c r="AG4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH4" s="35">
         <f>AK9</f>
@@ -33130,7 +33127,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52">
         <v>1922479.92</v>
@@ -33219,7 +33216,7 @@
       </c>
       <c r="AE5" s="57"/>
       <c r="AG5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH5" s="36">
         <f>AL9</f>
@@ -33238,7 +33235,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52">
         <v>1922479.92</v>
@@ -33345,7 +33342,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -33418,7 +33415,7 @@
       </c>
       <c r="AE7" s="57"/>
       <c r="AG7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH7" s="36">
         <v>0</v>
@@ -33436,7 +33433,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -33523,7 +33520,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -33652,7 +33649,7 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="65">
         <v>381671.63</v>
@@ -33741,7 +33738,7 @@
       </c>
       <c r="AE11" s="57"/>
       <c r="AG11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH11" s="35">
         <f>AK16</f>
@@ -33760,7 +33757,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>382219.49</v>
@@ -33849,7 +33846,7 @@
       </c>
       <c r="AE12" s="57"/>
       <c r="AG12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH12" s="36">
         <f>AL16</f>
@@ -33868,7 +33865,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52">
         <v>382219.49</v>
@@ -33971,7 +33968,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="65">
         <v>383409.63</v>
@@ -34052,7 +34049,7 @@
       </c>
       <c r="AE14" s="57"/>
       <c r="AG14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH14" s="36">
         <v>0</v>
@@ -34070,7 +34067,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="65">
         <v>383409.63</v>
@@ -34159,7 +34156,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="65">
         <v>383409.63</v>
@@ -34293,7 +34290,7 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>449818.08</v>
@@ -34386,7 +34383,7 @@
       </c>
       <c r="AE18" s="57"/>
       <c r="AG18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH18" s="35">
         <f>AK23</f>
@@ -34405,7 +34402,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52">
         <v>449818.08</v>
@@ -34496,7 +34493,7 @@
       </c>
       <c r="AE19" s="57"/>
       <c r="AG19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH19" s="36">
         <f>AL23</f>
@@ -34515,7 +34512,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="52">
         <v>449818.08</v>
@@ -34620,7 +34617,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -34695,7 +34692,7 @@
       </c>
       <c r="AE21" s="57"/>
       <c r="AG21" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH21" s="36">
         <v>0</v>
@@ -34713,7 +34710,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -34802,7 +34799,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -34935,7 +34932,7 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="52">
         <v>38856.96</v>
@@ -35028,7 +35025,7 @@
       </c>
       <c r="AE25" s="57"/>
       <c r="AG25" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH25" s="35">
         <f>AK30</f>
@@ -35047,7 +35044,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="52">
         <v>38856.96</v>
@@ -35140,7 +35137,7 @@
       </c>
       <c r="AE26" s="57"/>
       <c r="AG26" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH26" s="36">
         <f>AL30</f>
@@ -35159,7 +35156,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="52">
         <v>38856.96</v>
@@ -35266,7 +35263,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52">
@@ -35349,7 +35346,7 @@
       </c>
       <c r="AE28" s="57"/>
       <c r="AG28" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH28" s="36">
         <v>0</v>
@@ -35367,7 +35364,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -35464,7 +35461,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -35603,7 +35600,7 @@
         <v>Murney - 1 Freight Drive + 109 Iport</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="52">
         <v>69191.71</v>
@@ -35694,7 +35691,7 @@
       </c>
       <c r="AE32" s="57"/>
       <c r="AG32" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH32" s="35">
         <f>AK37</f>
@@ -35713,7 +35710,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="52">
         <v>69191.71</v>
@@ -35802,7 +35799,7 @@
       </c>
       <c r="AE33" s="57"/>
       <c r="AG33" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH33" s="36">
         <f>AL37</f>
@@ -35821,7 +35818,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="52">
         <v>69191.71</v>
@@ -35924,7 +35921,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -35997,7 +35994,7 @@
       </c>
       <c r="AE35" s="57"/>
       <c r="AG35" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH35" s="36">
         <v>0</v>
@@ -36015,7 +36012,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -36102,7 +36099,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -36231,7 +36228,7 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="52">
         <v>44956.29</v>
@@ -36318,7 +36315,7 @@
       </c>
       <c r="AE39" s="57"/>
       <c r="AG39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH39" s="35">
         <f>AK44</f>
@@ -36337,7 +36334,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="52">
         <v>44956.29</v>
@@ -36422,7 +36419,7 @@
       </c>
       <c r="AE40" s="57"/>
       <c r="AG40" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH40" s="36">
         <f>AL44</f>
@@ -36441,7 +36438,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" s="52">
         <v>44956.29</v>
@@ -36544,7 +36541,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -36621,7 +36618,7 @@
       </c>
       <c r="AE42" s="57"/>
       <c r="AG42" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH42" s="36">
         <v>0</v>
@@ -36639,7 +36636,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -36730,7 +36727,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -36863,7 +36860,7 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="52">
         <v>7495.54</v>
@@ -36956,7 +36953,7 @@
       </c>
       <c r="AE46" s="57"/>
       <c r="AG46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH46" s="35">
         <f>AK51</f>
@@ -36975,7 +36972,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="52">
         <v>7495.54</v>
@@ -37068,7 +37065,7 @@
       </c>
       <c r="AE47" s="57"/>
       <c r="AG47" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH47" s="36">
         <f>AL51</f>
@@ -37087,7 +37084,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="52">
         <v>7495.54</v>
@@ -37194,7 +37191,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52">
@@ -37275,7 +37272,7 @@
       </c>
       <c r="AE49" s="57"/>
       <c r="AG49" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH49" s="36">
         <v>0</v>
@@ -37293,7 +37290,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52">
@@ -37388,7 +37385,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52">
@@ -37525,7 +37522,7 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="52">
         <v>100348.26</v>
@@ -37618,7 +37615,7 @@
       </c>
       <c r="AE53" s="57"/>
       <c r="AG53" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH53" s="35">
         <f>AK58</f>
@@ -37637,7 +37634,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="52">
         <v>100348.26</v>
@@ -37726,7 +37723,7 @@
       </c>
       <c r="AE54" s="57"/>
       <c r="AG54" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH54" s="36">
         <f>AL58</f>
@@ -37745,7 +37742,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="52">
         <v>100348.26</v>
@@ -37848,7 +37845,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -37921,7 +37918,7 @@
       </c>
       <c r="AE56" s="57"/>
       <c r="AG56" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH56" s="36">
         <v>0</v>
@@ -37939,7 +37936,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -38026,7 +38023,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -38159,7 +38156,7 @@
         <v>35 Mania</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="52">
         <v>98524.85</v>
@@ -38250,7 +38247,7 @@
       </c>
       <c r="AE60" s="57"/>
       <c r="AG60" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH60" s="35">
         <f>AK65</f>
@@ -38269,7 +38266,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D61" s="52">
         <v>98524.85</v>
@@ -38360,7 +38357,7 @@
       </c>
       <c r="AE61" s="57"/>
       <c r="AG61" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH61" s="36">
         <f>AL65</f>
@@ -38379,7 +38376,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="52">
         <v>98524.85</v>
@@ -38484,7 +38481,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -38561,7 +38558,7 @@
       </c>
       <c r="AE63" s="57"/>
       <c r="AG63" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH63" s="36">
         <v>0</v>
@@ -38579,7 +38576,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -38670,7 +38667,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -38803,7 +38800,7 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="52">
         <v>87970.61</v>
@@ -38892,7 +38889,7 @@
       </c>
       <c r="AE67" s="57"/>
       <c r="AG67" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH67" s="35">
         <f>AK72</f>
@@ -38911,7 +38908,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="52">
         <v>87970.61</v>
@@ -39002,7 +38999,7 @@
       </c>
       <c r="AE68" s="57"/>
       <c r="AG68" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH68" s="36">
         <f>AL72</f>
@@ -39021,7 +39018,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -39110,7 +39107,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -39185,7 +39182,7 @@
       </c>
       <c r="AE70" s="57"/>
       <c r="AG70" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH70" s="36">
         <v>0</v>
@@ -39203,7 +39200,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -39292,7 +39289,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -39421,7 +39418,7 @@
         <v>Andrew Reeve Stage 2</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="52">
         <v>210242.4</v>
@@ -39514,7 +39511,7 @@
       </c>
       <c r="AE74" s="57"/>
       <c r="AG74" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH74" s="35">
         <f>AK79</f>
@@ -39533,7 +39530,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D75" s="52">
         <v>210242.4</v>
@@ -39624,7 +39621,7 @@
       </c>
       <c r="AE75" s="57"/>
       <c r="AG75" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH75" s="36">
         <f>AL79</f>
@@ -39643,7 +39640,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="52">
         <v>210242.4</v>
@@ -39748,7 +39745,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -39827,7 +39824,7 @@
       </c>
       <c r="AE77" s="57"/>
       <c r="AG77" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH77" s="36">
         <v>0</v>
@@ -39845,7 +39842,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -39940,7 +39937,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -40077,7 +40074,7 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" s="52">
         <v>43448.62</v>
@@ -40170,7 +40167,7 @@
       </c>
       <c r="AE81" s="57"/>
       <c r="AG81" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH81" s="35">
         <f>AK86</f>
@@ -40189,7 +40186,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="52">
         <v>43448.62</v>
@@ -40282,7 +40279,7 @@
       </c>
       <c r="AE82" s="57"/>
       <c r="AG82" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH82" s="36">
         <f>AL86</f>
@@ -40301,7 +40298,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="52">
         <v>0</v>
@@ -40406,7 +40403,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="52">
         <v>0</v>
@@ -40497,7 +40494,7 @@
       </c>
       <c r="AE84" s="57"/>
       <c r="AG84" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH84" s="36">
         <v>0</v>
@@ -40515,7 +40512,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" s="52">
         <v>0</v>
@@ -40618,7 +40615,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="52">
         <v>0</v>
@@ -40763,7 +40760,7 @@
         <v>Melhuish House</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="67">
         <v>49964.93</v>
@@ -40856,7 +40853,7 @@
       </c>
       <c r="AE88" s="57"/>
       <c r="AG88" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH88" s="35">
         <f>AK93</f>
@@ -40875,7 +40872,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D89" s="67">
         <v>49964.93</v>
@@ -40964,7 +40961,7 @@
       </c>
       <c r="AE89" s="57"/>
       <c r="AG89" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH89" s="36">
         <f>AL93</f>
@@ -40983,7 +40980,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="67">
         <v>0</v>
@@ -41086,7 +41083,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="67">
         <v>0</v>
@@ -41175,7 +41172,7 @@
       </c>
       <c r="AE91" s="57"/>
       <c r="AG91" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH91" s="36">
         <v>0</v>
@@ -41193,7 +41190,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="67">
         <v>0</v>
@@ -41296,7 +41293,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="67">
         <v>0</v>
@@ -41441,7 +41438,7 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D95" s="52">
         <v>109103.76</v>
@@ -41534,7 +41531,7 @@
       </c>
       <c r="AE95" s="57"/>
       <c r="AG95" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH95" s="35">
         <f>AK100</f>
@@ -41553,7 +41550,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="52">
         <v>109103.76</v>
@@ -41646,7 +41643,7 @@
       </c>
       <c r="AE96" s="57"/>
       <c r="AG96" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH96" s="36">
         <f>AL100</f>
@@ -41665,7 +41662,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="52">
         <v>0</v>
@@ -41772,7 +41769,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" s="52">
         <v>0</v>
@@ -41865,7 +41862,7 @@
       </c>
       <c r="AE98" s="57"/>
       <c r="AG98" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH98" s="36">
         <v>0</v>
@@ -41883,7 +41880,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" s="52">
         <v>0</v>
@@ -41988,7 +41985,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="52">
         <v>0</v>
@@ -42135,7 +42132,7 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="52">
         <v>27742.44</v>
@@ -42226,7 +42223,7 @@
       </c>
       <c r="AE102" s="57"/>
       <c r="AG102" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH102" s="35">
         <f>AK107</f>
@@ -42245,7 +42242,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D103" s="52">
         <v>27861.41</v>
@@ -42336,7 +42333,7 @@
       </c>
       <c r="AE103" s="57"/>
       <c r="AG103" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH103" s="36">
         <f>AL107</f>
@@ -42355,7 +42352,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="52">
         <v>0</v>
@@ -42460,7 +42457,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105" s="52">
         <v>0</v>
@@ -42551,7 +42548,7 @@
       </c>
       <c r="AE105" s="57"/>
       <c r="AG105" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH105" s="36">
         <v>0</v>
@@ -42569,7 +42566,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D106" s="52">
         <v>0</v>
@@ -42674,7 +42671,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D107" s="52">
         <v>0</v>
@@ -42821,7 +42818,7 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="52">
         <v>21300.45</v>
@@ -42913,7 +42910,7 @@
       </c>
       <c r="AE109" s="57"/>
       <c r="AG109" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH109" s="35">
         <f>AK114</f>
@@ -42932,7 +42929,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D110" s="52">
         <v>21300.45</v>
@@ -43025,7 +43022,7 @@
       </c>
       <c r="AE110" s="57"/>
       <c r="AG110" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH110" s="36">
         <f>AL114</f>
@@ -43044,7 +43041,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="52">
         <v>0</v>
@@ -43151,7 +43148,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="52">
         <v>0</v>
@@ -43244,7 +43241,7 @@
       </c>
       <c r="AE112" s="57"/>
       <c r="AG112" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH112" s="36">
         <v>0</v>
@@ -43262,7 +43259,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" s="52">
         <v>0</v>
@@ -43369,7 +43366,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D114" s="52">
         <v>0</v>
@@ -43518,7 +43515,7 @@
         <v>Percival Bach</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="52">
         <v>63405.46</v>
@@ -43611,7 +43608,7 @@
       </c>
       <c r="AE116" s="57"/>
       <c r="AG116" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH116" s="35">
         <f>AK121</f>
@@ -43630,7 +43627,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="52">
         <v>63405.46</v>
@@ -43723,7 +43720,7 @@
       </c>
       <c r="AE117" s="57"/>
       <c r="AG117" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH117" s="36">
         <f>AL121</f>
@@ -43742,7 +43739,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="52">
         <v>0</v>
@@ -43849,7 +43846,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="52">
         <v>0</v>
@@ -43942,7 +43939,7 @@
       </c>
       <c r="AE119" s="57"/>
       <c r="AG119" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH119" s="36">
         <v>0</v>
@@ -43960,7 +43957,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D120" s="52">
         <v>0</v>
@@ -44067,7 +44064,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D121" s="52">
         <v>0</v>
@@ -44216,7 +44213,7 @@
         <v>St Albans Street</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D123" s="52">
         <v>0</v>
@@ -44308,7 +44305,7 @@
       </c>
       <c r="AE123" s="57"/>
       <c r="AG123" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH123" s="35">
         <f>AK128</f>
@@ -44327,7 +44324,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="52">
         <v>0</v>
@@ -44416,7 +44413,7 @@
       </c>
       <c r="AE124" s="57"/>
       <c r="AG124" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH124" s="36">
         <f>AL128</f>
@@ -44435,7 +44432,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D125" s="52">
         <v>0</v>
@@ -44538,7 +44535,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="52">
         <v>0</v>
@@ -44627,7 +44624,7 @@
       </c>
       <c r="AE126" s="57"/>
       <c r="AG126" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH126" s="36">
         <v>0</v>
@@ -44645,7 +44642,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D127" s="52">
         <v>0</v>
@@ -44748,7 +44745,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="52">
         <v>0</v>
@@ -44893,7 +44890,7 @@
         <v>4 Perry St</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D130" s="52">
         <v>47191.69</v>
@@ -44986,7 +44983,7 @@
       </c>
       <c r="AE130" s="57"/>
       <c r="AG130" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH130" s="35">
         <f>AK135</f>
@@ -45005,7 +45002,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="52">
         <v>47191.69</v>
@@ -45098,7 +45095,7 @@
       </c>
       <c r="AE131" s="57"/>
       <c r="AG131" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH131" s="36">
         <f>AL135</f>
@@ -45117,7 +45114,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="52">
         <v>0</v>
@@ -45222,7 +45219,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="52">
         <v>0</v>
@@ -45313,7 +45310,7 @@
       </c>
       <c r="AE133" s="57"/>
       <c r="AG133" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH133" s="36">
         <v>0</v>
@@ -45331,7 +45328,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D134" s="52">
         <v>0</v>
@@ -45436,7 +45433,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D135" s="52">
         <v>0</v>
@@ -45583,7 +45580,7 @@
         <v>Ryans House</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D137" s="52">
         <v>0</v>
@@ -45676,7 +45673,7 @@
       </c>
       <c r="AE137" s="57"/>
       <c r="AG137" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH137" s="35">
         <f>AK142</f>
@@ -45695,7 +45692,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D138" s="52">
         <v>0</v>
@@ -45782,7 +45779,7 @@
       </c>
       <c r="AE138" s="57"/>
       <c r="AG138" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH138" s="36">
         <f>AL142</f>
@@ -45801,7 +45798,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" s="52">
         <v>0</v>
@@ -45902,7 +45899,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D140" s="52">
         <v>0</v>
@@ -45987,7 +45984,7 @@
       </c>
       <c r="AE140" s="57"/>
       <c r="AG140" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH140" s="36">
         <v>0</v>
@@ -46005,7 +46002,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D141" s="52">
         <v>0</v>
@@ -46104,7 +46101,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="52">
         <v>0</v>
@@ -46245,7 +46242,7 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D144" s="52">
         <v>23650.59</v>
@@ -46334,7 +46331,7 @@
       </c>
       <c r="AE144" s="57"/>
       <c r="AG144" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH144" s="35">
         <f>AK149</f>
@@ -46353,7 +46350,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D145" s="52">
         <v>23650.59</v>
@@ -46442,7 +46439,7 @@
       </c>
       <c r="AE145" s="57"/>
       <c r="AG145" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH145" s="36">
         <f>AL149</f>
@@ -46461,7 +46458,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" s="52">
         <v>23650.59</v>
@@ -46564,7 +46561,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D147" s="52">
         <v>23650.59</v>
@@ -46653,7 +46650,7 @@
       </c>
       <c r="AE147" s="57"/>
       <c r="AG147" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH147" s="36">
         <v>0</v>
@@ -46671,7 +46668,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D148" s="52">
         <v>23650.59</v>
@@ -46774,7 +46771,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D149" s="52">
         <v>23650.59</v>
@@ -46919,7 +46916,7 @@
         <v>Dixon House</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="52">
         <v>29188.19</v>
@@ -47008,7 +47005,7 @@
       </c>
       <c r="AE151" s="57"/>
       <c r="AG151" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH151" s="35">
         <f>AK156</f>
@@ -47027,7 +47024,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D152" s="52">
         <v>29188.19</v>
@@ -47116,7 +47113,7 @@
       </c>
       <c r="AE152" s="57"/>
       <c r="AG152" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH152" s="36">
         <f>AL156</f>
@@ -47135,7 +47132,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153" s="52">
         <v>29188.19</v>
@@ -47238,7 +47235,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D154" s="52">
         <v>29188.19</v>
@@ -47327,7 +47324,7 @@
       </c>
       <c r="AE154" s="57"/>
       <c r="AG154" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH154" s="36">
         <v>0</v>
@@ -47345,7 +47342,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -47432,7 +47429,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -47561,7 +47558,7 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158" s="52">
         <v>15025.89</v>
@@ -47648,7 +47645,7 @@
       </c>
       <c r="AE158" s="57"/>
       <c r="AG158" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH158" s="35">
         <f>AK163</f>
@@ -47667,7 +47664,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D159" s="52">
         <v>0</v>
@@ -47753,7 +47750,7 @@
       </c>
       <c r="AE159" s="57"/>
       <c r="AG159" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH159" s="36">
         <f>AL163</f>
@@ -47772,7 +47769,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -47859,7 +47856,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -47932,7 +47929,7 @@
       </c>
       <c r="AE161" s="57"/>
       <c r="AG161" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH161" s="36">
         <v>0</v>
@@ -47950,7 +47947,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -48037,7 +48034,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -48166,7 +48163,7 @@
         <v>Daves Twizel Shack</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D165" s="52">
         <v>300839.52</v>
@@ -48255,7 +48252,7 @@
       </c>
       <c r="AE165" s="57"/>
       <c r="AG165" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH165" s="35">
         <f>AK170</f>
@@ -48274,7 +48271,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D166" s="52">
         <v>300839.52</v>
@@ -48363,7 +48360,7 @@
       </c>
       <c r="AE166" s="57"/>
       <c r="AG166" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH166" s="36">
         <f>AL170</f>
@@ -48382,7 +48379,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="52">
         <v>0</v>
@@ -48485,7 +48482,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D168" s="52">
         <v>0</v>
@@ -48574,7 +48571,7 @@
       </c>
       <c r="AE168" s="57"/>
       <c r="AG168" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH168" s="36">
         <v>0</v>
@@ -48592,7 +48589,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D169" s="52">
         <v>0</v>
@@ -48695,7 +48692,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="52">
         <v>0</v>
@@ -48840,7 +48837,7 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="52">
         <v>58426.32</v>
@@ -48927,7 +48924,7 @@
       </c>
       <c r="AE172" s="57"/>
       <c r="AG172" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH172" s="35">
         <f>AK177</f>
@@ -48946,7 +48943,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="52">
         <v>58426.32</v>
@@ -49032,7 +49029,7 @@
       </c>
       <c r="AE173" s="57"/>
       <c r="AG173" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH173" s="36">
         <f>AL177</f>
@@ -49051,7 +49048,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D174" s="52">
         <v>0</v>
@@ -49154,7 +49151,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D175" s="52">
         <v>0</v>
@@ -49243,7 +49240,7 @@
       </c>
       <c r="AE175" s="57"/>
       <c r="AG175" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH175" s="36">
         <v>0</v>
@@ -49261,7 +49258,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D176" s="52">
         <v>0</v>
@@ -49364,7 +49361,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="52">
         <v>0</v>
@@ -49509,7 +49506,7 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="52">
         <v>18080.64</v>
@@ -49596,7 +49593,7 @@
       </c>
       <c r="AE179" s="57"/>
       <c r="AG179" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH179" s="35">
         <f>AK184</f>
@@ -49615,7 +49612,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D180" s="52">
         <v>18080.64</v>
@@ -49701,7 +49698,7 @@
       </c>
       <c r="AE180" s="57"/>
       <c r="AG180" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH180" s="36">
         <f>AL184</f>
@@ -49720,7 +49717,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="52">
         <v>0</v>
@@ -49823,7 +49820,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D182" s="52">
         <v>0</v>
@@ -49912,7 +49909,7 @@
       </c>
       <c r="AE182" s="57"/>
       <c r="AG182" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH182" s="36">
         <v>0</v>
@@ -49930,7 +49927,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D183" s="52">
         <v>0</v>
@@ -50033,7 +50030,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D184" s="52">
         <v>0</v>
@@ -50178,7 +50175,7 @@
         <v>Taggart House</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D186" s="52">
         <v>17608.26</v>
@@ -50265,7 +50262,7 @@
       </c>
       <c r="AE186" s="57"/>
       <c r="AG186" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH186" s="35">
         <f>AK191</f>
@@ -50284,7 +50281,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="52">
         <v>17608.26</v>
@@ -50370,7 +50367,7 @@
       </c>
       <c r="AE187" s="57"/>
       <c r="AG187" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH187" s="36">
         <f>AL191</f>
@@ -50389,7 +50386,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="52">
         <v>0</v>
@@ -50492,7 +50489,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D189" s="52">
         <v>0</v>
@@ -50581,7 +50578,7 @@
       </c>
       <c r="AE189" s="57"/>
       <c r="AG189" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH189" s="36">
         <v>0</v>
@@ -50599,7 +50596,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D190" s="52">
         <v>0</v>
@@ -50702,7 +50699,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D191" s="52">
         <v>0</v>
@@ -50847,7 +50844,7 @@
         <v>St Barnabas Church</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D193" s="52">
         <v>19572.81</v>
@@ -50938,7 +50935,7 @@
       </c>
       <c r="AE193" s="57"/>
       <c r="AG193" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH193" s="35">
         <f>AK198</f>
@@ -50957,7 +50954,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D194" s="52">
         <v>0</v>
@@ -51043,7 +51040,7 @@
       </c>
       <c r="AE194" s="57"/>
       <c r="AG194" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH194" s="36">
         <f>AL198</f>
@@ -51062,7 +51059,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" s="52">
         <v>0</v>
@@ -51165,7 +51162,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D196" s="52">
         <v>0</v>
@@ -51254,7 +51251,7 @@
       </c>
       <c r="AE196" s="57"/>
       <c r="AG196" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH196" s="36">
         <v>0</v>
@@ -51272,7 +51269,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D197" s="52">
         <v>0</v>
@@ -51375,7 +51372,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D198" s="52">
         <v>0</v>
@@ -51520,7 +51517,7 @@
         <v>0</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -51607,7 +51604,7 @@
       </c>
       <c r="AE200" s="57"/>
       <c r="AG200" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH200" s="35">
         <f>AK205</f>
@@ -51626,7 +51623,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D201" s="52">
         <v>0</v>
@@ -51712,7 +51709,7 @@
       </c>
       <c r="AE201" s="57"/>
       <c r="AG201" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH201" s="36">
         <f>AL205</f>
@@ -51731,7 +51728,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -51818,7 +51815,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -51891,7 +51888,7 @@
       </c>
       <c r="AE203" s="57"/>
       <c r="AG203" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH203" s="36">
         <v>0</v>
@@ -51909,7 +51906,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -51996,7 +51993,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -52125,7 +52122,7 @@
         <v>Contracting</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D207" s="52">
         <v>0</v>
@@ -52212,7 +52209,7 @@
       </c>
       <c r="AE207" s="57"/>
       <c r="AG207" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH207" s="35">
         <f>AK212</f>
@@ -52231,7 +52228,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D208" s="52">
         <v>0</v>
@@ -52317,7 +52314,7 @@
       </c>
       <c r="AE208" s="57"/>
       <c r="AG208" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH208" s="36">
         <f>AL212</f>
@@ -52336,7 +52333,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -52423,7 +52420,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -52496,7 +52493,7 @@
       </c>
       <c r="AE210" s="57"/>
       <c r="AG210" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH210" s="36">
         <v>0</v>
@@ -52514,7 +52511,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -52601,7 +52598,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -52730,7 +52727,7 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D214" s="52">
         <v>0</v>
@@ -52817,7 +52814,7 @@
       </c>
       <c r="AE214" s="57"/>
       <c r="AG214" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH214" s="35">
         <f>AK219</f>
@@ -52836,7 +52833,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D215" s="52">
         <v>0</v>
@@ -52922,7 +52919,7 @@
       </c>
       <c r="AE215" s="57"/>
       <c r="AG215" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH215" s="36">
         <f>AL219</f>
@@ -52941,7 +52938,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -53028,7 +53025,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -53101,7 +53098,7 @@
       </c>
       <c r="AE217" s="57"/>
       <c r="AG217" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH217" s="36">
         <v>0</v>
@@ -53119,7 +53116,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -53206,7 +53203,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -53335,7 +53332,7 @@
         <v>Roydvale</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D221" s="52">
         <v>0</v>
@@ -53422,7 +53419,7 @@
       </c>
       <c r="AE221" s="57"/>
       <c r="AG221" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH221" s="35">
         <f>AK226</f>
@@ -53441,7 +53438,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D222" s="52">
         <v>0</v>
@@ -53527,7 +53524,7 @@
       </c>
       <c r="AE222" s="57"/>
       <c r="AG222" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH222" s="36">
         <f>AL226</f>
@@ -53546,7 +53543,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -53633,7 +53630,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -53706,7 +53703,7 @@
       </c>
       <c r="AE224" s="57"/>
       <c r="AG224" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH224" s="36">
         <v>0</v>
@@ -53724,7 +53721,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -53811,7 +53808,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -54482,18 +54479,18 @@
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>220</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -54505,7 +54502,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -54516,7 +54513,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -54527,7 +54524,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9939,54 +9939,54 @@
         <v>101420.72</v>
       </c>
       <c r="I12" s="52">
-        <v>75109.37</v>
+        <v>76488.35</v>
       </c>
       <c r="J12" s="52">
         <v>83645.65</v>
       </c>
       <c r="K12" s="52">
-        <v>70211.29</v>
+        <v>70758.46</v>
       </c>
       <c r="L12" s="52">
-        <v>13434.36</v>
+        <v>12887.189999999988</v>
       </c>
       <c r="M12" s="53">
-        <v>0.16061038440134068</v>
+        <v>0.1540688607237793</v>
       </c>
       <c r="N12" s="53"/>
       <c r="O12" s="52">
         <v>17775.07</v>
       </c>
       <c r="P12" s="52">
-        <v>4898.08</v>
+        <v>5729.89</v>
       </c>
       <c r="Q12" s="52">
-        <v>12876.99</v>
+        <v>12045.18</v>
       </c>
       <c r="R12" s="53">
-        <v>0.724441028924218</v>
+        <v>0.6776445887414227</v>
       </c>
       <c r="S12" s="54">
         <v>356.07</v>
       </c>
       <c r="T12" s="54">
-        <v>100.75</v>
+        <v>117.75</v>
       </c>
       <c r="U12" s="54">
-        <v>255.32</v>
+        <v>238.32</v>
       </c>
       <c r="V12" s="53">
-        <v>0.7170500182548375</v>
+        <v>0.6693065970174403</v>
       </c>
       <c r="W12" s="53"/>
       <c r="X12" s="55">
-        <v>106.74650124069478</v>
+        <v>79.624033970276</v>
       </c>
       <c r="Y12" s="55">
         <v>77.66490997775718</v>
       </c>
       <c r="Z12" s="53">
-        <v>0.1253</v>
+        <v>0.1092</v>
       </c>
       <c r="AA12" s="56">
         <v>0.2142</v>
@@ -10302,19 +10302,19 @@
         <v>19565.83</v>
       </c>
       <c r="I19" s="52">
-        <v>7621.92</v>
+        <v>7921.92</v>
       </c>
       <c r="J19" s="52">
         <v>13767.340000000002</v>
       </c>
       <c r="K19" s="52">
-        <v>5911.24</v>
+        <v>6211.24</v>
       </c>
       <c r="L19" s="52">
-        <v>7856.100000000002</v>
+        <v>7556.100000000002</v>
       </c>
       <c r="M19" s="53">
-        <v>0.5706331070490016</v>
+        <v>0.5488424052867149</v>
       </c>
       <c r="N19" s="53"/>
       <c r="O19" s="52">
@@ -10343,13 +10343,13 @@
       </c>
       <c r="W19" s="53"/>
       <c r="X19" s="55">
-        <v>125.96143884892086</v>
+        <v>117.328345323741</v>
       </c>
       <c r="Y19" s="55">
         <v>63.27846478985563</v>
       </c>
       <c r="Z19" s="53">
-        <v>0.36479999999999996</v>
+        <v>0.3398</v>
       </c>
       <c r="AA19" s="56">
         <v>0.2885</v>
@@ -10667,19 +10667,19 @@
         <v>102178.42</v>
       </c>
       <c r="I26" s="52">
-        <v>87230.67</v>
+        <v>87101.11</v>
       </c>
       <c r="J26" s="52">
         <v>62464.86</v>
       </c>
       <c r="K26" s="52">
-        <v>58028.31</v>
+        <v>57898.75</v>
       </c>
       <c r="L26" s="52">
-        <v>4436.550000000003</v>
+        <v>4566.110000000001</v>
       </c>
       <c r="M26" s="53">
-        <v>0.07102473294585152</v>
+        <v>0.07309885910254182</v>
       </c>
       <c r="N26" s="53"/>
       <c r="O26" s="52">
@@ -10708,13 +10708,13 @@
       </c>
       <c r="W26" s="53"/>
       <c r="X26" s="55">
-        <v>96.11460050462573</v>
+        <v>96.3325315391085</v>
       </c>
       <c r="Y26" s="55">
         <v>61.20621468124544</v>
       </c>
       <c r="Z26" s="53">
-        <v>0.3958</v>
+        <v>0.3967</v>
       </c>
       <c r="AA26" s="56">
         <v>0.3227</v>
@@ -11030,54 +11030,54 @@
         <v>327431.12</v>
       </c>
       <c r="I33" s="65">
-        <v>219182.25</v>
+        <v>220187.84</v>
       </c>
       <c r="J33" s="52">
         <v>271519.78</v>
       </c>
       <c r="K33" s="52">
-        <v>196853</v>
+        <v>196879.33</v>
       </c>
       <c r="L33" s="52">
-        <v>74666.78000000003</v>
+        <v>74640.45000000004</v>
       </c>
       <c r="M33" s="53">
-        <v>0.2749957295928865</v>
+        <v>0.27489875691561044</v>
       </c>
       <c r="N33" s="53"/>
       <c r="O33" s="52">
         <v>55911.34</v>
       </c>
       <c r="P33" s="52">
-        <v>22329.25</v>
+        <v>23308.51</v>
       </c>
       <c r="Q33" s="52">
-        <v>33582.09</v>
+        <v>32602.829999999998</v>
       </c>
       <c r="R33" s="53">
-        <v>0.6006311063193978</v>
+        <v>0.5831165913748445</v>
       </c>
       <c r="S33" s="54">
         <v>1120.27</v>
       </c>
       <c r="T33" s="54">
-        <v>522.25</v>
+        <v>543.5</v>
       </c>
       <c r="U33" s="54">
-        <v>598.02</v>
+        <v>576.77</v>
       </c>
       <c r="V33" s="53">
-        <v>0.5338177403661617</v>
+        <v>0.514849098877949</v>
       </c>
       <c r="W33" s="53"/>
       <c r="X33" s="55">
-        <v>76.90849210148396</v>
+        <v>72.05127874885005</v>
       </c>
       <c r="Y33" s="55">
         <v>61.5841822414239</v>
       </c>
       <c r="Z33" s="53">
-        <v>0.1549</v>
+        <v>0.151</v>
       </c>
       <c r="AA33" s="56">
         <v>0.174</v>
@@ -11393,54 +11393,54 @@
         <v>94098.32</v>
       </c>
       <c r="I40" s="52">
-        <v>45499.87</v>
+        <v>46289.42</v>
       </c>
       <c r="J40" s="52">
         <v>69042.09000000001</v>
       </c>
       <c r="K40" s="52">
-        <v>35731.93</v>
+        <v>35507.08</v>
       </c>
       <c r="L40" s="52">
-        <v>33310.16000000001</v>
+        <v>33535.01000000001</v>
       </c>
       <c r="M40" s="53">
-        <v>0.4824616404283243</v>
+        <v>0.4857183494879718</v>
       </c>
       <c r="N40" s="53"/>
       <c r="O40" s="52">
         <v>25056.23</v>
       </c>
       <c r="P40" s="52">
-        <v>9767.94</v>
+        <v>10782.34</v>
       </c>
       <c r="Q40" s="52">
-        <v>15288.289999999999</v>
+        <v>14273.89</v>
       </c>
       <c r="R40" s="53">
-        <v>0.6101592298601984</v>
+        <v>0.5696742885901032</v>
       </c>
       <c r="S40" s="54">
         <v>501.83</v>
       </c>
       <c r="T40" s="54">
-        <v>205.75</v>
+        <v>232.25</v>
       </c>
       <c r="U40" s="54">
-        <v>296.08</v>
+        <v>269.58</v>
       </c>
       <c r="V40" s="53">
-        <v>0.5900005978120081</v>
+        <v>0.5371938704342107</v>
       </c>
       <c r="W40" s="53"/>
       <c r="X40" s="55">
-        <v>41.0447630619684</v>
+        <v>32.96193756727664</v>
       </c>
       <c r="Y40" s="55">
         <v>68.07122423898531</v>
       </c>
       <c r="Z40" s="53">
-        <v>0.1565</v>
+        <v>0.1419</v>
       </c>
       <c r="AA40" s="56">
         <v>0.2663</v>
@@ -11758,19 +11758,19 @@
         <v>50582.37</v>
       </c>
       <c r="I47" s="52">
-        <v>25337.26</v>
+        <v>25187.36</v>
       </c>
       <c r="J47" s="52">
         <v>39438.990000000005</v>
       </c>
       <c r="K47" s="52">
-        <v>20582.32</v>
+        <v>20432.420000000002</v>
       </c>
       <c r="L47" s="52">
-        <v>18856.670000000006</v>
+        <v>19006.570000000003</v>
       </c>
       <c r="M47" s="53">
-        <v>0.4781225381278781</v>
+        <v>0.48192334540007237</v>
       </c>
       <c r="N47" s="53"/>
       <c r="O47" s="52">
@@ -11799,13 +11799,13 @@
       </c>
       <c r="W47" s="53"/>
       <c r="X47" s="55">
-        <v>76.63529976019184</v>
+        <v>78.07318944844125</v>
       </c>
       <c r="Y47" s="55">
         <v>67.69550512136009</v>
       </c>
       <c r="Z47" s="53">
-        <v>0.2397</v>
+        <v>0.24420000000000003</v>
       </c>
       <c r="AA47" s="56">
         <v>0.23</v>
@@ -12121,19 +12121,19 @@
         <v>109364.97</v>
       </c>
       <c r="I54" s="52">
-        <v>95642.03</v>
+        <v>95597.19</v>
       </c>
       <c r="J54" s="52">
         <v>75135.01000000001</v>
       </c>
       <c r="K54" s="52">
-        <v>71188.63</v>
+        <v>71143.79000000001</v>
       </c>
       <c r="L54" s="52">
-        <v>3946.3800000000047</v>
+        <v>3991.220000000001</v>
       </c>
       <c r="M54" s="53">
-        <v>0.05252385006669999</v>
+        <v>0.05312064242754477</v>
       </c>
       <c r="N54" s="53"/>
       <c r="O54" s="52">
@@ -12162,13 +12162,13 @@
       </c>
       <c r="W54" s="53"/>
       <c r="X54" s="55">
-        <v>62.138966682761954</v>
+        <v>62.22557218734911</v>
       </c>
       <c r="Y54" s="55">
         <v>67.00679527854935</v>
       </c>
       <c r="Z54" s="53">
-        <v>0.25170000000000003</v>
+        <v>0.2521</v>
       </c>
       <c r="AA54" s="56">
         <v>0.2958</v>
@@ -12841,19 +12841,19 @@
         <v>35572.59</v>
       </c>
       <c r="I68" s="52">
-        <v>9981.43</v>
+        <v>10547.08</v>
       </c>
       <c r="J68" s="52">
         <v>27136.549999999996</v>
       </c>
       <c r="K68" s="52">
-        <v>9832.65</v>
+        <v>10398.3</v>
       </c>
       <c r="L68" s="52">
-        <v>17303.899999999994</v>
+        <v>16738.249999999996</v>
       </c>
       <c r="M68" s="53">
-        <v>0.6376602773749794</v>
+        <v>0.6168156969106242</v>
       </c>
       <c r="N68" s="53"/>
       <c r="O68" s="52">
@@ -12882,13 +12882,13 @@
       </c>
       <c r="W68" s="53"/>
       <c r="X68" s="55">
-        <v>243.27272727272728</v>
+        <v>37.58181818181818</v>
       </c>
       <c r="Y68" s="55">
         <v>72.22475431425701</v>
       </c>
       <c r="Z68" s="53">
-        <v>0.06280000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="AA68" s="56">
         <v>0.2558</v>
@@ -13916,19 +13916,19 @@
         <v>27002.93</v>
       </c>
       <c r="I89" s="52">
-        <v>26005.99</v>
+        <v>24950.27</v>
       </c>
       <c r="J89" s="52">
         <v>15440.32</v>
       </c>
       <c r="K89" s="52">
-        <v>14988.440000000002</v>
+        <v>13932.720000000001</v>
       </c>
       <c r="L89" s="52">
-        <v>451.8799999999974</v>
+        <v>1507.5999999999985</v>
       </c>
       <c r="M89" s="53">
-        <v>0.029266232824190004</v>
+        <v>0.09764046341008467</v>
       </c>
       <c r="N89" s="53"/>
       <c r="O89" s="52">
@@ -13957,13 +13957,13 @@
       </c>
       <c r="W89" s="53"/>
       <c r="X89" s="55">
-        <v>46.26684503901895</v>
+        <v>50.9746265328874</v>
       </c>
       <c r="Y89" s="55">
         <v>43.49557070636461</v>
       </c>
       <c r="Z89" s="53">
-        <v>0.2852</v>
+        <v>0.31420000000000003</v>
       </c>
       <c r="AA89" s="56">
         <v>0.2718</v>
@@ -14626,30 +14626,74 @@
       <c r="C103" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D103" s="52"/>
-      <c r="E103" s="69"/>
-      <c r="F103" s="52"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="52"/>
-      <c r="I103" s="52"/>
-      <c r="J103" s="52"/>
-      <c r="K103" s="52"/>
-      <c r="L103" s="52"/>
-      <c r="M103" s="53"/>
+      <c r="D103" s="52">
+        <v>32473.02</v>
+      </c>
+      <c r="E103" s="69">
+        <v>33188.03</v>
+      </c>
+      <c r="F103" s="52">
+        <v>-715.0099999999984</v>
+      </c>
+      <c r="G103" s="53">
+        <v>-0.022018586506582952</v>
+      </c>
+      <c r="H103" s="52">
+        <v>23075.07</v>
+      </c>
+      <c r="I103" s="52">
+        <v>30925.21</v>
+      </c>
+      <c r="J103" s="52">
+        <v>12691.21</v>
+      </c>
+      <c r="K103" s="52">
+        <v>15184.269999999999</v>
+      </c>
+      <c r="L103" s="52">
+        <v>-2493.0599999999995</v>
+      </c>
+      <c r="M103" s="53">
+        <v>-0.1964398981657383</v>
+      </c>
       <c r="N103" s="53"/>
-      <c r="O103" s="52"/>
-      <c r="P103" s="52"/>
-      <c r="Q103" s="52"/>
-      <c r="R103" s="53"/>
-      <c r="S103" s="54"/>
-      <c r="T103" s="54"/>
-      <c r="U103" s="54"/>
-      <c r="V103" s="53"/>
+      <c r="O103" s="52">
+        <v>10383.86</v>
+      </c>
+      <c r="P103" s="52">
+        <v>15740.94</v>
+      </c>
+      <c r="Q103" s="52">
+        <v>-5357.08</v>
+      </c>
+      <c r="R103" s="53">
+        <v>-0.5159044902377343</v>
+      </c>
+      <c r="S103" s="54">
+        <v>208.2</v>
+      </c>
+      <c r="T103" s="54">
+        <v>317.25</v>
+      </c>
+      <c r="U103" s="54">
+        <v>-109.05000000000001</v>
+      </c>
+      <c r="V103" s="53">
+        <v>-0.5237752161383286</v>
+      </c>
       <c r="W103" s="53"/>
-      <c r="X103" s="55"/>
-      <c r="Y103" s="55"/>
-      <c r="Z103" s="53"/>
-      <c r="AA103" s="56"/>
+      <c r="X103" s="55">
+        <v>7.132608353033885</v>
+      </c>
+      <c r="Y103" s="55">
+        <v>45.139084580403456</v>
+      </c>
+      <c r="Z103" s="53">
+        <v>0.0682</v>
+      </c>
+      <c r="AA103" s="56">
+        <v>0.2894</v>
+      </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
         <v>93</v>
@@ -14963,19 +15007,19 @@
         <v>37601.88</v>
       </c>
       <c r="I110" s="52">
-        <v>45837.23</v>
+        <v>45817.77</v>
       </c>
       <c r="J110" s="52">
         <v>21415.85</v>
       </c>
       <c r="K110" s="52">
-        <v>23958.850000000002</v>
+        <v>23939.389999999996</v>
       </c>
       <c r="L110" s="52">
-        <v>-2543.0000000000036</v>
+        <v>-2523.5399999999972</v>
       </c>
       <c r="M110" s="53">
-        <v>-0.11874382758564352</v>
+        <v>-0.11783515480356826</v>
       </c>
       <c r="N110" s="53"/>
       <c r="O110" s="52">
@@ -15004,13 +15048,13 @@
       </c>
       <c r="W110" s="53"/>
       <c r="X110" s="55">
-        <v>48.93201480698043</v>
+        <v>48.973178212585935</v>
       </c>
       <c r="Y110" s="55">
         <v>65.70431400737223</v>
       </c>
       <c r="Z110" s="53">
-        <v>0.3354</v>
+        <v>0.3357</v>
       </c>
       <c r="AA110" s="56">
         <v>0.3616</v>
@@ -15673,19 +15717,19 @@
         <v>82694.87</v>
       </c>
       <c r="I124" s="52">
-        <v>56983.56</v>
+        <v>56763.31</v>
       </c>
       <c r="J124" s="52">
         <v>68214.25</v>
       </c>
       <c r="K124" s="52">
-        <v>52178.049999999996</v>
+        <v>51957.799999999996</v>
       </c>
       <c r="L124" s="52">
-        <v>16036.200000000004</v>
+        <v>16256.450000000004</v>
       </c>
       <c r="M124" s="53">
-        <v>0.23508577753182075</v>
+        <v>0.23831457503380898</v>
       </c>
       <c r="N124" s="53"/>
       <c r="O124" s="52">
@@ -15714,13 +15758,13 @@
       </c>
       <c r="W124" s="53"/>
       <c r="X124" s="55">
-        <v>99.27371428571428</v>
+        <v>101.37133333333333</v>
       </c>
       <c r="Y124" s="55">
         <v>63.04545035767707</v>
       </c>
       <c r="Z124" s="53">
-        <v>0.15460000000000002</v>
+        <v>0.15789999999999998</v>
       </c>
       <c r="AA124" s="56">
         <v>0.1811</v>
@@ -18141,30 +18185,74 @@
       <c r="C173" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D173" s="52"/>
-      <c r="E173" s="52"/>
-      <c r="F173" s="52"/>
-      <c r="G173" s="53"/>
-      <c r="H173" s="52"/>
-      <c r="I173" s="52"/>
-      <c r="J173" s="52"/>
-      <c r="K173" s="52"/>
-      <c r="L173" s="52"/>
-      <c r="M173" s="53"/>
+      <c r="D173" s="52">
+        <v>146237.11</v>
+      </c>
+      <c r="E173" s="52">
+        <v>125386.21</v>
+      </c>
+      <c r="F173" s="52">
+        <v>20850.89999999998</v>
+      </c>
+      <c r="G173" s="53">
+        <v>0.14258282319720336</v>
+      </c>
+      <c r="H173" s="52">
+        <v>114651.87</v>
+      </c>
+      <c r="I173" s="52">
+        <v>105511.63</v>
+      </c>
+      <c r="J173" s="52">
+        <v>82888.07999999999</v>
+      </c>
+      <c r="K173" s="52">
+        <v>78161.06</v>
+      </c>
+      <c r="L173" s="52">
+        <v>4727.0199999999895</v>
+      </c>
+      <c r="M173" s="53">
+        <v>0.05702894795005495</v>
+      </c>
       <c r="N173" s="53"/>
-      <c r="O173" s="52"/>
-      <c r="P173" s="52"/>
-      <c r="Q173" s="52"/>
-      <c r="R173" s="53"/>
-      <c r="S173" s="54"/>
-      <c r="T173" s="54"/>
-      <c r="U173" s="54"/>
-      <c r="V173" s="53"/>
+      <c r="O173" s="52">
+        <v>31763.79</v>
+      </c>
+      <c r="P173" s="52">
+        <v>27350.57</v>
+      </c>
+      <c r="Q173" s="52">
+        <v>4413.220000000001</v>
+      </c>
+      <c r="R173" s="53">
+        <v>0.13893870976983544</v>
+      </c>
+      <c r="S173" s="54">
+        <v>659.73</v>
+      </c>
+      <c r="T173" s="54">
+        <v>548.75</v>
+      </c>
+      <c r="U173" s="54">
+        <v>110.98000000000002</v>
+      </c>
+      <c r="V173" s="53">
+        <v>0.16822033256028984</v>
+      </c>
       <c r="W173" s="53"/>
-      <c r="X173" s="55"/>
-      <c r="Y173" s="55"/>
-      <c r="Z173" s="53"/>
-      <c r="AA173" s="56"/>
+      <c r="X173" s="55">
+        <v>36.21791343963554</v>
+      </c>
+      <c r="Y173" s="55">
+        <v>47.87601261940491</v>
+      </c>
+      <c r="Z173" s="53">
+        <v>0.1585</v>
+      </c>
+      <c r="AA173" s="56">
+        <v>0.216</v>
+      </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
         <v>93</v>
@@ -18771,30 +18859,74 @@
       <c r="C187" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="D187" s="52"/>
-      <c r="E187" s="52"/>
-      <c r="F187" s="52"/>
-      <c r="G187" s="53"/>
-      <c r="H187" s="52"/>
-      <c r="I187" s="52"/>
-      <c r="J187" s="52"/>
-      <c r="K187" s="52"/>
-      <c r="L187" s="52"/>
-      <c r="M187" s="53"/>
+      <c r="D187" s="52">
+        <v>20992.12</v>
+      </c>
+      <c r="E187" s="52">
+        <v>14169.68</v>
+      </c>
+      <c r="F187" s="52">
+        <v>6822.439999999999</v>
+      </c>
+      <c r="G187" s="53">
+        <v>0.32500004763692275</v>
+      </c>
+      <c r="H187" s="52">
+        <v>16299.09</v>
+      </c>
+      <c r="I187" s="52">
+        <v>9699.51</v>
+      </c>
+      <c r="J187" s="52">
+        <v>9784.33</v>
+      </c>
+      <c r="K187" s="52">
+        <v>8137.88</v>
+      </c>
+      <c r="L187" s="52">
+        <v>1646.4499999999998</v>
+      </c>
+      <c r="M187" s="53">
+        <v>0.16827416900288522</v>
+      </c>
       <c r="N187" s="53"/>
-      <c r="O187" s="52"/>
-      <c r="P187" s="52"/>
-      <c r="Q187" s="52"/>
-      <c r="R187" s="53"/>
-      <c r="S187" s="54"/>
-      <c r="T187" s="54"/>
-      <c r="U187" s="54"/>
-      <c r="V187" s="53"/>
+      <c r="O187" s="52">
+        <v>6514.76</v>
+      </c>
+      <c r="P187" s="52">
+        <v>1561.63</v>
+      </c>
+      <c r="Q187" s="52">
+        <v>4953.13</v>
+      </c>
+      <c r="R187" s="53">
+        <v>0.7602935488030257</v>
+      </c>
+      <c r="S187" s="54">
+        <v>130.62</v>
+      </c>
+      <c r="T187" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U187" s="54">
+        <v>95.87</v>
+      </c>
+      <c r="V187" s="53">
+        <v>0.7339611085591793</v>
+      </c>
       <c r="W187" s="53"/>
-      <c r="X187" s="55"/>
-      <c r="Y187" s="55"/>
-      <c r="Z187" s="53"/>
-      <c r="AA187" s="56"/>
+      <c r="X187" s="55">
+        <v>128.6379856115108</v>
+      </c>
+      <c r="Y187" s="55">
+        <v>35.92887828502527</v>
+      </c>
+      <c r="Z187" s="53">
+        <v>0.3155</v>
+      </c>
+      <c r="AA187" s="56">
+        <v>0.2236</v>
+      </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
         <v>93</v>
@@ -20023,19 +20155,19 @@
         <v>117394.57</v>
       </c>
       <c r="I215" s="52">
-        <v>26124</v>
+        <v>30594.96</v>
       </c>
       <c r="J215" s="52">
         <v>99479.62000000001</v>
       </c>
       <c r="K215" s="52">
-        <v>26124</v>
+        <v>30594.96</v>
       </c>
       <c r="L215" s="52">
-        <v>73355.62000000001</v>
+        <v>68884.66</v>
       </c>
       <c r="M215" s="53">
-        <v>0.7373934480248316</v>
+        <v>0.692449971159922</v>
       </c>
       <c r="N215" s="53"/>
       <c r="O215" s="52">
@@ -20070,7 +20202,7 @@
         <v>54.93783457863793</v>
       </c>
       <c r="Z215" s="53">
-        <v>0.13419999999999999</v>
+        <v>-0.0139</v>
       </c>
       <c r="AA215" s="56">
         <v>0.1438</v>
@@ -20376,54 +20508,54 @@
         <v>295569.99</v>
       </c>
       <c r="I222" s="52">
-        <v>240067.38</v>
+        <v>241753.24</v>
       </c>
       <c r="J222" s="52">
         <v>178700.37</v>
       </c>
       <c r="K222" s="52">
-        <v>178119.89</v>
+        <v>178956.15</v>
       </c>
       <c r="L222" s="52">
-        <v>580.4799999999814</v>
+        <v>-255.77999999999884</v>
       </c>
       <c r="M222" s="53">
-        <v>0.003248342462861053</v>
+        <v>-0.0014313344734540776</v>
       </c>
       <c r="N222" s="53"/>
       <c r="O222" s="52">
         <v>116869.62</v>
       </c>
       <c r="P222" s="52">
-        <v>61947.49</v>
+        <v>62797.09</v>
       </c>
       <c r="Q222" s="52">
-        <v>54922.13</v>
+        <v>54072.53</v>
       </c>
       <c r="R222" s="53">
-        <v>0.4699436003984611</v>
+        <v>0.4626739609489618</v>
       </c>
       <c r="S222" s="54">
         <v>2344.68</v>
       </c>
       <c r="T222" s="54">
-        <v>1315</v>
+        <v>1335</v>
       </c>
       <c r="U222" s="54">
-        <v>1029.6799999999998</v>
+        <v>1009.6799999999998</v>
       </c>
       <c r="V222" s="53">
-        <v>0.4391558762816247</v>
+        <v>0.4306259276319156</v>
       </c>
       <c r="W222" s="53"/>
       <c r="X222" s="55">
-        <v>50.16819011406844</v>
+        <v>48.153790262172286</v>
       </c>
       <c r="Y222" s="55">
         <v>43.0265399367206</v>
       </c>
       <c r="Z222" s="53">
-        <v>0.21559999999999999</v>
+        <v>0.2101</v>
       </c>
       <c r="AA222" s="56">
         <v>0.2545</v>
@@ -21331,10 +21463,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="52">
-        <v>972.0499999999884</v>
+        <v>2351.029999999999</v>
       </c>
       <c r="E6" s="52">
-        <v>-972.0499999999884</v>
+        <v>-2351.029999999999</v>
       </c>
       <c r="F6" s="52">
         <v>0</v>
@@ -21358,13 +21490,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="52">
-        <v>-2844.6499999999883</v>
+        <v>-4223.629999999999</v>
       </c>
       <c r="N6" s="54">
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
-        <v>227.57199999999906</v>
+        <v>337.89039999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>115</v>
@@ -21398,10 +21530,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="52">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E8" s="52">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F8" s="52"/>
       <c r="G8" s="53">
@@ -21421,13 +21553,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="52">
-        <v>-640</v>
+        <v>-940</v>
       </c>
       <c r="N8" s="54">
         <v>-34.75</v>
       </c>
       <c r="O8" s="58">
-        <v>34.13333333333333</v>
+        <v>50.13333333333333</v>
       </c>
     </row>
     <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21458,10 +21590,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="52">
-        <v>1382.2599999999948</v>
+        <v>1252.699999999997</v>
       </c>
       <c r="E10" s="52">
-        <v>-1382.2599999999948</v>
+        <v>-1252.699999999997</v>
       </c>
       <c r="F10" s="52">
         <v>0</v>
@@ -21485,13 +21617,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="52">
-        <v>-6302.259999999995</v>
+        <v>-6172.699999999997</v>
       </c>
       <c r="N10" s="54">
         <v>-388.25</v>
       </c>
       <c r="O10" s="58">
-        <v>18.522439382806745</v>
+        <v>18.141660543717848</v>
       </c>
     </row>
     <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21522,10 +21654,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="52">
-        <v>2837.649999999994</v>
+        <v>3843.2399999999907</v>
       </c>
       <c r="E12" s="52">
-        <v>-2837.649999999994</v>
+        <v>-3843.2399999999907</v>
       </c>
       <c r="F12" s="52"/>
       <c r="G12" s="53">
@@ -21547,13 +21679,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="52">
-        <v>-5477.649999999994</v>
+        <v>-6483.239999999991</v>
       </c>
       <c r="N12" s="54">
         <v>53</v>
       </c>
       <c r="O12" s="58">
-        <v>-79.38623188405789</v>
+        <v>-93.95999999999987</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>117</v>
@@ -21587,10 +21719,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="52">
-        <v>3226.1800000000003</v>
+        <v>4015.729999999996</v>
       </c>
       <c r="E14" s="52">
-        <v>-3226.1800000000003</v>
+        <v>-4015.729999999996</v>
       </c>
       <c r="F14" s="52">
         <v>0</v>
@@ -21614,13 +21746,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="52">
-        <v>-6226.18</v>
+        <v>-7015.729999999996</v>
       </c>
       <c r="N14" s="54">
         <v>-112</v>
       </c>
       <c r="O14" s="58">
-        <v>55.59089285714286</v>
+        <v>62.640446428571394</v>
       </c>
     </row>
     <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21651,10 +21783,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="52">
-        <v>125.67999999999665</v>
+        <v>-24.220000000001164</v>
       </c>
       <c r="E16" s="52">
-        <v>-125.67999999999665</v>
+        <v>24.220000000001164</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="53">
@@ -21676,13 +21808,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="52">
-        <v>-3125.6799999999967</v>
+        <v>-2975.779999999999</v>
       </c>
       <c r="N16" s="54">
         <v>-86.75</v>
       </c>
       <c r="O16" s="58">
-        <v>36.030893371757884</v>
+        <v>34.302939481268</v>
       </c>
     </row>
     <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21713,10 +21845,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="52">
-        <v>321.5200000000041</v>
+        <v>276.68000000000757</v>
       </c>
       <c r="E18" s="52">
-        <v>-321.5200000000041</v>
+        <v>-276.68000000000757</v>
       </c>
       <c r="F18" s="52">
         <v>0</v>
@@ -21740,13 +21872,13 @@
         <v>0</v>
       </c>
       <c r="M18" s="52">
-        <v>-8521.520000000004</v>
+        <v>-8476.680000000008</v>
       </c>
       <c r="N18" s="54">
         <v>-269</v>
       </c>
       <c r="O18" s="58">
-        <v>45.087407407407426</v>
+        <v>44.85015873015877</v>
       </c>
       <c r="Q18" s="35" t="s">
         <v>118</v>
@@ -21836,10 +21968,10 @@
         <v>0</v>
       </c>
       <c r="D22" s="52">
-        <v>0</v>
+        <v>565.6499999999996</v>
       </c>
       <c r="E22" s="52">
-        <v>0</v>
+        <v>-565.6499999999996</v>
       </c>
       <c r="F22" s="52">
         <v>0</v>
@@ -21859,7 +21991,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="52">
-        <v>0</v>
+        <v>-565.6499999999996</v>
       </c>
       <c r="N22" s="54"/>
       <c r="O22" s="58">
@@ -22010,10 +22142,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="52">
-        <v>0</v>
+        <v>-1055.7200000000012</v>
       </c>
       <c r="E28" s="52">
-        <v>0</v>
+        <v>1055.7200000000012</v>
       </c>
       <c r="F28" s="52">
         <v>0</v>
@@ -22033,13 +22165,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="52">
-        <v>0</v>
+        <v>1055.7200000000012</v>
       </c>
       <c r="N28" s="54">
         <v>-148.5</v>
       </c>
       <c r="O28" s="58">
-        <v>0</v>
+        <v>-7.109225589225597</v>
       </c>
     </row>
     <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22194,10 +22326,10 @@
         <v>0</v>
       </c>
       <c r="D34" s="52">
-        <v>943.3400000000038</v>
+        <v>923.8799999999974</v>
       </c>
       <c r="E34" s="52">
-        <v>-943.3400000000038</v>
+        <v>-923.8799999999974</v>
       </c>
       <c r="F34" s="52">
         <v>0</v>
@@ -22219,13 +22351,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="52">
-        <v>-943.3400000000038</v>
+        <v>-923.8799999999974</v>
       </c>
       <c r="N34" s="54">
         <v>-204.75</v>
       </c>
       <c r="O34" s="58">
-        <v>4.607277167277186</v>
+        <v>4.512234432234419</v>
       </c>
     </row>
     <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22316,16 +22448,16 @@
         <v>52040.560000000005</v>
       </c>
       <c r="D38" s="52">
-        <v>746.3099999999977</v>
+        <v>526.0599999999977</v>
       </c>
       <c r="E38" s="52">
-        <v>51294.25000000001</v>
+        <v>51514.50000000001</v>
       </c>
       <c r="F38" s="52">
         <v>0</v>
       </c>
       <c r="G38" s="53">
-        <v>0.9856590705403632</v>
+        <v>0.9898913462883566</v>
       </c>
       <c r="H38" s="53">
         <v>0.1750921737769</v>
@@ -22336,10 +22468,10 @@
         <v>0</v>
       </c>
       <c r="L38" s="53">
-        <v>0.9856590705403632</v>
+        <v>0.9898913462883566</v>
       </c>
       <c r="M38" s="52">
-        <v>51294.25000000001</v>
+        <v>51514.50000000001</v>
       </c>
       <c r="N38" s="54"/>
       <c r="O38" s="58">
@@ -22727,10 +22859,10 @@
         <v>0</v>
       </c>
       <c r="D52" s="99">
-        <v>0</v>
+        <v>2629.5100000000093</v>
       </c>
       <c r="E52" s="99">
-        <v>0</v>
+        <v>-2629.5100000000093</v>
       </c>
       <c r="F52" s="99"/>
       <c r="G52" s="100">
@@ -22752,13 +22884,13 @@
         <v>0</v>
       </c>
       <c r="M52" s="99">
-        <v>-1280</v>
+        <v>-3909.5100000000093</v>
       </c>
       <c r="N52" s="98">
         <v>-304.75</v>
       </c>
       <c r="O52" s="60">
-        <v>4.692942254812099</v>
+        <v>14.333675527039448</v>
       </c>
     </row>
     <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -23039,10 +23171,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="99">
-        <v>0</v>
+        <v>4470.959999999999</v>
       </c>
       <c r="E64" s="99">
-        <v>0</v>
+        <v>-4470.959999999999</v>
       </c>
       <c r="F64" s="99"/>
       <c r="G64" s="100">
@@ -23062,7 +23194,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="99">
-        <v>-1750</v>
+        <v>-6220.959999999999</v>
       </c>
       <c r="N64" s="98"/>
       <c r="O64" s="60">
@@ -23097,14 +23229,14 @@
         <v>34650.399999999965</v>
       </c>
       <c r="D66" s="99">
-        <v>5744.570000000007</v>
+        <v>7430.429999999993</v>
       </c>
       <c r="E66" s="99">
-        <v>28905.829999999958</v>
+        <v>27219.969999999972</v>
       </c>
       <c r="F66" s="99"/>
       <c r="G66" s="100">
-        <v>0.8342134578533</v>
+        <v>0.7855600512548195</v>
       </c>
       <c r="H66" s="100">
         <v>0.256265521519856</v>
@@ -23119,16 +23251,16 @@
         <v>3200</v>
       </c>
       <c r="L66" s="100">
-        <v>0.7418624316025207</v>
+        <v>0.6932090250040402</v>
       </c>
       <c r="M66" s="99">
-        <v>25705.829999999958</v>
+        <v>24019.969999999972</v>
       </c>
       <c r="N66" s="98">
         <v>-1014.25</v>
       </c>
       <c r="O66" s="60">
-        <v>-27.51493711533311</v>
+        <v>-25.71043082686644</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -23176,22 +23308,22 @@
         <v>88818.76999999996</v>
       </c>
       <c r="D69" s="104">
-        <v>18681.369999999988</v>
+        <v>29887.739999999983</v>
       </c>
       <c r="E69" s="105">
-        <v>70137.39999999998</v>
+        <v>58931.02999999998</v>
       </c>
       <c r="F69" s="106" t="s">
         <v>122</v>
       </c>
       <c r="G69" s="107">
-        <v>0.7896686702596761</v>
+        <v>0.6634974791927427</v>
       </c>
       <c r="H69" s="108" t="s">
         <v>123</v>
       </c>
       <c r="I69" s="109">
-        <v>0.20609157276102777</v>
+        <v>0.0799203816940944</v>
       </c>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
@@ -23799,10 +23931,10 @@
         <v>356.07</v>
       </c>
       <c r="D6" s="54">
-        <v>100.75</v>
+        <v>117.75</v>
       </c>
       <c r="E6" s="54">
-        <v>255.32</v>
+        <v>238.32</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="54"/>
@@ -23962,10 +24094,10 @@
         <v>1120.27</v>
       </c>
       <c r="D12" s="54">
-        <v>522.25</v>
+        <v>543.5</v>
       </c>
       <c r="E12" s="54">
-        <v>598.02</v>
+        <v>576.77</v>
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="54"/>
@@ -24019,10 +24151,10 @@
         <v>501.83</v>
       </c>
       <c r="D14" s="54">
-        <v>205.75</v>
+        <v>232.25</v>
       </c>
       <c r="E14" s="54">
-        <v>296.08</v>
+        <v>269.58</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="54"/>
@@ -25011,10 +25143,10 @@
         <v>659.73</v>
       </c>
       <c r="D52" s="54">
-        <v>505.25</v>
+        <v>548.75</v>
       </c>
       <c r="E52" s="54">
-        <v>154.48000000000002</v>
+        <v>110.98000000000002</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="54"/>
@@ -25358,10 +25490,10 @@
         <v>2344.68</v>
       </c>
       <c r="D66" s="54">
-        <v>1315</v>
+        <v>1335</v>
       </c>
       <c r="E66" s="54">
-        <v>1029.6799999999998</v>
+        <v>1009.6799999999998</v>
       </c>
       <c r="F66" s="54"/>
       <c r="G66" s="54"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16176,7 +16176,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -21286,7 +21286,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21300,7 +21300,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21322,7 +21322,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -21370,7 +21370,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21388,7 +21388,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21452,7 +21452,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21502,7 +21502,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21519,7 +21519,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21562,7 +21562,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21579,7 +21579,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21643,7 +21643,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -21659,7 +21659,9 @@
       <c r="E12" s="52">
         <v>-3843.2399999999907</v>
       </c>
-      <c r="F12" s="52"/>
+      <c r="F12" s="52">
+        <v>3</v>
+      </c>
       <c r="G12" s="53">
         <v>0</v>
       </c>
@@ -21691,7 +21693,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21708,7 +21710,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21755,7 +21757,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21772,7 +21774,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21817,7 +21819,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21834,7 +21836,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -21884,7 +21886,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -21901,7 +21903,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -21940,7 +21942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -21957,7 +21959,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -21998,7 +22000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22015,7 +22017,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22052,7 +22054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22069,7 +22071,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22114,7 +22116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22131,7 +22133,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22174,7 +22176,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22191,7 +22193,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22234,7 +22236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22251,7 +22253,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22298,7 +22300,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22315,7 +22317,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22360,7 +22362,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22377,7 +22379,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22420,7 +22422,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22437,7 +22439,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22478,7 +22480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22495,7 +22497,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22540,7 +22542,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22557,7 +22559,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22600,7 +22602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22617,7 +22619,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22654,7 +22656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22671,7 +22673,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22712,7 +22714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22729,7 +22731,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22772,7 +22774,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22789,7 +22791,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22831,7 +22833,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22848,7 +22850,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -22893,7 +22895,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -22910,7 +22912,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -22955,7 +22957,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -22972,7 +22974,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23017,7 +23019,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23034,7 +23036,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23071,7 +23073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23088,7 +23090,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23105,7 +23107,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23122,7 +23124,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23143,7 +23145,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23160,7 +23162,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23201,7 +23203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23218,7 +23220,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23263,7 +23265,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -23280,7 +23282,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23297,7 +23299,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -23332,7 +23334,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -23715,7 +23717,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23726,7 +23728,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23747,7 +23749,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -23809,7 +23811,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -23867,7 +23869,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -23901,7 +23903,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -23920,7 +23922,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -23954,7 +23956,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -23973,7 +23975,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24007,7 +24009,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24026,7 +24028,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24064,7 +24066,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24083,7 +24085,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24121,7 +24123,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24140,7 +24142,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24178,7 +24180,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24197,7 +24199,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24230,7 +24232,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24249,7 +24251,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24282,7 +24284,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24301,7 +24303,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24332,7 +24334,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24351,7 +24353,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24386,7 +24388,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24405,7 +24407,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24438,7 +24440,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24457,7 +24459,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24488,7 +24490,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24507,7 +24509,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24539,7 +24541,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24558,7 +24560,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24594,7 +24596,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24613,7 +24615,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24642,7 +24644,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24661,7 +24663,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24692,7 +24694,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24711,7 +24713,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24744,7 +24746,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24763,7 +24765,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24799,7 +24801,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24818,7 +24820,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24853,7 +24855,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -24872,7 +24874,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24902,7 +24904,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -24921,7 +24923,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24961,7 +24963,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -24980,7 +24982,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25009,7 +25011,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25028,7 +25030,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25061,7 +25063,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25080,7 +25082,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25113,7 +25115,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25132,7 +25134,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25168,7 +25170,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25187,7 +25189,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25223,7 +25225,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25242,7 +25244,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25276,7 +25278,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25295,7 +25297,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25330,7 +25332,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25349,7 +25351,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25368,7 +25370,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25387,7 +25389,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25408,7 +25410,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25427,7 +25429,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25460,7 +25462,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25479,7 +25481,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25518,7 +25520,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -25537,7 +25539,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25556,7 +25558,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -25575,7 +25577,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -25620,7 +25622,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -25659,7 +25661,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -25688,7 +25690,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -25733,7 +25735,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -25778,7 +25780,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -25797,7 +25799,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -25844,7 +25846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -25889,7 +25891,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -25908,7 +25910,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -25931,7 +25933,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -25954,7 +25956,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -25977,7 +25979,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -26000,7 +26002,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -26023,7 +26025,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -26046,7 +26048,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -26069,7 +26071,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -26092,7 +26094,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -26115,7 +26117,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -26138,7 +26140,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -26161,7 +26163,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -26184,7 +26186,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -26205,7 +26207,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26226,7 +26228,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26247,7 +26249,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26268,7 +26270,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26289,7 +26291,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26310,7 +26312,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26331,7 +26333,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -26354,7 +26356,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -26377,7 +26379,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -26400,7 +26402,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -26423,7 +26425,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -26446,7 +26448,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -26469,7 +26471,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -26492,7 +26494,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -26511,7 +26513,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26530,7 +26532,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26549,7 +26551,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -26568,7 +26570,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -26642,11 +26644,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -26678,7 +26679,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -26711,7 +26712,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -26744,7 +26745,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -26777,7 +26778,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -26810,7 +26811,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -26843,7 +26844,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -26876,7 +26877,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -26909,7 +26910,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -26940,7 +26941,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -26971,7 +26972,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -27004,7 +27005,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -27037,7 +27038,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -27070,7 +27071,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -27103,7 +27104,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -27136,7 +27137,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -27169,7 +27170,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -27202,7 +27203,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -27235,7 +27236,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -27268,7 +27269,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -27301,7 +27302,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -27334,7 +27335,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -27367,7 +27368,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -27400,7 +27401,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -27433,7 +27434,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -27466,7 +27467,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -27499,7 +27500,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -27531,7 +27532,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -27563,7 +27564,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -27595,7 +27596,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -27627,7 +27628,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -27659,7 +27660,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27689,7 +27690,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27719,7 +27720,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -27751,7 +27752,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -27783,7 +27784,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -27815,7 +27816,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -27847,7 +27848,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -27879,7 +27880,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -27909,7 +27910,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -27941,7 +27942,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -27973,7 +27974,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -28005,7 +28006,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -28037,7 +28038,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28067,7 +28068,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28097,7 +28098,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28127,7 +28128,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28157,7 +28158,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -28189,7 +28190,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -28221,7 +28222,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28251,7 +28252,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28281,7 +28282,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28311,7 +28312,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28341,7 +28342,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28371,7 +28372,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28466,11 +28467,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -28502,7 +28502,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28533,7 +28533,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28564,7 +28564,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28595,7 +28595,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28626,7 +28626,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28657,7 +28657,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28688,7 +28688,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28719,7 +28719,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28750,7 +28750,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28781,7 +28781,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28812,7 +28812,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28843,7 +28843,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -28874,7 +28874,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -28905,7 +28905,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -28936,7 +28936,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -28967,7 +28967,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -28998,7 +28998,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29029,7 +29029,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29060,7 +29060,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29091,7 +29091,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29121,7 +29121,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29151,7 +29151,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29181,7 +29181,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29211,7 +29211,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29241,7 +29241,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29271,7 +29271,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29301,7 +29301,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29331,7 +29331,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29361,7 +29361,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29391,7 +29391,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29421,7 +29421,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29451,7 +29451,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29481,7 +29481,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29511,7 +29511,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29541,7 +29541,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29571,7 +29571,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -29603,7 +29603,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -29635,7 +29635,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29665,7 +29665,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29695,7 +29695,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29725,7 +29725,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29755,7 +29755,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29785,7 +29785,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -51528,19 +51528,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -51554,7 +51554,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -51566,7 +51566,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -51577,7 +51577,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -51588,7 +51588,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -51599,13 +51599,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">Major Hornbrook </t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>NA</t>
@@ -6734,7 +6737,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>28</v>
@@ -6749,7 +6752,7 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
@@ -6802,7 +6805,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>42</v>
@@ -6872,7 +6875,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6940,7 +6943,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -7008,7 +7011,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -7076,7 +7079,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7144,7 +7147,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>42</v>
@@ -7226,7 +7229,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>42</v>
@@ -7318,7 +7321,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -7386,7 +7389,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
@@ -7454,7 +7457,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="29" t="s">
         <v>42</v>
@@ -7542,7 +7545,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>42</v>
@@ -7612,7 +7615,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>42</v>
@@ -7702,7 +7705,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>42</v>
@@ -7860,7 +7863,7 @@
     <row r="62" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="27"/>
       <c r="B62" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -7928,7 +7931,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>26</v>
@@ -7998,7 +8001,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>42</v>
@@ -9388,79 +9391,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" s="43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R2" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S2" s="44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T2" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U2" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W2" s="42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X2" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Y2" s="47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z2" s="46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA2" s="48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9498,10 +9501,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI3" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9512,7 +9515,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="52">
         <v>245679.5</v>
@@ -9586,7 +9589,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9602,7 +9605,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
@@ -9630,7 +9633,7 @@
       <c r="AA5" s="56"/>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9642,7 +9645,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9678,7 +9681,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -9706,7 +9709,7 @@
       <c r="AA7" s="56"/>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9718,7 +9721,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -9754,7 +9757,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9831,7 +9834,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="52">
         <v>129074.86</v>
@@ -9905,7 +9908,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -9921,7 +9924,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -9993,7 +9996,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10005,7 +10008,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10041,7 +10044,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="52"/>
       <c r="E14" s="62"/>
@@ -10069,7 +10072,7 @@
       <c r="AA14" s="56"/>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10081,7 +10084,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="62"/>
@@ -10117,7 +10120,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10194,7 +10197,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10268,7 +10271,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10284,7 +10287,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="52">
         <v>27500.32</v>
@@ -10356,7 +10359,7 @@
       </c>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE19" s="36">
         <v>-5911.24</v>
@@ -10368,7 +10371,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
@@ -10404,7 +10407,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -10432,7 +10435,7 @@
       <c r="AA21" s="56"/>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE21" s="36">
         <v>0</v>
@@ -10444,7 +10447,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -10480,7 +10483,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -10557,7 +10560,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" s="55">
         <v>150850.82</v>
@@ -10633,7 +10636,7 @@
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE25" s="35">
         <v>-388.25</v>
@@ -10649,7 +10652,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" s="55">
         <v>150850.82</v>
@@ -10721,7 +10724,7 @@
       </c>
       <c r="AB26" s="57"/>
       <c r="AD26" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE26" s="36">
         <v>-56964.81</v>
@@ -10733,7 +10736,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="55"/>
@@ -10769,7 +10772,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="55"/>
       <c r="E28" s="55"/>
@@ -10797,7 +10800,7 @@
       <c r="AA28" s="56"/>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE28" s="36">
         <v>0</v>
@@ -10809,7 +10812,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="55"/>
@@ -10845,7 +10848,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="55"/>
@@ -10922,7 +10925,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="52">
         <v>396422.03</v>
@@ -10996,7 +10999,7 @@
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE32" s="35">
         <v>-387.5</v>
@@ -11012,7 +11015,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="52">
         <v>396422.03</v>
@@ -11084,7 +11087,7 @@
       </c>
       <c r="AB33" s="57"/>
       <c r="AD33" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE33" s="36">
         <v>-132316.71</v>
@@ -11096,7 +11099,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="52"/>
       <c r="E34" s="52"/>
@@ -11132,7 +11135,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -11160,7 +11163,7 @@
       <c r="AA35" s="56"/>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE35" s="36">
         <v>0</v>
@@ -11172,7 +11175,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -11208,7 +11211,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -11285,7 +11288,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="52">
         <v>128258.5</v>
@@ -11359,7 +11362,7 @@
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE39" s="35">
         <v>-112</v>
@@ -11375,7 +11378,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="52">
         <v>128258.5</v>
@@ -11447,7 +11450,7 @@
       </c>
       <c r="AB40" s="57"/>
       <c r="AD40" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE40" s="36">
         <v>-26847.46</v>
@@ -11459,7 +11462,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D41" s="52"/>
       <c r="E41" s="52"/>
@@ -11495,7 +11498,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -11523,7 +11526,7 @@
       <c r="AA42" s="56"/>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE42" s="36">
         <v>0</v>
@@ -11535,7 +11538,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -11571,7 +11574,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -11648,7 +11651,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="52">
         <v>65693.36</v>
@@ -11724,7 +11727,7 @@
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE46" s="35">
         <v>-86.75</v>
@@ -11740,7 +11743,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D47" s="52">
         <v>65693.36</v>
@@ -11812,7 +11815,7 @@
       </c>
       <c r="AB47" s="57"/>
       <c r="AD47" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE47" s="36">
         <v>-15639.05</v>
@@ -11824,7 +11827,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D48" s="52"/>
       <c r="E48" s="52"/>
@@ -11860,7 +11863,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52"/>
@@ -11888,7 +11891,7 @@
       <c r="AA49" s="56"/>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE49" s="36">
         <v>0</v>
@@ -11900,7 +11903,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52"/>
@@ -11936,7 +11939,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -12013,7 +12016,7 @@
         <v>37</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D53" s="52">
         <v>155296.79</v>
@@ -12087,7 +12090,7 @@
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE53" s="35">
         <v>-269</v>
@@ -12103,7 +12106,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D54" s="52">
         <v>155296.79</v>
@@ -12175,7 +12178,7 @@
       </c>
       <c r="AB54" s="57"/>
       <c r="AD54" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE54" s="36">
         <v>-66399.88</v>
@@ -12187,7 +12190,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D55" s="52"/>
       <c r="E55" s="52"/>
@@ -12223,7 +12226,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -12251,7 +12254,7 @@
       <c r="AA56" s="56"/>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE56" s="36">
         <v>0</v>
@@ -12263,7 +12266,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -12299,7 +12302,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -12376,7 +12379,7 @@
         <v>38</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D60" s="52">
         <v>20420.56</v>
@@ -12450,7 +12453,7 @@
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE60" s="35">
         <v>-26.75</v>
@@ -12466,7 +12469,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="52">
         <v>20420.56</v>
@@ -12538,7 +12541,7 @@
       </c>
       <c r="AB61" s="57"/>
       <c r="AD61" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE61" s="36">
         <v>-11159.14</v>
@@ -12550,7 +12553,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D62" s="52"/>
       <c r="E62" s="52"/>
@@ -12586,7 +12589,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -12614,7 +12617,7 @@
       <c r="AA63" s="56"/>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE63" s="36">
         <v>0</v>
@@ -12626,7 +12629,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -12662,7 +12665,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -12739,7 +12742,7 @@
         <v>39</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D67" s="52">
         <v>47801.68</v>
@@ -12811,7 +12814,7 @@
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE67" s="35"/>
       <c r="AH67" s="19"/>
@@ -12823,7 +12826,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D68" s="52">
         <v>47801.68</v>
@@ -12895,7 +12898,7 @@
       </c>
       <c r="AB68" s="57"/>
       <c r="AD68" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE68" s="36">
         <v>-5397.27</v>
@@ -12907,7 +12910,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -12943,7 +12946,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -12971,7 +12974,7 @@
       <c r="AA70" s="56"/>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE70" s="36">
         <v>0</v>
@@ -12983,7 +12986,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -13019,7 +13022,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -13094,7 +13097,7 @@
         <v>40</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D74" s="52">
         <v>77166.16</v>
@@ -13168,7 +13171,7 @@
       </c>
       <c r="AB74" s="57"/>
       <c r="AD74" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE74" s="35"/>
       <c r="AH74" s="19"/>
@@ -13178,7 +13181,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D75" s="52">
         <v>77166.16</v>
@@ -13250,7 +13253,7 @@
       </c>
       <c r="AB75" s="57"/>
       <c r="AD75" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE75" s="36"/>
       <c r="AH75" s="19"/>
@@ -13260,7 +13263,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D76" s="52"/>
       <c r="E76" s="52"/>
@@ -13296,7 +13299,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -13324,7 +13327,7 @@
       <c r="AA77" s="56"/>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE77" s="36">
         <v>0</v>
@@ -13336,7 +13339,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -13372,7 +13375,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -13445,7 +13448,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D81" s="52">
         <v>25467.84</v>
@@ -13519,7 +13522,7 @@
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE81" s="35">
         <v>-143.25</v>
@@ -13535,7 +13538,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D82" s="52">
         <v>25467.84</v>
@@ -13607,7 +13610,7 @@
       </c>
       <c r="AB82" s="57"/>
       <c r="AD82" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE82" s="36">
         <v>-5569.48</v>
@@ -13619,7 +13622,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -13655,7 +13658,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D84" s="52"/>
       <c r="E84" s="52"/>
@@ -13683,7 +13686,7 @@
       <c r="AA84" s="56"/>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE84" s="36">
         <v>0</v>
@@ -13695,7 +13698,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D85" s="52"/>
       <c r="E85" s="52"/>
@@ -13731,7 +13734,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
@@ -13808,7 +13811,7 @@
         <v>43</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D88" s="67">
         <v>37083.03</v>
@@ -13882,7 +13885,7 @@
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE88" s="35">
         <v>-148.5</v>
@@ -13898,7 +13901,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D89" s="67">
         <v>37083.03</v>
@@ -13970,7 +13973,7 @@
       </c>
       <c r="AB89" s="57"/>
       <c r="AD89" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE89" s="36">
         <v>-14143.19</v>
@@ -13982,7 +13985,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" s="67"/>
       <c r="E90" s="67"/>
@@ -14018,7 +14021,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D91" s="67"/>
       <c r="E91" s="67"/>
@@ -14046,7 +14049,7 @@
       <c r="AA91" s="56"/>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE91" s="36">
         <v>0</v>
@@ -14058,7 +14061,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92" s="67"/>
       <c r="E92" s="67"/>
@@ -14094,7 +14097,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D93" s="67"/>
       <c r="E93" s="67"/>
@@ -14171,7 +14174,7 @@
         <v>44</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D95" s="52">
         <v>26186.14</v>
@@ -14245,7 +14248,7 @@
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE95" s="35">
         <v>-5</v>
@@ -14261,7 +14264,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D96" s="52">
         <v>26186.14</v>
@@ -14333,7 +14336,7 @@
       </c>
       <c r="AB96" s="57"/>
       <c r="AD96" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE96" s="36">
         <v>-7679.91</v>
@@ -14345,7 +14348,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="52"/>
@@ -14381,7 +14384,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D98" s="52"/>
       <c r="E98" s="52"/>
@@ -14409,7 +14412,7 @@
       <c r="AA98" s="56"/>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE98" s="36">
         <v>0</v>
@@ -14421,7 +14424,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D99" s="52"/>
       <c r="E99" s="52"/>
@@ -14457,7 +14460,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -14534,7 +14537,7 @@
         <v>45</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D102" s="52">
         <v>32473.02</v>
@@ -14608,7 +14611,7 @@
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE102" s="35">
         <v>-317.25</v>
@@ -14624,7 +14627,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D103" s="52">
         <v>32473.02</v>
@@ -14696,7 +14699,7 @@
       </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE103" s="36">
         <v>-16562.52</v>
@@ -14708,7 +14711,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D104" s="52"/>
       <c r="E104" s="69"/>
@@ -14744,7 +14747,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D105" s="52"/>
       <c r="E105" s="69"/>
@@ -14772,7 +14775,7 @@
       <c r="AA105" s="56"/>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE105" s="36">
         <v>0</v>
@@ -14784,7 +14787,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D106" s="52"/>
       <c r="E106" s="69"/>
@@ -14820,7 +14823,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="67"/>
@@ -14894,10 +14897,10 @@
         <v>8840</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D109" s="52">
         <v>58902.56</v>
@@ -14973,7 +14976,7 @@
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE109" s="35">
         <v>-204.75</v>
@@ -14989,7 +14992,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D110" s="52">
         <v>58902.56</v>
@@ -15061,7 +15064,7 @@
       </c>
       <c r="AB110" s="57"/>
       <c r="AD110" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE110" s="36">
         <v>-12155.27</v>
@@ -15073,7 +15076,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D111" s="52"/>
       <c r="E111" s="52"/>
@@ -15109,7 +15112,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D112" s="52"/>
       <c r="E112" s="52"/>
@@ -15137,7 +15140,7 @@
       <c r="AA112" s="56"/>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE112" s="36">
         <v>0</v>
@@ -15149,7 +15152,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D113" s="52"/>
       <c r="E113" s="52"/>
@@ -15185,7 +15188,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D114" s="52"/>
       <c r="E114" s="52"/>
@@ -15259,10 +15262,10 @@
         <v>8769</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D116" s="52">
         <v>21404.82</v>
@@ -15338,7 +15341,7 @@
       </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE116" s="35"/>
       <c r="AH116" s="19"/>
@@ -15348,7 +15351,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D117" s="52">
         <v>21404.82</v>
@@ -15420,7 +15423,7 @@
       </c>
       <c r="AB117" s="57"/>
       <c r="AD117" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE117" s="36"/>
       <c r="AH117" s="19"/>
@@ -15430,7 +15433,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D118" s="52"/>
       <c r="E118" s="52"/>
@@ -15466,7 +15469,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D119" s="52"/>
       <c r="E119" s="52"/>
@@ -15494,7 +15497,7 @@
       <c r="AA119" s="56"/>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE119" s="36">
         <v>0</v>
@@ -15506,7 +15509,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D120" s="52"/>
       <c r="E120" s="52"/>
@@ -15542,7 +15545,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D121" s="52"/>
       <c r="E121" s="52"/>
@@ -15612,10 +15615,10 @@
         <v>7901</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D123" s="52">
         <v>100987.51</v>
@@ -15687,7 +15690,7 @@
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE123" s="35"/>
       <c r="AH123" s="19"/>
@@ -15699,7 +15702,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D124" s="52">
         <v>100987.51</v>
@@ -15771,7 +15774,7 @@
       </c>
       <c r="AB124" s="57"/>
       <c r="AD124" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE124" s="36">
         <v>-12186.08</v>
@@ -15783,7 +15786,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D125" s="52"/>
       <c r="E125" s="52"/>
@@ -15819,7 +15822,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D126" s="52"/>
       <c r="E126" s="52"/>
@@ -15847,7 +15850,7 @@
       <c r="AA126" s="56"/>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE126" s="36">
         <v>0</v>
@@ -15859,7 +15862,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D127" s="52"/>
       <c r="E127" s="52"/>
@@ -15895,7 +15898,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D128" s="52"/>
       <c r="E128" s="52"/>
@@ -15967,10 +15970,10 @@
         <v>8923</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D130" s="52">
         <v>31802.41</v>
@@ -16044,7 +16047,7 @@
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE130" s="35">
         <v>-2</v>
@@ -16060,7 +16063,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D131" s="52">
         <v>31802.41</v>
@@ -16132,7 +16135,7 @@
       </c>
       <c r="AB131" s="57"/>
       <c r="AD131" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE131" s="36">
         <v>-11154.51</v>
@@ -16144,7 +16147,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D132" s="52"/>
       <c r="E132" s="52"/>
@@ -16179,7 +16182,7 @@
     <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D133" s="52"/>
       <c r="E133" s="52"/>
@@ -16207,7 +16210,7 @@
       <c r="AA133" s="56"/>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE133" s="36">
         <v>0</v>
@@ -16219,7 +16222,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D134" s="52"/>
       <c r="E134" s="52"/>
@@ -16255,7 +16258,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D135" s="52"/>
       <c r="E135" s="52"/>
@@ -16329,10 +16332,10 @@
         <v>7864</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D137" s="52">
         <v>30749.24</v>
@@ -16406,7 +16409,7 @@
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE137" s="35">
         <v>-266.75</v>
@@ -16422,7 +16425,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D138" s="52">
         <v>30749.24</v>
@@ -16494,7 +16497,7 @@
       </c>
       <c r="AB138" s="57"/>
       <c r="AD138" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE138" s="36">
         <v>-11702.32</v>
@@ -16506,7 +16509,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D139" s="52"/>
       <c r="E139" s="52"/>
@@ -16542,7 +16545,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D140" s="52"/>
       <c r="E140" s="52"/>
@@ -16570,7 +16573,7 @@
       <c r="AA140" s="56"/>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE140" s="36">
         <v>0</v>
@@ -16582,7 +16585,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D141" s="52"/>
       <c r="E141" s="52"/>
@@ -16618,7 +16621,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D142" s="52"/>
       <c r="E142" s="52"/>
@@ -16692,10 +16695,10 @@
         <v>7912</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D144" s="52">
         <v>268228.26</v>
@@ -16767,7 +16770,7 @@
       </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE144" s="35"/>
       <c r="AH144" s="19"/>
@@ -16777,7 +16780,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D145" s="52">
         <v>268228.26</v>
@@ -16849,7 +16852,7 @@
       </c>
       <c r="AB145" s="57"/>
       <c r="AD145" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE145" s="36"/>
       <c r="AH145" s="19"/>
@@ -16859,7 +16862,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D146" s="52"/>
       <c r="E146" s="52"/>
@@ -16895,7 +16898,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D147" s="52"/>
       <c r="E147" s="52"/>
@@ -16923,7 +16926,7 @@
       <c r="AA147" s="56"/>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE147" s="36">
         <v>0</v>
@@ -16935,7 +16938,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D148" s="52"/>
       <c r="E148" s="52"/>
@@ -16971,7 +16974,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D149" s="52"/>
       <c r="E149" s="52"/>
@@ -17041,10 +17044,10 @@
         <v>8360</v>
       </c>
       <c r="B151" s="74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D151" s="52">
         <v>32773.41</v>
@@ -17116,7 +17119,7 @@
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE151" s="35">
         <v>-260.75</v>
@@ -17132,7 +17135,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D152" s="52">
         <v>32773.41</v>
@@ -17204,7 +17207,7 @@
       </c>
       <c r="AB152" s="57"/>
       <c r="AD152" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE152" s="36">
         <v>-9324.41</v>
@@ -17216,7 +17219,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D153" s="52"/>
       <c r="E153" s="52"/>
@@ -17252,7 +17255,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D154" s="52"/>
       <c r="E154" s="52"/>
@@ -17280,7 +17283,7 @@
       <c r="AA154" s="56"/>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE154" s="36">
         <v>0</v>
@@ -17292,7 +17295,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -17328,7 +17331,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -17402,10 +17405,10 @@
         <v>8337</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D158" s="52">
         <v>17899.33</v>
@@ -17477,7 +17480,7 @@
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE158" s="35">
         <v>-44.75</v>
@@ -17491,7 +17494,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D159" s="52">
         <v>17899.33</v>
@@ -17563,7 +17566,7 @@
       </c>
       <c r="AB159" s="57"/>
       <c r="AD159" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE159" s="36"/>
       <c r="AH159" s="19"/>
@@ -17573,7 +17576,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -17609,7 +17612,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -17637,7 +17640,7 @@
       <c r="AA161" s="56"/>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE161" s="36">
         <v>0</v>
@@ -17649,7 +17652,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -17685,7 +17688,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -17757,10 +17760,10 @@
         <v>9240</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D165" s="52">
         <v>10827.2</v>
@@ -17780,7 +17783,7 @@
         <v>4388.87</v>
       </c>
       <c r="K165" s="52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L165" s="52">
         <v>4388.87</v>
@@ -17820,7 +17823,7 @@
       </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE165" s="35"/>
       <c r="AH165" s="19"/>
@@ -17830,7 +17833,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D166" s="52">
         <v>10827.2</v>
@@ -17902,7 +17905,7 @@
       </c>
       <c r="AB166" s="57"/>
       <c r="AD166" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE166" s="36"/>
       <c r="AH166" s="19"/>
@@ -17912,7 +17915,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D167" s="52"/>
       <c r="E167" s="52"/>
@@ -17948,7 +17951,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D168" s="52"/>
       <c r="E168" s="52"/>
@@ -17976,7 +17979,7 @@
       <c r="AA168" s="56"/>
       <c r="AB168" s="57"/>
       <c r="AD168" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE168" s="36">
         <v>0</v>
@@ -17988,7 +17991,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
@@ -18024,7 +18027,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
@@ -18094,10 +18097,10 @@
         <v>7428</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D172" s="52">
         <v>146237.11</v>
@@ -18169,7 +18172,7 @@
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE172" s="35">
         <v>-304.75</v>
@@ -18183,7 +18186,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D173" s="52">
         <v>146237.11</v>
@@ -18255,7 +18258,7 @@
       </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE173" s="36"/>
       <c r="AH173" s="19"/>
@@ -18265,7 +18268,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D174" s="52"/>
       <c r="E174" s="52"/>
@@ -18301,7 +18304,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D175" s="52"/>
       <c r="E175" s="52"/>
@@ -18329,7 +18332,7 @@
       <c r="AA175" s="56"/>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE175" s="36">
         <v>0</v>
@@ -18341,7 +18344,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D176" s="52"/>
       <c r="E176" s="52"/>
@@ -18377,7 +18380,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D177" s="52"/>
       <c r="E177" s="52"/>
@@ -18451,10 +18454,10 @@
         <v>9351</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D179" s="52">
         <v>16897.53</v>
@@ -18526,7 +18529,7 @@
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE179" s="35">
         <v>-11.25</v>
@@ -18542,7 +18545,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D180" s="52"/>
       <c r="E180" s="52"/>
@@ -18570,7 +18573,7 @@
       <c r="AA180" s="56"/>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE180" s="36">
         <v>-2298.71</v>
@@ -18582,7 +18585,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D181" s="52"/>
       <c r="E181" s="52"/>
@@ -18618,7 +18621,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
@@ -18646,7 +18649,7 @@
       <c r="AA182" s="56"/>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE182" s="36">
         <v>0</v>
@@ -18658,7 +18661,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D183" s="52"/>
       <c r="E183" s="52"/>
@@ -18694,7 +18697,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
@@ -18768,10 +18771,10 @@
         <v>7429</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D186" s="52">
         <v>20992.12</v>
@@ -18843,7 +18846,7 @@
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE186" s="35">
         <v>-32.25</v>
@@ -18857,7 +18860,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D187" s="52">
         <v>20992.12</v>
@@ -18929,7 +18932,7 @@
       </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE187" s="36"/>
       <c r="AH187" s="19"/>
@@ -18939,7 +18942,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D188" s="52"/>
       <c r="E188" s="52"/>
@@ -18975,7 +18978,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D189" s="52"/>
       <c r="E189" s="52"/>
@@ -19003,7 +19006,7 @@
       <c r="AA189" s="56"/>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE189" s="36">
         <v>0</v>
@@ -19015,7 +19018,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D190" s="52"/>
       <c r="E190" s="52"/>
@@ -19051,7 +19054,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D191" s="52"/>
       <c r="E191" s="52"/>
@@ -19123,10 +19126,10 @@
         <v>9508</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D193" s="52">
         <v>23770.95</v>
@@ -19198,7 +19201,7 @@
       </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE193" s="35"/>
       <c r="AH193" s="19"/>
@@ -19208,7 +19211,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D194" s="52">
         <v>23770.95</v>
@@ -19280,7 +19283,7 @@
       </c>
       <c r="AB194" s="57"/>
       <c r="AD194" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE194" s="36"/>
       <c r="AH194" s="19"/>
@@ -19290,7 +19293,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D195" s="52"/>
       <c r="E195" s="52"/>
@@ -19326,7 +19329,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D196" s="52"/>
       <c r="E196" s="52"/>
@@ -19354,7 +19357,7 @@
       <c r="AA196" s="56"/>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE196" s="36">
         <v>0</v>
@@ -19366,7 +19369,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D197" s="52"/>
       <c r="E197" s="52"/>
@@ -19402,7 +19405,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D198" s="52"/>
       <c r="E198" s="52"/>
@@ -19471,7 +19474,7 @@
       <c r="A200" s="19"/>
       <c r="B200" s="19"/>
       <c r="C200" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -19519,7 +19522,7 @@
       <c r="AA200" s="56"/>
       <c r="AB200" s="57"/>
       <c r="AD200" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE200" s="35"/>
       <c r="AH200" s="19"/>
@@ -19529,7 +19532,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D201" s="52"/>
       <c r="E201" s="52"/>
@@ -19561,7 +19564,7 @@
       <c r="AA201" s="56"/>
       <c r="AB201" s="57"/>
       <c r="AD201" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE201" s="36"/>
       <c r="AH201" s="19"/>
@@ -19571,7 +19574,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -19611,7 +19614,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -19643,7 +19646,7 @@
       <c r="AA203" s="56"/>
       <c r="AB203" s="57"/>
       <c r="AD203" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE203" s="36">
         <v>0</v>
@@ -19655,7 +19658,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -19695,7 +19698,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -19767,10 +19770,10 @@
     <row r="207" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="19"/>
       <c r="B207" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D207" s="52"/>
       <c r="E207" s="52"/>
@@ -19802,7 +19805,7 @@
       <c r="AA207" s="56"/>
       <c r="AB207" s="57"/>
       <c r="AD207" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE207" s="35"/>
       <c r="AH207" s="19"/>
@@ -19812,7 +19815,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D208" s="52"/>
       <c r="E208" s="52"/>
@@ -19844,7 +19847,7 @@
       <c r="AA208" s="56"/>
       <c r="AB208" s="57"/>
       <c r="AD208" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE208" s="36"/>
       <c r="AH208" s="19"/>
@@ -19854,7 +19857,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -19894,7 +19897,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -19926,7 +19929,7 @@
       <c r="AA210" s="56"/>
       <c r="AB210" s="57"/>
       <c r="AD210" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE210" s="36">
         <v>0</v>
@@ -19938,7 +19941,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -19978,7 +19981,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -20052,10 +20055,10 @@
         <v>8946</v>
       </c>
       <c r="B214" s="77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D214" s="52">
         <v>137109.56</v>
@@ -20127,7 +20130,7 @@
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE214" s="35"/>
       <c r="AH214" s="19"/>
@@ -20137,7 +20140,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D215" s="52">
         <v>137109.56</v>
@@ -20209,7 +20212,7 @@
       </c>
       <c r="AB215" s="57"/>
       <c r="AD215" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE215" s="36"/>
       <c r="AH215" s="19"/>
@@ -20219,7 +20222,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -20255,7 +20258,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -20283,7 +20286,7 @@
       <c r="AA217" s="56"/>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE217" s="36">
         <v>0</v>
@@ -20295,7 +20298,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -20331,7 +20334,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -20401,10 +20404,10 @@
         <v>8308</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D221" s="52">
         <v>396453.46</v>
@@ -20476,7 +20479,7 @@
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE221" s="35">
         <v>-1014.25</v>
@@ -20490,7 +20493,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D222" s="52">
         <v>396453.46</v>
@@ -20562,7 +20565,7 @@
       </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE222" s="36"/>
       <c r="AH222" s="19"/>
@@ -20572,7 +20575,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -20608,7 +20611,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -20636,7 +20639,7 @@
       <c r="AA224" s="56"/>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AE224" s="36">
         <v>0</v>
@@ -20648,7 +20651,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -20684,7 +20687,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -21324,49 +21327,49 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="81" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F2" s="82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H2" s="83" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I2" s="81" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" s="82" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K2" s="82" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L2" s="83" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M2" s="83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N2" s="81" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O2" s="84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P2" s="35"/>
     </row>
@@ -21499,7 +21502,7 @@
         <v>337.89039999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21648,7 +21651,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="52">
         <v>0</v>
@@ -21690,7 +21693,7 @@
         <v>-93.95999999999987</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21883,7 +21886,7 @@
         <v>44.85015873015877</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -22322,7 +22325,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="52">
         <v>0</v>
@@ -22384,7 +22387,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="52">
         <v>0</v>
@@ -22444,7 +22447,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="52">
         <v>52040.560000000005</v>
@@ -22502,7 +22505,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="52">
         <v>2127.8099999999995</v>
@@ -22564,7 +22567,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="52">
         <v>0</v>
@@ -22624,7 +22627,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="52">
         <v>0</v>
@@ -22678,7 +22681,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="98" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="99">
         <v>0</v>
@@ -22736,7 +22739,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="99">
         <v>0</v>
@@ -22796,7 +22799,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="98" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="99">
         <v>0</v>
@@ -22830,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -22855,7 +22858,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="99">
         <v>0</v>
@@ -22917,7 +22920,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="99">
         <v>0</v>
@@ -22979,7 +22982,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="99">
         <v>0</v>
@@ -23041,7 +23044,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" s="99">
         <v>0</v>
@@ -23127,7 +23130,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" s="99"/>
       <c r="D62" s="99"/>
@@ -23167,7 +23170,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="98" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="99">
         <v>0</v>
@@ -23225,7 +23228,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="98" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="99">
         <v>34650.399999999965</v>
@@ -23301,10 +23304,10 @@
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B69" s="103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C69" s="104">
         <v>88818.76999999996</v>
@@ -23316,13 +23319,13 @@
         <v>58931.02999999998</v>
       </c>
       <c r="F69" s="106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G69" s="107">
         <v>0.6634974791927427</v>
       </c>
       <c r="H69" s="108" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I69" s="109">
         <v>0.0799203816940944</v>
@@ -23337,7 +23340,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C70" s="99">
         <v>-22865.6</v>
@@ -23353,7 +23356,7 @@
         <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I70" s="114">
         <v>2.685240710936954</v>
@@ -23752,52 +23755,52 @@
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C2" s="117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D2" s="117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E2" s="117" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="117" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" s="117" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H2" s="117" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I2" s="117" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J2" s="117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K2" s="117" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L2" s="117" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M2" s="117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N2" s="117" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O2" s="117" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P2" s="117" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q2" s="118" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -23813,10 +23816,10 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="123" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -23900,7 +23903,7 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -23953,7 +23956,7 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24006,7 +24009,7 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24063,7 +24066,7 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24090,7 +24093,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -24120,7 +24123,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24177,7 +24180,7 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24668,7 +24671,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="54">
         <v>324.19</v>
@@ -24718,7 +24721,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" s="54">
         <v>84.05</v>
@@ -24770,7 +24773,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38" s="54">
         <v>290.15</v>
@@ -24825,7 +24828,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="54">
         <v>156.69</v>
@@ -24879,7 +24882,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="54">
         <v>200.82</v>
@@ -24928,7 +24931,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="54">
         <v>497.55</v>
@@ -24987,7 +24990,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="75" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46" s="54">
         <v>210.6</v>
@@ -25035,7 +25038,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="54">
         <v>110.44</v>
@@ -25087,7 +25090,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C50" s="54">
         <v>65.13</v>
@@ -25139,7 +25142,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="54">
         <v>659.73</v>
@@ -25194,7 +25197,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="54">
         <v>125.17</v>
@@ -25249,7 +25252,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C56" s="54">
         <v>130.62</v>
@@ -25302,7 +25305,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C58" s="54">
         <v>140.15</v>
@@ -25392,7 +25395,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62" s="54"/>
       <c r="D62" s="54"/>
@@ -25434,7 +25437,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" s="54">
         <v>358.86</v>
@@ -25486,7 +25489,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C66" s="54">
         <v>2344.68</v>
@@ -25580,7 +25583,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C70" s="147"/>
       <c r="D70" s="147"/>
@@ -25625,7 +25628,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
@@ -25664,7 +25667,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C72" s="20">
         <v>4490.26</v>
@@ -25693,7 +25696,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
@@ -25738,7 +25741,7 @@
     <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C74" s="152"/>
       <c r="D74" s="152"/>
@@ -25802,10 +25805,10 @@
     <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C76" s="157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D76" s="157"/>
       <c r="E76" s="157"/>
@@ -25849,7 +25852,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C77" s="157"/>
       <c r="D77" s="157"/>
@@ -25913,7 +25916,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C79" s="165"/>
       <c r="D79" s="35"/>
@@ -25925,7 +25928,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="166" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M79" s="166"/>
       <c r="N79" s="35"/>
@@ -25936,7 +25939,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C80" s="168">
         <v>1</v>
@@ -25959,7 +25962,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C81" s="131">
         <v>1</v>
@@ -25982,7 +25985,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -26005,7 +26008,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -26028,7 +26031,7 @@
     <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -26051,7 +26054,7 @@
     <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C85" s="131">
         <v>0.5</v>
@@ -26074,7 +26077,7 @@
     <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" s="131">
         <v>1</v>
@@ -26097,7 +26100,7 @@
     <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -26120,7 +26123,7 @@
     <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -26143,7 +26146,7 @@
     <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C89" s="131">
         <v>0</v>
@@ -26166,7 +26169,7 @@
     <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C90" s="131">
         <v>1</v>
@@ -26336,7 +26339,7 @@
     <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C98" s="131">
         <v>1</v>
@@ -26359,7 +26362,7 @@
     <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -26382,7 +26385,7 @@
     <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -26405,7 +26408,7 @@
     <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -26428,7 +26431,7 @@
     <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -26451,7 +26454,7 @@
     <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -26474,7 +26477,7 @@
     <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -26573,7 +26576,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C109" s="170">
         <v>16.5</v>
@@ -26649,7 +26652,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -26681,7 +26684,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -26714,7 +26717,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -26747,7 +26750,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -26780,7 +26783,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -26813,7 +26816,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -26846,7 +26849,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -26879,7 +26882,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -26974,7 +26977,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -27007,7 +27010,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -27040,7 +27043,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -27073,7 +27076,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -27106,7 +27109,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -27139,7 +27142,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -27172,7 +27175,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -27205,7 +27208,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -27238,7 +27241,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -27271,7 +27274,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -27304,7 +27307,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -27337,7 +27340,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -27370,7 +27373,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -27403,7 +27406,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -27436,7 +27439,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -27469,7 +27472,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -27502,7 +27505,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -27534,7 +27537,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -27566,7 +27569,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -27598,7 +27601,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -27630,7 +27633,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -27722,7 +27725,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -27754,7 +27757,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -27786,7 +27789,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -27818,7 +27821,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -27850,7 +27853,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -27912,7 +27915,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -27944,7 +27947,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -27976,7 +27979,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -28008,7 +28011,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -28160,7 +28163,7 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -28192,7 +28195,7 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -28472,7 +28475,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -29573,7 +29576,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -29605,7 +29608,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -29940,88 +29943,88 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q2" s="42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R2" s="43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S2" s="43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U2" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V2" s="214" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W2" s="214" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X2" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y2" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA2" s="46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AC2" s="46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD2" s="48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="35"/>
       <c r="AH2" s="35"/>
@@ -30062,10 +30065,10 @@
       <c r="AG3" s="35"/>
       <c r="AH3" s="35"/>
       <c r="AK3" s="49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AL3" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -30078,7 +30081,7 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="52">
         <v>1914143.52</v>
@@ -30174,7 +30177,7 @@
       </c>
       <c r="AE4" s="57"/>
       <c r="AG4" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH4" s="35">
         <f>AK9</f>
@@ -30193,7 +30196,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" s="52">
         <v>1922479.92</v>
@@ -30282,7 +30285,7 @@
       </c>
       <c r="AE5" s="57"/>
       <c r="AG5" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH5" s="36">
         <f>AL9</f>
@@ -30301,7 +30304,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" s="52">
         <v>1922479.92</v>
@@ -30408,7 +30411,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -30481,7 +30484,7 @@
       </c>
       <c r="AE7" s="57"/>
       <c r="AG7" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH7" s="36">
         <v>0</v>
@@ -30499,7 +30502,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -30586,7 +30589,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -30715,7 +30718,7 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="65">
         <v>381671.63</v>
@@ -30804,7 +30807,7 @@
       </c>
       <c r="AE11" s="57"/>
       <c r="AG11" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH11" s="35">
         <f>AK16</f>
@@ -30823,7 +30826,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="52">
         <v>382219.49</v>
@@ -30912,7 +30915,7 @@
       </c>
       <c r="AE12" s="57"/>
       <c r="AG12" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH12" s="36">
         <f>AL16</f>
@@ -30931,7 +30934,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="52">
         <v>382219.49</v>
@@ -31034,7 +31037,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" s="65">
         <v>383409.63</v>
@@ -31115,7 +31118,7 @@
       </c>
       <c r="AE14" s="57"/>
       <c r="AG14" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH14" s="36">
         <v>0</v>
@@ -31133,7 +31136,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="65">
         <v>383409.63</v>
@@ -31222,7 +31225,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="65">
         <v>383409.63</v>
@@ -31356,7 +31359,7 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="52">
         <v>449818.08</v>
@@ -31449,7 +31452,7 @@
       </c>
       <c r="AE18" s="57"/>
       <c r="AG18" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH18" s="35">
         <f>AK23</f>
@@ -31468,7 +31471,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" s="52">
         <v>449818.08</v>
@@ -31559,7 +31562,7 @@
       </c>
       <c r="AE19" s="57"/>
       <c r="AG19" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH19" s="36">
         <f>AL23</f>
@@ -31578,7 +31581,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="52">
         <v>449818.08</v>
@@ -31683,7 +31686,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -31758,7 +31761,7 @@
       </c>
       <c r="AE21" s="57"/>
       <c r="AG21" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH21" s="36">
         <v>0</v>
@@ -31776,7 +31779,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -31865,7 +31868,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -31998,7 +32001,7 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" s="52">
         <v>38856.96</v>
@@ -32091,7 +32094,7 @@
       </c>
       <c r="AE25" s="57"/>
       <c r="AG25" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH25" s="35">
         <f>AK30</f>
@@ -32110,7 +32113,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" s="52">
         <v>38856.96</v>
@@ -32203,7 +32206,7 @@
       </c>
       <c r="AE26" s="57"/>
       <c r="AG26" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH26" s="36">
         <f>AL30</f>
@@ -32222,7 +32225,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="52">
         <v>38856.96</v>
@@ -32329,7 +32332,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52">
@@ -32412,7 +32415,7 @@
       </c>
       <c r="AE28" s="57"/>
       <c r="AG28" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH28" s="36">
         <v>0</v>
@@ -32430,7 +32433,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -32527,7 +32530,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -32666,7 +32669,7 @@
         <v>Murney - 1 Freight Drive + 109 Iport</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="52">
         <v>69191.71</v>
@@ -32757,7 +32760,7 @@
       </c>
       <c r="AE32" s="57"/>
       <c r="AG32" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH32" s="35">
         <f>AK37</f>
@@ -32776,7 +32779,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="52">
         <v>69191.71</v>
@@ -32865,7 +32868,7 @@
       </c>
       <c r="AE33" s="57"/>
       <c r="AG33" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH33" s="36">
         <f>AL37</f>
@@ -32884,7 +32887,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D34" s="52">
         <v>69191.71</v>
@@ -32987,7 +32990,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -33060,7 +33063,7 @@
       </c>
       <c r="AE35" s="57"/>
       <c r="AG35" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH35" s="36">
         <v>0</v>
@@ -33078,7 +33081,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -33165,7 +33168,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -33294,7 +33297,7 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="52">
         <v>44956.29</v>
@@ -33381,7 +33384,7 @@
       </c>
       <c r="AE39" s="57"/>
       <c r="AG39" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH39" s="35">
         <f>AK44</f>
@@ -33400,7 +33403,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="52">
         <v>44956.29</v>
@@ -33485,7 +33488,7 @@
       </c>
       <c r="AE40" s="57"/>
       <c r="AG40" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH40" s="36">
         <f>AL44</f>
@@ -33504,7 +33507,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D41" s="52">
         <v>44956.29</v>
@@ -33607,7 +33610,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -33684,7 +33687,7 @@
       </c>
       <c r="AE42" s="57"/>
       <c r="AG42" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH42" s="36">
         <v>0</v>
@@ -33702,7 +33705,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -33793,7 +33796,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -33926,7 +33929,7 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" s="52">
         <v>7495.54</v>
@@ -34019,7 +34022,7 @@
       </c>
       <c r="AE46" s="57"/>
       <c r="AG46" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH46" s="35">
         <f>AK51</f>
@@ -34038,7 +34041,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D47" s="52">
         <v>7495.54</v>
@@ -34131,7 +34134,7 @@
       </c>
       <c r="AE47" s="57"/>
       <c r="AG47" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH47" s="36">
         <f>AL51</f>
@@ -34150,7 +34153,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D48" s="52">
         <v>7495.54</v>
@@ -34257,7 +34260,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52">
@@ -34338,7 +34341,7 @@
       </c>
       <c r="AE49" s="57"/>
       <c r="AG49" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH49" s="36">
         <v>0</v>
@@ -34356,7 +34359,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52">
@@ -34451,7 +34454,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52">
@@ -34588,7 +34591,7 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D53" s="52">
         <v>100348.26</v>
@@ -34681,7 +34684,7 @@
       </c>
       <c r="AE53" s="57"/>
       <c r="AG53" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH53" s="35">
         <f>AK58</f>
@@ -34700,7 +34703,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D54" s="52">
         <v>100348.26</v>
@@ -34789,7 +34792,7 @@
       </c>
       <c r="AE54" s="57"/>
       <c r="AG54" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH54" s="36">
         <f>AL58</f>
@@ -34808,7 +34811,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D55" s="52">
         <v>100348.26</v>
@@ -34911,7 +34914,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -34984,7 +34987,7 @@
       </c>
       <c r="AE56" s="57"/>
       <c r="AG56" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH56" s="36">
         <v>0</v>
@@ -35002,7 +35005,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -35089,7 +35092,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -35222,7 +35225,7 @@
         <v>35 Mania</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D60" s="52">
         <v>98524.85</v>
@@ -35313,7 +35316,7 @@
       </c>
       <c r="AE60" s="57"/>
       <c r="AG60" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH60" s="35">
         <f>AK65</f>
@@ -35332,7 +35335,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="52">
         <v>98524.85</v>
@@ -35423,7 +35426,7 @@
       </c>
       <c r="AE61" s="57"/>
       <c r="AG61" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH61" s="36">
         <f>AL65</f>
@@ -35442,7 +35445,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D62" s="52">
         <v>98524.85</v>
@@ -35547,7 +35550,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -35624,7 +35627,7 @@
       </c>
       <c r="AE63" s="57"/>
       <c r="AG63" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH63" s="36">
         <v>0</v>
@@ -35642,7 +35645,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -35733,7 +35736,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -35866,7 +35869,7 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D67" s="52">
         <v>87970.61</v>
@@ -35955,7 +35958,7 @@
       </c>
       <c r="AE67" s="57"/>
       <c r="AG67" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH67" s="35">
         <f>AK72</f>
@@ -35974,7 +35977,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D68" s="52">
         <v>87970.61</v>
@@ -36065,7 +36068,7 @@
       </c>
       <c r="AE68" s="57"/>
       <c r="AG68" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH68" s="36">
         <f>AL72</f>
@@ -36084,7 +36087,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -36173,7 +36176,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -36248,7 +36251,7 @@
       </c>
       <c r="AE70" s="57"/>
       <c r="AG70" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH70" s="36">
         <v>0</v>
@@ -36266,7 +36269,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -36355,7 +36358,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -36484,7 +36487,7 @@
         <v>Andrew Reeve Stage 2</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D74" s="52">
         <v>210242.4</v>
@@ -36577,7 +36580,7 @@
       </c>
       <c r="AE74" s="57"/>
       <c r="AG74" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH74" s="35">
         <f>AK79</f>
@@ -36596,7 +36599,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D75" s="52">
         <v>210242.4</v>
@@ -36687,7 +36690,7 @@
       </c>
       <c r="AE75" s="57"/>
       <c r="AG75" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH75" s="36">
         <f>AL79</f>
@@ -36706,7 +36709,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D76" s="52">
         <v>210242.4</v>
@@ -36811,7 +36814,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -36890,7 +36893,7 @@
       </c>
       <c r="AE77" s="57"/>
       <c r="AG77" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH77" s="36">
         <v>0</v>
@@ -36908,7 +36911,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -37003,7 +37006,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -37140,7 +37143,7 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D81" s="52">
         <v>43448.62</v>
@@ -37233,7 +37236,7 @@
       </c>
       <c r="AE81" s="57"/>
       <c r="AG81" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH81" s="35">
         <f>AK86</f>
@@ -37252,7 +37255,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D82" s="52">
         <v>43448.62</v>
@@ -37345,7 +37348,7 @@
       </c>
       <c r="AE82" s="57"/>
       <c r="AG82" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH82" s="36">
         <f>AL86</f>
@@ -37364,7 +37367,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D83" s="52">
         <v>0</v>
@@ -37469,7 +37472,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D84" s="52">
         <v>0</v>
@@ -37560,7 +37563,7 @@
       </c>
       <c r="AE84" s="57"/>
       <c r="AG84" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH84" s="36">
         <v>0</v>
@@ -37578,7 +37581,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D85" s="52">
         <v>0</v>
@@ -37681,7 +37684,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D86" s="52">
         <v>0</v>
@@ -37826,7 +37829,7 @@
         <v>Melhuish House</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D88" s="67">
         <v>49964.93</v>
@@ -37919,7 +37922,7 @@
       </c>
       <c r="AE88" s="57"/>
       <c r="AG88" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH88" s="35">
         <f>AK93</f>
@@ -37938,7 +37941,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D89" s="67">
         <v>49964.93</v>
@@ -38027,7 +38030,7 @@
       </c>
       <c r="AE89" s="57"/>
       <c r="AG89" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH89" s="36">
         <f>AL93</f>
@@ -38046,7 +38049,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" s="67">
         <v>0</v>
@@ -38149,7 +38152,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D91" s="67">
         <v>0</v>
@@ -38238,7 +38241,7 @@
       </c>
       <c r="AE91" s="57"/>
       <c r="AG91" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH91" s="36">
         <v>0</v>
@@ -38256,7 +38259,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D92" s="67">
         <v>0</v>
@@ -38359,7 +38362,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D93" s="67">
         <v>0</v>
@@ -38504,7 +38507,7 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D95" s="52">
         <v>109103.76</v>
@@ -38597,7 +38600,7 @@
       </c>
       <c r="AE95" s="57"/>
       <c r="AG95" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH95" s="35">
         <f>AK100</f>
@@ -38616,7 +38619,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D96" s="52">
         <v>109103.76</v>
@@ -38709,7 +38712,7 @@
       </c>
       <c r="AE96" s="57"/>
       <c r="AG96" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH96" s="36">
         <f>AL100</f>
@@ -38728,7 +38731,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D97" s="52">
         <v>0</v>
@@ -38835,7 +38838,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D98" s="52">
         <v>0</v>
@@ -38928,7 +38931,7 @@
       </c>
       <c r="AE98" s="57"/>
       <c r="AG98" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH98" s="36">
         <v>0</v>
@@ -38946,7 +38949,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D99" s="52">
         <v>0</v>
@@ -39051,7 +39054,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D100" s="52">
         <v>0</v>
@@ -39198,7 +39201,7 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D102" s="52">
         <v>27742.44</v>
@@ -39289,7 +39292,7 @@
       </c>
       <c r="AE102" s="57"/>
       <c r="AG102" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH102" s="35">
         <f>AK107</f>
@@ -39308,7 +39311,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D103" s="52">
         <v>27861.41</v>
@@ -39399,7 +39402,7 @@
       </c>
       <c r="AE103" s="57"/>
       <c r="AG103" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH103" s="36">
         <f>AL107</f>
@@ -39418,7 +39421,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D104" s="52">
         <v>0</v>
@@ -39523,7 +39526,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D105" s="52">
         <v>0</v>
@@ -39614,7 +39617,7 @@
       </c>
       <c r="AE105" s="57"/>
       <c r="AG105" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH105" s="36">
         <v>0</v>
@@ -39632,7 +39635,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D106" s="52">
         <v>0</v>
@@ -39737,7 +39740,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D107" s="52">
         <v>0</v>
@@ -39884,7 +39887,7 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D109" s="52">
         <v>21300.45</v>
@@ -39976,7 +39979,7 @@
       </c>
       <c r="AE109" s="57"/>
       <c r="AG109" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH109" s="35">
         <f>AK114</f>
@@ -39995,7 +39998,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D110" s="52">
         <v>21300.45</v>
@@ -40088,7 +40091,7 @@
       </c>
       <c r="AE110" s="57"/>
       <c r="AG110" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH110" s="36">
         <f>AL114</f>
@@ -40107,7 +40110,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D111" s="52">
         <v>0</v>
@@ -40214,7 +40217,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D112" s="52">
         <v>0</v>
@@ -40307,7 +40310,7 @@
       </c>
       <c r="AE112" s="57"/>
       <c r="AG112" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH112" s="36">
         <v>0</v>
@@ -40325,7 +40328,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D113" s="52">
         <v>0</v>
@@ -40432,7 +40435,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D114" s="52">
         <v>0</v>
@@ -40581,7 +40584,7 @@
         <v>Percival Bach</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D116" s="52">
         <v>63405.46</v>
@@ -40674,7 +40677,7 @@
       </c>
       <c r="AE116" s="57"/>
       <c r="AG116" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH116" s="35">
         <f>AK121</f>
@@ -40693,7 +40696,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D117" s="52">
         <v>63405.46</v>
@@ -40786,7 +40789,7 @@
       </c>
       <c r="AE117" s="57"/>
       <c r="AG117" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH117" s="36">
         <f>AL121</f>
@@ -40805,7 +40808,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D118" s="52">
         <v>0</v>
@@ -40912,7 +40915,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D119" s="52">
         <v>0</v>
@@ -41005,7 +41008,7 @@
       </c>
       <c r="AE119" s="57"/>
       <c r="AG119" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH119" s="36">
         <v>0</v>
@@ -41023,7 +41026,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D120" s="52">
         <v>0</v>
@@ -41130,7 +41133,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D121" s="52">
         <v>0</v>
@@ -41279,7 +41282,7 @@
         <v>St Albans Street</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D123" s="52">
         <v>0</v>
@@ -41371,7 +41374,7 @@
       </c>
       <c r="AE123" s="57"/>
       <c r="AG123" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH123" s="35">
         <f>AK128</f>
@@ -41390,7 +41393,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D124" s="52">
         <v>0</v>
@@ -41479,7 +41482,7 @@
       </c>
       <c r="AE124" s="57"/>
       <c r="AG124" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH124" s="36">
         <f>AL128</f>
@@ -41498,7 +41501,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D125" s="52">
         <v>0</v>
@@ -41601,7 +41604,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D126" s="52">
         <v>0</v>
@@ -41690,7 +41693,7 @@
       </c>
       <c r="AE126" s="57"/>
       <c r="AG126" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH126" s="36">
         <v>0</v>
@@ -41708,7 +41711,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D127" s="52">
         <v>0</v>
@@ -41811,7 +41814,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D128" s="52">
         <v>0</v>
@@ -41956,7 +41959,7 @@
         <v>4 Perry St</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D130" s="52">
         <v>47191.69</v>
@@ -42049,7 +42052,7 @@
       </c>
       <c r="AE130" s="57"/>
       <c r="AG130" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH130" s="35">
         <f>AK135</f>
@@ -42068,7 +42071,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D131" s="52">
         <v>47191.69</v>
@@ -42161,7 +42164,7 @@
       </c>
       <c r="AE131" s="57"/>
       <c r="AG131" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH131" s="36">
         <f>AL135</f>
@@ -42180,7 +42183,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D132" s="52">
         <v>0</v>
@@ -42285,7 +42288,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D133" s="52">
         <v>0</v>
@@ -42376,7 +42379,7 @@
       </c>
       <c r="AE133" s="57"/>
       <c r="AG133" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH133" s="36">
         <v>0</v>
@@ -42394,7 +42397,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D134" s="52">
         <v>0</v>
@@ -42499,7 +42502,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D135" s="52">
         <v>0</v>
@@ -42646,7 +42649,7 @@
         <v>Ryans House</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D137" s="52">
         <v>0</v>
@@ -42739,7 +42742,7 @@
       </c>
       <c r="AE137" s="57"/>
       <c r="AG137" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH137" s="35">
         <f>AK142</f>
@@ -42758,7 +42761,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D138" s="52">
         <v>0</v>
@@ -42845,7 +42848,7 @@
       </c>
       <c r="AE138" s="57"/>
       <c r="AG138" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH138" s="36">
         <f>AL142</f>
@@ -42864,7 +42867,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D139" s="52">
         <v>0</v>
@@ -42965,7 +42968,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D140" s="52">
         <v>0</v>
@@ -43050,7 +43053,7 @@
       </c>
       <c r="AE140" s="57"/>
       <c r="AG140" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH140" s="36">
         <v>0</v>
@@ -43068,7 +43071,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D141" s="52">
         <v>0</v>
@@ -43167,7 +43170,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D142" s="52">
         <v>0</v>
@@ -43308,7 +43311,7 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D144" s="52">
         <v>23650.59</v>
@@ -43397,7 +43400,7 @@
       </c>
       <c r="AE144" s="57"/>
       <c r="AG144" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH144" s="35">
         <f>AK149</f>
@@ -43416,7 +43419,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D145" s="52">
         <v>23650.59</v>
@@ -43505,7 +43508,7 @@
       </c>
       <c r="AE145" s="57"/>
       <c r="AG145" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH145" s="36">
         <f>AL149</f>
@@ -43524,7 +43527,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D146" s="52">
         <v>23650.59</v>
@@ -43627,7 +43630,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D147" s="52">
         <v>23650.59</v>
@@ -43716,7 +43719,7 @@
       </c>
       <c r="AE147" s="57"/>
       <c r="AG147" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH147" s="36">
         <v>0</v>
@@ -43734,7 +43737,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D148" s="52">
         <v>23650.59</v>
@@ -43837,7 +43840,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D149" s="52">
         <v>23650.59</v>
@@ -43982,7 +43985,7 @@
         <v>Dixon House</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D151" s="52">
         <v>29188.19</v>
@@ -44071,7 +44074,7 @@
       </c>
       <c r="AE151" s="57"/>
       <c r="AG151" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH151" s="35">
         <f>AK156</f>
@@ -44090,7 +44093,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D152" s="52">
         <v>29188.19</v>
@@ -44179,7 +44182,7 @@
       </c>
       <c r="AE152" s="57"/>
       <c r="AG152" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH152" s="36">
         <f>AL156</f>
@@ -44198,7 +44201,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D153" s="52">
         <v>29188.19</v>
@@ -44301,7 +44304,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D154" s="52">
         <v>29188.19</v>
@@ -44390,7 +44393,7 @@
       </c>
       <c r="AE154" s="57"/>
       <c r="AG154" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH154" s="36">
         <v>0</v>
@@ -44408,7 +44411,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -44495,7 +44498,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -44624,7 +44627,7 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D158" s="52">
         <v>15025.89</v>
@@ -44711,7 +44714,7 @@
       </c>
       <c r="AE158" s="57"/>
       <c r="AG158" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH158" s="35">
         <f>AK163</f>
@@ -44730,7 +44733,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D159" s="52">
         <v>0</v>
@@ -44816,7 +44819,7 @@
       </c>
       <c r="AE159" s="57"/>
       <c r="AG159" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH159" s="36">
         <f>AL163</f>
@@ -44835,7 +44838,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -44922,7 +44925,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -44995,7 +44998,7 @@
       </c>
       <c r="AE161" s="57"/>
       <c r="AG161" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH161" s="36">
         <v>0</v>
@@ -45013,7 +45016,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -45100,7 +45103,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -45229,7 +45232,7 @@
         <v>Daves Twizel Shack</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D165" s="52">
         <v>300839.52</v>
@@ -45318,7 +45321,7 @@
       </c>
       <c r="AE165" s="57"/>
       <c r="AG165" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH165" s="35">
         <f>AK170</f>
@@ -45337,7 +45340,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D166" s="52">
         <v>300839.52</v>
@@ -45426,7 +45429,7 @@
       </c>
       <c r="AE166" s="57"/>
       <c r="AG166" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH166" s="36">
         <f>AL170</f>
@@ -45445,7 +45448,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D167" s="52">
         <v>0</v>
@@ -45548,7 +45551,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D168" s="52">
         <v>0</v>
@@ -45637,7 +45640,7 @@
       </c>
       <c r="AE168" s="57"/>
       <c r="AG168" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH168" s="36">
         <v>0</v>
@@ -45655,7 +45658,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D169" s="52">
         <v>0</v>
@@ -45758,7 +45761,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D170" s="52">
         <v>0</v>
@@ -45903,7 +45906,7 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D172" s="52">
         <v>58426.32</v>
@@ -45990,7 +45993,7 @@
       </c>
       <c r="AE172" s="57"/>
       <c r="AG172" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH172" s="35">
         <f>AK177</f>
@@ -46009,7 +46012,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D173" s="52">
         <v>58426.32</v>
@@ -46095,7 +46098,7 @@
       </c>
       <c r="AE173" s="57"/>
       <c r="AG173" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH173" s="36">
         <f>AL177</f>
@@ -46114,7 +46117,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D174" s="52">
         <v>0</v>
@@ -46217,7 +46220,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D175" s="52">
         <v>0</v>
@@ -46306,7 +46309,7 @@
       </c>
       <c r="AE175" s="57"/>
       <c r="AG175" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH175" s="36">
         <v>0</v>
@@ -46324,7 +46327,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D176" s="52">
         <v>0</v>
@@ -46427,7 +46430,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D177" s="52">
         <v>0</v>
@@ -46572,7 +46575,7 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D179" s="52">
         <v>18080.64</v>
@@ -46659,7 +46662,7 @@
       </c>
       <c r="AE179" s="57"/>
       <c r="AG179" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH179" s="35">
         <f>AK184</f>
@@ -46678,7 +46681,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D180" s="52">
         <v>18080.64</v>
@@ -46764,7 +46767,7 @@
       </c>
       <c r="AE180" s="57"/>
       <c r="AG180" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH180" s="36">
         <f>AL184</f>
@@ -46783,7 +46786,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D181" s="52">
         <v>0</v>
@@ -46886,7 +46889,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D182" s="52">
         <v>0</v>
@@ -46975,7 +46978,7 @@
       </c>
       <c r="AE182" s="57"/>
       <c r="AG182" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH182" s="36">
         <v>0</v>
@@ -46993,7 +46996,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D183" s="52">
         <v>0</v>
@@ -47096,7 +47099,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D184" s="52">
         <v>0</v>
@@ -47241,7 +47244,7 @@
         <v>Taggart House</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D186" s="52">
         <v>17608.26</v>
@@ -47328,7 +47331,7 @@
       </c>
       <c r="AE186" s="57"/>
       <c r="AG186" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH186" s="35">
         <f>AK191</f>
@@ -47347,7 +47350,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D187" s="52">
         <v>17608.26</v>
@@ -47433,7 +47436,7 @@
       </c>
       <c r="AE187" s="57"/>
       <c r="AG187" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH187" s="36">
         <f>AL191</f>
@@ -47452,7 +47455,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D188" s="52">
         <v>0</v>
@@ -47555,7 +47558,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D189" s="52">
         <v>0</v>
@@ -47644,7 +47647,7 @@
       </c>
       <c r="AE189" s="57"/>
       <c r="AG189" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH189" s="36">
         <v>0</v>
@@ -47662,7 +47665,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D190" s="52">
         <v>0</v>
@@ -47765,7 +47768,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D191" s="52">
         <v>0</v>
@@ -47910,7 +47913,7 @@
         <v>St Barnabas Church</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D193" s="52">
         <v>19572.81</v>
@@ -48001,7 +48004,7 @@
       </c>
       <c r="AE193" s="57"/>
       <c r="AG193" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH193" s="35">
         <f>AK198</f>
@@ -48020,7 +48023,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D194" s="52">
         <v>0</v>
@@ -48106,7 +48109,7 @@
       </c>
       <c r="AE194" s="57"/>
       <c r="AG194" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH194" s="36">
         <f>AL198</f>
@@ -48125,7 +48128,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D195" s="52">
         <v>0</v>
@@ -48228,7 +48231,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D196" s="52">
         <v>0</v>
@@ -48317,7 +48320,7 @@
       </c>
       <c r="AE196" s="57"/>
       <c r="AG196" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH196" s="36">
         <v>0</v>
@@ -48335,7 +48338,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D197" s="52">
         <v>0</v>
@@ -48438,7 +48441,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D198" s="52">
         <v>0</v>
@@ -48583,7 +48586,7 @@
         <v>0</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -48670,7 +48673,7 @@
       </c>
       <c r="AE200" s="57"/>
       <c r="AG200" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH200" s="35">
         <f>AK205</f>
@@ -48689,7 +48692,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D201" s="52">
         <v>0</v>
@@ -48775,7 +48778,7 @@
       </c>
       <c r="AE201" s="57"/>
       <c r="AG201" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH201" s="36">
         <f>AL205</f>
@@ -48794,7 +48797,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -48881,7 +48884,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -48954,7 +48957,7 @@
       </c>
       <c r="AE203" s="57"/>
       <c r="AG203" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH203" s="36">
         <v>0</v>
@@ -48972,7 +48975,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -49059,7 +49062,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -49188,7 +49191,7 @@
         <v>Contracting</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D207" s="52">
         <v>0</v>
@@ -49275,7 +49278,7 @@
       </c>
       <c r="AE207" s="57"/>
       <c r="AG207" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH207" s="35">
         <f>AK212</f>
@@ -49294,7 +49297,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D208" s="52">
         <v>0</v>
@@ -49380,7 +49383,7 @@
       </c>
       <c r="AE208" s="57"/>
       <c r="AG208" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH208" s="36">
         <f>AL212</f>
@@ -49399,7 +49402,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -49486,7 +49489,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -49559,7 +49562,7 @@
       </c>
       <c r="AE210" s="57"/>
       <c r="AG210" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH210" s="36">
         <v>0</v>
@@ -49577,7 +49580,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -49664,7 +49667,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -49793,7 +49796,7 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D214" s="52">
         <v>0</v>
@@ -49880,7 +49883,7 @@
       </c>
       <c r="AE214" s="57"/>
       <c r="AG214" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH214" s="35">
         <f>AK219</f>
@@ -49899,7 +49902,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D215" s="52">
         <v>0</v>
@@ -49985,7 +49988,7 @@
       </c>
       <c r="AE215" s="57"/>
       <c r="AG215" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH215" s="36">
         <f>AL219</f>
@@ -50004,7 +50007,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -50091,7 +50094,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -50164,7 +50167,7 @@
       </c>
       <c r="AE217" s="57"/>
       <c r="AG217" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH217" s="36">
         <v>0</v>
@@ -50182,7 +50185,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -50269,7 +50272,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -50398,7 +50401,7 @@
         <v>Roydvale</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D221" s="52">
         <v>0</v>
@@ -50485,7 +50488,7 @@
       </c>
       <c r="AE221" s="57"/>
       <c r="AG221" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AH221" s="35">
         <f>AK226</f>
@@ -50504,7 +50507,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D222" s="52">
         <v>0</v>
@@ -50590,7 +50593,7 @@
       </c>
       <c r="AE222" s="57"/>
       <c r="AG222" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH222" s="36">
         <f>AL226</f>
@@ -50609,7 +50612,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -50696,7 +50699,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -50769,7 +50772,7 @@
       </c>
       <c r="AE224" s="57"/>
       <c r="AG224" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH224" s="36">
         <v>0</v>
@@ -50787,7 +50790,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -50874,7 +50877,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -51545,18 +51548,18 @@
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -51568,7 +51571,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -51579,7 +51582,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -51590,7 +51593,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6757,7 +6757,9 @@
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
       <c r="T32" s="16"/>
-      <c r="U32" s="1"/>
+      <c r="U32" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5974,18 +5974,30 @@
       <c r="K12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="13"/>
+      <c r="L12" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="M12" s="13" t="s">
         <v>27</v>
       </c>
       <c r="N12" s="14"/>
       <c r="O12" s="18"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="T12" s="16"/>
-      <c r="U12" s="1"/>
+      <c r="U12" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="226">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5798,8 +5798,12 @@
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
+      <c r="F8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">Major Hornbrook </t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>NA</t>
@@ -5804,7 +5801,9 @@
       <c r="G8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="13"/>
+      <c r="H8" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
@@ -6747,13 +6746,13 @@
         <v>27</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I32" s="13" t="s">
         <v>27</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>28</v>
@@ -6768,7 +6767,7 @@
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
@@ -6823,7 +6822,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>42</v>
@@ -6893,7 +6892,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -6961,7 +6960,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -7029,7 +7028,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
@@ -7097,7 +7096,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="13"/>
@@ -7165,7 +7164,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>42</v>
@@ -7247,7 +7246,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>42</v>
@@ -7339,7 +7338,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -7407,7 +7406,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="29"/>
       <c r="D50" s="29"/>
@@ -7475,7 +7474,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="29" t="s">
         <v>42</v>
@@ -7563,7 +7562,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="29" t="s">
         <v>42</v>
@@ -7633,7 +7632,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="29" t="s">
         <v>42</v>
@@ -7723,7 +7722,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="29" t="s">
         <v>42</v>
@@ -7881,7 +7880,7 @@
     <row r="62" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="27"/>
       <c r="B62" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="29"/>
       <c r="D62" s="29"/>
@@ -7949,7 +7948,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>26</v>
@@ -8019,7 +8018,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="29" t="s">
         <v>42</v>
@@ -9409,79 +9408,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="E2" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="I2" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="43" t="s">
+      <c r="P2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="43" t="s">
+      <c r="Q2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="R2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="40" t="s">
+      <c r="S2" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="44" t="s">
+      <c r="T2" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="44" t="s">
+      <c r="U2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="45" t="s">
+      <c r="V2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="40" t="s">
+      <c r="W2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="42" t="s">
+      <c r="X2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="46" t="s">
+      <c r="Y2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Z2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="AA2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AA2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9519,10 +9518,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AI3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9533,7 +9532,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>245679.5</v>
@@ -9607,7 +9606,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9623,7 +9622,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
@@ -9651,7 +9650,7 @@
       <c r="AA5" s="56"/>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9663,7 +9662,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9699,7 +9698,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -9727,7 +9726,7 @@
       <c r="AA7" s="56"/>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9739,7 +9738,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -9775,7 +9774,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9852,7 +9851,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="52">
         <v>129074.86</v>
@@ -9926,7 +9925,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -9942,7 +9941,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -10014,7 +10013,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10026,7 +10025,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10062,7 +10061,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="52"/>
       <c r="E14" s="62"/>
@@ -10090,7 +10089,7 @@
       <c r="AA14" s="56"/>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10102,7 +10101,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="62"/>
@@ -10138,7 +10137,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10215,7 +10214,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10289,7 +10288,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10305,7 +10304,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52">
         <v>27500.32</v>
@@ -10377,7 +10376,7 @@
       </c>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE19" s="36">
         <v>-5911.24</v>
@@ -10389,7 +10388,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
@@ -10425,7 +10424,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -10453,7 +10452,7 @@
       <c r="AA21" s="56"/>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE21" s="36">
         <v>0</v>
@@ -10465,7 +10464,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -10501,7 +10500,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -10578,7 +10577,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="55">
         <v>150850.82</v>
@@ -10654,7 +10653,7 @@
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE25" s="35">
         <v>-388.25</v>
@@ -10670,7 +10669,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="55">
         <v>150850.82</v>
@@ -10742,7 +10741,7 @@
       </c>
       <c r="AB26" s="57"/>
       <c r="AD26" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE26" s="36">
         <v>-56964.81</v>
@@ -10754,7 +10753,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="55"/>
@@ -10790,7 +10789,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="55"/>
       <c r="E28" s="55"/>
@@ -10818,7 +10817,7 @@
       <c r="AA28" s="56"/>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE28" s="36">
         <v>0</v>
@@ -10830,7 +10829,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="55"/>
@@ -10866,7 +10865,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="55"/>
@@ -10943,7 +10942,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="52">
         <v>396422.03</v>
@@ -11017,7 +11016,7 @@
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE32" s="35">
         <v>-387.5</v>
@@ -11033,7 +11032,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="52">
         <v>396422.03</v>
@@ -11105,7 +11104,7 @@
       </c>
       <c r="AB33" s="57"/>
       <c r="AD33" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE33" s="36">
         <v>-132316.71</v>
@@ -11117,7 +11116,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="52"/>
       <c r="E34" s="52"/>
@@ -11153,7 +11152,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -11181,7 +11180,7 @@
       <c r="AA35" s="56"/>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE35" s="36">
         <v>0</v>
@@ -11193,7 +11192,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -11229,7 +11228,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -11306,7 +11305,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="52">
         <v>128258.5</v>
@@ -11380,7 +11379,7 @@
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE39" s="35">
         <v>-112</v>
@@ -11396,7 +11395,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="52">
         <v>128258.5</v>
@@ -11468,7 +11467,7 @@
       </c>
       <c r="AB40" s="57"/>
       <c r="AD40" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE40" s="36">
         <v>-26847.46</v>
@@ -11480,7 +11479,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" s="52"/>
       <c r="E41" s="52"/>
@@ -11516,7 +11515,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -11544,7 +11543,7 @@
       <c r="AA42" s="56"/>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE42" s="36">
         <v>0</v>
@@ -11556,7 +11555,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -11592,7 +11591,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -11669,7 +11668,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="52">
         <v>65693.36</v>
@@ -11745,7 +11744,7 @@
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE46" s="35">
         <v>-86.75</v>
@@ -11761,7 +11760,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="52">
         <v>65693.36</v>
@@ -11833,7 +11832,7 @@
       </c>
       <c r="AB47" s="57"/>
       <c r="AD47" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE47" s="36">
         <v>-15639.05</v>
@@ -11845,7 +11844,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="52"/>
       <c r="E48" s="52"/>
@@ -11881,7 +11880,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52"/>
@@ -11909,7 +11908,7 @@
       <c r="AA49" s="56"/>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE49" s="36">
         <v>0</v>
@@ -11921,7 +11920,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52"/>
@@ -11957,7 +11956,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -12034,7 +12033,7 @@
         <v>37</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="52">
         <v>155296.79</v>
@@ -12108,7 +12107,7 @@
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE53" s="35">
         <v>-269</v>
@@ -12124,7 +12123,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="52">
         <v>155296.79</v>
@@ -12196,7 +12195,7 @@
       </c>
       <c r="AB54" s="57"/>
       <c r="AD54" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE54" s="36">
         <v>-66399.88</v>
@@ -12208,7 +12207,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="52"/>
       <c r="E55" s="52"/>
@@ -12244,7 +12243,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -12272,7 +12271,7 @@
       <c r="AA56" s="56"/>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE56" s="36">
         <v>0</v>
@@ -12284,7 +12283,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -12320,7 +12319,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -12397,7 +12396,7 @@
         <v>38</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="52">
         <v>20420.56</v>
@@ -12471,7 +12470,7 @@
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE60" s="35">
         <v>-26.75</v>
@@ -12487,7 +12486,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D61" s="52">
         <v>20420.56</v>
@@ -12559,7 +12558,7 @@
       </c>
       <c r="AB61" s="57"/>
       <c r="AD61" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE61" s="36">
         <v>-11159.14</v>
@@ -12571,7 +12570,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="52"/>
       <c r="E62" s="52"/>
@@ -12607,7 +12606,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -12635,7 +12634,7 @@
       <c r="AA63" s="56"/>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE63" s="36">
         <v>0</v>
@@ -12647,7 +12646,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -12683,7 +12682,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -12760,7 +12759,7 @@
         <v>39</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="52">
         <v>47801.68</v>
@@ -12832,7 +12831,7 @@
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE67" s="35"/>
       <c r="AH67" s="19"/>
@@ -12844,7 +12843,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="52">
         <v>47801.68</v>
@@ -12916,7 +12915,7 @@
       </c>
       <c r="AB68" s="57"/>
       <c r="AD68" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE68" s="36">
         <v>-5397.27</v>
@@ -12928,7 +12927,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -12964,7 +12963,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -12992,7 +12991,7 @@
       <c r="AA70" s="56"/>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE70" s="36">
         <v>0</v>
@@ -13004,7 +13003,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -13040,7 +13039,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -13115,7 +13114,7 @@
         <v>40</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="52">
         <v>77166.16</v>
@@ -13189,7 +13188,7 @@
       </c>
       <c r="AB74" s="57"/>
       <c r="AD74" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE74" s="35"/>
       <c r="AH74" s="19"/>
@@ -13199,7 +13198,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D75" s="52">
         <v>77166.16</v>
@@ -13271,7 +13270,7 @@
       </c>
       <c r="AB75" s="57"/>
       <c r="AD75" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE75" s="36"/>
       <c r="AH75" s="19"/>
@@ -13281,7 +13280,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="52"/>
       <c r="E76" s="52"/>
@@ -13317,7 +13316,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -13345,7 +13344,7 @@
       <c r="AA77" s="56"/>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE77" s="36">
         <v>0</v>
@@ -13357,7 +13356,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -13393,7 +13392,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -13466,7 +13465,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" s="52">
         <v>25467.84</v>
@@ -13540,7 +13539,7 @@
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE81" s="35">
         <v>-143.25</v>
@@ -13556,7 +13555,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="52">
         <v>25467.84</v>
@@ -13628,7 +13627,7 @@
       </c>
       <c r="AB82" s="57"/>
       <c r="AD82" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE82" s="36">
         <v>-5569.48</v>
@@ -13640,7 +13639,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -13676,7 +13675,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="52"/>
       <c r="E84" s="52"/>
@@ -13704,7 +13703,7 @@
       <c r="AA84" s="56"/>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE84" s="36">
         <v>0</v>
@@ -13716,7 +13715,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" s="52"/>
       <c r="E85" s="52"/>
@@ -13752,7 +13751,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
@@ -13829,7 +13828,7 @@
         <v>43</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="67">
         <v>37083.03</v>
@@ -13903,7 +13902,7 @@
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE88" s="35">
         <v>-148.5</v>
@@ -13919,7 +13918,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D89" s="67">
         <v>37083.03</v>
@@ -13991,7 +13990,7 @@
       </c>
       <c r="AB89" s="57"/>
       <c r="AD89" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE89" s="36">
         <v>-14143.19</v>
@@ -14003,7 +14002,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="67"/>
       <c r="E90" s="67"/>
@@ -14039,7 +14038,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="67"/>
       <c r="E91" s="67"/>
@@ -14067,7 +14066,7 @@
       <c r="AA91" s="56"/>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE91" s="36">
         <v>0</v>
@@ -14079,7 +14078,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="67"/>
       <c r="E92" s="67"/>
@@ -14115,7 +14114,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="67"/>
       <c r="E93" s="67"/>
@@ -14192,7 +14191,7 @@
         <v>44</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D95" s="52">
         <v>26186.14</v>
@@ -14266,7 +14265,7 @@
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE95" s="35">
         <v>-5</v>
@@ -14282,7 +14281,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="52">
         <v>26186.14</v>
@@ -14354,7 +14353,7 @@
       </c>
       <c r="AB96" s="57"/>
       <c r="AD96" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE96" s="36">
         <v>-7679.91</v>
@@ -14366,7 +14365,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="52"/>
@@ -14402,7 +14401,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" s="52"/>
       <c r="E98" s="52"/>
@@ -14430,7 +14429,7 @@
       <c r="AA98" s="56"/>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE98" s="36">
         <v>0</v>
@@ -14442,7 +14441,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" s="52"/>
       <c r="E99" s="52"/>
@@ -14478,7 +14477,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -14555,7 +14554,7 @@
         <v>45</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="52">
         <v>32473.02</v>
@@ -14629,7 +14628,7 @@
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE102" s="35">
         <v>-317.25</v>
@@ -14645,7 +14644,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D103" s="52">
         <v>32473.02</v>
@@ -14717,7 +14716,7 @@
       </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE103" s="36">
         <v>-16562.52</v>
@@ -14729,7 +14728,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="52"/>
       <c r="E104" s="69"/>
@@ -14765,7 +14764,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105" s="52"/>
       <c r="E105" s="69"/>
@@ -14793,7 +14792,7 @@
       <c r="AA105" s="56"/>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE105" s="36">
         <v>0</v>
@@ -14805,7 +14804,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D106" s="52"/>
       <c r="E106" s="69"/>
@@ -14841,7 +14840,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="67"/>
@@ -14915,10 +14914,10 @@
         <v>8840</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="52">
         <v>58902.56</v>
@@ -14994,7 +14993,7 @@
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE109" s="35">
         <v>-204.75</v>
@@ -15010,7 +15009,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D110" s="52">
         <v>58902.56</v>
@@ -15082,7 +15081,7 @@
       </c>
       <c r="AB110" s="57"/>
       <c r="AD110" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE110" s="36">
         <v>-12155.27</v>
@@ -15094,7 +15093,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="52"/>
       <c r="E111" s="52"/>
@@ -15130,7 +15129,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="52"/>
       <c r="E112" s="52"/>
@@ -15158,7 +15157,7 @@
       <c r="AA112" s="56"/>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE112" s="36">
         <v>0</v>
@@ -15170,7 +15169,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" s="52"/>
       <c r="E113" s="52"/>
@@ -15206,7 +15205,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D114" s="52"/>
       <c r="E114" s="52"/>
@@ -15280,10 +15279,10 @@
         <v>8769</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="52">
         <v>21404.82</v>
@@ -15359,7 +15358,7 @@
       </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE116" s="35"/>
       <c r="AH116" s="19"/>
@@ -15369,7 +15368,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="52">
         <v>21404.82</v>
@@ -15441,7 +15440,7 @@
       </c>
       <c r="AB117" s="57"/>
       <c r="AD117" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE117" s="36"/>
       <c r="AH117" s="19"/>
@@ -15451,7 +15450,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="52"/>
       <c r="E118" s="52"/>
@@ -15487,7 +15486,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="52"/>
       <c r="E119" s="52"/>
@@ -15515,7 +15514,7 @@
       <c r="AA119" s="56"/>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE119" s="36">
         <v>0</v>
@@ -15527,7 +15526,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D120" s="52"/>
       <c r="E120" s="52"/>
@@ -15563,7 +15562,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D121" s="52"/>
       <c r="E121" s="52"/>
@@ -15633,10 +15632,10 @@
         <v>7901</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D123" s="52">
         <v>100987.51</v>
@@ -15708,7 +15707,7 @@
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE123" s="35"/>
       <c r="AH123" s="19"/>
@@ -15720,7 +15719,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="52">
         <v>100987.51</v>
@@ -15792,7 +15791,7 @@
       </c>
       <c r="AB124" s="57"/>
       <c r="AD124" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE124" s="36">
         <v>-12186.08</v>
@@ -15804,7 +15803,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D125" s="52"/>
       <c r="E125" s="52"/>
@@ -15840,7 +15839,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="52"/>
       <c r="E126" s="52"/>
@@ -15868,7 +15867,7 @@
       <c r="AA126" s="56"/>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE126" s="36">
         <v>0</v>
@@ -15880,7 +15879,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D127" s="52"/>
       <c r="E127" s="52"/>
@@ -15916,7 +15915,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="52"/>
       <c r="E128" s="52"/>
@@ -15988,10 +15987,10 @@
         <v>8923</v>
       </c>
       <c r="B130" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D130" s="52">
         <v>31802.41</v>
@@ -16065,7 +16064,7 @@
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE130" s="35">
         <v>-2</v>
@@ -16081,7 +16080,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="52">
         <v>31802.41</v>
@@ -16153,7 +16152,7 @@
       </c>
       <c r="AB131" s="57"/>
       <c r="AD131" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE131" s="36">
         <v>-11154.51</v>
@@ -16165,7 +16164,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="52"/>
       <c r="E132" s="52"/>
@@ -16200,7 +16199,7 @@
     <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="52"/>
       <c r="E133" s="52"/>
@@ -16228,7 +16227,7 @@
       <c r="AA133" s="56"/>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE133" s="36">
         <v>0</v>
@@ -16240,7 +16239,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D134" s="52"/>
       <c r="E134" s="52"/>
@@ -16276,7 +16275,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D135" s="52"/>
       <c r="E135" s="52"/>
@@ -16350,10 +16349,10 @@
         <v>7864</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D137" s="52">
         <v>30749.24</v>
@@ -16427,7 +16426,7 @@
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE137" s="35">
         <v>-266.75</v>
@@ -16443,7 +16442,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D138" s="52">
         <v>30749.24</v>
@@ -16515,7 +16514,7 @@
       </c>
       <c r="AB138" s="57"/>
       <c r="AD138" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE138" s="36">
         <v>-11702.32</v>
@@ -16527,7 +16526,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" s="52"/>
       <c r="E139" s="52"/>
@@ -16563,7 +16562,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D140" s="52"/>
       <c r="E140" s="52"/>
@@ -16591,7 +16590,7 @@
       <c r="AA140" s="56"/>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE140" s="36">
         <v>0</v>
@@ -16603,7 +16602,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D141" s="52"/>
       <c r="E141" s="52"/>
@@ -16639,7 +16638,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="52"/>
       <c r="E142" s="52"/>
@@ -16713,10 +16712,10 @@
         <v>7912</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D144" s="52">
         <v>268228.26</v>
@@ -16788,7 +16787,7 @@
       </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE144" s="35"/>
       <c r="AH144" s="19"/>
@@ -16798,7 +16797,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D145" s="52">
         <v>268228.26</v>
@@ -16870,7 +16869,7 @@
       </c>
       <c r="AB145" s="57"/>
       <c r="AD145" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE145" s="36"/>
       <c r="AH145" s="19"/>
@@ -16880,7 +16879,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" s="52"/>
       <c r="E146" s="52"/>
@@ -16916,7 +16915,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D147" s="52"/>
       <c r="E147" s="52"/>
@@ -16944,7 +16943,7 @@
       <c r="AA147" s="56"/>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE147" s="36">
         <v>0</v>
@@ -16956,7 +16955,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D148" s="52"/>
       <c r="E148" s="52"/>
@@ -16992,7 +16991,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D149" s="52"/>
       <c r="E149" s="52"/>
@@ -17062,10 +17061,10 @@
         <v>8360</v>
       </c>
       <c r="B151" s="74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="52">
         <v>32773.41</v>
@@ -17137,7 +17136,7 @@
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE151" s="35">
         <v>-260.75</v>
@@ -17153,7 +17152,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D152" s="52">
         <v>32773.41</v>
@@ -17225,7 +17224,7 @@
       </c>
       <c r="AB152" s="57"/>
       <c r="AD152" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE152" s="36">
         <v>-9324.41</v>
@@ -17237,7 +17236,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153" s="52"/>
       <c r="E153" s="52"/>
@@ -17273,7 +17272,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D154" s="52"/>
       <c r="E154" s="52"/>
@@ -17301,7 +17300,7 @@
       <c r="AA154" s="56"/>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE154" s="36">
         <v>0</v>
@@ -17313,7 +17312,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -17349,7 +17348,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -17423,10 +17422,10 @@
         <v>8337</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158" s="52">
         <v>17899.33</v>
@@ -17498,7 +17497,7 @@
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE158" s="35">
         <v>-44.75</v>
@@ -17512,7 +17511,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D159" s="52">
         <v>17899.33</v>
@@ -17584,7 +17583,7 @@
       </c>
       <c r="AB159" s="57"/>
       <c r="AD159" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE159" s="36"/>
       <c r="AH159" s="19"/>
@@ -17594,7 +17593,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -17630,7 +17629,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -17658,7 +17657,7 @@
       <c r="AA161" s="56"/>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE161" s="36">
         <v>0</v>
@@ -17670,7 +17669,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -17706,7 +17705,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -17778,10 +17777,10 @@
         <v>9240</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D165" s="52">
         <v>10827.2</v>
@@ -17801,7 +17800,7 @@
         <v>4388.87</v>
       </c>
       <c r="K165" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L165" s="52">
         <v>4388.87</v>
@@ -17841,7 +17840,7 @@
       </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE165" s="35"/>
       <c r="AH165" s="19"/>
@@ -17851,7 +17850,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D166" s="52">
         <v>10827.2</v>
@@ -17923,7 +17922,7 @@
       </c>
       <c r="AB166" s="57"/>
       <c r="AD166" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE166" s="36"/>
       <c r="AH166" s="19"/>
@@ -17933,7 +17932,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="52"/>
       <c r="E167" s="52"/>
@@ -17969,7 +17968,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D168" s="52"/>
       <c r="E168" s="52"/>
@@ -17997,7 +17996,7 @@
       <c r="AA168" s="56"/>
       <c r="AB168" s="57"/>
       <c r="AD168" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE168" s="36">
         <v>0</v>
@@ -18009,7 +18008,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
@@ -18045,7 +18044,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
@@ -18115,10 +18114,10 @@
         <v>7428</v>
       </c>
       <c r="B172" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="52">
         <v>146237.11</v>
@@ -18190,7 +18189,7 @@
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE172" s="35">
         <v>-304.75</v>
@@ -18204,7 +18203,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="52">
         <v>146237.11</v>
@@ -18276,7 +18275,7 @@
       </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE173" s="36"/>
       <c r="AH173" s="19"/>
@@ -18286,7 +18285,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D174" s="52"/>
       <c r="E174" s="52"/>
@@ -18322,7 +18321,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D175" s="52"/>
       <c r="E175" s="52"/>
@@ -18350,7 +18349,7 @@
       <c r="AA175" s="56"/>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE175" s="36">
         <v>0</v>
@@ -18362,7 +18361,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D176" s="52"/>
       <c r="E176" s="52"/>
@@ -18398,7 +18397,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="52"/>
       <c r="E177" s="52"/>
@@ -18472,10 +18471,10 @@
         <v>9351</v>
       </c>
       <c r="B179" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="52">
         <v>16897.53</v>
@@ -18547,7 +18546,7 @@
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE179" s="35">
         <v>-11.25</v>
@@ -18563,7 +18562,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D180" s="52"/>
       <c r="E180" s="52"/>
@@ -18591,7 +18590,7 @@
       <c r="AA180" s="56"/>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE180" s="36">
         <v>-2298.71</v>
@@ -18603,7 +18602,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="52"/>
       <c r="E181" s="52"/>
@@ -18639,7 +18638,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
@@ -18667,7 +18666,7 @@
       <c r="AA182" s="56"/>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE182" s="36">
         <v>0</v>
@@ -18679,7 +18678,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D183" s="52"/>
       <c r="E183" s="52"/>
@@ -18715,7 +18714,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
@@ -18789,10 +18788,10 @@
         <v>7429</v>
       </c>
       <c r="B186" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D186" s="52">
         <v>20992.12</v>
@@ -18864,7 +18863,7 @@
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE186" s="35">
         <v>-32.25</v>
@@ -18878,7 +18877,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="52">
         <v>20992.12</v>
@@ -18950,7 +18949,7 @@
       </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE187" s="36"/>
       <c r="AH187" s="19"/>
@@ -18960,7 +18959,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="52"/>
       <c r="E188" s="52"/>
@@ -18996,7 +18995,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D189" s="52"/>
       <c r="E189" s="52"/>
@@ -19024,7 +19023,7 @@
       <c r="AA189" s="56"/>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE189" s="36">
         <v>0</v>
@@ -19036,7 +19035,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D190" s="52"/>
       <c r="E190" s="52"/>
@@ -19072,7 +19071,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D191" s="52"/>
       <c r="E191" s="52"/>
@@ -19144,10 +19143,10 @@
         <v>9508</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D193" s="52">
         <v>23770.95</v>
@@ -19219,7 +19218,7 @@
       </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE193" s="35"/>
       <c r="AH193" s="19"/>
@@ -19229,7 +19228,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D194" s="52">
         <v>23770.95</v>
@@ -19301,7 +19300,7 @@
       </c>
       <c r="AB194" s="57"/>
       <c r="AD194" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE194" s="36"/>
       <c r="AH194" s="19"/>
@@ -19311,7 +19310,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" s="52"/>
       <c r="E195" s="52"/>
@@ -19347,7 +19346,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D196" s="52"/>
       <c r="E196" s="52"/>
@@ -19375,7 +19374,7 @@
       <c r="AA196" s="56"/>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE196" s="36">
         <v>0</v>
@@ -19387,7 +19386,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D197" s="52"/>
       <c r="E197" s="52"/>
@@ -19423,7 +19422,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D198" s="52"/>
       <c r="E198" s="52"/>
@@ -19492,7 +19491,7 @@
       <c r="A200" s="19"/>
       <c r="B200" s="19"/>
       <c r="C200" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -19540,7 +19539,7 @@
       <c r="AA200" s="56"/>
       <c r="AB200" s="57"/>
       <c r="AD200" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE200" s="35"/>
       <c r="AH200" s="19"/>
@@ -19550,7 +19549,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D201" s="52"/>
       <c r="E201" s="52"/>
@@ -19582,7 +19581,7 @@
       <c r="AA201" s="56"/>
       <c r="AB201" s="57"/>
       <c r="AD201" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE201" s="36"/>
       <c r="AH201" s="19"/>
@@ -19592,7 +19591,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -19632,7 +19631,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -19664,7 +19663,7 @@
       <c r="AA203" s="56"/>
       <c r="AB203" s="57"/>
       <c r="AD203" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE203" s="36">
         <v>0</v>
@@ -19676,7 +19675,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -19716,7 +19715,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -19788,10 +19787,10 @@
     <row r="207" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A207" s="19"/>
       <c r="B207" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D207" s="52"/>
       <c r="E207" s="52"/>
@@ -19823,7 +19822,7 @@
       <c r="AA207" s="56"/>
       <c r="AB207" s="57"/>
       <c r="AD207" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE207" s="35"/>
       <c r="AH207" s="19"/>
@@ -19833,7 +19832,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D208" s="52"/>
       <c r="E208" s="52"/>
@@ -19865,7 +19864,7 @@
       <c r="AA208" s="56"/>
       <c r="AB208" s="57"/>
       <c r="AD208" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE208" s="36"/>
       <c r="AH208" s="19"/>
@@ -19875,7 +19874,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -19915,7 +19914,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -19947,7 +19946,7 @@
       <c r="AA210" s="56"/>
       <c r="AB210" s="57"/>
       <c r="AD210" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE210" s="36">
         <v>0</v>
@@ -19959,7 +19958,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -19999,7 +19998,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -20073,10 +20072,10 @@
         <v>8946</v>
       </c>
       <c r="B214" s="77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D214" s="52">
         <v>137109.56</v>
@@ -20148,7 +20147,7 @@
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE214" s="35"/>
       <c r="AH214" s="19"/>
@@ -20158,7 +20157,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D215" s="52">
         <v>137109.56</v>
@@ -20230,7 +20229,7 @@
       </c>
       <c r="AB215" s="57"/>
       <c r="AD215" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE215" s="36"/>
       <c r="AH215" s="19"/>
@@ -20240,7 +20239,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -20276,7 +20275,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -20304,7 +20303,7 @@
       <c r="AA217" s="56"/>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE217" s="36">
         <v>0</v>
@@ -20316,7 +20315,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -20352,7 +20351,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -20422,10 +20421,10 @@
         <v>8308</v>
       </c>
       <c r="B221" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D221" s="52">
         <v>396453.46</v>
@@ -20497,7 +20496,7 @@
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE221" s="35">
         <v>-1014.25</v>
@@ -20511,7 +20510,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D222" s="52">
         <v>396453.46</v>
@@ -20583,7 +20582,7 @@
       </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE222" s="36"/>
       <c r="AH222" s="19"/>
@@ -20593,7 +20592,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -20629,7 +20628,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -20657,7 +20656,7 @@
       <c r="AA224" s="56"/>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE224" s="36">
         <v>0</v>
@@ -20669,7 +20668,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -20705,7 +20704,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -21345,49 +21344,49 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="C2" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="D2" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="E2" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="F2" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="H2" s="83" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="83" t="s">
+      <c r="I2" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="J2" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="J2" s="82" t="s">
+      <c r="K2" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="L2" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="83" t="s">
+      <c r="M2" s="83" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="83" t="s">
+      <c r="N2" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="N2" s="81" t="s">
+      <c r="O2" s="84" t="s">
         <v>114</v>
-      </c>
-      <c r="O2" s="84" t="s">
-        <v>115</v>
       </c>
       <c r="P2" s="35"/>
     </row>
@@ -21520,7 +21519,7 @@
         <v>337.89039999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21669,7 +21668,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="52">
         <v>0</v>
@@ -21711,7 +21710,7 @@
         <v>-93.95999999999987</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -21904,7 +21903,7 @@
         <v>44.85015873015877</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -22343,7 +22342,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="52">
         <v>0</v>
@@ -22405,7 +22404,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="52">
         <v>0</v>
@@ -22465,7 +22464,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="52">
         <v>52040.560000000005</v>
@@ -22523,7 +22522,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="52">
         <v>2127.8099999999995</v>
@@ -22585,7 +22584,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="52">
         <v>0</v>
@@ -22645,7 +22644,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="52">
         <v>0</v>
@@ -22699,7 +22698,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="99">
         <v>0</v>
@@ -22757,7 +22756,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="98" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="99">
         <v>0</v>
@@ -22817,7 +22816,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="99">
         <v>0</v>
@@ -22851,7 +22850,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -22876,7 +22875,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="99">
         <v>0</v>
@@ -22938,7 +22937,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="98" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="99">
         <v>0</v>
@@ -23000,7 +22999,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="99">
         <v>0</v>
@@ -23062,7 +23061,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="98" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="99">
         <v>0</v>
@@ -23148,7 +23147,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="99"/>
       <c r="D62" s="99"/>
@@ -23188,7 +23187,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="99">
         <v>0</v>
@@ -23246,7 +23245,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="99">
         <v>34650.399999999965</v>
@@ -23322,10 +23321,10 @@
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="103" t="s">
         <v>121</v>
-      </c>
-      <c r="B69" s="103" t="s">
-        <v>122</v>
       </c>
       <c r="C69" s="104">
         <v>88818.76999999996</v>
@@ -23337,13 +23336,13 @@
         <v>58931.02999999998</v>
       </c>
       <c r="F69" s="106" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G69" s="107">
         <v>0.6634974791927427</v>
       </c>
       <c r="H69" s="108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I69" s="109">
         <v>0.0799203816940944</v>
@@ -23358,7 +23357,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C70" s="99">
         <v>-22865.6</v>
@@ -23374,7 +23373,7 @@
         <v>2.433333916450914</v>
       </c>
       <c r="H70" s="113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I70" s="114">
         <v>2.685240710936954</v>
@@ -23773,52 +23772,52 @@
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="D2" s="117" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="117" t="s">
+      <c r="E2" s="117" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="117" t="s">
+      <c r="F2" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="117" t="s">
+      <c r="G2" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="H2" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="I2" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="J2" s="117" t="s">
         <v>133</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="K2" s="117" t="s">
         <v>134</v>
       </c>
-      <c r="K2" s="117" t="s">
+      <c r="L2" s="117" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="117" t="s">
+      <c r="M2" s="117" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="117" t="s">
+      <c r="N2" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="N2" s="117" t="s">
+      <c r="O2" s="117" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="117" t="s">
+      <c r="P2" s="117" t="s">
         <v>139</v>
       </c>
-      <c r="P2" s="117" t="s">
+      <c r="Q2" s="118" t="s">
         <v>140</v>
-      </c>
-      <c r="Q2" s="118" t="s">
-        <v>141</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -23834,10 +23833,10 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="123" t="s">
         <v>142</v>
-      </c>
-      <c r="B3" s="123" t="s">
-        <v>143</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -23921,7 +23920,7 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -23974,7 +23973,7 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24027,7 +24026,7 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24084,7 +24083,7 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24111,7 +24110,7 @@
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -24141,7 +24140,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24198,7 +24197,7 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -24689,7 +24688,7 @@
         <v>8840</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="54">
         <v>324.19</v>
@@ -24739,7 +24738,7 @@
         <v>8769</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="54">
         <v>84.05</v>
@@ -24791,7 +24790,7 @@
         <v>7901</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" s="54">
         <v>290.15</v>
@@ -24846,7 +24845,7 @@
         <v>8923</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="54">
         <v>156.69</v>
@@ -24900,7 +24899,7 @@
         <v>7864</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="54">
         <v>200.82</v>
@@ -24949,7 +24948,7 @@
         <v>7912</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="54">
         <v>497.55</v>
@@ -25008,7 +25007,7 @@
         <v>8360</v>
       </c>
       <c r="B46" s="75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="54">
         <v>210.6</v>
@@ -25056,7 +25055,7 @@
         <v>8337</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="54">
         <v>110.44</v>
@@ -25108,7 +25107,7 @@
         <v>9240</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="54">
         <v>65.13</v>
@@ -25160,7 +25159,7 @@
         <v>7428</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="54">
         <v>659.73</v>
@@ -25215,7 +25214,7 @@
         <v>9351</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="54">
         <v>125.17</v>
@@ -25270,7 +25269,7 @@
         <v>7429</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="54">
         <v>130.62</v>
@@ -25323,7 +25322,7 @@
         <v>9508</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="54">
         <v>140.15</v>
@@ -25413,7 +25412,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C62" s="54"/>
       <c r="D62" s="54"/>
@@ -25455,7 +25454,7 @@
         <v>8946</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C64" s="54">
         <v>358.86</v>
@@ -25507,7 +25506,7 @@
         <v>8308</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="54">
         <v>2344.68</v>
@@ -25601,7 +25600,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C70" s="147"/>
       <c r="D70" s="147"/>
@@ -25646,7 +25645,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
@@ -25685,7 +25684,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C72" s="20">
         <v>4490.26</v>
@@ -25714,7 +25713,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
@@ -25759,7 +25758,7 @@
     <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C74" s="152"/>
       <c r="D74" s="152"/>
@@ -25823,10 +25822,10 @@
     <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="157" t="s">
         <v>151</v>
-      </c>
-      <c r="C76" s="157" t="s">
-        <v>152</v>
       </c>
       <c r="D76" s="157"/>
       <c r="E76" s="157"/>
@@ -25870,7 +25869,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C77" s="157"/>
       <c r="D77" s="157"/>
@@ -25934,7 +25933,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C79" s="165"/>
       <c r="D79" s="35"/>
@@ -25946,7 +25945,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="166" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M79" s="166"/>
       <c r="N79" s="35"/>
@@ -25957,7 +25956,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C80" s="168">
         <v>1</v>
@@ -25980,7 +25979,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C81" s="131">
         <v>1</v>
@@ -26003,7 +26002,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -26026,7 +26025,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -26049,7 +26048,7 @@
     <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -26072,7 +26071,7 @@
     <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C85" s="131">
         <v>0.5</v>
@@ -26095,7 +26094,7 @@
     <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C86" s="131">
         <v>1</v>
@@ -26118,7 +26117,7 @@
     <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -26141,7 +26140,7 @@
     <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -26164,7 +26163,7 @@
     <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C89" s="131">
         <v>0</v>
@@ -26187,7 +26186,7 @@
     <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C90" s="131">
         <v>1</v>
@@ -26357,7 +26356,7 @@
     <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C98" s="131">
         <v>1</v>
@@ -26380,7 +26379,7 @@
     <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -26403,7 +26402,7 @@
     <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -26426,7 +26425,7 @@
     <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -26449,7 +26448,7 @@
     <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -26472,7 +26471,7 @@
     <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -26495,7 +26494,7 @@
     <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -26594,7 +26593,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C109" s="170">
         <v>16.5</v>
@@ -26670,7 +26669,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -26702,7 +26701,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -26735,7 +26734,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -26768,7 +26767,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -26801,7 +26800,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -26834,7 +26833,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -26867,7 +26866,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -26900,7 +26899,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -26995,7 +26994,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -27028,7 +27027,7 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -27061,7 +27060,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -27094,7 +27093,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -27127,7 +27126,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -27160,7 +27159,7 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -27193,7 +27192,7 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -27226,7 +27225,7 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -27259,7 +27258,7 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -27292,7 +27291,7 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -27325,7 +27324,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -27358,7 +27357,7 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -27391,7 +27390,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -27424,7 +27423,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -27457,7 +27456,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -27490,7 +27489,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -27523,7 +27522,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -27555,7 +27554,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -27587,7 +27586,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -27619,7 +27618,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -27651,7 +27650,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -27743,7 +27742,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -27775,7 +27774,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -27807,7 +27806,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -27839,7 +27838,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -27871,7 +27870,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -27933,7 +27932,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -27965,7 +27964,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -27997,7 +27996,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -28029,7 +28028,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -28181,7 +28180,7 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -28213,7 +28212,7 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -28493,7 +28492,7 @@
   <sheetData>
     <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -29594,7 +29593,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -29626,7 +29625,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -29961,88 +29960,88 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="E2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="F2" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="I2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="J2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="N2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="42" t="s">
+      <c r="O2" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="P2" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q2" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="R2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="P2" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q2" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="R2" s="43" t="s">
+      <c r="S2" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="43" t="s">
+      <c r="T2" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="U2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="V2" s="214" t="s">
         <v>79</v>
       </c>
-      <c r="V2" s="214" t="s">
+      <c r="W2" s="214" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="214" t="s">
+      <c r="X2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="X2" s="45" t="s">
+      <c r="Y2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="40" t="s">
+      <c r="Z2" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="42" t="s">
+      <c r="AA2" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="AA2" s="46" t="s">
+      <c r="AB2" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="AB2" s="47" t="s">
+      <c r="AC2" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="AC2" s="46" t="s">
+      <c r="AD2" s="48" t="s">
         <v>87</v>
-      </c>
-      <c r="AD2" s="48" t="s">
-        <v>88</v>
       </c>
       <c r="AG2" s="35"/>
       <c r="AH2" s="35"/>
@@ -30083,10 +30082,10 @@
       <c r="AG3" s="35"/>
       <c r="AH3" s="35"/>
       <c r="AK3" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL3" s="50" t="s">
         <v>89</v>
-      </c>
-      <c r="AL3" s="50" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -30099,7 +30098,7 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" s="52">
         <v>1914143.52</v>
@@ -30195,7 +30194,7 @@
       </c>
       <c r="AE4" s="57"/>
       <c r="AG4" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH4" s="35">
         <f>AK9</f>
@@ -30214,7 +30213,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" s="52">
         <v>1922479.92</v>
@@ -30303,7 +30302,7 @@
       </c>
       <c r="AE5" s="57"/>
       <c r="AG5" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH5" s="36">
         <f>AL9</f>
@@ -30322,7 +30321,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52">
         <v>1922479.92</v>
@@ -30429,7 +30428,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -30502,7 +30501,7 @@
       </c>
       <c r="AE7" s="57"/>
       <c r="AG7" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH7" s="36">
         <v>0</v>
@@ -30520,7 +30519,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -30607,7 +30606,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -30736,7 +30735,7 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="65">
         <v>381671.63</v>
@@ -30825,7 +30824,7 @@
       </c>
       <c r="AE11" s="57"/>
       <c r="AG11" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH11" s="35">
         <f>AK16</f>
@@ -30844,7 +30843,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" s="52">
         <v>382219.49</v>
@@ -30933,7 +30932,7 @@
       </c>
       <c r="AE12" s="57"/>
       <c r="AG12" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH12" s="36">
         <f>AL16</f>
@@ -30952,7 +30951,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D13" s="52">
         <v>382219.49</v>
@@ -31055,7 +31054,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="65">
         <v>383409.63</v>
@@ -31136,7 +31135,7 @@
       </c>
       <c r="AE14" s="57"/>
       <c r="AG14" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH14" s="36">
         <v>0</v>
@@ -31154,7 +31153,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D15" s="65">
         <v>383409.63</v>
@@ -31243,7 +31242,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="65">
         <v>383409.63</v>
@@ -31377,7 +31376,7 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" s="52">
         <v>449818.08</v>
@@ -31470,7 +31469,7 @@
       </c>
       <c r="AE18" s="57"/>
       <c r="AG18" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH18" s="35">
         <f>AK23</f>
@@ -31489,7 +31488,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="52">
         <v>449818.08</v>
@@ -31580,7 +31579,7 @@
       </c>
       <c r="AE19" s="57"/>
       <c r="AG19" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH19" s="36">
         <f>AL23</f>
@@ -31599,7 +31598,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="52">
         <v>449818.08</v>
@@ -31704,7 +31703,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -31779,7 +31778,7 @@
       </c>
       <c r="AE21" s="57"/>
       <c r="AG21" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH21" s="36">
         <v>0</v>
@@ -31797,7 +31796,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -31886,7 +31885,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -32019,7 +32018,7 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="52">
         <v>38856.96</v>
@@ -32112,7 +32111,7 @@
       </c>
       <c r="AE25" s="57"/>
       <c r="AG25" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH25" s="35">
         <f>AK30</f>
@@ -32131,7 +32130,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="52">
         <v>38856.96</v>
@@ -32224,7 +32223,7 @@
       </c>
       <c r="AE26" s="57"/>
       <c r="AG26" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH26" s="36">
         <f>AL30</f>
@@ -32243,7 +32242,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D27" s="52">
         <v>38856.96</v>
@@ -32350,7 +32349,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52">
@@ -32433,7 +32432,7 @@
       </c>
       <c r="AE28" s="57"/>
       <c r="AG28" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH28" s="36">
         <v>0</v>
@@ -32451,7 +32450,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -32548,7 +32547,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -32687,7 +32686,7 @@
         <v>Murney - 1 Freight Drive + 109 Iport</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D32" s="52">
         <v>69191.71</v>
@@ -32778,7 +32777,7 @@
       </c>
       <c r="AE32" s="57"/>
       <c r="AG32" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH32" s="35">
         <f>AK37</f>
@@ -32797,7 +32796,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="52">
         <v>69191.71</v>
@@ -32886,7 +32885,7 @@
       </c>
       <c r="AE33" s="57"/>
       <c r="AG33" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH33" s="36">
         <f>AL37</f>
@@ -32905,7 +32904,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" s="52">
         <v>69191.71</v>
@@ -33008,7 +33007,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -33081,7 +33080,7 @@
       </c>
       <c r="AE35" s="57"/>
       <c r="AG35" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH35" s="36">
         <v>0</v>
@@ -33099,7 +33098,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -33186,7 +33185,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -33315,7 +33314,7 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="52">
         <v>44956.29</v>
@@ -33402,7 +33401,7 @@
       </c>
       <c r="AE39" s="57"/>
       <c r="AG39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH39" s="35">
         <f>AK44</f>
@@ -33421,7 +33420,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="52">
         <v>44956.29</v>
@@ -33506,7 +33505,7 @@
       </c>
       <c r="AE40" s="57"/>
       <c r="AG40" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH40" s="36">
         <f>AL44</f>
@@ -33525,7 +33524,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D41" s="52">
         <v>44956.29</v>
@@ -33628,7 +33627,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -33705,7 +33704,7 @@
       </c>
       <c r="AE42" s="57"/>
       <c r="AG42" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH42" s="36">
         <v>0</v>
@@ -33723,7 +33722,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -33814,7 +33813,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -33947,7 +33946,7 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="52">
         <v>7495.54</v>
@@ -34040,7 +34039,7 @@
       </c>
       <c r="AE46" s="57"/>
       <c r="AG46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH46" s="35">
         <f>AK51</f>
@@ -34059,7 +34058,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="52">
         <v>7495.54</v>
@@ -34152,7 +34151,7 @@
       </c>
       <c r="AE47" s="57"/>
       <c r="AG47" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH47" s="36">
         <f>AL51</f>
@@ -34171,7 +34170,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D48" s="52">
         <v>7495.54</v>
@@ -34278,7 +34277,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52">
@@ -34359,7 +34358,7 @@
       </c>
       <c r="AE49" s="57"/>
       <c r="AG49" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH49" s="36">
         <v>0</v>
@@ -34377,7 +34376,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52">
@@ -34472,7 +34471,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52">
@@ -34609,7 +34608,7 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D53" s="52">
         <v>100348.26</v>
@@ -34702,7 +34701,7 @@
       </c>
       <c r="AE53" s="57"/>
       <c r="AG53" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH53" s="35">
         <f>AK58</f>
@@ -34721,7 +34720,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D54" s="52">
         <v>100348.26</v>
@@ -34810,7 +34809,7 @@
       </c>
       <c r="AE54" s="57"/>
       <c r="AG54" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH54" s="36">
         <f>AL58</f>
@@ -34829,7 +34828,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D55" s="52">
         <v>100348.26</v>
@@ -34932,7 +34931,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -35005,7 +35004,7 @@
       </c>
       <c r="AE56" s="57"/>
       <c r="AG56" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH56" s="36">
         <v>0</v>
@@ -35023,7 +35022,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -35110,7 +35109,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -35243,7 +35242,7 @@
         <v>35 Mania</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" s="52">
         <v>98524.85</v>
@@ -35334,7 +35333,7 @@
       </c>
       <c r="AE60" s="57"/>
       <c r="AG60" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH60" s="35">
         <f>AK65</f>
@@ -35353,7 +35352,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D61" s="52">
         <v>98524.85</v>
@@ -35444,7 +35443,7 @@
       </c>
       <c r="AE61" s="57"/>
       <c r="AG61" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH61" s="36">
         <f>AL65</f>
@@ -35463,7 +35462,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="52">
         <v>98524.85</v>
@@ -35568,7 +35567,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -35645,7 +35644,7 @@
       </c>
       <c r="AE63" s="57"/>
       <c r="AG63" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH63" s="36">
         <v>0</v>
@@ -35663,7 +35662,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -35754,7 +35753,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -35887,7 +35886,7 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="52">
         <v>87970.61</v>
@@ -35976,7 +35975,7 @@
       </c>
       <c r="AE67" s="57"/>
       <c r="AG67" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH67" s="35">
         <f>AK72</f>
@@ -35995,7 +35994,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="52">
         <v>87970.61</v>
@@ -36086,7 +36085,7 @@
       </c>
       <c r="AE68" s="57"/>
       <c r="AG68" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH68" s="36">
         <f>AL72</f>
@@ -36105,7 +36104,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -36194,7 +36193,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -36269,7 +36268,7 @@
       </c>
       <c r="AE70" s="57"/>
       <c r="AG70" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH70" s="36">
         <v>0</v>
@@ -36287,7 +36286,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -36376,7 +36375,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -36505,7 +36504,7 @@
         <v>Andrew Reeve Stage 2</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D74" s="52">
         <v>210242.4</v>
@@ -36598,7 +36597,7 @@
       </c>
       <c r="AE74" s="57"/>
       <c r="AG74" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH74" s="35">
         <f>AK79</f>
@@ -36617,7 +36616,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D75" s="52">
         <v>210242.4</v>
@@ -36708,7 +36707,7 @@
       </c>
       <c r="AE75" s="57"/>
       <c r="AG75" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH75" s="36">
         <f>AL79</f>
@@ -36727,7 +36726,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="52">
         <v>210242.4</v>
@@ -36832,7 +36831,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -36911,7 +36910,7 @@
       </c>
       <c r="AE77" s="57"/>
       <c r="AG77" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH77" s="36">
         <v>0</v>
@@ -36929,7 +36928,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -37024,7 +37023,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -37161,7 +37160,7 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" s="52">
         <v>43448.62</v>
@@ -37254,7 +37253,7 @@
       </c>
       <c r="AE81" s="57"/>
       <c r="AG81" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH81" s="35">
         <f>AK86</f>
@@ -37273,7 +37272,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D82" s="52">
         <v>43448.62</v>
@@ -37366,7 +37365,7 @@
       </c>
       <c r="AE82" s="57"/>
       <c r="AG82" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH82" s="36">
         <f>AL86</f>
@@ -37385,7 +37384,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" s="52">
         <v>0</v>
@@ -37490,7 +37489,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="52">
         <v>0</v>
@@ -37581,7 +37580,7 @@
       </c>
       <c r="AE84" s="57"/>
       <c r="AG84" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH84" s="36">
         <v>0</v>
@@ -37599,7 +37598,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D85" s="52">
         <v>0</v>
@@ -37702,7 +37701,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="52">
         <v>0</v>
@@ -37847,7 +37846,7 @@
         <v>Melhuish House</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="67">
         <v>49964.93</v>
@@ -37940,7 +37939,7 @@
       </c>
       <c r="AE88" s="57"/>
       <c r="AG88" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH88" s="35">
         <f>AK93</f>
@@ -37959,7 +37958,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D89" s="67">
         <v>49964.93</v>
@@ -38048,7 +38047,7 @@
       </c>
       <c r="AE89" s="57"/>
       <c r="AG89" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH89" s="36">
         <f>AL93</f>
@@ -38067,7 +38066,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D90" s="67">
         <v>0</v>
@@ -38170,7 +38169,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91" s="67">
         <v>0</v>
@@ -38259,7 +38258,7 @@
       </c>
       <c r="AE91" s="57"/>
       <c r="AG91" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH91" s="36">
         <v>0</v>
@@ -38277,7 +38276,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="67">
         <v>0</v>
@@ -38380,7 +38379,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D93" s="67">
         <v>0</v>
@@ -38525,7 +38524,7 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D95" s="52">
         <v>109103.76</v>
@@ -38618,7 +38617,7 @@
       </c>
       <c r="AE95" s="57"/>
       <c r="AG95" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH95" s="35">
         <f>AK100</f>
@@ -38637,7 +38636,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="52">
         <v>109103.76</v>
@@ -38730,7 +38729,7 @@
       </c>
       <c r="AE96" s="57"/>
       <c r="AG96" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH96" s="36">
         <f>AL100</f>
@@ -38749,7 +38748,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D97" s="52">
         <v>0</v>
@@ -38856,7 +38855,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98" s="52">
         <v>0</v>
@@ -38949,7 +38948,7 @@
       </c>
       <c r="AE98" s="57"/>
       <c r="AG98" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH98" s="36">
         <v>0</v>
@@ -38967,7 +38966,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" s="52">
         <v>0</v>
@@ -39072,7 +39071,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" s="52">
         <v>0</v>
@@ -39219,7 +39218,7 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="52">
         <v>27742.44</v>
@@ -39310,7 +39309,7 @@
       </c>
       <c r="AE102" s="57"/>
       <c r="AG102" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH102" s="35">
         <f>AK107</f>
@@ -39329,7 +39328,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D103" s="52">
         <v>27861.41</v>
@@ -39420,7 +39419,7 @@
       </c>
       <c r="AE103" s="57"/>
       <c r="AG103" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH103" s="36">
         <f>AL107</f>
@@ -39439,7 +39438,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D104" s="52">
         <v>0</v>
@@ -39544,7 +39543,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105" s="52">
         <v>0</v>
@@ -39635,7 +39634,7 @@
       </c>
       <c r="AE105" s="57"/>
       <c r="AG105" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH105" s="36">
         <v>0</v>
@@ -39653,7 +39652,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D106" s="52">
         <v>0</v>
@@ -39758,7 +39757,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D107" s="52">
         <v>0</v>
@@ -39905,7 +39904,7 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D109" s="52">
         <v>21300.45</v>
@@ -39997,7 +39996,7 @@
       </c>
       <c r="AE109" s="57"/>
       <c r="AG109" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH109" s="35">
         <f>AK114</f>
@@ -40016,7 +40015,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D110" s="52">
         <v>21300.45</v>
@@ -40109,7 +40108,7 @@
       </c>
       <c r="AE110" s="57"/>
       <c r="AG110" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH110" s="36">
         <f>AL114</f>
@@ -40128,7 +40127,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="52">
         <v>0</v>
@@ -40235,7 +40234,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112" s="52">
         <v>0</v>
@@ -40328,7 +40327,7 @@
       </c>
       <c r="AE112" s="57"/>
       <c r="AG112" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH112" s="36">
         <v>0</v>
@@ -40346,7 +40345,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" s="52">
         <v>0</v>
@@ -40453,7 +40452,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D114" s="52">
         <v>0</v>
@@ -40602,7 +40601,7 @@
         <v>Percival Bach</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="52">
         <v>63405.46</v>
@@ -40695,7 +40694,7 @@
       </c>
       <c r="AE116" s="57"/>
       <c r="AG116" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH116" s="35">
         <f>AK121</f>
@@ -40714,7 +40713,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D117" s="52">
         <v>63405.46</v>
@@ -40807,7 +40806,7 @@
       </c>
       <c r="AE117" s="57"/>
       <c r="AG117" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH117" s="36">
         <f>AL121</f>
@@ -40826,7 +40825,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D118" s="52">
         <v>0</v>
@@ -40933,7 +40932,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119" s="52">
         <v>0</v>
@@ -41026,7 +41025,7 @@
       </c>
       <c r="AE119" s="57"/>
       <c r="AG119" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH119" s="36">
         <v>0</v>
@@ -41044,7 +41043,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D120" s="52">
         <v>0</v>
@@ -41151,7 +41150,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D121" s="52">
         <v>0</v>
@@ -41300,7 +41299,7 @@
         <v>St Albans Street</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D123" s="52">
         <v>0</v>
@@ -41392,7 +41391,7 @@
       </c>
       <c r="AE123" s="57"/>
       <c r="AG123" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH123" s="35">
         <f>AK128</f>
@@ -41411,7 +41410,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D124" s="52">
         <v>0</v>
@@ -41500,7 +41499,7 @@
       </c>
       <c r="AE124" s="57"/>
       <c r="AG124" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH124" s="36">
         <f>AL128</f>
@@ -41519,7 +41518,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D125" s="52">
         <v>0</v>
@@ -41622,7 +41621,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="52">
         <v>0</v>
@@ -41711,7 +41710,7 @@
       </c>
       <c r="AE126" s="57"/>
       <c r="AG126" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH126" s="36">
         <v>0</v>
@@ -41729,7 +41728,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D127" s="52">
         <v>0</v>
@@ -41832,7 +41831,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D128" s="52">
         <v>0</v>
@@ -41977,7 +41976,7 @@
         <v>4 Perry St</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D130" s="52">
         <v>47191.69</v>
@@ -42070,7 +42069,7 @@
       </c>
       <c r="AE130" s="57"/>
       <c r="AG130" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH130" s="35">
         <f>AK135</f>
@@ -42089,7 +42088,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D131" s="52">
         <v>47191.69</v>
@@ -42182,7 +42181,7 @@
       </c>
       <c r="AE131" s="57"/>
       <c r="AG131" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH131" s="36">
         <f>AL135</f>
@@ -42201,7 +42200,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D132" s="52">
         <v>0</v>
@@ -42306,7 +42305,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D133" s="52">
         <v>0</v>
@@ -42397,7 +42396,7 @@
       </c>
       <c r="AE133" s="57"/>
       <c r="AG133" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH133" s="36">
         <v>0</v>
@@ -42415,7 +42414,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D134" s="52">
         <v>0</v>
@@ -42520,7 +42519,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D135" s="52">
         <v>0</v>
@@ -42667,7 +42666,7 @@
         <v>Ryans House</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D137" s="52">
         <v>0</v>
@@ -42760,7 +42759,7 @@
       </c>
       <c r="AE137" s="57"/>
       <c r="AG137" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH137" s="35">
         <f>AK142</f>
@@ -42779,7 +42778,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D138" s="52">
         <v>0</v>
@@ -42866,7 +42865,7 @@
       </c>
       <c r="AE138" s="57"/>
       <c r="AG138" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH138" s="36">
         <f>AL142</f>
@@ -42885,7 +42884,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D139" s="52">
         <v>0</v>
@@ -42986,7 +42985,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D140" s="52">
         <v>0</v>
@@ -43071,7 +43070,7 @@
       </c>
       <c r="AE140" s="57"/>
       <c r="AG140" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH140" s="36">
         <v>0</v>
@@ -43089,7 +43088,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D141" s="52">
         <v>0</v>
@@ -43188,7 +43187,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D142" s="52">
         <v>0</v>
@@ -43329,7 +43328,7 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D144" s="52">
         <v>23650.59</v>
@@ -43418,7 +43417,7 @@
       </c>
       <c r="AE144" s="57"/>
       <c r="AG144" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH144" s="35">
         <f>AK149</f>
@@ -43437,7 +43436,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D145" s="52">
         <v>23650.59</v>
@@ -43526,7 +43525,7 @@
       </c>
       <c r="AE145" s="57"/>
       <c r="AG145" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH145" s="36">
         <f>AL149</f>
@@ -43545,7 +43544,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D146" s="52">
         <v>23650.59</v>
@@ -43648,7 +43647,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D147" s="52">
         <v>23650.59</v>
@@ -43737,7 +43736,7 @@
       </c>
       <c r="AE147" s="57"/>
       <c r="AG147" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH147" s="36">
         <v>0</v>
@@ -43755,7 +43754,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D148" s="52">
         <v>23650.59</v>
@@ -43858,7 +43857,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D149" s="52">
         <v>23650.59</v>
@@ -44003,7 +44002,7 @@
         <v>Dixon House</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D151" s="52">
         <v>29188.19</v>
@@ -44092,7 +44091,7 @@
       </c>
       <c r="AE151" s="57"/>
       <c r="AG151" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH151" s="35">
         <f>AK156</f>
@@ -44111,7 +44110,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D152" s="52">
         <v>29188.19</v>
@@ -44200,7 +44199,7 @@
       </c>
       <c r="AE152" s="57"/>
       <c r="AG152" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH152" s="36">
         <f>AL156</f>
@@ -44219,7 +44218,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D153" s="52">
         <v>29188.19</v>
@@ -44322,7 +44321,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D154" s="52">
         <v>29188.19</v>
@@ -44411,7 +44410,7 @@
       </c>
       <c r="AE154" s="57"/>
       <c r="AG154" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH154" s="36">
         <v>0</v>
@@ -44429,7 +44428,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -44516,7 +44515,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -44645,7 +44644,7 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D158" s="52">
         <v>15025.89</v>
@@ -44732,7 +44731,7 @@
       </c>
       <c r="AE158" s="57"/>
       <c r="AG158" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH158" s="35">
         <f>AK163</f>
@@ -44751,7 +44750,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D159" s="52">
         <v>0</v>
@@ -44837,7 +44836,7 @@
       </c>
       <c r="AE159" s="57"/>
       <c r="AG159" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH159" s="36">
         <f>AL163</f>
@@ -44856,7 +44855,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -44943,7 +44942,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -45016,7 +45015,7 @@
       </c>
       <c r="AE161" s="57"/>
       <c r="AG161" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH161" s="36">
         <v>0</v>
@@ -45034,7 +45033,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -45121,7 +45120,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -45250,7 +45249,7 @@
         <v>Daves Twizel Shack</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D165" s="52">
         <v>300839.52</v>
@@ -45339,7 +45338,7 @@
       </c>
       <c r="AE165" s="57"/>
       <c r="AG165" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH165" s="35">
         <f>AK170</f>
@@ -45358,7 +45357,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D166" s="52">
         <v>300839.52</v>
@@ -45447,7 +45446,7 @@
       </c>
       <c r="AE166" s="57"/>
       <c r="AG166" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH166" s="36">
         <f>AL170</f>
@@ -45466,7 +45465,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="52">
         <v>0</v>
@@ -45569,7 +45568,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D168" s="52">
         <v>0</v>
@@ -45658,7 +45657,7 @@
       </c>
       <c r="AE168" s="57"/>
       <c r="AG168" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH168" s="36">
         <v>0</v>
@@ -45676,7 +45675,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D169" s="52">
         <v>0</v>
@@ -45779,7 +45778,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="52">
         <v>0</v>
@@ -45924,7 +45923,7 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D172" s="52">
         <v>58426.32</v>
@@ -46011,7 +46010,7 @@
       </c>
       <c r="AE172" s="57"/>
       <c r="AG172" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH172" s="35">
         <f>AK177</f>
@@ -46030,7 +46029,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="52">
         <v>58426.32</v>
@@ -46116,7 +46115,7 @@
       </c>
       <c r="AE173" s="57"/>
       <c r="AG173" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH173" s="36">
         <f>AL177</f>
@@ -46135,7 +46134,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D174" s="52">
         <v>0</v>
@@ -46238,7 +46237,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D175" s="52">
         <v>0</v>
@@ -46327,7 +46326,7 @@
       </c>
       <c r="AE175" s="57"/>
       <c r="AG175" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH175" s="36">
         <v>0</v>
@@ -46345,7 +46344,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D176" s="52">
         <v>0</v>
@@ -46448,7 +46447,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D177" s="52">
         <v>0</v>
@@ -46593,7 +46592,7 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D179" s="52">
         <v>18080.64</v>
@@ -46680,7 +46679,7 @@
       </c>
       <c r="AE179" s="57"/>
       <c r="AG179" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH179" s="35">
         <f>AK184</f>
@@ -46699,7 +46698,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D180" s="52">
         <v>18080.64</v>
@@ -46785,7 +46784,7 @@
       </c>
       <c r="AE180" s="57"/>
       <c r="AG180" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH180" s="36">
         <f>AL184</f>
@@ -46804,7 +46803,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="52">
         <v>0</v>
@@ -46907,7 +46906,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D182" s="52">
         <v>0</v>
@@ -46996,7 +46995,7 @@
       </c>
       <c r="AE182" s="57"/>
       <c r="AG182" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH182" s="36">
         <v>0</v>
@@ -47014,7 +47013,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D183" s="52">
         <v>0</v>
@@ -47117,7 +47116,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D184" s="52">
         <v>0</v>
@@ -47262,7 +47261,7 @@
         <v>Taggart House</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D186" s="52">
         <v>17608.26</v>
@@ -47349,7 +47348,7 @@
       </c>
       <c r="AE186" s="57"/>
       <c r="AG186" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH186" s="35">
         <f>AK191</f>
@@ -47368,7 +47367,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="52">
         <v>17608.26</v>
@@ -47454,7 +47453,7 @@
       </c>
       <c r="AE187" s="57"/>
       <c r="AG187" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH187" s="36">
         <f>AL191</f>
@@ -47473,7 +47472,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="52">
         <v>0</v>
@@ -47576,7 +47575,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D189" s="52">
         <v>0</v>
@@ -47665,7 +47664,7 @@
       </c>
       <c r="AE189" s="57"/>
       <c r="AG189" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH189" s="36">
         <v>0</v>
@@ -47683,7 +47682,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D190" s="52">
         <v>0</v>
@@ -47786,7 +47785,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D191" s="52">
         <v>0</v>
@@ -47931,7 +47930,7 @@
         <v>St Barnabas Church</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D193" s="52">
         <v>19572.81</v>
@@ -48022,7 +48021,7 @@
       </c>
       <c r="AE193" s="57"/>
       <c r="AG193" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH193" s="35">
         <f>AK198</f>
@@ -48041,7 +48040,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D194" s="52">
         <v>0</v>
@@ -48127,7 +48126,7 @@
       </c>
       <c r="AE194" s="57"/>
       <c r="AG194" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH194" s="36">
         <f>AL198</f>
@@ -48146,7 +48145,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D195" s="52">
         <v>0</v>
@@ -48249,7 +48248,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D196" s="52">
         <v>0</v>
@@ -48338,7 +48337,7 @@
       </c>
       <c r="AE196" s="57"/>
       <c r="AG196" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH196" s="36">
         <v>0</v>
@@ -48356,7 +48355,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D197" s="52">
         <v>0</v>
@@ -48459,7 +48458,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D198" s="52">
         <v>0</v>
@@ -48604,7 +48603,7 @@
         <v>0</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -48691,7 +48690,7 @@
       </c>
       <c r="AE200" s="57"/>
       <c r="AG200" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH200" s="35">
         <f>AK205</f>
@@ -48710,7 +48709,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D201" s="52">
         <v>0</v>
@@ -48796,7 +48795,7 @@
       </c>
       <c r="AE201" s="57"/>
       <c r="AG201" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH201" s="36">
         <f>AL205</f>
@@ -48815,7 +48814,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -48902,7 +48901,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -48975,7 +48974,7 @@
       </c>
       <c r="AE203" s="57"/>
       <c r="AG203" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH203" s="36">
         <v>0</v>
@@ -48993,7 +48992,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -49080,7 +49079,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -49209,7 +49208,7 @@
         <v>Contracting</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D207" s="52">
         <v>0</v>
@@ -49296,7 +49295,7 @@
       </c>
       <c r="AE207" s="57"/>
       <c r="AG207" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH207" s="35">
         <f>AK212</f>
@@ -49315,7 +49314,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D208" s="52">
         <v>0</v>
@@ -49401,7 +49400,7 @@
       </c>
       <c r="AE208" s="57"/>
       <c r="AG208" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH208" s="36">
         <f>AL212</f>
@@ -49420,7 +49419,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -49507,7 +49506,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -49580,7 +49579,7 @@
       </c>
       <c r="AE210" s="57"/>
       <c r="AG210" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH210" s="36">
         <v>0</v>
@@ -49598,7 +49597,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -49685,7 +49684,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -49814,7 +49813,7 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D214" s="52">
         <v>0</v>
@@ -49901,7 +49900,7 @@
       </c>
       <c r="AE214" s="57"/>
       <c r="AG214" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH214" s="35">
         <f>AK219</f>
@@ -49920,7 +49919,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D215" s="52">
         <v>0</v>
@@ -50006,7 +50005,7 @@
       </c>
       <c r="AE215" s="57"/>
       <c r="AG215" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH215" s="36">
         <f>AL219</f>
@@ -50025,7 +50024,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -50112,7 +50111,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -50185,7 +50184,7 @@
       </c>
       <c r="AE217" s="57"/>
       <c r="AG217" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH217" s="36">
         <v>0</v>
@@ -50203,7 +50202,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -50290,7 +50289,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -50419,7 +50418,7 @@
         <v>Roydvale</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D221" s="52">
         <v>0</v>
@@ -50506,7 +50505,7 @@
       </c>
       <c r="AE221" s="57"/>
       <c r="AG221" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH221" s="35">
         <f>AK226</f>
@@ -50525,7 +50524,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D222" s="52">
         <v>0</v>
@@ -50611,7 +50610,7 @@
       </c>
       <c r="AE222" s="57"/>
       <c r="AG222" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH222" s="36">
         <f>AL226</f>
@@ -50630,7 +50629,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -50717,7 +50716,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -50790,7 +50789,7 @@
       </c>
       <c r="AE224" s="57"/>
       <c r="AG224" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH224" s="36">
         <v>0</v>
@@ -50808,7 +50807,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -50895,7 +50894,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -51566,18 +51565,18 @@
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>220</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -51589,7 +51588,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -51600,7 +51599,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -51611,7 +51610,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6758,7 +6758,7 @@
         <v>28</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="14"/>
@@ -21701,13 +21701,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="52">
-        <v>-6483.239999999991</v>
+        <v>-6480.239999999991</v>
       </c>
       <c r="N12" s="54">
         <v>53</v>
       </c>
       <c r="O12" s="58">
-        <v>-93.95999999999987</v>
+        <v>-93.9165217391303</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>117</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6760,8 +6760,12 @@
       <c r="L32" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="14"/>
+      <c r="M32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="O32" s="13" t="s">
         <v>33</v>
       </c>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5804,13 +5804,25 @@
       <c r="H8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+      <c r="I8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="13"/>
+      <c r="L8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="P8" s="13"/>
       <c r="Q8" s="15"/>
       <c r="R8" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5824,9 +5824,15 @@
         <v>27</v>
       </c>
       <c r="P8" s="13"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
+      <c r="Q8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="T8" s="16"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -5834,7 +5834,9 @@
         <v>27</v>
       </c>
       <c r="T8" s="16"/>
-      <c r="U8" s="1"/>
+      <c r="U8" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -7977,10 +7977,18 @@
       <c r="C64" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="14"/>
+      <c r="D64" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -7990,9 +7990,15 @@
         <v>27</v>
       </c>
       <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
+      <c r="I64" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
       <c r="N64" s="14"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -8001,7 +8001,9 @@
       </c>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
-      <c r="N64" s="14"/>
+      <c r="N64" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="O64" s="13"/>
       <c r="P64" s="18"/>
       <c r="Q64" s="15"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -8006,7 +8006,9 @@
       </c>
       <c r="O64" s="13"/>
       <c r="P64" s="18"/>
-      <c r="Q64" s="15"/>
+      <c r="Q64" s="15" t="s">
+        <v>27</v>
+      </c>
       <c r="R64" s="13"/>
       <c r="S64" s="13"/>
       <c r="T64" s="16"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -7989,7 +7989,9 @@
       <c r="G64" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H64" s="13"/>
+      <c r="H64" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="I64" s="13" t="s">
         <v>27</v>
       </c>
@@ -7999,7 +8001,9 @@
       <c r="K64" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L64" s="13"/>
+      <c r="L64" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="M64" s="13"/>
       <c r="N64" s="14" t="s">
         <v>27</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -8014,7 +8014,9 @@
         <v>27</v>
       </c>
       <c r="R64" s="13"/>
-      <c r="S64" s="13"/>
+      <c r="S64" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="T64" s="16"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16244,7 +16244,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -21354,7 +21354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21368,7 +21368,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21390,7 +21390,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21456,7 +21456,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21503,7 +21503,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21520,7 +21520,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21570,7 +21570,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21587,7 +21587,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21647,7 +21647,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21694,7 +21694,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21711,7 +21711,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -21761,7 +21761,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21778,7 +21778,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21825,7 +21825,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21842,7 +21842,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21887,7 +21887,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21904,7 +21904,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -21971,7 +21971,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22010,7 +22010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22027,7 +22027,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22068,7 +22068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22085,7 +22085,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22139,7 +22139,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22184,7 +22184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22201,7 +22201,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22244,7 +22244,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22261,7 +22261,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22304,7 +22304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22321,7 +22321,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22385,7 +22385,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22430,7 +22430,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22447,7 +22447,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22490,7 +22490,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22507,7 +22507,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22565,7 +22565,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22610,7 +22610,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22627,7 +22627,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22670,7 +22670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22687,7 +22687,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22724,7 +22724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22741,7 +22741,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22799,7 +22799,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22859,7 +22859,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22901,7 +22901,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22918,7 +22918,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -22963,7 +22963,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -22980,7 +22980,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23025,7 +23025,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23042,7 +23042,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23087,7 +23087,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23104,7 +23104,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23141,7 +23141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23158,7 +23158,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23175,7 +23175,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23192,7 +23192,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23213,7 +23213,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23230,7 +23230,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23288,7 +23288,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23333,7 +23333,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -23350,7 +23350,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23367,7 +23367,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -23402,7 +23402,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -23785,7 +23785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23796,7 +23796,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23817,7 +23817,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -23879,7 +23879,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -23937,7 +23937,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -23971,7 +23971,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -23990,7 +23990,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24043,7 +24043,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24077,7 +24077,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24096,7 +24096,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24134,7 +24134,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24153,7 +24153,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24191,7 +24191,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24210,7 +24210,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24248,7 +24248,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24267,7 +24267,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24300,7 +24300,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24319,7 +24319,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24352,7 +24352,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24371,7 +24371,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24402,7 +24402,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24421,7 +24421,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24456,7 +24456,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24475,7 +24475,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24508,7 +24508,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24527,7 +24527,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24558,7 +24558,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24577,7 +24577,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24609,7 +24609,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24628,7 +24628,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24664,7 +24664,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24683,7 +24683,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24712,7 +24712,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24731,7 +24731,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24762,7 +24762,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24781,7 +24781,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24814,7 +24814,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24833,7 +24833,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24869,7 +24869,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24888,7 +24888,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24923,7 +24923,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -24942,7 +24942,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24972,7 +24972,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -24991,7 +24991,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25050,7 +25050,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25079,7 +25079,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25098,7 +25098,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25131,7 +25131,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25150,7 +25150,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25183,7 +25183,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25202,7 +25202,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25238,7 +25238,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25257,7 +25257,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25293,7 +25293,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25312,7 +25312,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25346,7 +25346,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25365,7 +25365,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25400,7 +25400,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25419,7 +25419,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25438,7 +25438,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25457,7 +25457,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25478,7 +25478,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25497,7 +25497,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25549,7 +25549,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -25607,7 +25607,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25626,7 +25626,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -25645,7 +25645,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -25690,7 +25690,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -25729,7 +25729,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -25758,7 +25758,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -25803,7 +25803,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -25848,7 +25848,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -25867,7 +25867,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -25914,7 +25914,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -25959,7 +25959,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -25978,7 +25978,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -26001,7 +26001,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -26024,7 +26024,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -26047,7 +26047,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -26070,7 +26070,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -26093,7 +26093,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -26116,7 +26116,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -26139,7 +26139,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -26162,7 +26162,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -26185,7 +26185,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -26208,7 +26208,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -26231,7 +26231,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -26254,7 +26254,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -26275,7 +26275,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26296,7 +26296,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26317,7 +26317,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26338,7 +26338,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26359,7 +26359,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26380,7 +26380,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26401,7 +26401,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -26424,7 +26424,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -26447,7 +26447,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -26470,7 +26470,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -26493,7 +26493,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -26516,7 +26516,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -26539,7 +26539,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -26562,7 +26562,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -26581,7 +26581,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26600,7 +26600,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26619,7 +26619,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -26638,7 +26638,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -26712,10 +26712,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -26747,7 +26748,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -26780,7 +26781,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -26813,7 +26814,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -26846,7 +26847,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -26879,7 +26880,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -26912,7 +26913,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -26945,7 +26946,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -26978,7 +26979,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27009,7 +27010,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27040,7 +27041,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -27073,7 +27074,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -27106,7 +27107,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -27139,7 +27140,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -27172,7 +27173,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -27205,7 +27206,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -27238,7 +27239,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -27271,7 +27272,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -27304,7 +27305,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -27337,7 +27338,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -27370,7 +27371,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -27403,7 +27404,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -27436,7 +27437,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -27469,7 +27470,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -27502,7 +27503,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -27535,7 +27536,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -27568,7 +27569,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -27600,7 +27601,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -27632,7 +27633,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -27664,7 +27665,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -27696,7 +27697,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -27728,7 +27729,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27758,7 +27759,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27788,7 +27789,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -27820,7 +27821,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -27852,7 +27853,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -27884,7 +27885,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -27916,7 +27917,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -27948,7 +27949,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -27978,7 +27979,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -28010,7 +28011,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -28042,7 +28043,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -28074,7 +28075,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -28106,7 +28107,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28136,7 +28137,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28166,7 +28167,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28196,7 +28197,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28226,7 +28227,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -28258,7 +28259,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -28290,7 +28291,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28320,7 +28321,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28350,7 +28351,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28380,7 +28381,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28410,7 +28411,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28440,7 +28441,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28535,10 +28536,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -28570,7 +28572,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28601,7 +28603,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28632,7 +28634,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28663,7 +28665,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28694,7 +28696,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28725,7 +28727,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28756,7 +28758,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28787,7 +28789,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28818,7 +28820,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28849,7 +28851,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28880,7 +28882,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28911,7 +28913,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -28942,7 +28944,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -28973,7 +28975,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29004,7 +29006,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29035,7 +29037,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29066,7 +29068,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29097,7 +29099,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29128,7 +29130,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29159,7 +29161,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29189,7 +29191,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29219,7 +29221,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29249,7 +29251,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29279,7 +29281,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29309,7 +29311,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29339,7 +29341,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29369,7 +29371,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29399,7 +29401,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29429,7 +29431,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29459,7 +29461,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29489,7 +29491,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29519,7 +29521,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29549,7 +29551,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29579,7 +29581,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29609,7 +29611,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29639,7 +29641,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -29671,7 +29673,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -29703,7 +29705,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29733,7 +29735,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29763,7 +29765,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29793,7 +29795,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29823,7 +29825,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29853,7 +29855,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -51596,19 +51598,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -51622,7 +51624,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -51634,7 +51636,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -51645,7 +51647,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -51656,7 +51658,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -51667,13 +51669,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16244,7 +16244,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -21354,7 +21354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21368,7 +21368,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21390,7 +21390,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21456,7 +21456,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21503,7 +21503,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21520,7 +21520,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21570,7 +21570,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21587,7 +21587,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21647,7 +21647,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21694,7 +21694,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21711,7 +21711,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -21761,7 +21761,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21778,7 +21778,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21825,7 +21825,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21842,7 +21842,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21887,7 +21887,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21904,7 +21904,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -21954,7 +21954,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -21971,7 +21971,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22010,7 +22010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22027,7 +22027,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22068,7 +22068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22085,7 +22085,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22139,7 +22139,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22184,7 +22184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22201,7 +22201,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22244,7 +22244,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22261,7 +22261,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22304,7 +22304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22321,7 +22321,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22385,7 +22385,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22430,7 +22430,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22447,7 +22447,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22490,7 +22490,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22507,7 +22507,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22565,7 +22565,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22610,7 +22610,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22627,7 +22627,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22670,7 +22670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22687,7 +22687,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22724,7 +22724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22741,7 +22741,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22799,7 +22799,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22859,7 +22859,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22901,7 +22901,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22918,7 +22918,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -22963,7 +22963,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -22980,7 +22980,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23025,7 +23025,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23042,7 +23042,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23087,7 +23087,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23104,7 +23104,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23141,7 +23141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23158,7 +23158,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23175,7 +23175,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23192,7 +23192,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23213,7 +23213,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23230,7 +23230,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23271,7 +23271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23288,7 +23288,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23333,7 +23333,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -23350,7 +23350,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23367,7 +23367,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -23402,7 +23402,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -23785,7 +23785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23796,7 +23796,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23817,7 +23817,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -23879,7 +23879,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -23937,7 +23937,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -23971,7 +23971,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -23990,7 +23990,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24043,7 +24043,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24077,7 +24077,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24096,7 +24096,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24134,7 +24134,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24153,7 +24153,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24191,7 +24191,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24210,7 +24210,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24248,7 +24248,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24267,7 +24267,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24300,7 +24300,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24319,7 +24319,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24352,7 +24352,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24371,7 +24371,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24402,7 +24402,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24421,7 +24421,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24456,7 +24456,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24475,7 +24475,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24508,7 +24508,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24527,7 +24527,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24558,7 +24558,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24577,7 +24577,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24609,7 +24609,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24628,7 +24628,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24664,7 +24664,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24683,7 +24683,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24712,7 +24712,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24731,7 +24731,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24762,7 +24762,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24781,7 +24781,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24814,7 +24814,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24833,7 +24833,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24869,7 +24869,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24888,7 +24888,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24923,7 +24923,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -24942,7 +24942,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24972,7 +24972,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -24991,7 +24991,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25050,7 +25050,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25079,7 +25079,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25098,7 +25098,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25131,7 +25131,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25150,7 +25150,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25183,7 +25183,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25202,7 +25202,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25238,7 +25238,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25257,7 +25257,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25293,7 +25293,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25312,7 +25312,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25346,7 +25346,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25365,7 +25365,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25400,7 +25400,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25419,7 +25419,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25438,7 +25438,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25457,7 +25457,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25478,7 +25478,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25497,7 +25497,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25549,7 +25549,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -25607,7 +25607,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25626,7 +25626,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -25645,7 +25645,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -25690,7 +25690,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -25729,7 +25729,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -25758,7 +25758,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -25803,7 +25803,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -25848,7 +25848,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -25867,7 +25867,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -25914,7 +25914,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -25959,7 +25959,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -25978,7 +25978,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -26001,7 +26001,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -26024,7 +26024,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -26047,7 +26047,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -26070,7 +26070,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -26093,7 +26093,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -26116,7 +26116,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -26139,7 +26139,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -26162,7 +26162,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -26185,7 +26185,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -26208,7 +26208,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -26231,7 +26231,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -26254,7 +26254,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -26275,7 +26275,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26296,7 +26296,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26317,7 +26317,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26338,7 +26338,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26359,7 +26359,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26380,7 +26380,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26401,7 +26401,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -26424,7 +26424,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -26447,7 +26447,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -26470,7 +26470,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -26493,7 +26493,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -26516,7 +26516,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -26539,7 +26539,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -26562,7 +26562,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -26581,7 +26581,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26600,7 +26600,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26619,7 +26619,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -26638,7 +26638,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -26712,11 +26712,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -26748,7 +26747,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -26781,7 +26780,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -26814,7 +26813,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -26847,7 +26846,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -26880,7 +26879,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -26913,7 +26912,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -26946,7 +26945,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -26979,7 +26978,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27010,7 +27009,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27041,7 +27040,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -27074,7 +27073,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -27107,7 +27106,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -27140,7 +27139,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -27173,7 +27172,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -27206,7 +27205,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -27239,7 +27238,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -27272,7 +27271,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -27305,7 +27304,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -27338,7 +27337,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -27371,7 +27370,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -27404,7 +27403,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -27437,7 +27436,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -27470,7 +27469,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -27503,7 +27502,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -27536,7 +27535,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -27569,7 +27568,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -27601,7 +27600,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -27633,7 +27632,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -27665,7 +27664,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -27697,7 +27696,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -27729,7 +27728,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27759,7 +27758,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27789,7 +27788,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -27821,7 +27820,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -27853,7 +27852,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -27885,7 +27884,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -27917,7 +27916,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -27949,7 +27948,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -27979,7 +27978,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -28011,7 +28010,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -28043,7 +28042,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -28075,7 +28074,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -28107,7 +28106,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28137,7 +28136,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28167,7 +28166,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28197,7 +28196,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28227,7 +28226,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -28259,7 +28258,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -28291,7 +28290,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28321,7 +28320,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28351,7 +28350,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28381,7 +28380,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28411,7 +28410,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28441,7 +28440,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28536,11 +28535,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -28572,7 +28570,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28603,7 +28601,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28634,7 +28632,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28665,7 +28663,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28696,7 +28694,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28727,7 +28725,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28758,7 +28756,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28789,7 +28787,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28820,7 +28818,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28851,7 +28849,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28882,7 +28880,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28913,7 +28911,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -28944,7 +28942,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -28975,7 +28973,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29006,7 +29004,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29037,7 +29035,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29068,7 +29066,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29099,7 +29097,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29130,7 +29128,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29161,7 +29159,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29191,7 +29189,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29221,7 +29219,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29251,7 +29249,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29281,7 +29279,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29311,7 +29309,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29341,7 +29339,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29371,7 +29369,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29401,7 +29399,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29431,7 +29429,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29461,7 +29459,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29491,7 +29489,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29521,7 +29519,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29551,7 +29549,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29581,7 +29579,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29611,7 +29609,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29641,7 +29639,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -29673,7 +29671,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -29705,7 +29703,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29735,7 +29733,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29765,7 +29763,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29795,7 +29793,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29825,7 +29823,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29855,7 +29853,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -51598,19 +51596,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -51624,7 +51622,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -51636,7 +51634,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -51647,7 +51645,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -51658,7 +51656,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -51669,13 +51667,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -8013,12 +8013,16 @@
       <c r="Q64" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="R64" s="13"/>
+      <c r="R64" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="S64" s="13" t="s">
         <v>27</v>
       </c>
       <c r="T64" s="16"/>
-      <c r="U64" s="1"/>
+      <c r="U64" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6381,9 +6381,13 @@
       <c r="C22" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="13"/>
+      <c r="D22" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="F22" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="G22" s="14"/>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6388,11 +6388,21 @@
       <c r="F22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="G22" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
       <c r="N22" s="14"/>
@@ -22052,7 +22062,7 @@
         <v>-565.6499999999996</v>
       </c>
       <c r="F22" s="52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="53">
         <v>0</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6403,7 +6403,9 @@
       <c r="K22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L22" s="13"/>
+      <c r="L22" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="M22" s="13"/>
       <c r="N22" s="14"/>
       <c r="O22" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6797,7 +6797,7 @@
         <v>27</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N32" s="14" t="s">
         <v>28</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6800,7 +6800,7 @@
         <v>27</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O32" s="13" t="s">
         <v>33</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6406,13 +6406,23 @@
       <c r="L22" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="M22" s="13"/>
-      <c r="N22" s="14"/>
+      <c r="M22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
+      <c r="Q22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="T22" s="16"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6424,7 +6424,9 @@
         <v>28</v>
       </c>
       <c r="T22" s="16"/>
-      <c r="U22" s="1"/>
+      <c r="U22" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6479,7 +6479,9 @@
       <c r="C24" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="13"/>
+      <c r="D24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6483,10 +6483,18 @@
         <v>27</v>
       </c>
       <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="F24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
@@ -22135,7 +22143,9 @@
       <c r="E24" s="52">
         <v>-1528.260000000002</v>
       </c>
-      <c r="F24" s="52"/>
+      <c r="F24" s="52">
+        <v>3</v>
+      </c>
       <c r="G24" s="53">
         <v>0</v>
       </c>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6495,9 +6495,15 @@
       <c r="I24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
+      <c r="J24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="M24" s="13"/>
       <c r="N24" s="14"/>
       <c r="O24" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6504,7 +6504,9 @@
       <c r="L24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="M24" s="13"/>
+      <c r="M24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="13"/>
       <c r="P24" s="13"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6507,11 +6507,21 @@
       <c r="M24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N24" s="14"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="13"/>
+      <c r="N24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>27</v>
+      </c>
       <c r="S24" s="13"/>
       <c r="T24" s="16"/>
       <c r="U24" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6522,7 +6522,9 @@
       <c r="R24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="S24" s="13"/>
+      <c r="S24" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="T24" s="16"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6845,7 +6845,7 @@
         <v>27</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="225">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -6526,7 +6526,9 @@
         <v>28</v>
       </c>
       <c r="T24" s="16"/>
-      <c r="U24" s="1"/>
+      <c r="U24" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16308,7 +16308,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -21418,7 +21418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21432,7 +21432,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21454,7 +21454,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -21502,7 +21502,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21520,7 +21520,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21567,7 +21567,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21584,7 +21584,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21634,7 +21634,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21651,7 +21651,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21694,7 +21694,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21711,7 +21711,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21758,7 +21758,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21775,7 +21775,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -21825,7 +21825,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21842,7 +21842,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21889,7 +21889,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21906,7 +21906,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21951,7 +21951,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21968,7 +21968,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -22035,7 +22035,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22091,7 +22091,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22125,14 +22125,14 @@
         <v>0</v>
       </c>
       <c r="M22" s="52">
-        <v>-565.6499999999996</v>
+        <v>-562.6499999999996</v>
       </c>
       <c r="N22" s="54"/>
       <c r="O22" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22149,7 +22149,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22181,14 +22181,14 @@
         <v>0</v>
       </c>
       <c r="M24" s="52">
-        <v>-1528.260000000002</v>
+        <v>-1525.260000000002</v>
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="58">
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22205,7 +22205,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22267,7 +22267,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22310,7 +22310,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22327,7 +22327,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22370,7 +22370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22387,7 +22387,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22434,7 +22434,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22451,7 +22451,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22496,7 +22496,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22513,7 +22513,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22556,7 +22556,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22573,7 +22573,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22614,7 +22614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22631,7 +22631,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22693,7 +22693,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22753,7 +22753,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22790,7 +22790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22807,7 +22807,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22848,7 +22848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22865,7 +22865,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22908,7 +22908,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22925,7 +22925,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22984,7 +22984,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -23029,7 +23029,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -23046,7 +23046,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23108,7 +23108,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23153,7 +23153,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23170,7 +23170,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23207,7 +23207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23224,7 +23224,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23241,7 +23241,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23258,7 +23258,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23279,7 +23279,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23296,7 +23296,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23337,7 +23337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23354,7 +23354,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -23416,7 +23416,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23433,7 +23433,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -23468,7 +23468,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -23851,7 +23851,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23862,7 +23862,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23883,7 +23883,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -23945,7 +23945,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -24003,7 +24003,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -24037,7 +24037,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -24056,7 +24056,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24090,7 +24090,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24109,7 +24109,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24143,7 +24143,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24162,7 +24162,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24200,7 +24200,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24219,7 +24219,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24257,7 +24257,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24276,7 +24276,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24314,7 +24314,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24333,7 +24333,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24366,7 +24366,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24385,7 +24385,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24418,7 +24418,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24437,7 +24437,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24468,7 +24468,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24487,7 +24487,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24522,7 +24522,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24541,7 +24541,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24574,7 +24574,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24593,7 +24593,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24624,7 +24624,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24643,7 +24643,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24675,7 +24675,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24694,7 +24694,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24730,7 +24730,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24749,7 +24749,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24778,7 +24778,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24797,7 +24797,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24828,7 +24828,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24847,7 +24847,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24880,7 +24880,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24899,7 +24899,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24935,7 +24935,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24954,7 +24954,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24989,7 +24989,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -25008,7 +25008,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25038,7 +25038,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -25057,7 +25057,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25116,7 +25116,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25145,7 +25145,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25164,7 +25164,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25197,7 +25197,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25216,7 +25216,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25249,7 +25249,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25268,7 +25268,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25304,7 +25304,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25323,7 +25323,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25359,7 +25359,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25378,7 +25378,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25412,7 +25412,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25431,7 +25431,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25466,7 +25466,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25485,7 +25485,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25504,7 +25504,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25523,7 +25523,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25544,7 +25544,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25563,7 +25563,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25615,7 +25615,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25654,7 +25654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -25673,7 +25673,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25692,7 +25692,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -25711,7 +25711,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -25756,7 +25756,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -25795,7 +25795,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -25824,7 +25824,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -25869,7 +25869,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -25914,7 +25914,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -25933,7 +25933,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -25980,7 +25980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -26025,7 +26025,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -26044,7 +26044,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -26067,7 +26067,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -26090,7 +26090,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -26113,7 +26113,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -26136,7 +26136,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -26159,7 +26159,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -26182,7 +26182,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -26205,7 +26205,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -26228,7 +26228,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -26251,7 +26251,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -26274,7 +26274,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -26297,7 +26297,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -26320,7 +26320,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -26341,7 +26341,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26362,7 +26362,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26383,7 +26383,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26404,7 +26404,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26425,7 +26425,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26446,7 +26446,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26467,7 +26467,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -26490,7 +26490,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -26513,7 +26513,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -26536,7 +26536,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -26559,7 +26559,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -26582,7 +26582,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -26605,7 +26605,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -26628,7 +26628,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -26647,7 +26647,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26666,7 +26666,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26685,7 +26685,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -26704,7 +26704,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -26778,10 +26778,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -26813,7 +26814,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -26846,7 +26847,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -26879,7 +26880,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -26912,7 +26913,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -26945,7 +26946,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -26978,7 +26979,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -27011,7 +27012,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -27044,7 +27045,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27075,7 +27076,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27106,7 +27107,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -27139,7 +27140,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -27172,7 +27173,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -27205,7 +27206,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -27238,7 +27239,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -27271,7 +27272,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -27304,7 +27305,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -27337,7 +27338,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -27370,7 +27371,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -27403,7 +27404,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -27436,7 +27437,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -27469,7 +27470,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -27502,7 +27503,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -27535,7 +27536,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -27568,7 +27569,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -27601,7 +27602,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -27634,7 +27635,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -27666,7 +27667,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -27698,7 +27699,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -27730,7 +27731,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -27762,7 +27763,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -27794,7 +27795,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27824,7 +27825,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27854,7 +27855,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -27886,7 +27887,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -27918,7 +27919,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -27950,7 +27951,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -27982,7 +27983,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -28014,7 +28015,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -28044,7 +28045,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -28076,7 +28077,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -28108,7 +28109,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -28140,7 +28141,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -28172,7 +28173,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28202,7 +28203,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28232,7 +28233,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28262,7 +28263,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28292,7 +28293,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -28324,7 +28325,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -28356,7 +28357,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28386,7 +28387,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28416,7 +28417,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28446,7 +28447,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28476,7 +28477,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28506,7 +28507,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28601,10 +28602,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -28636,7 +28638,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28667,7 +28669,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28698,7 +28700,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28729,7 +28731,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28760,7 +28762,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28791,7 +28793,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28822,7 +28824,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28853,7 +28855,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28884,7 +28886,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28915,7 +28917,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28946,7 +28948,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28977,7 +28979,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -29008,7 +29010,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -29039,7 +29041,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29070,7 +29072,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29101,7 +29103,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29132,7 +29134,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29163,7 +29165,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29194,7 +29196,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29225,7 +29227,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29255,7 +29257,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29285,7 +29287,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29315,7 +29317,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29345,7 +29347,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29375,7 +29377,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29405,7 +29407,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29435,7 +29437,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29465,7 +29467,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29495,7 +29497,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29525,7 +29527,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29555,7 +29557,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29585,7 +29587,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29615,7 +29617,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29645,7 +29647,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29675,7 +29677,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29705,7 +29707,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -29737,7 +29739,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -29769,7 +29771,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29799,7 +29801,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29829,7 +29831,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29859,7 +29861,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29889,7 +29891,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29919,7 +29921,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -51662,19 +51664,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -51688,7 +51690,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -51700,7 +51702,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -51711,7 +51713,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -51722,7 +51724,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -51733,13 +51735,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16308,7 +16308,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>95</v>
@@ -21418,7 +21418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD70"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21432,7 +21432,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21454,7 +21454,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>100</v>
       </c>
@@ -21502,7 +21502,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21520,7 +21520,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21567,7 +21567,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21584,7 +21584,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21634,7 +21634,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21651,7 +21651,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21694,7 +21694,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21711,7 +21711,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21758,7 +21758,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21775,7 +21775,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -21825,7 +21825,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21842,7 +21842,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21889,7 +21889,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21906,7 +21906,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21951,7 +21951,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21968,7 +21968,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -22035,7 +22035,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22091,7 +22091,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22149,7 +22149,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22205,7 +22205,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22267,7 +22267,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22310,7 +22310,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22327,7 +22327,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22370,7 +22370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22387,7 +22387,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22434,7 +22434,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22451,7 +22451,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22496,7 +22496,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22513,7 +22513,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22556,7 +22556,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22573,7 +22573,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22614,7 +22614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22631,7 +22631,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22676,7 +22676,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22693,7 +22693,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22753,7 +22753,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22790,7 +22790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22807,7 +22807,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22848,7 +22848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22865,7 +22865,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22908,7 +22908,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22925,7 +22925,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22984,7 +22984,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -23029,7 +23029,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -23046,7 +23046,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23108,7 +23108,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23153,7 +23153,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23170,7 +23170,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23207,7 +23207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23224,7 +23224,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23241,7 +23241,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23258,7 +23258,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23279,7 +23279,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23296,7 +23296,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23337,7 +23337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23354,7 +23354,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="36"/>
@@ -23416,7 +23416,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23433,7 +23433,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="35"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="49" t="s">
         <v>120</v>
       </c>
@@ -23468,7 +23468,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="59"/>
       <c r="B70" s="98" t="s">
         <v>124</v>
@@ -23851,7 +23851,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23862,7 +23862,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23883,7 +23883,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>125</v>
@@ -23945,7 +23945,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>141</v>
       </c>
@@ -24003,7 +24003,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -24037,7 +24037,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -24056,7 +24056,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24090,7 +24090,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24109,7 +24109,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24143,7 +24143,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24162,7 +24162,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24200,7 +24200,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24219,7 +24219,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24257,7 +24257,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24276,7 +24276,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24314,7 +24314,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24333,7 +24333,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24366,7 +24366,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24385,7 +24385,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24418,7 +24418,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24437,7 +24437,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24468,7 +24468,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24487,7 +24487,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24522,7 +24522,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24541,7 +24541,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24574,7 +24574,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24593,7 +24593,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24624,7 +24624,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24643,7 +24643,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24675,7 +24675,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24694,7 +24694,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24730,7 +24730,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24749,7 +24749,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24778,7 +24778,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24797,7 +24797,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24828,7 +24828,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24847,7 +24847,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24880,7 +24880,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24899,7 +24899,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24935,7 +24935,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24954,7 +24954,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24989,7 +24989,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -25008,7 +25008,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25038,7 +25038,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -25057,7 +25057,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25116,7 +25116,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25145,7 +25145,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25164,7 +25164,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25197,7 +25197,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25216,7 +25216,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25249,7 +25249,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25268,7 +25268,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25304,7 +25304,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25323,7 +25323,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25359,7 +25359,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25378,7 +25378,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25412,7 +25412,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25431,7 +25431,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25466,7 +25466,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25485,7 +25485,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25504,7 +25504,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25523,7 +25523,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25544,7 +25544,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25563,7 +25563,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25596,7 +25596,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25615,7 +25615,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25654,7 +25654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="142"/>
       <c r="B67" s="143"/>
       <c r="C67" s="35"/>
@@ -25673,7 +25673,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="144"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25692,7 +25692,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="145"/>
       <c r="B69" s="145"/>
       <c r="C69" s="145"/>
@@ -25711,7 +25711,7 @@
       <c r="P69" s="145"/>
       <c r="Q69" s="145"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="142"/>
       <c r="B70" s="146" t="s">
         <v>145</v>
@@ -25756,7 +25756,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="77" t="s">
         <v>146</v>
@@ -25795,7 +25795,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>147</v>
@@ -25824,7 +25824,7 @@
       <c r="P72" s="20"/>
       <c r="Q72" s="20"/>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="148" t="s">
         <v>148</v>
@@ -25869,7 +25869,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="151" t="s">
         <v>149</v>
@@ -25914,7 +25914,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -25933,7 +25933,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="144"/>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="156" t="s">
         <v>150</v>
@@ -25980,7 +25980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="161"/>
       <c r="B77" s="162" t="s">
         <v>152</v>
@@ -26025,7 +26025,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -26044,7 +26044,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
     </row>
-    <row r="79" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="164" t="s">
         <v>153</v>
@@ -26067,7 +26067,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="167" t="s">
         <v>155</v>
@@ -26090,7 +26090,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="19" t="s">
         <v>156</v>
@@ -26113,7 +26113,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>157</v>
@@ -26136,7 +26136,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>158</v>
@@ -26159,7 +26159,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>159</v>
@@ -26182,7 +26182,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>160</v>
@@ -26205,7 +26205,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>161</v>
@@ -26228,7 +26228,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>162</v>
@@ -26251,7 +26251,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>163</v>
@@ -26274,7 +26274,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>164</v>
@@ -26297,7 +26297,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>165</v>
@@ -26320,7 +26320,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19"/>
       <c r="C91" s="131">
@@ -26341,7 +26341,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26362,7 +26362,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26383,7 +26383,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26404,7 +26404,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26425,7 +26425,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26446,7 +26446,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26467,7 +26467,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19" t="s">
         <v>166</v>
@@ -26490,7 +26490,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>167</v>
@@ -26513,7 +26513,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>168</v>
@@ -26536,7 +26536,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>169</v>
@@ -26559,7 +26559,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>170</v>
@@ -26582,7 +26582,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>171</v>
@@ -26605,7 +26605,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>172</v>
@@ -26628,7 +26628,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19"/>
       <c r="C105" s="131"/>
@@ -26647,7 +26647,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26666,7 +26666,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26685,7 +26685,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="169"/>
       <c r="C108" s="150"/>
@@ -26704,7 +26704,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="164" t="s">
         <v>173</v>
@@ -26778,11 +26778,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>174</v>
       </c>
@@ -26814,7 +26813,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>175</v>
       </c>
@@ -26847,7 +26846,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>176</v>
       </c>
@@ -26880,7 +26879,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>177</v>
       </c>
@@ -26913,7 +26912,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>178</v>
       </c>
@@ -26946,7 +26945,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>179</v>
       </c>
@@ -26979,7 +26978,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>180</v>
       </c>
@@ -27012,7 +27011,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>181</v>
       </c>
@@ -27045,7 +27044,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27076,7 +27075,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27107,7 +27106,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>182</v>
       </c>
@@ -27140,7 +27139,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>183</v>
       </c>
@@ -27173,7 +27172,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>184</v>
       </c>
@@ -27206,7 +27205,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>185</v>
       </c>
@@ -27239,7 +27238,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>186</v>
       </c>
@@ -27272,7 +27271,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>187</v>
       </c>
@@ -27305,7 +27304,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>188</v>
       </c>
@@ -27338,7 +27337,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>189</v>
       </c>
@@ -27371,7 +27370,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>190</v>
       </c>
@@ -27404,7 +27403,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>191</v>
       </c>
@@ -27437,7 +27436,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>192</v>
       </c>
@@ -27470,7 +27469,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
@@ -27503,7 +27502,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>194</v>
       </c>
@@ -27536,7 +27535,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>195</v>
       </c>
@@ -27569,7 +27568,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>196</v>
       </c>
@@ -27602,7 +27601,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>197</v>
       </c>
@@ -27635,7 +27634,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>198</v>
       </c>
@@ -27667,7 +27666,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>199</v>
       </c>
@@ -27699,7 +27698,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>200</v>
       </c>
@@ -27731,7 +27730,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>201</v>
       </c>
@@ -27763,7 +27762,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>202</v>
       </c>
@@ -27795,7 +27794,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27825,7 +27824,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27855,7 +27854,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>203</v>
       </c>
@@ -27887,7 +27886,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>204</v>
       </c>
@@ -27919,7 +27918,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>205</v>
       </c>
@@ -27951,7 +27950,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>206</v>
       </c>
@@ -27983,7 +27982,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>207</v>
       </c>
@@ -28015,7 +28014,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -28045,7 +28044,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>208</v>
       </c>
@@ -28077,7 +28076,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>209</v>
       </c>
@@ -28109,7 +28108,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>210</v>
       </c>
@@ -28141,7 +28140,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>211</v>
       </c>
@@ -28173,7 +28172,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28203,7 +28202,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28233,7 +28232,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28263,7 +28262,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28293,7 +28292,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>212</v>
       </c>
@@ -28325,7 +28324,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>213</v>
       </c>
@@ -28357,7 +28356,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28387,7 +28386,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28417,7 +28416,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28447,7 +28446,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28477,7 +28476,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28507,7 +28506,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28602,11 +28601,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>214</v>
       </c>
@@ -28638,7 +28636,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28669,7 +28667,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28700,7 +28698,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28731,7 +28729,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28762,7 +28760,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28793,7 +28791,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28824,7 +28822,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28855,7 +28853,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28886,7 +28884,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28917,7 +28915,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28948,7 +28946,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28979,7 +28977,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -29010,7 +29008,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -29041,7 +29039,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29072,7 +29070,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29103,7 +29101,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29134,7 +29132,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29165,7 +29163,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29196,7 +29194,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29227,7 +29225,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29257,7 +29255,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29287,7 +29285,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29317,7 +29315,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29347,7 +29345,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29377,7 +29375,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29407,7 +29405,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29437,7 +29435,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29467,7 +29465,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29497,7 +29495,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29527,7 +29525,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29557,7 +29555,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29587,7 +29585,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29617,7 +29615,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29647,7 +29645,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29677,7 +29675,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29707,7 +29705,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>212</v>
       </c>
@@ -29739,7 +29737,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>213</v>
       </c>
@@ -29771,7 +29769,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29801,7 +29799,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29831,7 +29829,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29861,7 +29859,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29891,7 +29889,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29921,7 +29919,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -51664,19 +51662,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -51690,7 +51688,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>221</v>
       </c>
@@ -51702,7 +51700,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>222</v>
       </c>
@@ -51713,7 +51711,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>223</v>
       </c>
@@ -51724,7 +51722,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>224</v>
       </c>
@@ -51735,13 +51733,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6835,13 +6835,13 @@
         <v>27</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L32" s="13" t="s">
         <v>27</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N32" s="14" t="s">
         <v>27</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6841,7 +6841,7 @@
         <v>27</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N32" s="14" t="s">
         <v>27</v>
@@ -24019,7 +24019,9 @@
       <c r="E4" s="54">
         <v>-22.799999999999955</v>
       </c>
-      <c r="F4" s="54"/>
+      <c r="F4" s="54">
+        <v>0</v>
+      </c>
       <c r="G4" s="54"/>
       <c r="H4" s="54"/>
       <c r="I4" s="54"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -6841,7 +6841,7 @@
         <v>27</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N32" s="14" t="s">
         <v>27</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="227">
   <si>
     <t xml:space="preserve">                        Updated Job Spreadsheet</t>
   </si>
@@ -246,6 +246,12 @@
   </si>
   <si>
     <t>Roydvale</t>
+  </si>
+  <si>
+    <t>224 Cashel St - Eastern WC Block Reno</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Week</t>
@@ -5452,7 +5458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD67"/>
+  <dimension ref="A1:AD68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.14453125"/>
   <cols>
     <col min="1" max="1" width="8.29" style="1" customWidth="1"/>
@@ -8202,6 +8208,44 @@
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A68" s="27">
+        <v>8530</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68" s="29"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="13"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="13"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="16"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
+      <c r="AC68" s="1"/>
+      <c r="AD68" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -9452,7 +9496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI226"/>
+  <dimension ref="A1:AI233"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="2" max="3" width="26.43" style="35" customWidth="1"/>
@@ -9520,79 +9564,79 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O2" s="43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="39" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R2" s="40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="S2" s="44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T2" s="44" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="U2" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="V2" s="40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W2" s="42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="X2" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Y2" s="47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA2" s="48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AD2" s="35"/>
       <c r="AE2" s="35"/>
@@ -9630,10 +9674,10 @@
       <c r="AD3" s="35"/>
       <c r="AE3" s="35"/>
       <c r="AH3" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI3" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
@@ -9644,7 +9688,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="52">
         <v>245679.5</v>
@@ -9718,7 +9762,7 @@
       </c>
       <c r="AB4" s="57"/>
       <c r="AD4" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE4" s="35">
         <v>-418</v>
@@ -9734,7 +9778,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
@@ -9762,7 +9806,7 @@
       <c r="AA5" s="56"/>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE5" s="36">
         <v>-92952.56</v>
@@ -9774,7 +9818,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
@@ -9810,7 +9854,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -9838,7 +9882,7 @@
       <c r="AA7" s="56"/>
       <c r="AB7" s="57"/>
       <c r="AD7" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE7" s="36">
         <v>0</v>
@@ -9850,7 +9894,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -9886,7 +9930,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -9963,7 +10007,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" s="52">
         <v>129074.86</v>
@@ -10037,7 +10081,7 @@
       </c>
       <c r="AB11" s="57"/>
       <c r="AD11" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE11" s="35">
         <v>-52.5</v>
@@ -10053,7 +10097,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="52">
         <v>129074.86</v>
@@ -10125,7 +10169,7 @@
       </c>
       <c r="AB12" s="57"/>
       <c r="AD12" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE12" s="36">
         <v>-45701.86</v>
@@ -10137,7 +10181,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" s="52"/>
       <c r="E13" s="62"/>
@@ -10173,7 +10217,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="52"/>
       <c r="E14" s="62"/>
@@ -10201,7 +10245,7 @@
       <c r="AA14" s="56"/>
       <c r="AB14" s="57"/>
       <c r="AD14" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE14" s="36">
         <v>0</v>
@@ -10213,7 +10257,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" s="52"/>
       <c r="E15" s="62"/>
@@ -10249,7 +10293,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" s="52"/>
       <c r="E16" s="62"/>
@@ -10326,7 +10370,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D18" s="52">
         <v>27500.32</v>
@@ -10400,7 +10444,7 @@
       </c>
       <c r="AB18" s="57"/>
       <c r="AD18" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE18" s="35">
         <v>-34.75</v>
@@ -10416,7 +10460,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D19" s="52">
         <v>27500.32</v>
@@ -10488,7 +10532,7 @@
       </c>
       <c r="AB19" s="57"/>
       <c r="AD19" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE19" s="36">
         <v>-5911.24</v>
@@ -10500,7 +10544,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
@@ -10536,7 +10580,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -10564,7 +10608,7 @@
       <c r="AA21" s="56"/>
       <c r="AB21" s="57"/>
       <c r="AD21" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE21" s="36">
         <v>0</v>
@@ -10576,7 +10620,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -10612,7 +10656,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -10689,7 +10733,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D25" s="55">
         <v>150850.82</v>
@@ -10765,7 +10809,7 @@
       </c>
       <c r="AB25" s="57"/>
       <c r="AD25" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE25" s="35">
         <v>-388.25</v>
@@ -10781,7 +10825,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D26" s="55">
         <v>150850.82</v>
@@ -10853,7 +10897,7 @@
       </c>
       <c r="AB26" s="57"/>
       <c r="AD26" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE26" s="36">
         <v>-56964.81</v>
@@ -10865,7 +10909,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D27" s="55"/>
       <c r="E27" s="55"/>
@@ -10901,7 +10945,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D28" s="55"/>
       <c r="E28" s="55"/>
@@ -10929,7 +10973,7 @@
       <c r="AA28" s="56"/>
       <c r="AB28" s="57"/>
       <c r="AD28" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE28" s="36">
         <v>0</v>
@@ -10941,7 +10985,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D29" s="55"/>
       <c r="E29" s="55"/>
@@ -10977,7 +11021,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D30" s="55"/>
       <c r="E30" s="55"/>
@@ -11054,7 +11098,7 @@
         <v>34</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D32" s="52">
         <v>396422.03</v>
@@ -11128,7 +11172,7 @@
       </c>
       <c r="AB32" s="57"/>
       <c r="AD32" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE32" s="35">
         <v>-387.5</v>
@@ -11144,7 +11188,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D33" s="52">
         <v>396422.03</v>
@@ -11216,7 +11260,7 @@
       </c>
       <c r="AB33" s="57"/>
       <c r="AD33" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE33" s="36">
         <v>-132316.71</v>
@@ -11228,7 +11272,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D34" s="52"/>
       <c r="E34" s="52"/>
@@ -11264,7 +11308,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -11292,7 +11336,7 @@
       <c r="AA35" s="56"/>
       <c r="AB35" s="57"/>
       <c r="AD35" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE35" s="36">
         <v>0</v>
@@ -11304,7 +11348,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -11340,7 +11384,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -11417,7 +11461,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D39" s="52">
         <v>128258.5</v>
@@ -11491,7 +11535,7 @@
       </c>
       <c r="AB39" s="57"/>
       <c r="AD39" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE39" s="35">
         <v>-112</v>
@@ -11507,7 +11551,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D40" s="52">
         <v>128258.5</v>
@@ -11579,7 +11623,7 @@
       </c>
       <c r="AB40" s="57"/>
       <c r="AD40" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE40" s="36">
         <v>-26847.46</v>
@@ -11591,7 +11635,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D41" s="52"/>
       <c r="E41" s="52"/>
@@ -11627,7 +11671,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -11655,7 +11699,7 @@
       <c r="AA42" s="56"/>
       <c r="AB42" s="57"/>
       <c r="AD42" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE42" s="36">
         <v>0</v>
@@ -11667,7 +11711,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -11703,7 +11747,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -11780,7 +11824,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D46" s="52">
         <v>65693.36</v>
@@ -11856,7 +11900,7 @@
       </c>
       <c r="AB46" s="57"/>
       <c r="AD46" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE46" s="35">
         <v>-86.75</v>
@@ -11872,7 +11916,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D47" s="52">
         <v>65693.36</v>
@@ -11944,7 +11988,7 @@
       </c>
       <c r="AB47" s="57"/>
       <c r="AD47" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE47" s="36">
         <v>-15639.05</v>
@@ -11956,7 +12000,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D48" s="52"/>
       <c r="E48" s="52"/>
@@ -11992,7 +12036,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52"/>
@@ -12020,7 +12064,7 @@
       <c r="AA49" s="56"/>
       <c r="AB49" s="57"/>
       <c r="AD49" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE49" s="36">
         <v>0</v>
@@ -12032,7 +12076,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52"/>
@@ -12068,7 +12112,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52"/>
@@ -12145,7 +12189,7 @@
         <v>37</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D53" s="52">
         <v>155296.79</v>
@@ -12219,7 +12263,7 @@
       </c>
       <c r="AB53" s="57"/>
       <c r="AD53" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE53" s="35">
         <v>-269</v>
@@ -12235,7 +12279,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D54" s="52">
         <v>155296.79</v>
@@ -12307,7 +12351,7 @@
       </c>
       <c r="AB54" s="57"/>
       <c r="AD54" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE54" s="36">
         <v>-66399.88</v>
@@ -12319,7 +12363,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D55" s="52"/>
       <c r="E55" s="52"/>
@@ -12355,7 +12399,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -12383,7 +12427,7 @@
       <c r="AA56" s="56"/>
       <c r="AB56" s="57"/>
       <c r="AD56" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE56" s="36">
         <v>0</v>
@@ -12395,7 +12439,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -12431,7 +12475,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -12508,7 +12552,7 @@
         <v>38</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D60" s="52">
         <v>20420.56</v>
@@ -12582,7 +12626,7 @@
       </c>
       <c r="AB60" s="57"/>
       <c r="AD60" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE60" s="35">
         <v>-26.75</v>
@@ -12598,7 +12642,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D61" s="52">
         <v>20420.56</v>
@@ -12670,7 +12714,7 @@
       </c>
       <c r="AB61" s="57"/>
       <c r="AD61" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE61" s="36">
         <v>-11159.14</v>
@@ -12682,7 +12726,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D62" s="52"/>
       <c r="E62" s="52"/>
@@ -12718,7 +12762,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -12746,7 +12790,7 @@
       <c r="AA63" s="56"/>
       <c r="AB63" s="57"/>
       <c r="AD63" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE63" s="36">
         <v>0</v>
@@ -12758,7 +12802,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -12794,7 +12838,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -12871,7 +12915,7 @@
         <v>39</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D67" s="52">
         <v>47801.68</v>
@@ -12943,7 +12987,7 @@
       </c>
       <c r="AB67" s="57"/>
       <c r="AD67" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE67" s="35"/>
       <c r="AH67" s="19"/>
@@ -12955,7 +12999,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D68" s="52">
         <v>47801.68</v>
@@ -13027,7 +13071,7 @@
       </c>
       <c r="AB68" s="57"/>
       <c r="AD68" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE68" s="36">
         <v>-5397.27</v>
@@ -13039,7 +13083,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -13075,7 +13119,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -13103,7 +13147,7 @@
       <c r="AA70" s="56"/>
       <c r="AB70" s="57"/>
       <c r="AD70" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE70" s="36">
         <v>0</v>
@@ -13115,7 +13159,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -13151,7 +13195,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -13226,7 +13270,7 @@
         <v>40</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D74" s="52">
         <v>77166.16</v>
@@ -13300,7 +13344,7 @@
       </c>
       <c r="AB74" s="57"/>
       <c r="AD74" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE74" s="35"/>
       <c r="AH74" s="19"/>
@@ -13310,7 +13354,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D75" s="52">
         <v>77166.16</v>
@@ -13382,7 +13426,7 @@
       </c>
       <c r="AB75" s="57"/>
       <c r="AD75" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE75" s="36"/>
       <c r="AH75" s="19"/>
@@ -13392,7 +13436,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D76" s="52"/>
       <c r="E76" s="52"/>
@@ -13428,7 +13472,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -13456,7 +13500,7 @@
       <c r="AA77" s="56"/>
       <c r="AB77" s="57"/>
       <c r="AD77" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE77" s="36">
         <v>0</v>
@@ -13468,7 +13512,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -13504,7 +13548,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -13577,7 +13621,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D81" s="52">
         <v>25467.84</v>
@@ -13651,7 +13695,7 @@
       </c>
       <c r="AB81" s="57"/>
       <c r="AD81" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE81" s="35">
         <v>-143.25</v>
@@ -13667,7 +13711,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D82" s="52">
         <v>25467.84</v>
@@ -13739,7 +13783,7 @@
       </c>
       <c r="AB82" s="57"/>
       <c r="AD82" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE82" s="36">
         <v>-5569.48</v>
@@ -13751,7 +13795,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
@@ -13787,7 +13831,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D84" s="52"/>
       <c r="E84" s="52"/>
@@ -13815,7 +13859,7 @@
       <c r="AA84" s="56"/>
       <c r="AB84" s="57"/>
       <c r="AD84" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE84" s="36">
         <v>0</v>
@@ -13827,7 +13871,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D85" s="52"/>
       <c r="E85" s="52"/>
@@ -13863,7 +13907,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
@@ -13940,7 +13984,7 @@
         <v>43</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D88" s="67">
         <v>37083.03</v>
@@ -14014,7 +14058,7 @@
       </c>
       <c r="AB88" s="57"/>
       <c r="AD88" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE88" s="35">
         <v>-148.5</v>
@@ -14030,7 +14074,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D89" s="67">
         <v>37083.03</v>
@@ -14102,7 +14146,7 @@
       </c>
       <c r="AB89" s="57"/>
       <c r="AD89" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE89" s="36">
         <v>-14143.19</v>
@@ -14114,7 +14158,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D90" s="67"/>
       <c r="E90" s="67"/>
@@ -14150,7 +14194,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D91" s="67"/>
       <c r="E91" s="67"/>
@@ -14178,7 +14222,7 @@
       <c r="AA91" s="56"/>
       <c r="AB91" s="57"/>
       <c r="AD91" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE91" s="36">
         <v>0</v>
@@ -14190,7 +14234,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D92" s="67"/>
       <c r="E92" s="67"/>
@@ -14226,7 +14270,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D93" s="67"/>
       <c r="E93" s="67"/>
@@ -14303,7 +14347,7 @@
         <v>44</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D95" s="52">
         <v>26186.14</v>
@@ -14377,7 +14421,7 @@
       </c>
       <c r="AB95" s="57"/>
       <c r="AD95" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE95" s="35">
         <v>-5</v>
@@ -14393,7 +14437,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D96" s="52">
         <v>26186.14</v>
@@ -14465,7 +14509,7 @@
       </c>
       <c r="AB96" s="57"/>
       <c r="AD96" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE96" s="36">
         <v>-7679.91</v>
@@ -14477,7 +14521,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D97" s="52"/>
       <c r="E97" s="52"/>
@@ -14513,7 +14557,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D98" s="52"/>
       <c r="E98" s="52"/>
@@ -14541,7 +14585,7 @@
       <c r="AA98" s="56"/>
       <c r="AB98" s="57"/>
       <c r="AD98" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE98" s="36">
         <v>0</v>
@@ -14553,7 +14597,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D99" s="52"/>
       <c r="E99" s="52"/>
@@ -14589,7 +14633,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -14666,7 +14710,7 @@
         <v>45</v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D102" s="52">
         <v>32473.02</v>
@@ -14740,7 +14784,7 @@
       </c>
       <c r="AB102" s="57"/>
       <c r="AD102" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE102" s="35">
         <v>-317.25</v>
@@ -14756,7 +14800,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D103" s="52">
         <v>32473.02</v>
@@ -14828,7 +14872,7 @@
       </c>
       <c r="AB103" s="57"/>
       <c r="AD103" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE103" s="36">
         <v>-16562.52</v>
@@ -14840,7 +14884,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D104" s="52"/>
       <c r="E104" s="69"/>
@@ -14876,7 +14920,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D105" s="52"/>
       <c r="E105" s="69"/>
@@ -14904,7 +14948,7 @@
       <c r="AA105" s="56"/>
       <c r="AB105" s="57"/>
       <c r="AD105" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE105" s="36">
         <v>0</v>
@@ -14916,7 +14960,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D106" s="52"/>
       <c r="E106" s="69"/>
@@ -14952,7 +14996,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D107" s="52"/>
       <c r="E107" s="67"/>
@@ -15029,7 +15073,7 @@
         <v>47</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D109" s="52">
         <v>58902.56</v>
@@ -15105,7 +15149,7 @@
       </c>
       <c r="AB109" s="57"/>
       <c r="AD109" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE109" s="35">
         <v>-204.75</v>
@@ -15121,7 +15165,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D110" s="52">
         <v>58902.56</v>
@@ -15193,7 +15237,7 @@
       </c>
       <c r="AB110" s="57"/>
       <c r="AD110" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE110" s="36">
         <v>-12155.27</v>
@@ -15205,7 +15249,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D111" s="52"/>
       <c r="E111" s="52"/>
@@ -15241,7 +15285,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D112" s="52"/>
       <c r="E112" s="52"/>
@@ -15269,7 +15313,7 @@
       <c r="AA112" s="56"/>
       <c r="AB112" s="57"/>
       <c r="AD112" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE112" s="36">
         <v>0</v>
@@ -15281,7 +15325,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D113" s="52"/>
       <c r="E113" s="52"/>
@@ -15317,7 +15361,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D114" s="52"/>
       <c r="E114" s="52"/>
@@ -15394,7 +15438,7 @@
         <v>48</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D116" s="52">
         <v>21404.82</v>
@@ -15470,7 +15514,7 @@
       </c>
       <c r="AB116" s="57"/>
       <c r="AD116" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE116" s="35"/>
       <c r="AH116" s="19"/>
@@ -15480,7 +15524,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D117" s="52">
         <v>21404.82</v>
@@ -15552,7 +15596,7 @@
       </c>
       <c r="AB117" s="57"/>
       <c r="AD117" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE117" s="36"/>
       <c r="AH117" s="19"/>
@@ -15562,7 +15606,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D118" s="52"/>
       <c r="E118" s="52"/>
@@ -15598,7 +15642,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D119" s="52"/>
       <c r="E119" s="52"/>
@@ -15626,7 +15670,7 @@
       <c r="AA119" s="56"/>
       <c r="AB119" s="57"/>
       <c r="AD119" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE119" s="36">
         <v>0</v>
@@ -15638,7 +15682,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D120" s="52"/>
       <c r="E120" s="52"/>
@@ -15674,7 +15718,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D121" s="52"/>
       <c r="E121" s="52"/>
@@ -15747,7 +15791,7 @@
         <v>49</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D123" s="52">
         <v>100987.51</v>
@@ -15819,7 +15863,7 @@
       </c>
       <c r="AB123" s="57"/>
       <c r="AD123" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE123" s="35"/>
       <c r="AH123" s="19"/>
@@ -15831,7 +15875,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D124" s="52">
         <v>100987.51</v>
@@ -15903,7 +15947,7 @@
       </c>
       <c r="AB124" s="57"/>
       <c r="AD124" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE124" s="36">
         <v>-12186.08</v>
@@ -15915,7 +15959,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D125" s="52"/>
       <c r="E125" s="52"/>
@@ -15951,7 +15995,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D126" s="52"/>
       <c r="E126" s="52"/>
@@ -15979,7 +16023,7 @@
       <c r="AA126" s="56"/>
       <c r="AB126" s="57"/>
       <c r="AD126" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE126" s="36">
         <v>0</v>
@@ -15991,7 +16035,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D127" s="52"/>
       <c r="E127" s="52"/>
@@ -16027,7 +16071,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D128" s="52"/>
       <c r="E128" s="52"/>
@@ -16102,7 +16146,7 @@
         <v>50</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D130" s="52">
         <v>31802.41</v>
@@ -16176,7 +16220,7 @@
       </c>
       <c r="AB130" s="57"/>
       <c r="AD130" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE130" s="35">
         <v>-2</v>
@@ -16192,7 +16236,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D131" s="52">
         <v>31802.41</v>
@@ -16264,7 +16308,7 @@
       </c>
       <c r="AB131" s="57"/>
       <c r="AD131" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE131" s="36">
         <v>-11154.51</v>
@@ -16276,7 +16320,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D132" s="52"/>
       <c r="E132" s="52"/>
@@ -16308,10 +16352,10 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D133" s="52"/>
       <c r="E133" s="52"/>
@@ -16339,7 +16383,7 @@
       <c r="AA133" s="56"/>
       <c r="AB133" s="57"/>
       <c r="AD133" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE133" s="36">
         <v>0</v>
@@ -16351,7 +16395,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D134" s="52"/>
       <c r="E134" s="52"/>
@@ -16387,7 +16431,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D135" s="52"/>
       <c r="E135" s="52"/>
@@ -16464,7 +16508,7 @@
         <v>51</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D137" s="52">
         <v>30749.24</v>
@@ -16538,7 +16582,7 @@
       </c>
       <c r="AB137" s="57"/>
       <c r="AD137" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE137" s="35">
         <v>-266.75</v>
@@ -16554,7 +16598,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D138" s="52">
         <v>30749.24</v>
@@ -16626,7 +16670,7 @@
       </c>
       <c r="AB138" s="57"/>
       <c r="AD138" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE138" s="36">
         <v>-11702.32</v>
@@ -16638,7 +16682,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D139" s="52"/>
       <c r="E139" s="52"/>
@@ -16674,7 +16718,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D140" s="52"/>
       <c r="E140" s="52"/>
@@ -16702,7 +16746,7 @@
       <c r="AA140" s="56"/>
       <c r="AB140" s="57"/>
       <c r="AD140" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE140" s="36">
         <v>0</v>
@@ -16714,7 +16758,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D141" s="52"/>
       <c r="E141" s="52"/>
@@ -16750,7 +16794,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D142" s="52"/>
       <c r="E142" s="52"/>
@@ -16827,7 +16871,7 @@
         <v>52</v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D144" s="52">
         <v>268228.26</v>
@@ -16899,7 +16943,7 @@
       </c>
       <c r="AB144" s="57"/>
       <c r="AD144" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE144" s="35"/>
       <c r="AH144" s="19"/>
@@ -16909,7 +16953,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D145" s="52">
         <v>268228.26</v>
@@ -16981,7 +17025,7 @@
       </c>
       <c r="AB145" s="57"/>
       <c r="AD145" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE145" s="36"/>
       <c r="AH145" s="19"/>
@@ -16991,7 +17035,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D146" s="52"/>
       <c r="E146" s="52"/>
@@ -17027,7 +17071,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D147" s="52"/>
       <c r="E147" s="52"/>
@@ -17055,7 +17099,7 @@
       <c r="AA147" s="56"/>
       <c r="AB147" s="57"/>
       <c r="AD147" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE147" s="36">
         <v>0</v>
@@ -17067,7 +17111,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D148" s="52"/>
       <c r="E148" s="52"/>
@@ -17103,7 +17147,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D149" s="52"/>
       <c r="E149" s="52"/>
@@ -17176,7 +17220,7 @@
         <v>53</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D151" s="52">
         <v>32773.41</v>
@@ -17248,7 +17292,7 @@
       </c>
       <c r="AB151" s="57"/>
       <c r="AD151" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE151" s="35">
         <v>-260.75</v>
@@ -17264,7 +17308,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D152" s="52">
         <v>32773.41</v>
@@ -17336,7 +17380,7 @@
       </c>
       <c r="AB152" s="57"/>
       <c r="AD152" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE152" s="36">
         <v>-9324.41</v>
@@ -17348,7 +17392,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D153" s="52"/>
       <c r="E153" s="52"/>
@@ -17384,7 +17428,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D154" s="52"/>
       <c r="E154" s="52"/>
@@ -17412,7 +17456,7 @@
       <c r="AA154" s="56"/>
       <c r="AB154" s="57"/>
       <c r="AD154" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE154" s="36">
         <v>0</v>
@@ -17424,7 +17468,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -17460,7 +17504,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -17537,7 +17581,7 @@
         <v>54</v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D158" s="52">
         <v>17899.33</v>
@@ -17609,7 +17653,7 @@
       </c>
       <c r="AB158" s="57"/>
       <c r="AD158" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE158" s="35">
         <v>-44.75</v>
@@ -17623,7 +17667,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D159" s="52">
         <v>17899.33</v>
@@ -17695,7 +17739,7 @@
       </c>
       <c r="AB159" s="57"/>
       <c r="AD159" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE159" s="36"/>
       <c r="AH159" s="19"/>
@@ -17705,7 +17749,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -17741,7 +17785,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -17769,7 +17813,7 @@
       <c r="AA161" s="56"/>
       <c r="AB161" s="57"/>
       <c r="AD161" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE161" s="36">
         <v>0</v>
@@ -17781,7 +17825,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -17817,7 +17861,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -17892,7 +17936,7 @@
         <v>55</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D165" s="52">
         <v>10827.2</v>
@@ -17912,7 +17956,7 @@
         <v>4388.87</v>
       </c>
       <c r="K165" s="52" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L165" s="52">
         <v>4388.87</v>
@@ -17952,7 +17996,7 @@
       </c>
       <c r="AB165" s="57"/>
       <c r="AD165" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE165" s="35"/>
       <c r="AH165" s="19"/>
@@ -17962,7 +18006,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D166" s="52">
         <v>10827.2</v>
@@ -18034,7 +18078,7 @@
       </c>
       <c r="AB166" s="57"/>
       <c r="AD166" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE166" s="36"/>
       <c r="AH166" s="19"/>
@@ -18044,7 +18088,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D167" s="52"/>
       <c r="E167" s="52"/>
@@ -18080,7 +18124,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D168" s="52"/>
       <c r="E168" s="52"/>
@@ -18108,7 +18152,7 @@
       <c r="AA168" s="56"/>
       <c r="AB168" s="57"/>
       <c r="AD168" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE168" s="36">
         <v>0</v>
@@ -18120,7 +18164,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
@@ -18156,7 +18200,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
@@ -18229,7 +18273,7 @@
         <v>56</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D172" s="52">
         <v>146237.11</v>
@@ -18301,7 +18345,7 @@
       </c>
       <c r="AB172" s="57"/>
       <c r="AD172" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE172" s="35">
         <v>-304.75</v>
@@ -18315,7 +18359,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D173" s="52">
         <v>146237.11</v>
@@ -18387,7 +18431,7 @@
       </c>
       <c r="AB173" s="57"/>
       <c r="AD173" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE173" s="36"/>
       <c r="AH173" s="19"/>
@@ -18397,7 +18441,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D174" s="52"/>
       <c r="E174" s="52"/>
@@ -18433,7 +18477,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D175" s="52"/>
       <c r="E175" s="52"/>
@@ -18461,7 +18505,7 @@
       <c r="AA175" s="56"/>
       <c r="AB175" s="57"/>
       <c r="AD175" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE175" s="36">
         <v>0</v>
@@ -18473,7 +18517,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D176" s="52"/>
       <c r="E176" s="52"/>
@@ -18509,7 +18553,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D177" s="52"/>
       <c r="E177" s="52"/>
@@ -18586,7 +18630,7 @@
         <v>57</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D179" s="52">
         <v>16897.53</v>
@@ -18658,7 +18702,7 @@
       </c>
       <c r="AB179" s="57"/>
       <c r="AD179" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE179" s="35">
         <v>-11.25</v>
@@ -18674,7 +18718,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D180" s="52"/>
       <c r="E180" s="52"/>
@@ -18702,7 +18746,7 @@
       <c r="AA180" s="56"/>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE180" s="36">
         <v>-2298.71</v>
@@ -18714,7 +18758,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D181" s="52"/>
       <c r="E181" s="52"/>
@@ -18750,7 +18794,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
@@ -18778,7 +18822,7 @@
       <c r="AA182" s="56"/>
       <c r="AB182" s="57"/>
       <c r="AD182" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE182" s="36">
         <v>0</v>
@@ -18790,7 +18834,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D183" s="52"/>
       <c r="E183" s="52"/>
@@ -18826,7 +18870,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
@@ -18903,7 +18947,7 @@
         <v>58</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D186" s="52">
         <v>20992.12</v>
@@ -18975,7 +19019,7 @@
       </c>
       <c r="AB186" s="57"/>
       <c r="AD186" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE186" s="35">
         <v>-32.25</v>
@@ -18989,7 +19033,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D187" s="52">
         <v>20992.12</v>
@@ -19061,7 +19105,7 @@
       </c>
       <c r="AB187" s="57"/>
       <c r="AD187" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE187" s="36"/>
       <c r="AH187" s="19"/>
@@ -19071,7 +19115,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D188" s="52"/>
       <c r="E188" s="52"/>
@@ -19107,7 +19151,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D189" s="52"/>
       <c r="E189" s="52"/>
@@ -19135,7 +19179,7 @@
       <c r="AA189" s="56"/>
       <c r="AB189" s="57"/>
       <c r="AD189" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE189" s="36">
         <v>0</v>
@@ -19147,7 +19191,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D190" s="52"/>
       <c r="E190" s="52"/>
@@ -19183,7 +19227,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D191" s="52"/>
       <c r="E191" s="52"/>
@@ -19258,7 +19302,7 @@
         <v>59</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D193" s="52">
         <v>23770.95</v>
@@ -19330,7 +19374,7 @@
       </c>
       <c r="AB193" s="57"/>
       <c r="AD193" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE193" s="35"/>
       <c r="AH193" s="19"/>
@@ -19340,7 +19384,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D194" s="52">
         <v>23770.95</v>
@@ -19412,7 +19456,7 @@
       </c>
       <c r="AB194" s="57"/>
       <c r="AD194" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE194" s="36"/>
       <c r="AH194" s="19"/>
@@ -19422,7 +19466,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D195" s="52"/>
       <c r="E195" s="52"/>
@@ -19458,7 +19502,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D196" s="52"/>
       <c r="E196" s="52"/>
@@ -19486,7 +19530,7 @@
       <c r="AA196" s="56"/>
       <c r="AB196" s="57"/>
       <c r="AD196" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE196" s="36">
         <v>0</v>
@@ -19498,7 +19542,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D197" s="52"/>
       <c r="E197" s="52"/>
@@ -19534,7 +19578,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D198" s="52"/>
       <c r="E198" s="52"/>
@@ -19603,7 +19647,7 @@
       <c r="A200" s="19"/>
       <c r="B200" s="19"/>
       <c r="C200" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -19651,7 +19695,7 @@
       <c r="AA200" s="56"/>
       <c r="AB200" s="57"/>
       <c r="AD200" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE200" s="35"/>
       <c r="AH200" s="19"/>
@@ -19661,7 +19705,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D201" s="52"/>
       <c r="E201" s="52"/>
@@ -19693,7 +19737,7 @@
       <c r="AA201" s="56"/>
       <c r="AB201" s="57"/>
       <c r="AD201" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE201" s="36"/>
       <c r="AH201" s="19"/>
@@ -19703,7 +19747,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -19743,7 +19787,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -19775,7 +19819,7 @@
       <c r="AA203" s="56"/>
       <c r="AB203" s="57"/>
       <c r="AD203" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE203" s="36">
         <v>0</v>
@@ -19787,7 +19831,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -19827,7 +19871,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -19902,7 +19946,7 @@
         <v>60</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D207" s="52"/>
       <c r="E207" s="52"/>
@@ -19934,7 +19978,7 @@
       <c r="AA207" s="56"/>
       <c r="AB207" s="57"/>
       <c r="AD207" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE207" s="35"/>
       <c r="AH207" s="19"/>
@@ -19944,7 +19988,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D208" s="52"/>
       <c r="E208" s="52"/>
@@ -19976,7 +20020,7 @@
       <c r="AA208" s="56"/>
       <c r="AB208" s="57"/>
       <c r="AD208" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE208" s="36"/>
       <c r="AH208" s="19"/>
@@ -19986,7 +20030,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -20026,7 +20070,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -20058,7 +20102,7 @@
       <c r="AA210" s="56"/>
       <c r="AB210" s="57"/>
       <c r="AD210" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE210" s="36">
         <v>0</v>
@@ -20070,7 +20114,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -20110,7 +20154,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -20187,7 +20231,7 @@
         <v>61</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D214" s="52">
         <v>137109.56</v>
@@ -20259,7 +20303,7 @@
       </c>
       <c r="AB214" s="57"/>
       <c r="AD214" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE214" s="35"/>
       <c r="AH214" s="19"/>
@@ -20269,7 +20313,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D215" s="52">
         <v>137109.56</v>
@@ -20341,7 +20385,7 @@
       </c>
       <c r="AB215" s="57"/>
       <c r="AD215" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE215" s="36"/>
       <c r="AH215" s="19"/>
@@ -20351,7 +20395,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -20387,7 +20431,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -20415,7 +20459,7 @@
       <c r="AA217" s="56"/>
       <c r="AB217" s="57"/>
       <c r="AD217" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE217" s="36">
         <v>0</v>
@@ -20427,7 +20471,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -20463,7 +20507,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -20536,7 +20580,7 @@
         <v>62</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D221" s="52">
         <v>396453.46</v>
@@ -20608,7 +20652,7 @@
       </c>
       <c r="AB221" s="57"/>
       <c r="AD221" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AE221" s="35">
         <v>-1014.25</v>
@@ -20622,7 +20666,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D222" s="52">
         <v>396453.46</v>
@@ -20694,7 +20738,7 @@
       </c>
       <c r="AB222" s="57"/>
       <c r="AD222" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AE222" s="36"/>
       <c r="AH222" s="19"/>
@@ -20704,7 +20748,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -20740,7 +20784,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -20768,7 +20812,7 @@
       <c r="AA224" s="56"/>
       <c r="AB224" s="57"/>
       <c r="AD224" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AE224" s="36">
         <v>0</v>
@@ -20780,7 +20824,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -20816,7 +20860,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -20849,6 +20893,303 @@
         <v>-1014.25</v>
       </c>
       <c r="AI226" s="60"/>
+    </row>
+    <row r="227" ht="9" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A227" s="61"/>
+      <c r="B227" s="61"/>
+      <c r="C227" s="61"/>
+      <c r="D227" s="61"/>
+      <c r="E227" s="61"/>
+      <c r="F227" s="61"/>
+      <c r="G227" s="61"/>
+      <c r="H227" s="61"/>
+      <c r="I227" s="61"/>
+      <c r="J227" s="61"/>
+      <c r="K227" s="61"/>
+      <c r="L227" s="61"/>
+      <c r="M227" s="61"/>
+      <c r="N227" s="61"/>
+      <c r="O227" s="61"/>
+      <c r="P227" s="61"/>
+      <c r="Q227" s="61"/>
+      <c r="R227" s="61"/>
+      <c r="S227" s="61"/>
+      <c r="T227" s="61"/>
+      <c r="U227" s="61"/>
+      <c r="V227" s="61"/>
+      <c r="W227" s="61"/>
+      <c r="X227" s="61"/>
+      <c r="Y227" s="61"/>
+      <c r="Z227" s="61"/>
+      <c r="AA227" s="61"/>
+      <c r="AD227" s="35"/>
+      <c r="AE227" s="35"/>
+      <c r="AH227" s="35"/>
+      <c r="AI227" s="35"/>
+    </row>
+    <row r="228" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A228" s="19">
+        <v>8530</v>
+      </c>
+      <c r="B228" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C228" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D228" s="52">
+        <v>0</v>
+      </c>
+      <c r="E228" s="52">
+        <v>0</v>
+      </c>
+      <c r="F228" s="52">
+        <v>0</v>
+      </c>
+      <c r="G228" s="53">
+        <v>0</v>
+      </c>
+      <c r="H228" s="52">
+        <v>0</v>
+      </c>
+      <c r="I228" s="52">
+        <v>0</v>
+      </c>
+      <c r="J228" s="52">
+        <v>0</v>
+      </c>
+      <c r="K228" s="52">
+        <v>0</v>
+      </c>
+      <c r="L228" s="52">
+        <v>0</v>
+      </c>
+      <c r="M228" s="53">
+        <v>0</v>
+      </c>
+      <c r="N228" s="53"/>
+      <c r="O228" s="52">
+        <v>0</v>
+      </c>
+      <c r="P228" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q228" s="52">
+        <v>0</v>
+      </c>
+      <c r="R228" s="53">
+        <v>0</v>
+      </c>
+      <c r="S228" s="54">
+        <v>0</v>
+      </c>
+      <c r="T228" s="54">
+        <v>0</v>
+      </c>
+      <c r="U228" s="54">
+        <v>0</v>
+      </c>
+      <c r="V228" s="53">
+        <v>0</v>
+      </c>
+      <c r="W228" s="53"/>
+      <c r="X228" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y228" s="55">
+        <v>0</v>
+      </c>
+      <c r="Z228" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA228" s="56">
+        <v>0</v>
+      </c>
+      <c r="AB228" s="57"/>
+      <c r="AD228" s="35"/>
+      <c r="AE228" s="35"/>
+      <c r="AH228" s="19"/>
+      <c r="AI228" s="58"/>
+    </row>
+    <row r="229" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A229" s="19"/>
+      <c r="B229" s="20"/>
+      <c r="C229" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="D229" s="52"/>
+      <c r="E229" s="52"/>
+      <c r="F229" s="52"/>
+      <c r="G229" s="53"/>
+      <c r="H229" s="52"/>
+      <c r="I229" s="52"/>
+      <c r="J229" s="52"/>
+      <c r="K229" s="52"/>
+      <c r="L229" s="52"/>
+      <c r="M229" s="53"/>
+      <c r="N229" s="53"/>
+      <c r="O229" s="52"/>
+      <c r="P229" s="52"/>
+      <c r="Q229" s="52"/>
+      <c r="R229" s="53"/>
+      <c r="S229" s="54"/>
+      <c r="T229" s="54"/>
+      <c r="U229" s="54"/>
+      <c r="V229" s="53"/>
+      <c r="W229" s="53"/>
+      <c r="X229" s="55"/>
+      <c r="Y229" s="55"/>
+      <c r="Z229" s="53"/>
+      <c r="AA229" s="56"/>
+      <c r="AB229" s="57"/>
+      <c r="AD229" s="35"/>
+      <c r="AE229" s="36"/>
+      <c r="AH229" s="19"/>
+      <c r="AI229" s="58"/>
+    </row>
+    <row r="230" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A230" s="19"/>
+      <c r="B230" s="20"/>
+      <c r="C230" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D230" s="52"/>
+      <c r="E230" s="52"/>
+      <c r="F230" s="52"/>
+      <c r="G230" s="53"/>
+      <c r="H230" s="52"/>
+      <c r="I230" s="52"/>
+      <c r="J230" s="52"/>
+      <c r="K230" s="52"/>
+      <c r="L230" s="52"/>
+      <c r="M230" s="53"/>
+      <c r="N230" s="53"/>
+      <c r="O230" s="52"/>
+      <c r="P230" s="52"/>
+      <c r="Q230" s="52"/>
+      <c r="R230" s="53"/>
+      <c r="S230" s="54"/>
+      <c r="T230" s="54"/>
+      <c r="U230" s="54"/>
+      <c r="V230" s="53"/>
+      <c r="W230" s="53"/>
+      <c r="X230" s="55"/>
+      <c r="Y230" s="55"/>
+      <c r="Z230" s="53"/>
+      <c r="AA230" s="56"/>
+      <c r="AB230" s="57"/>
+      <c r="AD230" s="35"/>
+      <c r="AE230" s="35"/>
+      <c r="AH230" s="19"/>
+      <c r="AI230" s="58"/>
+    </row>
+    <row r="231" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A231" s="19"/>
+      <c r="B231" s="20"/>
+      <c r="C231" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D231" s="52"/>
+      <c r="E231" s="52"/>
+      <c r="F231" s="52"/>
+      <c r="G231" s="53"/>
+      <c r="H231" s="52"/>
+      <c r="I231" s="52"/>
+      <c r="J231" s="52"/>
+      <c r="K231" s="52"/>
+      <c r="L231" s="52"/>
+      <c r="M231" s="53"/>
+      <c r="N231" s="53"/>
+      <c r="O231" s="52"/>
+      <c r="P231" s="52"/>
+      <c r="Q231" s="52"/>
+      <c r="R231" s="53"/>
+      <c r="S231" s="54"/>
+      <c r="T231" s="54"/>
+      <c r="U231" s="54"/>
+      <c r="V231" s="53"/>
+      <c r="W231" s="53"/>
+      <c r="X231" s="55"/>
+      <c r="Y231" s="55"/>
+      <c r="Z231" s="53"/>
+      <c r="AA231" s="56"/>
+      <c r="AB231" s="57"/>
+      <c r="AD231" s="35"/>
+      <c r="AE231" s="36"/>
+      <c r="AH231" s="19"/>
+      <c r="AI231" s="58"/>
+    </row>
+    <row r="232" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A232" s="19"/>
+      <c r="B232" s="20"/>
+      <c r="C232" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D232" s="52"/>
+      <c r="E232" s="52"/>
+      <c r="F232" s="52"/>
+      <c r="G232" s="53"/>
+      <c r="H232" s="52"/>
+      <c r="I232" s="52"/>
+      <c r="J232" s="52"/>
+      <c r="K232" s="52"/>
+      <c r="L232" s="52"/>
+      <c r="M232" s="53"/>
+      <c r="N232" s="53"/>
+      <c r="O232" s="52"/>
+      <c r="P232" s="52"/>
+      <c r="Q232" s="52"/>
+      <c r="R232" s="53"/>
+      <c r="S232" s="54"/>
+      <c r="T232" s="54"/>
+      <c r="U232" s="54"/>
+      <c r="V232" s="53"/>
+      <c r="W232" s="53"/>
+      <c r="X232" s="55"/>
+      <c r="Y232" s="55"/>
+      <c r="Z232" s="53"/>
+      <c r="AA232" s="56"/>
+      <c r="AB232" s="57"/>
+      <c r="AD232" s="35"/>
+      <c r="AE232" s="35"/>
+      <c r="AH232" s="19"/>
+      <c r="AI232" s="58"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A233" s="59"/>
+      <c r="B233" s="75"/>
+      <c r="C233" s="76" t="s">
+        <v>100</v>
+      </c>
+      <c r="D233" s="52"/>
+      <c r="E233" s="52"/>
+      <c r="F233" s="52"/>
+      <c r="G233" s="53"/>
+      <c r="H233" s="52"/>
+      <c r="I233" s="52"/>
+      <c r="J233" s="52"/>
+      <c r="K233" s="52"/>
+      <c r="L233" s="52"/>
+      <c r="M233" s="53"/>
+      <c r="N233" s="53"/>
+      <c r="O233" s="52"/>
+      <c r="P233" s="52"/>
+      <c r="Q233" s="52"/>
+      <c r="R233" s="53"/>
+      <c r="S233" s="54"/>
+      <c r="T233" s="54"/>
+      <c r="U233" s="54"/>
+      <c r="V233" s="53"/>
+      <c r="W233" s="53"/>
+      <c r="X233" s="55"/>
+      <c r="Y233" s="55"/>
+      <c r="Z233" s="53"/>
+      <c r="AA233" s="56"/>
+      <c r="AB233" s="57"/>
+      <c r="AD233" s="35"/>
+      <c r="AE233" s="35"/>
+      <c r="AH233" s="59"/>
+      <c r="AI233" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="58">
@@ -21418,7 +21759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21432,7 +21773,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21454,55 +21795,55 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2" s="81" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" s="82" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G2" s="83" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H2" s="83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I2" s="81" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J2" s="82" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K2" s="82" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L2" s="83" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M2" s="83" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N2" s="81" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O2" s="84" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21520,7 +21861,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21567,7 +21908,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21584,7 +21925,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -21631,10 +21972,10 @@
         <v>337.89039999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -21651,7 +21992,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -21694,7 +22035,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -21711,7 +22052,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -21758,7 +22099,7 @@
         <v>18.141660543717848</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -21775,12 +22116,12 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
       <c r="B12" s="54" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="52">
         <v>0</v>
@@ -21822,10 +22163,10 @@
         <v>-93.9165217391303</v>
       </c>
       <c r="Q12" s="35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -21842,7 +22183,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -21889,7 +22230,7 @@
         <v>62.640446428571394</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -21906,7 +22247,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -21951,7 +22292,7 @@
         <v>34.302939481268</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -21968,7 +22309,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -22015,10 +22356,10 @@
         <v>44.85015873015877</v>
       </c>
       <c r="Q18" s="35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -22035,7 +22376,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22074,7 +22415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22091,7 +22432,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22132,7 +22473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22149,7 +22490,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22188,7 +22529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22205,7 +22546,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22250,7 +22591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22267,7 +22608,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22310,7 +22651,7 @@
         <v>-7.109225589225597</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22327,7 +22668,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22370,7 +22711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22387,7 +22728,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22434,7 +22775,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22451,7 +22792,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22496,7 +22837,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22513,7 +22854,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22556,7 +22897,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22573,7 +22914,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22614,7 +22955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -22631,7 +22972,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -22676,7 +23017,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -22693,7 +23034,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -22736,7 +23077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -22753,7 +23094,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -22790,7 +23131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -22807,7 +23148,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -22848,7 +23189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -22865,7 +23206,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -22908,7 +23249,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -22925,7 +23266,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -22964,10 +23305,10 @@
         <v>0</v>
       </c>
       <c r="Q50" s="35" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -22984,7 +23325,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -23029,7 +23370,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -23046,7 +23387,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23091,7 +23432,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23108,7 +23449,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23153,7 +23494,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23170,7 +23511,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23207,7 +23548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23224,7 +23565,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23241,7 +23582,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23258,7 +23599,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23279,7 +23620,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23296,7 +23637,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23337,7 +23678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23354,7 +23695,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23399,24 +23740,42 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="35"/>
-      <c r="B67" s="35"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="36"/>
-      <c r="K67" s="36"/>
-      <c r="L67" s="37"/>
-      <c r="M67" s="36"/>
-      <c r="N67" s="35"/>
-      <c r="O67" s="36"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A67" s="102">
+        <f>'Main Sheet'!A68</f>
+      </c>
+      <c r="B67" s="98">
+        <f>'Main Sheet'!B68</f>
+      </c>
+      <c r="C67" s="99"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99">
+        <f>C67-D67</f>
+      </c>
+      <c r="F67" s="99"/>
+      <c r="G67" s="100">
+        <f>(E67+F67)/C67</f>
+      </c>
+      <c r="H67" s="100">
+        <f>'Deliverables Sheet'!AA228</f>
+      </c>
+      <c r="I67" s="98"/>
+      <c r="J67" s="99"/>
+      <c r="K67" s="99">
+        <f>(I67*40)+J67</f>
+      </c>
+      <c r="L67" s="100">
+        <f>((E67-K67)+F67)/C67</f>
+      </c>
+      <c r="M67" s="99">
+        <f>SUM(E67:F67)-K67</f>
+      </c>
+      <c r="N67" s="98"/>
+      <c r="O67" s="60">
+        <f>SUM(M67/(N67+I67))</f>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23429,38 +23788,20 @@
       <c r="J68" s="36"/>
       <c r="K68" s="36"/>
       <c r="L68" s="37"/>
-      <c r="M68" s="37"/>
+      <c r="M68" s="36"/>
       <c r="N68" s="35"/>
-      <c r="O68" s="35"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="B69" s="103" t="s">
-        <v>121</v>
-      </c>
-      <c r="C69" s="104">
-        <v>88818.76999999996</v>
-      </c>
-      <c r="D69" s="104">
-        <v>29887.739999999983</v>
-      </c>
-      <c r="E69" s="105">
-        <v>58931.02999999998</v>
-      </c>
-      <c r="F69" s="106" t="s">
-        <v>122</v>
-      </c>
-      <c r="G69" s="107">
-        <v>0.6634974791927427</v>
-      </c>
-      <c r="H69" s="108" t="s">
-        <v>123</v>
-      </c>
-      <c r="I69" s="109">
-        <v>0.0799203816940944</v>
-      </c>
+      <c r="O68" s="36"/>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A69" s="35"/>
+      <c r="B69" s="35"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="37"/>
+      <c r="I69" s="35"/>
       <c r="J69" s="36"/>
       <c r="K69" s="36"/>
       <c r="L69" s="37"/>
@@ -23468,29 +23809,33 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="59"/>
-      <c r="B70" s="98" t="s">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A70" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="B70" s="103" t="s">
+        <v>123</v>
+      </c>
+      <c r="C70" s="104">
+        <v>88818.76999999996</v>
+      </c>
+      <c r="D70" s="104">
+        <v>29887.739999999983</v>
+      </c>
+      <c r="E70" s="105">
+        <v>58931.02999999998</v>
+      </c>
+      <c r="F70" s="106" t="s">
         <v>124</v>
       </c>
-      <c r="C70" s="99">
-        <v>-22865.6</v>
-      </c>
-      <c r="D70" s="99">
-        <v>32774.04000000001</v>
-      </c>
-      <c r="E70" s="110">
-        <v>-55639.640000000014</v>
-      </c>
-      <c r="F70" s="111"/>
-      <c r="G70" s="112">
-        <v>2.433333916450914</v>
-      </c>
-      <c r="H70" s="113" t="s">
-        <v>123</v>
-      </c>
-      <c r="I70" s="114">
-        <v>2.685240710936954</v>
+      <c r="G70" s="107">
+        <v>0.6634974791927427</v>
+      </c>
+      <c r="H70" s="108" t="s">
+        <v>125</v>
+      </c>
+      <c r="I70" s="109">
+        <v>0.0799203816940944</v>
       </c>
       <c r="J70" s="36"/>
       <c r="K70" s="36"/>
@@ -23498,6 +23843,37 @@
       <c r="M70" s="37"/>
       <c r="N70" s="35"/>
       <c r="O70" s="35"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A71" s="59"/>
+      <c r="B71" s="98" t="s">
+        <v>126</v>
+      </c>
+      <c r="C71" s="99">
+        <v>-22865.6</v>
+      </c>
+      <c r="D71" s="99">
+        <v>32774.04000000001</v>
+      </c>
+      <c r="E71" s="110">
+        <v>-55639.640000000014</v>
+      </c>
+      <c r="F71" s="111"/>
+      <c r="G71" s="112">
+        <v>2.433333916450914</v>
+      </c>
+      <c r="H71" s="113" t="s">
+        <v>125</v>
+      </c>
+      <c r="I71" s="114">
+        <v>2.685240710936954</v>
+      </c>
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="37"/>
+      <c r="M71" s="37"/>
+      <c r="N71" s="35"/>
+      <c r="O71" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -23851,7 +24227,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AD110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -23862,7 +24238,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23883,55 +24259,55 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C2" s="117" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D2" s="117" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E2" s="117" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F2" s="117" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G2" s="117" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H2" s="117" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I2" s="117" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J2" s="117" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K2" s="117" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L2" s="117" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M2" s="117" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N2" s="117" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O2" s="117" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P2" s="117" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q2" s="118" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="R2" s="119"/>
       <c r="S2" s="120"/>
@@ -23945,12 +24321,12 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B3" s="123" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C3" s="124"/>
       <c r="D3" s="124"/>
@@ -24003,7 +24379,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -24036,10 +24412,10 @@
       <c r="P4" s="54"/>
       <c r="Q4" s="131"/>
       <c r="S4" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -24058,7 +24434,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24089,10 +24465,10 @@
       <c r="P6" s="54"/>
       <c r="Q6" s="131"/>
       <c r="S6" s="35" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24111,7 +24487,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24142,10 +24518,10 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="131"/>
       <c r="S8" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24164,7 +24540,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24199,10 +24575,10 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="131"/>
       <c r="S10" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24221,12 +24597,12 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="54">
         <v>1120.27</v>
@@ -24256,10 +24632,10 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="131"/>
       <c r="S12" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24278,7 +24654,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24313,10 +24689,10 @@
       <c r="P14" s="54"/>
       <c r="Q14" s="131"/>
       <c r="S14" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24335,7 +24711,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24368,7 +24744,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24387,7 +24763,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24420,7 +24796,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24439,7 +24815,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24470,7 +24846,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24489,7 +24865,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24524,7 +24900,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24543,7 +24919,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24576,7 +24952,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -24595,7 +24971,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -24626,7 +25002,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -24645,7 +25021,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -24677,7 +25053,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -24696,7 +25072,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -24732,7 +25108,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -24751,7 +25127,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -24780,7 +25156,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -24799,7 +25175,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -24830,7 +25206,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -24849,7 +25225,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -24882,7 +25258,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -24901,7 +25277,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -24937,7 +25313,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -24956,7 +25332,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -24991,7 +25367,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -25010,7 +25386,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25040,7 +25416,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -25059,7 +25435,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25099,7 +25475,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25118,7 +25494,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25147,7 +25523,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25166,7 +25542,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25199,7 +25575,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25218,7 +25594,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25251,7 +25627,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25270,7 +25646,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25306,7 +25682,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25325,7 +25701,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25361,7 +25737,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25380,7 +25756,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25414,7 +25790,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25433,7 +25809,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25468,7 +25844,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25487,7 +25863,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25506,7 +25882,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25525,7 +25901,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25546,7 +25922,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25565,7 +25941,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -25598,7 +25974,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -25617,7 +25993,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -25656,26 +26032,36 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67" s="142"/>
-      <c r="B67" s="143"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
-      <c r="L67" s="35"/>
-      <c r="M67" s="35"/>
-      <c r="N67" s="35"/>
-      <c r="O67" s="35"/>
-      <c r="P67" s="35"/>
-      <c r="Q67" s="144"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A67" s="19">
+        <f>'Main Sheet'!A68</f>
+      </c>
+      <c r="B67" s="20">
+        <f>'Main Sheet'!B68</f>
+      </c>
+      <c r="C67" s="54">
+        <f>LOOKUP(2,1/('Deliverables Sheet'!S229:S233&lt;&gt;0),'Deliverables Sheet'!S229:S233)</f>
+      </c>
+      <c r="D67" s="54">
+        <f>LOOKUP(2,1/('Deliverables Sheet'!T229:T233&lt;&gt;0),'Deliverables Sheet'!T229:T233)</f>
+      </c>
+      <c r="E67" s="54">
+        <f>LOOKUP(2,1/('Deliverables Sheet'!U229:U233&lt;&gt;0),'Deliverables Sheet'!U229:U233)</f>
+      </c>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="54"/>
+      <c r="J67" s="54"/>
+      <c r="K67" s="54"/>
+      <c r="L67" s="54"/>
+      <c r="M67" s="54"/>
+      <c r="N67" s="54"/>
+      <c r="O67" s="54"/>
+      <c r="P67" s="54"/>
+      <c r="Q67" s="54"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -25694,364 +26080,362 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="145"/>
-      <c r="B69" s="145"/>
-      <c r="C69" s="145"/>
-      <c r="D69" s="145"/>
-      <c r="E69" s="145"/>
-      <c r="F69" s="145"/>
-      <c r="G69" s="145"/>
-      <c r="H69" s="145"/>
-      <c r="I69" s="145"/>
-      <c r="J69" s="145"/>
-      <c r="K69" s="145"/>
-      <c r="L69" s="145"/>
-      <c r="M69" s="145"/>
-      <c r="N69" s="145"/>
-      <c r="O69" s="145"/>
-      <c r="P69" s="145"/>
-      <c r="Q69" s="145"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="142"/>
-      <c r="B70" s="146" t="s">
-        <v>145</v>
-      </c>
-      <c r="C70" s="147"/>
-      <c r="D70" s="147"/>
-      <c r="E70" s="147"/>
-      <c r="F70" s="147">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A69" s="142"/>
+      <c r="B69" s="143"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="35"/>
+      <c r="K69" s="35"/>
+      <c r="L69" s="35"/>
+      <c r="M69" s="35"/>
+      <c r="N69" s="35"/>
+      <c r="O69" s="35"/>
+      <c r="P69" s="35"/>
+      <c r="Q69" s="144"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A70" s="145"/>
+      <c r="B70" s="145"/>
+      <c r="C70" s="145"/>
+      <c r="D70" s="145"/>
+      <c r="E70" s="145"/>
+      <c r="F70" s="145"/>
+      <c r="G70" s="145"/>
+      <c r="H70" s="145"/>
+      <c r="I70" s="145"/>
+      <c r="J70" s="145"/>
+      <c r="K70" s="145"/>
+      <c r="L70" s="145"/>
+      <c r="M70" s="145"/>
+      <c r="N70" s="145"/>
+      <c r="O70" s="145"/>
+      <c r="P70" s="145"/>
+      <c r="Q70" s="145"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A71" s="142"/>
+      <c r="B71" s="146" t="s">
+        <v>147</v>
+      </c>
+      <c r="C71" s="147"/>
+      <c r="D71" s="147"/>
+      <c r="E71" s="147"/>
+      <c r="F71" s="147">
         <v>640</v>
       </c>
-      <c r="G70" s="147">
+      <c r="G71" s="147">
         <v>715</v>
       </c>
-      <c r="H70" s="147">
+      <c r="H71" s="147">
         <v>790</v>
       </c>
-      <c r="I70" s="147">
+      <c r="I71" s="147">
         <v>700</v>
       </c>
-      <c r="J70" s="147">
+      <c r="J71" s="147">
         <v>700</v>
       </c>
-      <c r="K70" s="147">
+      <c r="K71" s="147">
         <v>700</v>
       </c>
-      <c r="L70" s="147">
+      <c r="L71" s="147">
         <v>716</v>
       </c>
-      <c r="M70" s="147">
+      <c r="M71" s="147">
         <v>2520</v>
       </c>
-      <c r="N70" s="147">
+      <c r="N71" s="147">
         <v>3060</v>
       </c>
-      <c r="O70" s="147">
+      <c r="O71" s="147">
         <v>1316</v>
       </c>
-      <c r="P70" s="147">
+      <c r="P71" s="147">
         <v>914</v>
       </c>
-      <c r="Q70" s="147">
+      <c r="Q71" s="147">
         <v>650</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71" s="142"/>
-      <c r="B71" s="77" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20">
-        <v>140</v>
-      </c>
-      <c r="G71" s="20">
-        <v>15</v>
-      </c>
-      <c r="H71" s="20">
-        <v>90</v>
-      </c>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="20"/>
-      <c r="L71" s="20">
-        <v>16</v>
-      </c>
-      <c r="M71" s="20">
-        <v>800</v>
-      </c>
-      <c r="N71" s="20">
-        <v>858</v>
-      </c>
-      <c r="O71" s="20">
-        <v>476</v>
-      </c>
-      <c r="P71" s="20">
-        <v>214</v>
-      </c>
-      <c r="Q71" s="20">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
-        <v>147</v>
-      </c>
-      <c r="C72" s="20">
-        <v>4490.26</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
+      <c r="F72" s="20">
+        <v>140</v>
+      </c>
+      <c r="G72" s="20">
+        <v>15</v>
+      </c>
+      <c r="H72" s="20">
+        <v>90</v>
+      </c>
       <c r="I72" s="20"/>
       <c r="J72" s="20"/>
       <c r="K72" s="20"/>
-      <c r="L72" s="20"/>
+      <c r="L72" s="20">
+        <v>16</v>
+      </c>
       <c r="M72" s="20">
+        <v>800</v>
+      </c>
+      <c r="N72" s="20">
+        <v>858</v>
+      </c>
+      <c r="O72" s="20">
+        <v>476</v>
+      </c>
+      <c r="P72" s="20">
+        <v>214</v>
+      </c>
+      <c r="Q72" s="20">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A73" s="142"/>
+      <c r="B73" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="20">
+        <v>4490.26</v>
+      </c>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="20"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="20">
         <v>1020</v>
       </c>
-      <c r="N72" s="20">
+      <c r="N73" s="20">
         <v>1502</v>
       </c>
-      <c r="O72" s="20">
+      <c r="O73" s="20">
         <v>140</v>
       </c>
-      <c r="P72" s="20"/>
-      <c r="Q72" s="20"/>
-    </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73" s="142"/>
-      <c r="B73" s="148" t="s">
-        <v>148</v>
-      </c>
-      <c r="C73" s="149"/>
-      <c r="D73" s="149"/>
-      <c r="E73" s="149"/>
-      <c r="F73" s="149">
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A74" s="142"/>
+      <c r="B74" s="148" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="149"/>
+      <c r="D74" s="149"/>
+      <c r="E74" s="149"/>
+      <c r="F74" s="149">
         <v>1488</v>
       </c>
-      <c r="G73" s="149">
+      <c r="G74" s="149">
         <v>2112</v>
       </c>
-      <c r="H73" s="149">
+      <c r="H74" s="149">
         <v>1984</v>
       </c>
-      <c r="I73" s="149">
+      <c r="I74" s="149">
         <v>1884.8</v>
       </c>
-      <c r="J73" s="149">
+      <c r="J74" s="149">
         <v>1948.8</v>
       </c>
-      <c r="K73" s="149">
+      <c r="K74" s="149">
         <v>2083.2</v>
       </c>
-      <c r="L73" s="149">
+      <c r="L74" s="149">
         <v>2604.8</v>
       </c>
-      <c r="M73" s="149">
+      <c r="M74" s="149">
         <v>2486.4</v>
       </c>
-      <c r="N73" s="149">
+      <c r="N74" s="149">
         <v>2604.8</v>
       </c>
-      <c r="O73" s="149">
+      <c r="O74" s="149">
         <v>2217.6</v>
       </c>
-      <c r="P73" s="149">
+      <c r="P74" s="149">
         <v>2112</v>
       </c>
-      <c r="Q73" s="150">
+      <c r="Q74" s="150">
         <v>1478.4</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74" s="142"/>
-      <c r="B74" s="151" t="s">
-        <v>149</v>
-      </c>
-      <c r="C74" s="152"/>
-      <c r="D74" s="152"/>
-      <c r="E74" s="152"/>
-      <c r="F74" s="153">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A75" s="142"/>
+      <c r="B75" s="151" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="152"/>
+      <c r="D75" s="152"/>
+      <c r="E75" s="152"/>
+      <c r="F75" s="153">
         <v>-848</v>
       </c>
-      <c r="G74" s="153">
+      <c r="G75" s="153">
         <v>-1397</v>
       </c>
-      <c r="H74" s="154">
+      <c r="H75" s="154">
         <v>-1194</v>
       </c>
-      <c r="I74" s="153">
+      <c r="I75" s="153">
         <v>-1184.8</v>
       </c>
-      <c r="J74" s="153">
+      <c r="J75" s="153">
         <v>-1248.8</v>
       </c>
-      <c r="K74" s="153">
+      <c r="K75" s="153">
         <v>-1383.2</v>
       </c>
-      <c r="L74" s="153">
+      <c r="L75" s="153">
         <v>-1888.8</v>
       </c>
-      <c r="M74" s="153">
+      <c r="M75" s="153">
         <v>33.5999999999999</v>
       </c>
-      <c r="N74" s="153">
+      <c r="N75" s="153">
         <v>455.2</v>
       </c>
-      <c r="O74" s="153">
+      <c r="O75" s="153">
         <v>-901.6</v>
       </c>
-      <c r="P74" s="153">
+      <c r="P75" s="153">
         <v>-1198</v>
       </c>
-      <c r="Q74" s="155">
+      <c r="Q75" s="155">
         <v>-828.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="142"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
-      <c r="L75" s="35"/>
-      <c r="M75" s="35"/>
-      <c r="N75" s="35"/>
-      <c r="O75" s="35"/>
-      <c r="P75" s="35"/>
-      <c r="Q75" s="144"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
-      <c r="B76" s="156" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" s="157" t="s">
-        <v>151</v>
-      </c>
-      <c r="D76" s="157"/>
-      <c r="E76" s="157"/>
-      <c r="F76" s="158">
-        <v>15</v>
-      </c>
-      <c r="G76" s="159">
-        <v>20</v>
-      </c>
-      <c r="H76" s="159">
-        <v>20</v>
-      </c>
-      <c r="I76" s="159">
-        <v>19</v>
-      </c>
-      <c r="J76" s="159">
-        <v>21</v>
-      </c>
-      <c r="K76" s="159">
-        <v>21</v>
-      </c>
-      <c r="L76" s="159">
-        <v>22</v>
-      </c>
-      <c r="M76" s="159">
-        <v>21</v>
-      </c>
-      <c r="N76" s="159">
-        <v>22</v>
-      </c>
-      <c r="O76" s="159">
-        <v>21</v>
-      </c>
-      <c r="P76" s="159">
-        <v>20</v>
-      </c>
-      <c r="Q76" s="160">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A77" s="161"/>
-      <c r="B77" s="162" t="s">
+      <c r="B76" s="35"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="35"/>
+      <c r="M76" s="35"/>
+      <c r="N76" s="35"/>
+      <c r="O76" s="35"/>
+      <c r="P76" s="35"/>
+      <c r="Q76" s="144"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A77" s="142"/>
+      <c r="B77" s="156" t="s">
         <v>152</v>
       </c>
-      <c r="C77" s="157"/>
+      <c r="C77" s="157" t="s">
+        <v>153</v>
+      </c>
       <c r="D77" s="157"/>
       <c r="E77" s="157"/>
-      <c r="F77" s="163">
+      <c r="F77" s="158">
+        <v>15</v>
+      </c>
+      <c r="G77" s="159">
+        <v>20</v>
+      </c>
+      <c r="H77" s="159">
+        <v>20</v>
+      </c>
+      <c r="I77" s="159">
+        <v>19</v>
+      </c>
+      <c r="J77" s="159">
+        <v>21</v>
+      </c>
+      <c r="K77" s="159">
+        <v>21</v>
+      </c>
+      <c r="L77" s="159">
+        <v>22</v>
+      </c>
+      <c r="M77" s="159">
+        <v>21</v>
+      </c>
+      <c r="N77" s="159">
+        <v>22</v>
+      </c>
+      <c r="O77" s="159">
+        <v>21</v>
+      </c>
+      <c r="P77" s="159">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="160">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A78" s="161"/>
+      <c r="B78" s="162" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="157"/>
+      <c r="D78" s="157"/>
+      <c r="E78" s="157"/>
+      <c r="F78" s="163">
         <v>15.5</v>
       </c>
-      <c r="G77" s="163">
+      <c r="G78" s="163">
         <v>16.5</v>
       </c>
-      <c r="H77" s="163">
+      <c r="H78" s="163">
         <v>15.5</v>
       </c>
-      <c r="I77" s="163">
+      <c r="I78" s="163">
         <v>15.5</v>
       </c>
-      <c r="J77" s="163">
+      <c r="J78" s="163">
         <v>14.5</v>
       </c>
-      <c r="K77" s="163">
+      <c r="K78" s="163">
         <v>15.5</v>
       </c>
-      <c r="L77" s="163">
+      <c r="L78" s="163">
         <v>18.5</v>
       </c>
-      <c r="M77" s="163">
+      <c r="M78" s="163">
         <v>18.5</v>
       </c>
-      <c r="N77" s="163">
+      <c r="N78" s="163">
         <v>18.5</v>
       </c>
-      <c r="O77" s="163">
+      <c r="O78" s="163">
         <v>16.5</v>
       </c>
-      <c r="P77" s="163">
+      <c r="P78" s="163">
         <v>16.5</v>
       </c>
-      <c r="Q77" s="163">
+      <c r="Q78" s="163">
         <v>16.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="35"/>
-      <c r="B78" s="35"/>
-      <c r="C78" s="35"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
-      <c r="J78" s="35"/>
-      <c r="K78" s="35"/>
-      <c r="L78" s="35"/>
-      <c r="M78" s="35"/>
-      <c r="N78" s="35"/>
-      <c r="O78" s="35"/>
-      <c r="P78" s="35"/>
-      <c r="Q78" s="35"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
-      <c r="B79" s="164" t="s">
-        <v>153</v>
-      </c>
-      <c r="C79" s="165"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="35"/>
       <c r="D79" s="35"/>
       <c r="E79" s="35"/>
       <c r="F79" s="35"/>
@@ -26060,23 +26444,19 @@
       <c r="I79" s="35"/>
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
-      <c r="L79" s="166" t="s">
-        <v>154</v>
-      </c>
-      <c r="M79" s="166"/>
+      <c r="L79" s="35"/>
+      <c r="M79" s="35"/>
       <c r="N79" s="35"/>
       <c r="O79" s="35"/>
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
-      <c r="B80" s="167" t="s">
+      <c r="B80" s="164" t="s">
         <v>155</v>
       </c>
-      <c r="C80" s="168">
-        <v>1</v>
-      </c>
+      <c r="C80" s="165"/>
       <c r="D80" s="35"/>
       <c r="E80" s="35"/>
       <c r="F80" s="35"/>
@@ -26085,19 +26465,21 @@
       <c r="I80" s="35"/>
       <c r="J80" s="35"/>
       <c r="K80" s="35"/>
-      <c r="L80" s="35"/>
-      <c r="M80" s="35"/>
+      <c r="L80" s="166" t="s">
+        <v>156</v>
+      </c>
+      <c r="M80" s="166"/>
       <c r="N80" s="35"/>
       <c r="O80" s="35"/>
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
-      <c r="B81" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="C81" s="131">
+      <c r="B81" s="167" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" s="168">
         <v>1</v>
       </c>
       <c r="D81" s="35"/>
@@ -26115,10 +26497,10 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C82" s="131">
         <v>1</v>
@@ -26138,10 +26520,10 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C83" s="131">
         <v>1</v>
@@ -26161,10 +26543,10 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C84" s="131">
         <v>1</v>
@@ -26184,13 +26566,13 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C85" s="131">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D85" s="35"/>
       <c r="E85" s="35"/>
@@ -26207,13 +26589,13 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" s="131">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D86" s="35"/>
       <c r="E86" s="35"/>
@@ -26230,10 +26612,10 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C87" s="131">
         <v>1</v>
@@ -26253,10 +26635,10 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C88" s="131">
         <v>1</v>
@@ -26276,13 +26658,13 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C89" s="131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" s="35"/>
       <c r="E89" s="35"/>
@@ -26299,13 +26681,13 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C90" s="131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" s="35"/>
       <c r="E90" s="35"/>
@@ -26322,11 +26704,13 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
-      <c r="B91" s="19"/>
+      <c r="B91" s="19" t="s">
+        <v>167</v>
+      </c>
       <c r="C91" s="131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" s="35"/>
       <c r="E91" s="35"/>
@@ -26343,7 +26727,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26364,7 +26748,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26385,7 +26769,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26406,7 +26790,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26427,7 +26811,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26448,7 +26832,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26469,13 +26853,11 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
-      <c r="B98" s="19" t="s">
-        <v>166</v>
-      </c>
+      <c r="B98" s="19"/>
       <c r="C98" s="131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" s="35"/>
       <c r="E98" s="35"/>
@@ -26492,10 +26874,10 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C99" s="131">
         <v>1</v>
@@ -26515,10 +26897,10 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C100" s="131">
         <v>1</v>
@@ -26538,10 +26920,10 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C101" s="131">
         <v>1</v>
@@ -26561,10 +26943,10 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C102" s="131">
         <v>1</v>
@@ -26584,10 +26966,10 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C103" s="131">
         <v>1</v>
@@ -26607,10 +26989,10 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C104" s="131">
         <v>1</v>
@@ -26630,10 +27012,14 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="131"/>
+      <c r="B105" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C105" s="131">
+        <v>1</v>
+      </c>
       <c r="D105" s="35"/>
       <c r="E105" s="35"/>
       <c r="F105" s="35"/>
@@ -26649,7 +27035,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -26668,7 +27054,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -26687,10 +27073,10 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
-      <c r="B108" s="169"/>
-      <c r="C108" s="150"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="131"/>
       <c r="D108" s="35"/>
       <c r="E108" s="35"/>
       <c r="F108" s="35"/>
@@ -26706,14 +27092,10 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
-      <c r="B109" s="164" t="s">
-        <v>173</v>
-      </c>
-      <c r="C109" s="170">
-        <v>16.5</v>
-      </c>
+      <c r="B109" s="169"/>
+      <c r="C109" s="150"/>
       <c r="D109" s="35"/>
       <c r="E109" s="35"/>
       <c r="F109" s="35"/>
@@ -26728,6 +27110,29 @@
       <c r="O109" s="35"/>
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
+    </row>
+    <row r="110" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A110" s="35"/>
+      <c r="B110" s="164" t="s">
+        <v>175</v>
+      </c>
+      <c r="C110" s="170">
+        <v>16.5</v>
+      </c>
+      <c r="D110" s="35"/>
+      <c r="E110" s="35"/>
+      <c r="F110" s="35"/>
+      <c r="G110" s="35"/>
+      <c r="H110" s="35"/>
+      <c r="I110" s="35"/>
+      <c r="J110" s="35"/>
+      <c r="K110" s="35"/>
+      <c r="L110" s="35"/>
+      <c r="M110" s="35"/>
+      <c r="N110" s="35"/>
+      <c r="O110" s="35"/>
+      <c r="P110" s="35"/>
+      <c r="Q110" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -26762,8 +27167,8 @@
     <mergeCell ref="A61:Q61"/>
     <mergeCell ref="A63:Q63"/>
     <mergeCell ref="A65:Q65"/>
-    <mergeCell ref="A69:Q69"/>
-    <mergeCell ref="C76:E77"/>
+    <mergeCell ref="A70:Q70"/>
+    <mergeCell ref="C77:E78"/>
   </mergeCells>
   <conditionalFormatting sqref="F74:Q74">
     <cfRule type="cellIs" dxfId="229" priority="2" operator="lessThan">
@@ -26780,12 +27185,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -26815,9 +27221,9 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -26848,9 +27254,9 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -26881,9 +27287,9 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B5" s="175"/>
       <c r="C5" s="175"/>
@@ -26914,9 +27320,9 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -26947,9 +27353,9 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B7" s="177"/>
       <c r="C7" s="177"/>
@@ -26980,9 +27386,9 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -27013,9 +27419,9 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B9" s="178"/>
       <c r="C9" s="178"/>
@@ -27046,7 +27452,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27077,7 +27483,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27108,9 +27514,9 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B12" s="181"/>
       <c r="C12" s="181"/>
@@ -27141,9 +27547,9 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B13" s="182"/>
       <c r="C13" s="182"/>
@@ -27174,9 +27580,9 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B14" s="183"/>
       <c r="C14" s="183"/>
@@ -27207,9 +27613,9 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B15" s="172"/>
       <c r="C15" s="172"/>
@@ -27240,9 +27646,9 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B16" s="184"/>
       <c r="C16" s="184"/>
@@ -27273,9 +27679,9 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B17" s="185"/>
       <c r="C17" s="185"/>
@@ -27306,9 +27712,9 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B18" s="186"/>
       <c r="C18" s="186"/>
@@ -27339,9 +27745,9 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
@@ -27372,9 +27778,9 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" s="187"/>
       <c r="C20" s="187"/>
@@ -27405,9 +27811,9 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B21" s="188"/>
       <c r="C21" s="188"/>
@@ -27438,9 +27844,9 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B22" s="188"/>
       <c r="C22" s="188"/>
@@ -27471,9 +27877,9 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B23" s="188"/>
       <c r="C23" s="188"/>
@@ -27504,9 +27910,9 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B24" s="188"/>
       <c r="C24" s="188"/>
@@ -27537,9 +27943,9 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B25" s="189"/>
       <c r="C25" s="189"/>
@@ -27570,9 +27976,9 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181"/>
@@ -27603,9 +28009,9 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B27" s="190"/>
       <c r="C27" s="190"/>
@@ -27636,9 +28042,9 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -27668,9 +28074,9 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B29" s="190"/>
       <c r="C29" s="190"/>
@@ -27700,9 +28106,9 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B30" s="191"/>
       <c r="C30" s="191"/>
@@ -27732,9 +28138,9 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B31" s="191"/>
       <c r="C31" s="191"/>
@@ -27764,9 +28170,9 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B32" s="191"/>
       <c r="C32" s="191"/>
@@ -27796,7 +28202,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -27826,7 +28232,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -27856,9 +28262,9 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" s="192"/>
       <c r="C35" s="192"/>
@@ -27888,9 +28294,9 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B36" s="193"/>
       <c r="C36" s="193"/>
@@ -27920,9 +28326,9 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B37" s="194"/>
       <c r="C37" s="194"/>
@@ -27952,9 +28358,9 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B38" s="179"/>
       <c r="C38" s="179"/>
@@ -27984,9 +28390,9 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B39" s="181"/>
       <c r="C39" s="181"/>
@@ -28016,7 +28422,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -28046,9 +28452,9 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B41" s="172"/>
       <c r="C41" s="172"/>
@@ -28078,9 +28484,9 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B42" s="196"/>
       <c r="C42" s="196"/>
@@ -28110,9 +28516,9 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B43" s="172"/>
       <c r="C43" s="172"/>
@@ -28142,9 +28548,9 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B44" s="197"/>
       <c r="C44" s="197"/>
@@ -28174,7 +28580,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28204,7 +28610,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28234,7 +28640,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28264,7 +28670,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28294,9 +28700,9 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B49" s="172"/>
       <c r="C49" s="172"/>
@@ -28326,9 +28732,9 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B50" s="200"/>
       <c r="C50" s="200"/>
@@ -28358,7 +28764,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28388,7 +28794,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28418,7 +28824,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28448,7 +28854,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28478,7 +28884,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28508,7 +28914,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -28603,12 +29009,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B2" s="171"/>
       <c r="C2" s="171"/>
@@ -28638,7 +29045,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -28669,7 +29076,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -28700,7 +29107,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -28731,7 +29138,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -28762,7 +29169,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -28793,7 +29200,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -28824,7 +29231,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -28855,7 +29262,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -28886,7 +29293,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -28917,7 +29324,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -28948,7 +29355,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -28979,7 +29386,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -29010,7 +29417,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -29041,7 +29448,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29072,7 +29479,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29103,7 +29510,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29134,7 +29541,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29165,7 +29572,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29196,7 +29603,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29227,7 +29634,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29257,7 +29664,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29287,7 +29694,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29317,7 +29724,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29347,7 +29754,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29377,7 +29784,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29407,7 +29814,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29437,7 +29844,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29467,7 +29874,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29497,7 +29904,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29527,7 +29934,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -29557,7 +29964,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -29587,7 +29994,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -29617,7 +30024,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -29647,7 +30054,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -29677,7 +30084,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -29707,9 +30114,9 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B38" s="172"/>
       <c r="C38" s="172"/>
@@ -29739,9 +30146,9 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B39" s="200"/>
       <c r="C39" s="200"/>
@@ -29771,7 +30178,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -29801,7 +30208,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -29831,7 +30238,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -29861,7 +30268,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -29891,7 +30298,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -29921,7 +30328,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -30076,88 +30483,88 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" s="43" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" s="43" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" s="43" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O2" s="42" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q2" s="42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R2" s="43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S2" s="43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" s="40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="V2" s="214" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W2" s="214" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X2" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Y2" s="40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="46" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="47" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="46" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="48" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AG2" s="35"/>
       <c r="AH2" s="35"/>
@@ -30198,10 +30605,10 @@
       <c r="AG3" s="35"/>
       <c r="AH3" s="35"/>
       <c r="AK3" s="49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AL3" s="50" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -30214,7 +30621,7 @@
         <v>Charity Hospital</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="52">
         <v>1914143.52</v>
@@ -30310,7 +30717,7 @@
       </c>
       <c r="AE4" s="57"/>
       <c r="AG4" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH4" s="35">
         <f>AK9</f>
@@ -30329,7 +30736,7 @@
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" s="52">
         <v>1922479.92</v>
@@ -30418,7 +30825,7 @@
       </c>
       <c r="AE5" s="57"/>
       <c r="AG5" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH5" s="36">
         <f>AL9</f>
@@ -30437,7 +30844,7 @@
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" s="52">
         <v>1922479.92</v>
@@ -30544,7 +30951,7 @@
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
@@ -30617,7 +31024,7 @@
       </c>
       <c r="AE7" s="57"/>
       <c r="AG7" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH7" s="36">
         <v>0</v>
@@ -30635,7 +31042,7 @@
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
@@ -30722,7 +31129,7 @@
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -30851,7 +31258,7 @@
         <v>Fisher Developements</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" s="65">
         <v>381671.63</v>
@@ -30940,7 +31347,7 @@
       </c>
       <c r="AE11" s="57"/>
       <c r="AG11" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH11" s="35">
         <f>AK16</f>
@@ -30959,7 +31366,7 @@
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="63" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="52">
         <v>382219.49</v>
@@ -31048,7 +31455,7 @@
       </c>
       <c r="AE12" s="57"/>
       <c r="AG12" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH12" s="36">
         <f>AL16</f>
@@ -31067,7 +31474,7 @@
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" s="52">
         <v>382219.49</v>
@@ -31170,7 +31577,7 @@
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="63" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="65">
         <v>383409.63</v>
@@ -31251,7 +31658,7 @@
       </c>
       <c r="AE14" s="57"/>
       <c r="AG14" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH14" s="36">
         <v>0</v>
@@ -31269,7 +31676,7 @@
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="63" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" s="65">
         <v>383409.63</v>
@@ -31358,7 +31765,7 @@
       <c r="A16" s="19"/>
       <c r="B16" s="20"/>
       <c r="C16" s="63" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" s="65">
         <v>383409.63</v>
@@ -31492,7 +31899,7 @@
         <v>3 Innovation Road</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D18" s="52">
         <v>449818.08</v>
@@ -31585,7 +31992,7 @@
       </c>
       <c r="AE18" s="57"/>
       <c r="AG18" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH18" s="35">
         <f>AK23</f>
@@ -31604,7 +32011,7 @@
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
       <c r="C19" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D19" s="52">
         <v>449818.08</v>
@@ -31695,7 +32102,7 @@
       </c>
       <c r="AE19" s="57"/>
       <c r="AG19" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH19" s="36">
         <f>AL23</f>
@@ -31714,7 +32121,7 @@
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" s="52">
         <v>449818.08</v>
@@ -31819,7 +32226,7 @@
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
@@ -31894,7 +32301,7 @@
       </c>
       <c r="AE21" s="57"/>
       <c r="AG21" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH21" s="36">
         <v>0</v>
@@ -31912,7 +32319,7 @@
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
@@ -32001,7 +32408,7 @@
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
@@ -32134,7 +32541,7 @@
         <v>Rolly Autowash</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D25" s="52">
         <v>38856.96</v>
@@ -32227,7 +32634,7 @@
       </c>
       <c r="AE25" s="57"/>
       <c r="AG25" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH25" s="35">
         <f>AK30</f>
@@ -32246,7 +32653,7 @@
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D26" s="52">
         <v>38856.96</v>
@@ -32339,7 +32746,7 @@
       </c>
       <c r="AE26" s="57"/>
       <c r="AG26" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH26" s="36">
         <f>AL30</f>
@@ -32358,7 +32765,7 @@
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D27" s="52">
         <v>38856.96</v>
@@ -32465,7 +32872,7 @@
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52">
@@ -32548,7 +32955,7 @@
       </c>
       <c r="AE28" s="57"/>
       <c r="AG28" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH28" s="36">
         <v>0</v>
@@ -32566,7 +32973,7 @@
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D29" s="52"/>
       <c r="E29" s="52">
@@ -32663,7 +33070,7 @@
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52">
@@ -32802,7 +33209,7 @@
         <v>Murney - 1 Freight Drive + 109 Iport</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D32" s="52">
         <v>69191.71</v>
@@ -32893,7 +33300,7 @@
       </c>
       <c r="AE32" s="57"/>
       <c r="AG32" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH32" s="35">
         <f>AK37</f>
@@ -32912,7 +33319,7 @@
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D33" s="52">
         <v>69191.71</v>
@@ -33001,7 +33408,7 @@
       </c>
       <c r="AE33" s="57"/>
       <c r="AG33" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH33" s="36">
         <f>AL37</f>
@@ -33020,7 +33427,7 @@
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D34" s="52">
         <v>69191.71</v>
@@ -33123,7 +33530,7 @@
       <c r="A35" s="19"/>
       <c r="B35" s="20"/>
       <c r="C35" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D35" s="52"/>
       <c r="E35" s="52"/>
@@ -33196,7 +33603,7 @@
       </c>
       <c r="AE35" s="57"/>
       <c r="AG35" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH35" s="36">
         <v>0</v>
@@ -33214,7 +33621,7 @@
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D36" s="52"/>
       <c r="E36" s="52"/>
@@ -33301,7 +33708,7 @@
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D37" s="52"/>
       <c r="E37" s="52"/>
@@ -33430,7 +33837,7 @@
         <v>Monkey Toe - Fisher fit out</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D39" s="52">
         <v>44956.29</v>
@@ -33517,7 +33924,7 @@
       </c>
       <c r="AE39" s="57"/>
       <c r="AG39" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH39" s="35">
         <f>AK44</f>
@@ -33536,7 +33943,7 @@
       <c r="A40" s="19"/>
       <c r="B40" s="20"/>
       <c r="C40" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D40" s="52">
         <v>44956.29</v>
@@ -33621,7 +34028,7 @@
       </c>
       <c r="AE40" s="57"/>
       <c r="AG40" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH40" s="36">
         <f>AL44</f>
@@ -33640,7 +34047,7 @@
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D41" s="52">
         <v>44956.29</v>
@@ -33743,7 +34150,7 @@
       <c r="A42" s="19"/>
       <c r="B42" s="20"/>
       <c r="C42" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -33820,7 +34227,7 @@
       </c>
       <c r="AE42" s="57"/>
       <c r="AG42" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH42" s="36">
         <v>0</v>
@@ -33838,7 +34245,7 @@
       <c r="A43" s="19"/>
       <c r="B43" s="20"/>
       <c r="C43" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D43" s="52"/>
       <c r="E43" s="52"/>
@@ -33929,7 +34336,7 @@
       <c r="A44" s="19"/>
       <c r="B44" s="20"/>
       <c r="C44" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -34062,7 +34469,7 @@
         <v>Tenancy 2 - Fisher Fit out</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D46" s="52">
         <v>7495.54</v>
@@ -34155,7 +34562,7 @@
       </c>
       <c r="AE46" s="57"/>
       <c r="AG46" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH46" s="35">
         <f>AK51</f>
@@ -34174,7 +34581,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D47" s="52">
         <v>7495.54</v>
@@ -34267,7 +34674,7 @@
       </c>
       <c r="AE47" s="57"/>
       <c r="AG47" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH47" s="36">
         <f>AL51</f>
@@ -34286,7 +34693,7 @@
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D48" s="52">
         <v>7495.54</v>
@@ -34393,7 +34800,7 @@
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D49" s="52"/>
       <c r="E49" s="52">
@@ -34474,7 +34881,7 @@
       </c>
       <c r="AE49" s="57"/>
       <c r="AG49" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH49" s="36">
         <v>0</v>
@@ -34492,7 +34899,7 @@
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D50" s="52"/>
       <c r="E50" s="52">
@@ -34587,7 +34994,7 @@
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D51" s="52"/>
       <c r="E51" s="52">
@@ -34724,7 +35131,7 @@
         <v>Studio DB - tautara fit out</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D53" s="52">
         <v>100348.26</v>
@@ -34817,7 +35224,7 @@
       </c>
       <c r="AE53" s="57"/>
       <c r="AG53" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH53" s="35">
         <f>AK58</f>
@@ -34836,7 +35243,7 @@
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D54" s="52">
         <v>100348.26</v>
@@ -34925,7 +35332,7 @@
       </c>
       <c r="AE54" s="57"/>
       <c r="AG54" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH54" s="36">
         <f>AL58</f>
@@ -34944,7 +35351,7 @@
       <c r="A55" s="19"/>
       <c r="B55" s="20"/>
       <c r="C55" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D55" s="52">
         <v>100348.26</v>
@@ -35047,7 +35454,7 @@
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D56" s="52"/>
       <c r="E56" s="52"/>
@@ -35120,7 +35527,7 @@
       </c>
       <c r="AE56" s="57"/>
       <c r="AG56" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH56" s="36">
         <v>0</v>
@@ -35138,7 +35545,7 @@
       <c r="A57" s="19"/>
       <c r="B57" s="20"/>
       <c r="C57" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D57" s="52"/>
       <c r="E57" s="52"/>
@@ -35225,7 +35632,7 @@
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D58" s="52"/>
       <c r="E58" s="52"/>
@@ -35358,7 +35765,7 @@
         <v>35 Mania</v>
       </c>
       <c r="C60" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D60" s="52">
         <v>98524.85</v>
@@ -35449,7 +35856,7 @@
       </c>
       <c r="AE60" s="57"/>
       <c r="AG60" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH60" s="35">
         <f>AK65</f>
@@ -35468,7 +35875,7 @@
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D61" s="52">
         <v>98524.85</v>
@@ -35559,7 +35966,7 @@
       </c>
       <c r="AE61" s="57"/>
       <c r="AG61" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH61" s="36">
         <f>AL65</f>
@@ -35578,7 +35985,7 @@
       <c r="A62" s="19"/>
       <c r="B62" s="20"/>
       <c r="C62" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D62" s="52">
         <v>98524.85</v>
@@ -35683,7 +36090,7 @@
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52"/>
@@ -35760,7 +36167,7 @@
       </c>
       <c r="AE63" s="57"/>
       <c r="AG63" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH63" s="36">
         <v>0</v>
@@ -35778,7 +36185,7 @@
       <c r="A64" s="19"/>
       <c r="B64" s="20"/>
       <c r="C64" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D64" s="52"/>
       <c r="E64" s="52"/>
@@ -35869,7 +36276,7 @@
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D65" s="52"/>
       <c r="E65" s="52"/>
@@ -36002,7 +36409,7 @@
         <v>Cooltranz stage 4</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D67" s="52">
         <v>87970.61</v>
@@ -36091,7 +36498,7 @@
       </c>
       <c r="AE67" s="57"/>
       <c r="AG67" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH67" s="35">
         <f>AK72</f>
@@ -36110,7 +36517,7 @@
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D68" s="52">
         <v>87970.61</v>
@@ -36201,7 +36608,7 @@
       </c>
       <c r="AE68" s="57"/>
       <c r="AG68" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH68" s="36">
         <f>AL72</f>
@@ -36220,7 +36627,7 @@
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
@@ -36309,7 +36716,7 @@
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D70" s="52"/>
       <c r="E70" s="52"/>
@@ -36384,7 +36791,7 @@
       </c>
       <c r="AE70" s="57"/>
       <c r="AG70" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH70" s="36">
         <v>0</v>
@@ -36402,7 +36809,7 @@
       <c r="A71" s="19"/>
       <c r="B71" s="20"/>
       <c r="C71" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D71" s="52"/>
       <c r="E71" s="52"/>
@@ -36491,7 +36898,7 @@
       <c r="A72" s="19"/>
       <c r="B72" s="20"/>
       <c r="C72" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D72" s="52"/>
       <c r="E72" s="52"/>
@@ -36620,7 +37027,7 @@
         <v>Andrew Reeve Stage 2</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D74" s="52">
         <v>210242.4</v>
@@ -36713,7 +37120,7 @@
       </c>
       <c r="AE74" s="57"/>
       <c r="AG74" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH74" s="35">
         <f>AK79</f>
@@ -36732,7 +37139,7 @@
       <c r="A75" s="19"/>
       <c r="B75" s="20"/>
       <c r="C75" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D75" s="52">
         <v>210242.4</v>
@@ -36823,7 +37230,7 @@
       </c>
       <c r="AE75" s="57"/>
       <c r="AG75" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH75" s="36">
         <f>AL79</f>
@@ -36842,7 +37249,7 @@
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D76" s="52">
         <v>210242.4</v>
@@ -36947,7 +37354,7 @@
       <c r="A77" s="19"/>
       <c r="B77" s="20"/>
       <c r="C77" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D77" s="52"/>
       <c r="E77" s="52"/>
@@ -37026,7 +37433,7 @@
       </c>
       <c r="AE77" s="57"/>
       <c r="AG77" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH77" s="36">
         <v>0</v>
@@ -37044,7 +37451,7 @@
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -37139,7 +37546,7 @@
       <c r="A79" s="19"/>
       <c r="B79" s="20"/>
       <c r="C79" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D79" s="52"/>
       <c r="E79" s="52"/>
@@ -37276,7 +37683,7 @@
         <v>5 Sanscrit Place</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D81" s="52">
         <v>43448.62</v>
@@ -37369,7 +37776,7 @@
       </c>
       <c r="AE81" s="57"/>
       <c r="AG81" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH81" s="35">
         <f>AK86</f>
@@ -37388,7 +37795,7 @@
       <c r="A82" s="19"/>
       <c r="B82" s="20"/>
       <c r="C82" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D82" s="52">
         <v>43448.62</v>
@@ -37481,7 +37888,7 @@
       </c>
       <c r="AE82" s="57"/>
       <c r="AG82" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH82" s="36">
         <f>AL86</f>
@@ -37500,7 +37907,7 @@
       <c r="A83" s="19"/>
       <c r="B83" s="20"/>
       <c r="C83" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D83" s="52">
         <v>0</v>
@@ -37605,7 +38012,7 @@
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D84" s="52">
         <v>0</v>
@@ -37696,7 +38103,7 @@
       </c>
       <c r="AE84" s="57"/>
       <c r="AG84" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH84" s="36">
         <v>0</v>
@@ -37714,7 +38121,7 @@
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D85" s="52">
         <v>0</v>
@@ -37817,7 +38224,7 @@
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D86" s="52">
         <v>0</v>
@@ -37962,7 +38369,7 @@
         <v>Melhuish House</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D88" s="67">
         <v>49964.93</v>
@@ -38055,7 +38462,7 @@
       </c>
       <c r="AE88" s="57"/>
       <c r="AG88" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH88" s="35">
         <f>AK93</f>
@@ -38074,7 +38481,7 @@
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D89" s="67">
         <v>49964.93</v>
@@ -38163,7 +38570,7 @@
       </c>
       <c r="AE89" s="57"/>
       <c r="AG89" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH89" s="36">
         <f>AL93</f>
@@ -38182,7 +38589,7 @@
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D90" s="67">
         <v>0</v>
@@ -38285,7 +38692,7 @@
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D91" s="67">
         <v>0</v>
@@ -38374,7 +38781,7 @@
       </c>
       <c r="AE91" s="57"/>
       <c r="AG91" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH91" s="36">
         <v>0</v>
@@ -38392,7 +38799,7 @@
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D92" s="67">
         <v>0</v>
@@ -38495,7 +38902,7 @@
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D93" s="67">
         <v>0</v>
@@ -38640,7 +39047,7 @@
         <v>6 Tiroroa Lane</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D95" s="52">
         <v>109103.76</v>
@@ -38733,7 +39140,7 @@
       </c>
       <c r="AE95" s="57"/>
       <c r="AG95" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH95" s="35">
         <f>AK100</f>
@@ -38752,7 +39159,7 @@
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D96" s="52">
         <v>109103.76</v>
@@ -38845,7 +39252,7 @@
       </c>
       <c r="AE96" s="57"/>
       <c r="AG96" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH96" s="36">
         <f>AL100</f>
@@ -38864,7 +39271,7 @@
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D97" s="52">
         <v>0</v>
@@ -38971,7 +39378,7 @@
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D98" s="52">
         <v>0</v>
@@ -39064,7 +39471,7 @@
       </c>
       <c r="AE98" s="57"/>
       <c r="AG98" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH98" s="36">
         <v>0</v>
@@ -39082,7 +39489,7 @@
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D99" s="52">
         <v>0</v>
@@ -39187,7 +39594,7 @@
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D100" s="52">
         <v>0</v>
@@ -39334,7 +39741,7 @@
         <v>Major Hornbrook </v>
       </c>
       <c r="C102" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D102" s="52">
         <v>27742.44</v>
@@ -39425,7 +39832,7 @@
       </c>
       <c r="AE102" s="57"/>
       <c r="AG102" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH102" s="35">
         <f>AK107</f>
@@ -39444,7 +39851,7 @@
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D103" s="52">
         <v>27861.41</v>
@@ -39535,7 +39942,7 @@
       </c>
       <c r="AE103" s="57"/>
       <c r="AG103" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH103" s="36">
         <f>AL107</f>
@@ -39554,7 +39961,7 @@
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D104" s="52">
         <v>0</v>
@@ -39659,7 +40066,7 @@
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D105" s="52">
         <v>0</v>
@@ -39750,7 +40157,7 @@
       </c>
       <c r="AE105" s="57"/>
       <c r="AG105" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH105" s="36">
         <v>0</v>
@@ -39768,7 +40175,7 @@
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D106" s="52">
         <v>0</v>
@@ -39873,7 +40280,7 @@
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D107" s="52">
         <v>0</v>
@@ -40020,7 +40427,7 @@
         <v>Inline Architecture</v>
       </c>
       <c r="C109" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D109" s="52">
         <v>21300.45</v>
@@ -40112,7 +40519,7 @@
       </c>
       <c r="AE109" s="57"/>
       <c r="AG109" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH109" s="35">
         <f>AK114</f>
@@ -40131,7 +40538,7 @@
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D110" s="52">
         <v>21300.45</v>
@@ -40224,7 +40631,7 @@
       </c>
       <c r="AE110" s="57"/>
       <c r="AG110" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH110" s="36">
         <f>AL114</f>
@@ -40243,7 +40650,7 @@
       <c r="A111" s="19"/>
       <c r="B111" s="20"/>
       <c r="C111" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D111" s="52">
         <v>0</v>
@@ -40350,7 +40757,7 @@
       <c r="A112" s="19"/>
       <c r="B112" s="20"/>
       <c r="C112" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D112" s="52">
         <v>0</v>
@@ -40443,7 +40850,7 @@
       </c>
       <c r="AE112" s="57"/>
       <c r="AG112" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH112" s="36">
         <v>0</v>
@@ -40461,7 +40868,7 @@
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D113" s="52">
         <v>0</v>
@@ -40568,7 +40975,7 @@
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D114" s="52">
         <v>0</v>
@@ -40717,7 +41124,7 @@
         <v>Percival Bach</v>
       </c>
       <c r="C116" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D116" s="52">
         <v>63405.46</v>
@@ -40810,7 +41217,7 @@
       </c>
       <c r="AE116" s="57"/>
       <c r="AG116" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH116" s="35">
         <f>AK121</f>
@@ -40829,7 +41236,7 @@
       <c r="A117" s="19"/>
       <c r="B117" s="20"/>
       <c r="C117" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D117" s="52">
         <v>63405.46</v>
@@ -40922,7 +41329,7 @@
       </c>
       <c r="AE117" s="57"/>
       <c r="AG117" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH117" s="36">
         <f>AL121</f>
@@ -40941,7 +41348,7 @@
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D118" s="52">
         <v>0</v>
@@ -41048,7 +41455,7 @@
       <c r="A119" s="19"/>
       <c r="B119" s="20"/>
       <c r="C119" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D119" s="52">
         <v>0</v>
@@ -41141,7 +41548,7 @@
       </c>
       <c r="AE119" s="57"/>
       <c r="AG119" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH119" s="36">
         <v>0</v>
@@ -41159,7 +41566,7 @@
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D120" s="52">
         <v>0</v>
@@ -41266,7 +41673,7 @@
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D121" s="52">
         <v>0</v>
@@ -41415,7 +41822,7 @@
         <v>St Albans Street</v>
       </c>
       <c r="C123" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D123" s="52">
         <v>0</v>
@@ -41507,7 +41914,7 @@
       </c>
       <c r="AE123" s="57"/>
       <c r="AG123" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH123" s="35">
         <f>AK128</f>
@@ -41526,7 +41933,7 @@
       <c r="A124" s="19"/>
       <c r="B124" s="20"/>
       <c r="C124" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D124" s="52">
         <v>0</v>
@@ -41615,7 +42022,7 @@
       </c>
       <c r="AE124" s="57"/>
       <c r="AG124" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH124" s="36">
         <f>AL128</f>
@@ -41634,7 +42041,7 @@
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D125" s="52">
         <v>0</v>
@@ -41737,7 +42144,7 @@
       <c r="A126" s="19"/>
       <c r="B126" s="20"/>
       <c r="C126" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D126" s="52">
         <v>0</v>
@@ -41826,7 +42233,7 @@
       </c>
       <c r="AE126" s="57"/>
       <c r="AG126" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH126" s="36">
         <v>0</v>
@@ -41844,7 +42251,7 @@
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D127" s="52">
         <v>0</v>
@@ -41947,7 +42354,7 @@
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D128" s="52">
         <v>0</v>
@@ -42092,7 +42499,7 @@
         <v>4 Perry St</v>
       </c>
       <c r="C130" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D130" s="52">
         <v>47191.69</v>
@@ -42185,7 +42592,7 @@
       </c>
       <c r="AE130" s="57"/>
       <c r="AG130" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH130" s="35">
         <f>AK135</f>
@@ -42204,7 +42611,7 @@
       <c r="A131" s="19"/>
       <c r="B131" s="20"/>
       <c r="C131" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D131" s="52">
         <v>47191.69</v>
@@ -42297,7 +42704,7 @@
       </c>
       <c r="AE131" s="57"/>
       <c r="AG131" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH131" s="36">
         <f>AL135</f>
@@ -42316,7 +42723,7 @@
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D132" s="52">
         <v>0</v>
@@ -42421,7 +42828,7 @@
       <c r="A133" s="19"/>
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D133" s="52">
         <v>0</v>
@@ -42512,7 +42919,7 @@
       </c>
       <c r="AE133" s="57"/>
       <c r="AG133" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH133" s="36">
         <v>0</v>
@@ -42530,7 +42937,7 @@
       <c r="A134" s="19"/>
       <c r="B134" s="20"/>
       <c r="C134" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D134" s="52">
         <v>0</v>
@@ -42635,7 +43042,7 @@
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D135" s="52">
         <v>0</v>
@@ -42782,7 +43189,7 @@
         <v>Ryans House</v>
       </c>
       <c r="C137" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D137" s="52">
         <v>0</v>
@@ -42875,7 +43282,7 @@
       </c>
       <c r="AE137" s="57"/>
       <c r="AG137" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH137" s="35">
         <f>AK142</f>
@@ -42894,7 +43301,7 @@
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D138" s="52">
         <v>0</v>
@@ -42981,7 +43388,7 @@
       </c>
       <c r="AE138" s="57"/>
       <c r="AG138" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH138" s="36">
         <f>AL142</f>
@@ -43000,7 +43407,7 @@
       <c r="A139" s="19"/>
       <c r="B139" s="20"/>
       <c r="C139" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D139" s="52">
         <v>0</v>
@@ -43101,7 +43508,7 @@
       <c r="A140" s="19"/>
       <c r="B140" s="20"/>
       <c r="C140" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D140" s="52">
         <v>0</v>
@@ -43186,7 +43593,7 @@
       </c>
       <c r="AE140" s="57"/>
       <c r="AG140" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH140" s="36">
         <v>0</v>
@@ -43204,7 +43611,7 @@
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D141" s="52">
         <v>0</v>
@@ -43303,7 +43710,7 @@
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D142" s="52">
         <v>0</v>
@@ -43444,7 +43851,7 @@
         <v>71A Fendalton Road </v>
       </c>
       <c r="C144" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D144" s="52">
         <v>23650.59</v>
@@ -43533,7 +43940,7 @@
       </c>
       <c r="AE144" s="57"/>
       <c r="AG144" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH144" s="35">
         <f>AK149</f>
@@ -43552,7 +43959,7 @@
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D145" s="52">
         <v>23650.59</v>
@@ -43641,7 +44048,7 @@
       </c>
       <c r="AE145" s="57"/>
       <c r="AG145" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH145" s="36">
         <f>AL149</f>
@@ -43660,7 +44067,7 @@
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D146" s="52">
         <v>23650.59</v>
@@ -43763,7 +44170,7 @@
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D147" s="52">
         <v>23650.59</v>
@@ -43852,7 +44259,7 @@
       </c>
       <c r="AE147" s="57"/>
       <c r="AG147" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH147" s="36">
         <v>0</v>
@@ -43870,7 +44277,7 @@
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D148" s="52">
         <v>23650.59</v>
@@ -43973,7 +44380,7 @@
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D149" s="52">
         <v>23650.59</v>
@@ -44118,7 +44525,7 @@
         <v>Dixon House</v>
       </c>
       <c r="C151" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D151" s="52">
         <v>29188.19</v>
@@ -44207,7 +44614,7 @@
       </c>
       <c r="AE151" s="57"/>
       <c r="AG151" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH151" s="35">
         <f>AK156</f>
@@ -44226,7 +44633,7 @@
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D152" s="52">
         <v>29188.19</v>
@@ -44315,7 +44722,7 @@
       </c>
       <c r="AE152" s="57"/>
       <c r="AG152" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH152" s="36">
         <f>AL156</f>
@@ -44334,7 +44741,7 @@
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D153" s="52">
         <v>29188.19</v>
@@ -44437,7 +44844,7 @@
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D154" s="52">
         <v>29188.19</v>
@@ -44526,7 +44933,7 @@
       </c>
       <c r="AE154" s="57"/>
       <c r="AG154" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH154" s="36">
         <v>0</v>
@@ -44544,7 +44951,7 @@
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D155" s="52"/>
       <c r="E155" s="52"/>
@@ -44631,7 +45038,7 @@
       <c r="A156" s="59"/>
       <c r="B156" s="75"/>
       <c r="C156" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D156" s="52"/>
       <c r="E156" s="52"/>
@@ -44760,7 +45167,7 @@
         <v>Waimak Dairys </v>
       </c>
       <c r="C158" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D158" s="52">
         <v>15025.89</v>
@@ -44847,7 +45254,7 @@
       </c>
       <c r="AE158" s="57"/>
       <c r="AG158" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH158" s="35">
         <f>AK163</f>
@@ -44866,7 +45273,7 @@
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D159" s="52">
         <v>0</v>
@@ -44952,7 +45359,7 @@
       </c>
       <c r="AE159" s="57"/>
       <c r="AG159" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH159" s="36">
         <f>AL163</f>
@@ -44971,7 +45378,7 @@
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D160" s="52"/>
       <c r="E160" s="52"/>
@@ -45058,7 +45465,7 @@
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D161" s="52"/>
       <c r="E161" s="52"/>
@@ -45131,7 +45538,7 @@
       </c>
       <c r="AE161" s="57"/>
       <c r="AG161" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH161" s="36">
         <v>0</v>
@@ -45149,7 +45556,7 @@
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D162" s="52"/>
       <c r="E162" s="52"/>
@@ -45236,7 +45643,7 @@
       <c r="A163" s="59"/>
       <c r="B163" s="75"/>
       <c r="C163" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D163" s="52"/>
       <c r="E163" s="52"/>
@@ -45365,7 +45772,7 @@
         <v>Daves Twizel Shack</v>
       </c>
       <c r="C165" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D165" s="52">
         <v>300839.52</v>
@@ -45454,7 +45861,7 @@
       </c>
       <c r="AE165" s="57"/>
       <c r="AG165" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH165" s="35">
         <f>AK170</f>
@@ -45473,7 +45880,7 @@
       <c r="A166" s="19"/>
       <c r="B166" s="20"/>
       <c r="C166" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D166" s="52">
         <v>300839.52</v>
@@ -45562,7 +45969,7 @@
       </c>
       <c r="AE166" s="57"/>
       <c r="AG166" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH166" s="36">
         <f>AL170</f>
@@ -45581,7 +45988,7 @@
       <c r="A167" s="19"/>
       <c r="B167" s="20"/>
       <c r="C167" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D167" s="52">
         <v>0</v>
@@ -45684,7 +46091,7 @@
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D168" s="52">
         <v>0</v>
@@ -45773,7 +46180,7 @@
       </c>
       <c r="AE168" s="57"/>
       <c r="AG168" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH168" s="36">
         <v>0</v>
@@ -45791,7 +46198,7 @@
       <c r="A169" s="19"/>
       <c r="B169" s="20"/>
       <c r="C169" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D169" s="52">
         <v>0</v>
@@ -45894,7 +46301,7 @@
       <c r="A170" s="59"/>
       <c r="B170" s="75"/>
       <c r="C170" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D170" s="52">
         <v>0</v>
@@ -46039,7 +46446,7 @@
         <v>FAB Pegasus Lakeside</v>
       </c>
       <c r="C172" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D172" s="52">
         <v>58426.32</v>
@@ -46126,7 +46533,7 @@
       </c>
       <c r="AE172" s="57"/>
       <c r="AG172" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH172" s="35">
         <f>AK177</f>
@@ -46145,7 +46552,7 @@
       <c r="A173" s="19"/>
       <c r="B173" s="20"/>
       <c r="C173" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D173" s="52">
         <v>58426.32</v>
@@ -46231,7 +46638,7 @@
       </c>
       <c r="AE173" s="57"/>
       <c r="AG173" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH173" s="36">
         <f>AL177</f>
@@ -46250,7 +46657,7 @@
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D174" s="52">
         <v>0</v>
@@ -46353,7 +46760,7 @@
       <c r="A175" s="19"/>
       <c r="B175" s="20"/>
       <c r="C175" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D175" s="52">
         <v>0</v>
@@ -46442,7 +46849,7 @@
       </c>
       <c r="AE175" s="57"/>
       <c r="AG175" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH175" s="36">
         <v>0</v>
@@ -46460,7 +46867,7 @@
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D176" s="52">
         <v>0</v>
@@ -46563,7 +46970,7 @@
       <c r="A177" s="59"/>
       <c r="B177" s="75"/>
       <c r="C177" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D177" s="52">
         <v>0</v>
@@ -46708,7 +47115,7 @@
         <v>Harewood Golf Club</v>
       </c>
       <c r="C179" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D179" s="52">
         <v>18080.64</v>
@@ -46795,7 +47202,7 @@
       </c>
       <c r="AE179" s="57"/>
       <c r="AG179" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH179" s="35">
         <f>AK184</f>
@@ -46814,7 +47221,7 @@
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D180" s="52">
         <v>18080.64</v>
@@ -46900,7 +47307,7 @@
       </c>
       <c r="AE180" s="57"/>
       <c r="AG180" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH180" s="36">
         <f>AL184</f>
@@ -46919,7 +47326,7 @@
       <c r="A181" s="19"/>
       <c r="B181" s="20"/>
       <c r="C181" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D181" s="52">
         <v>0</v>
@@ -47022,7 +47429,7 @@
       <c r="A182" s="19"/>
       <c r="B182" s="20"/>
       <c r="C182" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D182" s="52">
         <v>0</v>
@@ -47111,7 +47518,7 @@
       </c>
       <c r="AE182" s="57"/>
       <c r="AG182" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH182" s="36">
         <v>0</v>
@@ -47129,7 +47536,7 @@
       <c r="A183" s="19"/>
       <c r="B183" s="20"/>
       <c r="C183" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D183" s="52">
         <v>0</v>
@@ -47232,7 +47639,7 @@
       <c r="A184" s="59"/>
       <c r="B184" s="75"/>
       <c r="C184" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D184" s="52">
         <v>0</v>
@@ -47377,7 +47784,7 @@
         <v>Taggart House</v>
       </c>
       <c r="C186" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D186" s="52">
         <v>17608.26</v>
@@ -47464,7 +47871,7 @@
       </c>
       <c r="AE186" s="57"/>
       <c r="AG186" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH186" s="35">
         <f>AK191</f>
@@ -47483,7 +47890,7 @@
       <c r="A187" s="19"/>
       <c r="B187" s="20"/>
       <c r="C187" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D187" s="52">
         <v>17608.26</v>
@@ -47569,7 +47976,7 @@
       </c>
       <c r="AE187" s="57"/>
       <c r="AG187" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH187" s="36">
         <f>AL191</f>
@@ -47588,7 +47995,7 @@
       <c r="A188" s="19"/>
       <c r="B188" s="20"/>
       <c r="C188" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D188" s="52">
         <v>0</v>
@@ -47691,7 +48098,7 @@
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D189" s="52">
         <v>0</v>
@@ -47780,7 +48187,7 @@
       </c>
       <c r="AE189" s="57"/>
       <c r="AG189" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH189" s="36">
         <v>0</v>
@@ -47798,7 +48205,7 @@
       <c r="A190" s="19"/>
       <c r="B190" s="20"/>
       <c r="C190" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D190" s="52">
         <v>0</v>
@@ -47901,7 +48308,7 @@
       <c r="A191" s="59"/>
       <c r="B191" s="75"/>
       <c r="C191" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D191" s="52">
         <v>0</v>
@@ -48046,7 +48453,7 @@
         <v>St Barnabas Church</v>
       </c>
       <c r="C193" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D193" s="52">
         <v>19572.81</v>
@@ -48137,7 +48544,7 @@
       </c>
       <c r="AE193" s="57"/>
       <c r="AG193" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH193" s="35">
         <f>AK198</f>
@@ -48156,7 +48563,7 @@
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D194" s="52">
         <v>0</v>
@@ -48242,7 +48649,7 @@
       </c>
       <c r="AE194" s="57"/>
       <c r="AG194" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH194" s="36">
         <f>AL198</f>
@@ -48261,7 +48668,7 @@
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D195" s="52">
         <v>0</v>
@@ -48364,7 +48771,7 @@
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D196" s="52">
         <v>0</v>
@@ -48453,7 +48860,7 @@
       </c>
       <c r="AE196" s="57"/>
       <c r="AG196" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH196" s="36">
         <v>0</v>
@@ -48471,7 +48878,7 @@
       <c r="A197" s="19"/>
       <c r="B197" s="20"/>
       <c r="C197" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D197" s="52">
         <v>0</v>
@@ -48574,7 +48981,7 @@
       <c r="A198" s="59"/>
       <c r="B198" s="75"/>
       <c r="C198" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D198" s="52">
         <v>0</v>
@@ -48719,7 +49126,7 @@
         <v>0</v>
       </c>
       <c r="C200" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D200" s="52">
         <v>0</v>
@@ -48806,7 +49213,7 @@
       </c>
       <c r="AE200" s="57"/>
       <c r="AG200" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH200" s="35">
         <f>AK205</f>
@@ -48825,7 +49232,7 @@
       <c r="A201" s="19"/>
       <c r="B201" s="20"/>
       <c r="C201" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D201" s="52">
         <v>0</v>
@@ -48911,7 +49318,7 @@
       </c>
       <c r="AE201" s="57"/>
       <c r="AG201" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH201" s="36">
         <f>AL205</f>
@@ -48930,7 +49337,7 @@
       <c r="A202" s="19"/>
       <c r="B202" s="20"/>
       <c r="C202" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D202" s="52"/>
       <c r="E202" s="52"/>
@@ -49017,7 +49424,7 @@
       <c r="A203" s="19"/>
       <c r="B203" s="20"/>
       <c r="C203" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D203" s="52"/>
       <c r="E203" s="52"/>
@@ -49090,7 +49497,7 @@
       </c>
       <c r="AE203" s="57"/>
       <c r="AG203" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH203" s="36">
         <v>0</v>
@@ -49108,7 +49515,7 @@
       <c r="A204" s="19"/>
       <c r="B204" s="20"/>
       <c r="C204" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D204" s="52"/>
       <c r="E204" s="52"/>
@@ -49195,7 +49602,7 @@
       <c r="A205" s="59"/>
       <c r="B205" s="75"/>
       <c r="C205" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D205" s="52"/>
       <c r="E205" s="52"/>
@@ -49324,7 +49731,7 @@
         <v>Contracting</v>
       </c>
       <c r="C207" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D207" s="52">
         <v>0</v>
@@ -49411,7 +49818,7 @@
       </c>
       <c r="AE207" s="57"/>
       <c r="AG207" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH207" s="35">
         <f>AK212</f>
@@ -49430,7 +49837,7 @@
       <c r="A208" s="19"/>
       <c r="B208" s="20"/>
       <c r="C208" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D208" s="52">
         <v>0</v>
@@ -49516,7 +49923,7 @@
       </c>
       <c r="AE208" s="57"/>
       <c r="AG208" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH208" s="36">
         <f>AL212</f>
@@ -49535,7 +49942,7 @@
       <c r="A209" s="19"/>
       <c r="B209" s="20"/>
       <c r="C209" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D209" s="52"/>
       <c r="E209" s="52"/>
@@ -49622,7 +50029,7 @@
       <c r="A210" s="19"/>
       <c r="B210" s="20"/>
       <c r="C210" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D210" s="52"/>
       <c r="E210" s="52"/>
@@ -49695,7 +50102,7 @@
       </c>
       <c r="AE210" s="57"/>
       <c r="AG210" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH210" s="36">
         <v>0</v>
@@ -49713,7 +50120,7 @@
       <c r="A211" s="19"/>
       <c r="B211" s="20"/>
       <c r="C211" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D211" s="52"/>
       <c r="E211" s="52"/>
@@ -49800,7 +50207,7 @@
       <c r="A212" s="59"/>
       <c r="B212" s="75"/>
       <c r="C212" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
@@ -49929,7 +50336,7 @@
         <v>Westcoast Vaults</v>
       </c>
       <c r="C214" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D214" s="52">
         <v>0</v>
@@ -50016,7 +50423,7 @@
       </c>
       <c r="AE214" s="57"/>
       <c r="AG214" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH214" s="35">
         <f>AK219</f>
@@ -50035,7 +50442,7 @@
       <c r="A215" s="19"/>
       <c r="B215" s="20"/>
       <c r="C215" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D215" s="52">
         <v>0</v>
@@ -50121,7 +50528,7 @@
       </c>
       <c r="AE215" s="57"/>
       <c r="AG215" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH215" s="36">
         <f>AL219</f>
@@ -50140,7 +50547,7 @@
       <c r="A216" s="19"/>
       <c r="B216" s="20"/>
       <c r="C216" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D216" s="52"/>
       <c r="E216" s="52"/>
@@ -50227,7 +50634,7 @@
       <c r="A217" s="19"/>
       <c r="B217" s="20"/>
       <c r="C217" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D217" s="52"/>
       <c r="E217" s="52"/>
@@ -50300,7 +50707,7 @@
       </c>
       <c r="AE217" s="57"/>
       <c r="AG217" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH217" s="36">
         <v>0</v>
@@ -50318,7 +50725,7 @@
       <c r="A218" s="19"/>
       <c r="B218" s="20"/>
       <c r="C218" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D218" s="52"/>
       <c r="E218" s="52"/>
@@ -50405,7 +50812,7 @@
       <c r="A219" s="59"/>
       <c r="B219" s="75"/>
       <c r="C219" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D219" s="52"/>
       <c r="E219" s="52"/>
@@ -50534,7 +50941,7 @@
         <v>Roydvale</v>
       </c>
       <c r="C221" s="51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D221" s="52">
         <v>0</v>
@@ -50621,7 +51028,7 @@
       </c>
       <c r="AE221" s="57"/>
       <c r="AG221" s="35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AH221" s="35">
         <f>AK226</f>
@@ -50640,7 +51047,7 @@
       <c r="A222" s="19"/>
       <c r="B222" s="20"/>
       <c r="C222" s="51" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D222" s="52">
         <v>0</v>
@@ -50726,7 +51133,7 @@
       </c>
       <c r="AE222" s="57"/>
       <c r="AG222" s="35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AH222" s="36">
         <f>AL226</f>
@@ -50745,7 +51152,7 @@
       <c r="A223" s="19"/>
       <c r="B223" s="20"/>
       <c r="C223" s="51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D223" s="52"/>
       <c r="E223" s="52"/>
@@ -50832,7 +51239,7 @@
       <c r="A224" s="19"/>
       <c r="B224" s="20"/>
       <c r="C224" s="51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D224" s="52"/>
       <c r="E224" s="52"/>
@@ -50905,7 +51312,7 @@
       </c>
       <c r="AE224" s="57"/>
       <c r="AG224" s="35" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AH224" s="36">
         <v>0</v>
@@ -50923,7 +51330,7 @@
       <c r="A225" s="19"/>
       <c r="B225" s="20"/>
       <c r="C225" s="51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D225" s="52"/>
       <c r="E225" s="52"/>
@@ -51010,7 +51417,7 @@
       <c r="A226" s="59"/>
       <c r="B226" s="75"/>
       <c r="C226" s="76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D226" s="52"/>
       <c r="E226" s="52"/>
@@ -51664,35 +52071,35 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B4" s="35">
         <v>30</v>
@@ -51702,9 +52109,9 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B5" s="35">
         <v>60</v>
@@ -51713,9 +52120,9 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B6" s="35">
         <v>100</v>
@@ -51724,9 +52131,9 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B7" s="35">
         <v>150</v>
@@ -51735,13 +52142,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9780,30 +9780,74 @@
       <c r="C5" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53"/>
+      <c r="D5" s="52">
+        <v>245679.5</v>
+      </c>
+      <c r="E5" s="52">
+        <v>216530.08</v>
+      </c>
+      <c r="F5" s="52">
+        <v>29149.420000000013</v>
+      </c>
+      <c r="G5" s="53">
+        <v>0.11864815745717495</v>
+      </c>
+      <c r="H5" s="52">
+        <v>208360.5</v>
+      </c>
+      <c r="I5" s="52">
+        <v>168361.6</v>
+      </c>
+      <c r="J5" s="52">
+        <v>180366.49</v>
+      </c>
+      <c r="K5" s="52">
+        <v>138438.46000000002</v>
+      </c>
+      <c r="L5" s="52">
+        <v>41928.02999999997</v>
+      </c>
+      <c r="M5" s="53">
+        <v>0.23246019812216767</v>
+      </c>
       <c r="N5" s="53"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="53"/>
+      <c r="O5" s="52">
+        <v>27994.01</v>
+      </c>
+      <c r="P5" s="52">
+        <v>29923.14</v>
+      </c>
+      <c r="Q5" s="52">
+        <v>-1929.130000000001</v>
+      </c>
+      <c r="R5" s="53">
+        <v>-0.06891224229754869</v>
+      </c>
+      <c r="S5" s="54">
+        <v>565.45</v>
+      </c>
+      <c r="T5" s="54">
+        <v>600.25</v>
+      </c>
+      <c r="U5" s="54">
+        <v>-34.799999999999955</v>
+      </c>
+      <c r="V5" s="53">
+        <v>-0.061543903086037584</v>
+      </c>
       <c r="W5" s="53"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="56"/>
+      <c r="X5" s="55">
+        <v>80.24736359850063</v>
+      </c>
+      <c r="Y5" s="55">
+        <v>65.99877634098505</v>
+      </c>
+      <c r="Z5" s="53">
+        <v>0.2225</v>
+      </c>
+      <c r="AA5" s="56">
+        <v>0.1519</v>
+      </c>
       <c r="AB5" s="57"/>
       <c r="AD5" s="35" t="s">
         <v>95</v>
@@ -10115,54 +10159,54 @@
         <v>101420.72</v>
       </c>
       <c r="I12" s="52">
-        <v>76488.35</v>
+        <v>79791.03</v>
       </c>
       <c r="J12" s="52">
         <v>83645.65</v>
       </c>
       <c r="K12" s="52">
-        <v>70758.46</v>
+        <v>71604.5</v>
       </c>
       <c r="L12" s="52">
-        <v>12887.189999999988</v>
+        <v>12041.149999999994</v>
       </c>
       <c r="M12" s="53">
-        <v>0.1540688607237793</v>
+        <v>0.1439542881189876</v>
       </c>
       <c r="N12" s="53"/>
       <c r="O12" s="52">
         <v>17775.07</v>
       </c>
       <c r="P12" s="52">
-        <v>5729.89</v>
+        <v>8186.53</v>
       </c>
       <c r="Q12" s="52">
-        <v>12045.18</v>
+        <v>9588.54</v>
       </c>
       <c r="R12" s="53">
-        <v>0.6776445887414227</v>
+        <v>0.5394375380800188</v>
       </c>
       <c r="S12" s="54">
         <v>356.07</v>
       </c>
       <c r="T12" s="54">
-        <v>117.75</v>
+        <v>168.25</v>
       </c>
       <c r="U12" s="54">
-        <v>238.32</v>
+        <v>187.82</v>
       </c>
       <c r="V12" s="53">
-        <v>0.6693065970174403</v>
+        <v>0.5274805515769371</v>
       </c>
       <c r="W12" s="53"/>
       <c r="X12" s="55">
-        <v>79.624033970276</v>
+        <v>36.09539375928678</v>
       </c>
       <c r="Y12" s="55">
         <v>77.66490997775718</v>
       </c>
       <c r="Z12" s="53">
-        <v>0.1092</v>
+        <v>0.0707</v>
       </c>
       <c r="AA12" s="56">
         <v>0.2142</v>
@@ -10843,54 +10887,54 @@
         <v>102178.42</v>
       </c>
       <c r="I26" s="52">
-        <v>87101.11</v>
+        <v>89222.05</v>
       </c>
       <c r="J26" s="52">
         <v>62464.86</v>
       </c>
       <c r="K26" s="52">
-        <v>57898.75</v>
+        <v>58984</v>
       </c>
       <c r="L26" s="52">
-        <v>4566.110000000001</v>
+        <v>3480.8600000000006</v>
       </c>
       <c r="M26" s="53">
-        <v>0.07309885910254182</v>
+        <v>0.05572509087509362</v>
       </c>
       <c r="N26" s="53"/>
       <c r="O26" s="52">
         <v>39713.56</v>
       </c>
       <c r="P26" s="52">
-        <v>29202.36</v>
+        <v>30238.05</v>
       </c>
       <c r="Q26" s="52">
-        <v>10511.199999999997</v>
+        <v>9475.509999999998</v>
       </c>
       <c r="R26" s="53">
-        <v>0.26467534011053145</v>
+        <v>0.23859633837913294</v>
       </c>
       <c r="S26" s="54">
         <v>795.22</v>
       </c>
       <c r="T26" s="54">
-        <v>594.5</v>
+        <v>615</v>
       </c>
       <c r="U26" s="54">
-        <v>200.72000000000003</v>
+        <v>180.22000000000003</v>
       </c>
       <c r="V26" s="53">
-        <v>0.25240813862830414</v>
+        <v>0.22662910892583188</v>
       </c>
       <c r="W26" s="53"/>
       <c r="X26" s="55">
-        <v>96.3325315391085</v>
+        <v>89.67276422764228</v>
       </c>
       <c r="Y26" s="55">
         <v>61.20621468124544</v>
       </c>
       <c r="Z26" s="53">
-        <v>0.3967</v>
+        <v>0.382</v>
       </c>
       <c r="AA26" s="56">
         <v>0.3227</v>
@@ -11206,54 +11250,54 @@
         <v>327431.12</v>
       </c>
       <c r="I33" s="65">
-        <v>220187.84</v>
+        <v>223659.54</v>
       </c>
       <c r="J33" s="52">
         <v>271519.78</v>
       </c>
       <c r="K33" s="52">
-        <v>196879.33</v>
+        <v>197370.72</v>
       </c>
       <c r="L33" s="52">
-        <v>74640.45000000004</v>
+        <v>74149.06000000003</v>
       </c>
       <c r="M33" s="53">
-        <v>0.27489875691561044</v>
+        <v>0.27308898084699396</v>
       </c>
       <c r="N33" s="53"/>
       <c r="O33" s="52">
         <v>55911.34</v>
       </c>
       <c r="P33" s="52">
-        <v>23308.51</v>
+        <v>26288.82</v>
       </c>
       <c r="Q33" s="52">
-        <v>32602.829999999998</v>
+        <v>29622.519999999997</v>
       </c>
       <c r="R33" s="53">
-        <v>0.5831165913748445</v>
+        <v>0.5298123779540966</v>
       </c>
       <c r="S33" s="54">
         <v>1120.27</v>
       </c>
       <c r="T33" s="54">
-        <v>543.5</v>
+        <v>607.75</v>
       </c>
       <c r="U33" s="54">
-        <v>576.77</v>
+        <v>512.52</v>
       </c>
       <c r="V33" s="53">
-        <v>0.514849098877949</v>
+        <v>0.4574968534371178</v>
       </c>
       <c r="W33" s="53"/>
       <c r="X33" s="55">
-        <v>72.05127874885005</v>
+        <v>58.721793500617025</v>
       </c>
       <c r="Y33" s="55">
         <v>61.5841822414239</v>
       </c>
       <c r="Z33" s="53">
-        <v>0.151</v>
+        <v>0.1376</v>
       </c>
       <c r="AA33" s="56">
         <v>0.174</v>
@@ -11569,54 +11613,54 @@
         <v>94098.32</v>
       </c>
       <c r="I40" s="52">
-        <v>46289.42</v>
+        <v>49261.61</v>
       </c>
       <c r="J40" s="52">
         <v>69042.09000000001</v>
       </c>
       <c r="K40" s="52">
-        <v>35507.08</v>
+        <v>35683.74</v>
       </c>
       <c r="L40" s="52">
-        <v>33535.01000000001</v>
+        <v>33358.35000000001</v>
       </c>
       <c r="M40" s="53">
-        <v>0.4857183494879718</v>
+        <v>0.4831596204576079</v>
       </c>
       <c r="N40" s="53"/>
       <c r="O40" s="52">
         <v>25056.23</v>
       </c>
       <c r="P40" s="52">
-        <v>10782.34</v>
+        <v>13577.87</v>
       </c>
       <c r="Q40" s="52">
-        <v>14273.89</v>
+        <v>11478.359999999999</v>
       </c>
       <c r="R40" s="53">
-        <v>0.5696742885901032</v>
+        <v>0.45810403241030273</v>
       </c>
       <c r="S40" s="54">
         <v>501.83</v>
       </c>
       <c r="T40" s="54">
-        <v>232.25</v>
+        <v>299.5</v>
       </c>
       <c r="U40" s="54">
-        <v>269.58</v>
+        <v>202.32999999999998</v>
       </c>
       <c r="V40" s="53">
-        <v>0.5371938704342107</v>
+        <v>0.40318434529621583</v>
       </c>
       <c r="W40" s="53"/>
       <c r="X40" s="55">
-        <v>32.96193756727664</v>
+        <v>15.63679465776294</v>
       </c>
       <c r="Y40" s="55">
         <v>68.07122423898531</v>
       </c>
       <c r="Z40" s="53">
-        <v>0.1419</v>
+        <v>0.0868</v>
       </c>
       <c r="AA40" s="56">
         <v>0.2663</v>
@@ -11934,54 +11978,54 @@
         <v>50582.37</v>
       </c>
       <c r="I47" s="52">
-        <v>25187.36</v>
+        <v>25196.36</v>
       </c>
       <c r="J47" s="52">
         <v>39438.990000000005</v>
       </c>
       <c r="K47" s="52">
-        <v>20432.420000000002</v>
+        <v>20036.420000000002</v>
       </c>
       <c r="L47" s="52">
-        <v>19006.570000000003</v>
+        <v>19402.570000000003</v>
       </c>
       <c r="M47" s="53">
-        <v>0.48192334540007237</v>
+        <v>0.49196417048205343</v>
       </c>
       <c r="N47" s="53"/>
       <c r="O47" s="52">
         <v>11143.38</v>
       </c>
       <c r="P47" s="52">
-        <v>4754.94</v>
+        <v>5159.94</v>
       </c>
       <c r="Q47" s="52">
-        <v>6388.44</v>
+        <v>5983.44</v>
       </c>
       <c r="R47" s="53">
-        <v>0.5732946377131535</v>
+        <v>0.5369501892603501</v>
       </c>
       <c r="S47" s="54">
         <v>223.22</v>
       </c>
       <c r="T47" s="54">
-        <v>104.25</v>
+        <v>113.25</v>
       </c>
       <c r="U47" s="54">
-        <v>118.97</v>
+        <v>109.97</v>
       </c>
       <c r="V47" s="53">
-        <v>0.5329719559179285</v>
+        <v>0.49265298808350505</v>
       </c>
       <c r="W47" s="53"/>
       <c r="X47" s="55">
-        <v>78.07318944844125</v>
+        <v>71.78922737306843</v>
       </c>
       <c r="Y47" s="55">
         <v>67.69550512136009</v>
       </c>
       <c r="Z47" s="53">
-        <v>0.24420000000000003</v>
+        <v>0.244</v>
       </c>
       <c r="AA47" s="56">
         <v>0.23</v>
@@ -12297,54 +12341,54 @@
         <v>109364.97</v>
       </c>
       <c r="I54" s="52">
-        <v>95597.19</v>
+        <v>96483.38</v>
       </c>
       <c r="J54" s="52">
         <v>75135.01000000001</v>
       </c>
       <c r="K54" s="52">
-        <v>71143.79000000001</v>
+        <v>71221.34</v>
       </c>
       <c r="L54" s="52">
-        <v>3991.220000000001</v>
+        <v>3913.670000000013</v>
       </c>
       <c r="M54" s="53">
-        <v>0.05312064242754477</v>
+        <v>0.05208850042077604</v>
       </c>
       <c r="N54" s="53"/>
       <c r="O54" s="52">
         <v>34229.96</v>
       </c>
       <c r="P54" s="52">
-        <v>24453.4</v>
+        <v>25262.04</v>
       </c>
       <c r="Q54" s="52">
-        <v>9776.559999999998</v>
+        <v>8967.919999999998</v>
       </c>
       <c r="R54" s="53">
-        <v>0.28561412283274645</v>
+        <v>0.2619903733454552</v>
       </c>
       <c r="S54" s="54">
         <v>685.48</v>
       </c>
       <c r="T54" s="54">
-        <v>517.75</v>
+        <v>533.75</v>
       </c>
       <c r="U54" s="54">
-        <v>167.73000000000002</v>
+        <v>151.73000000000002</v>
       </c>
       <c r="V54" s="53">
-        <v>0.24468985236622515</v>
+        <v>0.22134854408589605</v>
       </c>
       <c r="W54" s="53"/>
       <c r="X54" s="55">
-        <v>62.22557218734911</v>
+        <v>58.699953161592504</v>
       </c>
       <c r="Y54" s="55">
         <v>67.00679527854935</v>
       </c>
       <c r="Z54" s="53">
-        <v>0.2521</v>
+        <v>0.2451</v>
       </c>
       <c r="AA54" s="56">
         <v>0.2958</v>
@@ -13372,19 +13416,19 @@
         <v>54302.66</v>
       </c>
       <c r="I75" s="52">
-        <v>33447.19</v>
+        <v>29696.65</v>
       </c>
       <c r="J75" s="52">
         <v>31383.390000000003</v>
       </c>
       <c r="K75" s="52">
-        <v>27343.140000000003</v>
+        <v>23592.600000000002</v>
       </c>
       <c r="L75" s="52">
-        <v>4040.25</v>
+        <v>7790.790000000001</v>
       </c>
       <c r="M75" s="53">
-        <v>0.128738482362804</v>
+        <v>0.24824564841465502</v>
       </c>
       <c r="N75" s="53"/>
       <c r="O75" s="52">
@@ -13413,13 +13457,13 @@
       </c>
       <c r="W75" s="53"/>
       <c r="X75" s="55">
-        <v>94.11891891891891</v>
+        <v>125.30844074844074</v>
       </c>
       <c r="Y75" s="55">
         <v>48.58165977967362</v>
       </c>
       <c r="Z75" s="53">
-        <v>0.2528</v>
+        <v>0.33659999999999995</v>
       </c>
       <c r="AA75" s="56">
         <v>0.2963</v>
@@ -14092,54 +14136,54 @@
         <v>27002.93</v>
       </c>
       <c r="I89" s="52">
-        <v>24950.27</v>
+        <v>25060.53</v>
       </c>
       <c r="J89" s="52">
         <v>15440.32</v>
       </c>
       <c r="K89" s="52">
-        <v>13932.720000000001</v>
+        <v>13974.73</v>
       </c>
       <c r="L89" s="52">
-        <v>1507.5999999999985</v>
+        <v>1465.5900000000001</v>
       </c>
       <c r="M89" s="53">
-        <v>0.09764046341008467</v>
+        <v>0.09491966487741188</v>
       </c>
       <c r="N89" s="53"/>
       <c r="O89" s="52">
         <v>11562.61</v>
       </c>
       <c r="P89" s="52">
-        <v>11017.55</v>
+        <v>11085.8</v>
       </c>
       <c r="Q89" s="52">
-        <v>545.0600000000013</v>
+        <v>476.8100000000013</v>
       </c>
       <c r="R89" s="53">
-        <v>0.04713987585847843</v>
+        <v>0.041237229310683424</v>
       </c>
       <c r="S89" s="68">
         <v>231.75</v>
       </c>
       <c r="T89" s="68">
-        <v>224.25</v>
+        <v>225.5</v>
       </c>
       <c r="U89" s="54">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="V89" s="53">
-        <v>0.032362459546925564</v>
+        <v>0.02696871628910464</v>
       </c>
       <c r="W89" s="53"/>
       <c r="X89" s="55">
-        <v>50.9746265328874</v>
+        <v>50.20310421286031</v>
       </c>
       <c r="Y89" s="55">
         <v>43.49557070636461</v>
       </c>
       <c r="Z89" s="53">
-        <v>0.31420000000000003</v>
+        <v>0.31120000000000003</v>
       </c>
       <c r="AA89" s="56">
         <v>0.2718</v>
@@ -21872,10 +21916,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="52">
-        <v>0</v>
+        <v>403.9200000000128</v>
       </c>
       <c r="E4" s="52">
-        <v>0</v>
+        <v>-403.9200000000128</v>
       </c>
       <c r="F4" s="52">
         <v>0</v>
@@ -21899,13 +21943,13 @@
         <v>0</v>
       </c>
       <c r="M4" s="52">
-        <v>-7000</v>
+        <v>-7403.920000000013</v>
       </c>
       <c r="N4" s="54">
         <v>20</v>
       </c>
       <c r="O4" s="58">
-        <v>-100</v>
+        <v>-105.77028571428589</v>
       </c>
     </row>
     <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -21936,10 +21980,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="52">
-        <v>2351.029999999999</v>
+        <v>5653.709999999992</v>
       </c>
       <c r="E6" s="52">
-        <v>-2351.029999999999</v>
+        <v>-5653.709999999992</v>
       </c>
       <c r="F6" s="52">
         <v>0</v>
@@ -21963,13 +22007,13 @@
         <v>0</v>
       </c>
       <c r="M6" s="52">
-        <v>-4223.629999999999</v>
+        <v>-7526.309999999992</v>
       </c>
       <c r="N6" s="54">
         <v>-52.5</v>
       </c>
       <c r="O6" s="58">
-        <v>337.89039999999994</v>
+        <v>602.1047999999994</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>117</v>
@@ -22063,10 +22107,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="52">
-        <v>1252.699999999997</v>
+        <v>3373.6399999999994</v>
       </c>
       <c r="E10" s="52">
-        <v>-1252.699999999997</v>
+        <v>-3373.6399999999994</v>
       </c>
       <c r="F10" s="52">
         <v>0</v>
@@ -22090,13 +22134,13 @@
         <v>0</v>
       </c>
       <c r="M10" s="52">
-        <v>-6172.699999999997</v>
+        <v>-8293.64</v>
       </c>
       <c r="N10" s="54">
         <v>-388.25</v>
       </c>
       <c r="O10" s="58">
-        <v>18.141660543717848</v>
+        <v>24.375135929463628</v>
       </c>
     </row>
     <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22127,10 +22171,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="52">
-        <v>3843.2399999999907</v>
+        <v>7314.940000000002</v>
       </c>
       <c r="E12" s="52">
-        <v>-3843.2399999999907</v>
+        <v>-7314.940000000002</v>
       </c>
       <c r="F12" s="52">
         <v>3</v>
@@ -22154,13 +22198,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="52">
-        <v>-6480.239999999991</v>
+        <v>-9951.940000000002</v>
       </c>
       <c r="N12" s="54">
         <v>53</v>
       </c>
       <c r="O12" s="58">
-        <v>-93.9165217391303</v>
+        <v>-144.23101449275364</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>119</v>
@@ -22194,10 +22238,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="52">
-        <v>4015.729999999996</v>
+        <v>6987.919999999998</v>
       </c>
       <c r="E14" s="52">
-        <v>-4015.729999999996</v>
+        <v>-6987.919999999998</v>
       </c>
       <c r="F14" s="52">
         <v>0</v>
@@ -22221,13 +22265,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="52">
-        <v>-7015.729999999996</v>
+        <v>-9987.919999999998</v>
       </c>
       <c r="N14" s="54">
         <v>-112</v>
       </c>
       <c r="O14" s="58">
-        <v>62.640446428571394</v>
+        <v>89.17785714285712</v>
       </c>
     </row>
     <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22258,10 +22302,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="52">
-        <v>-24.220000000001164</v>
+        <v>-15.220000000001164</v>
       </c>
       <c r="E16" s="52">
-        <v>24.220000000001164</v>
+        <v>15.220000000001164</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="53">
@@ -22283,13 +22327,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="52">
-        <v>-2975.779999999999</v>
+        <v>-2984.779999999999</v>
       </c>
       <c r="N16" s="54">
         <v>-86.75</v>
       </c>
       <c r="O16" s="58">
-        <v>34.302939481268</v>
+        <v>34.40668587896252</v>
       </c>
     </row>
     <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -22320,10 +22364,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="52">
-        <v>276.68000000000757</v>
+        <v>1162.87000000001</v>
       </c>
       <c r="E18" s="52">
-        <v>-276.68000000000757</v>
+        <v>-1162.87000000001</v>
       </c>
       <c r="F18" s="52">
         <v>0</v>
@@ -22347,13 +22391,13 @@
         <v>0</v>
       </c>
       <c r="M18" s="52">
-        <v>-8476.680000000008</v>
+        <v>-9362.87000000001</v>
       </c>
       <c r="N18" s="54">
         <v>-269</v>
       </c>
       <c r="O18" s="58">
-        <v>44.85015873015877</v>
+        <v>49.538994708994764</v>
       </c>
       <c r="Q18" s="35" t="s">
         <v>120</v>
@@ -22501,10 +22545,10 @@
         <v>0</v>
       </c>
       <c r="D24" s="52">
-        <v>1528.260000000002</v>
+        <v>-2222.279999999999</v>
       </c>
       <c r="E24" s="52">
-        <v>-1528.260000000002</v>
+        <v>2222.279999999999</v>
       </c>
       <c r="F24" s="52">
         <v>3</v>
@@ -22522,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="52">
-        <v>-1525.260000000002</v>
+        <v>2225.279999999999</v>
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="58">
@@ -22619,10 +22663,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="52">
-        <v>-1055.7200000000012</v>
+        <v>-945.4600000000028</v>
       </c>
       <c r="E28" s="52">
-        <v>1055.7200000000012</v>
+        <v>945.4600000000028</v>
       </c>
       <c r="F28" s="52">
         <v>0</v>
@@ -22642,13 +22686,13 @@
         <v>0</v>
       </c>
       <c r="M28" s="52">
-        <v>1055.7200000000012</v>
+        <v>945.4600000000028</v>
       </c>
       <c r="N28" s="54">
         <v>-148.5</v>
       </c>
       <c r="O28" s="58">
-        <v>-7.109225589225597</v>
+        <v>-6.366734006734025</v>
       </c>
     </row>
     <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -23820,22 +23864,22 @@
         <v>88818.76999999996</v>
       </c>
       <c r="D70" s="104">
-        <v>29887.739999999983</v>
+        <v>39414.08000000001</v>
       </c>
       <c r="E70" s="105">
-        <v>58931.02999999998</v>
+        <v>49404.68999999996</v>
       </c>
       <c r="F70" s="106" t="s">
         <v>124</v>
       </c>
       <c r="G70" s="107">
-        <v>0.6634974791927427</v>
+        <v>0.5562415466910877</v>
       </c>
       <c r="H70" s="108" t="s">
         <v>125</v>
       </c>
       <c r="I70" s="109">
-        <v>0.0799203816940944</v>
+        <v>-0.02733555080756062</v>
       </c>
       <c r="J70" s="36"/>
       <c r="K70" s="36"/>
@@ -24390,10 +24434,10 @@
         <v>565.45</v>
       </c>
       <c r="D4" s="54">
-        <v>588.25</v>
+        <v>600.25</v>
       </c>
       <c r="E4" s="54">
-        <v>-22.799999999999955</v>
+        <v>-34.799999999999955</v>
       </c>
       <c r="F4" s="54">
         <v>0</v>
@@ -24445,10 +24489,10 @@
         <v>356.07</v>
       </c>
       <c r="D6" s="54">
-        <v>117.75</v>
+        <v>168.25</v>
       </c>
       <c r="E6" s="54">
-        <v>238.32</v>
+        <v>187.82</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="54"/>
@@ -24551,10 +24595,10 @@
         <v>795.22</v>
       </c>
       <c r="D10" s="54">
-        <v>594.5</v>
+        <v>615</v>
       </c>
       <c r="E10" s="54">
-        <v>200.72000000000003</v>
+        <v>180.22000000000003</v>
       </c>
       <c r="F10" s="54"/>
       <c r="G10" s="54"/>
@@ -24608,10 +24652,10 @@
         <v>1120.27</v>
       </c>
       <c r="D12" s="54">
-        <v>543.5</v>
+        <v>607.75</v>
       </c>
       <c r="E12" s="54">
-        <v>576.77</v>
+        <v>512.52</v>
       </c>
       <c r="F12" s="54"/>
       <c r="G12" s="54"/>
@@ -24665,10 +24709,10 @@
         <v>501.83</v>
       </c>
       <c r="D14" s="54">
-        <v>232.25</v>
+        <v>299.5</v>
       </c>
       <c r="E14" s="54">
-        <v>269.58</v>
+        <v>202.32999999999998</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="54"/>
@@ -24722,10 +24766,10 @@
         <v>223.22</v>
       </c>
       <c r="D16" s="54">
-        <v>104.25</v>
+        <v>113.25</v>
       </c>
       <c r="E16" s="54">
-        <v>118.97</v>
+        <v>109.97</v>
       </c>
       <c r="F16" s="54"/>
       <c r="G16" s="54"/>
@@ -24774,10 +24818,10 @@
         <v>685.48</v>
       </c>
       <c r="D18" s="54">
-        <v>517.75</v>
+        <v>533.75</v>
       </c>
       <c r="E18" s="54">
-        <v>167.73000000000002</v>
+        <v>151.73000000000002</v>
       </c>
       <c r="F18" s="54"/>
       <c r="G18" s="54"/>
@@ -25032,10 +25076,10 @@
         <v>231.75</v>
       </c>
       <c r="D28" s="54">
-        <v>224.25</v>
+        <v>225.5</v>
       </c>
       <c r="E28" s="54">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="F28" s="54"/>
       <c r="G28" s="54"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16396,7 +16396,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>97</v>
@@ -21803,7 +21803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD71"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21817,7 +21817,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21839,7 +21839,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>102</v>
       </c>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21905,7 +21905,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21952,7 +21952,7 @@
         <v>-105.77028571428589</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21969,7 +21969,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -22019,7 +22019,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -22036,7 +22036,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -22079,7 +22079,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -22096,7 +22096,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -22143,7 +22143,7 @@
         <v>24.375135929463628</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -22160,7 +22160,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -22210,7 +22210,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -22227,7 +22227,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -22274,7 +22274,7 @@
         <v>89.17785714285712</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -22291,7 +22291,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -22336,7 +22336,7 @@
         <v>34.40668587896252</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -22353,7 +22353,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -22403,7 +22403,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -22420,7 +22420,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22459,7 +22459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22476,7 +22476,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22517,7 +22517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22534,7 +22534,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22573,7 +22573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22590,7 +22590,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22652,7 +22652,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22695,7 +22695,7 @@
         <v>-6.366734006734025</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22712,7 +22712,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22772,7 +22772,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22819,7 +22819,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22836,7 +22836,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22881,7 +22881,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22898,7 +22898,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22941,7 +22941,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22958,7 +22958,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22999,7 +22999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -23016,7 +23016,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -23061,7 +23061,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -23078,7 +23078,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -23121,7 +23121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -23138,7 +23138,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -23175,7 +23175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -23192,7 +23192,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -23233,7 +23233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -23250,7 +23250,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -23293,7 +23293,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -23310,7 +23310,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -23352,7 +23352,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -23369,7 +23369,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -23414,7 +23414,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -23431,7 +23431,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23476,7 +23476,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23493,7 +23493,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23555,7 +23555,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23592,7 +23592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23609,7 +23609,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23626,7 +23626,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23643,7 +23643,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23664,7 +23664,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23681,7 +23681,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23722,7 +23722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23739,7 +23739,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23784,7 +23784,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="102">
         <f>'Main Sheet'!A68</f>
       </c>
@@ -23819,7 +23819,7 @@
         <f>SUM(M67/(N67+I67))</f>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23836,7 +23836,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="36"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="35"/>
       <c r="B69" s="35"/>
       <c r="C69" s="36"/>
@@ -23853,7 +23853,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
         <v>122</v>
       </c>
@@ -23888,7 +23888,7 @@
       <c r="N70" s="35"/>
       <c r="O70" s="35"/>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="59"/>
       <c r="B71" s="98" t="s">
         <v>126</v>
@@ -24271,7 +24271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD110"/>
+  <dimension ref="A1:AB110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -24282,7 +24282,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24303,7 +24303,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>127</v>
@@ -24365,7 +24365,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>143</v>
       </c>
@@ -24423,7 +24423,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -24459,7 +24459,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -24478,7 +24478,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24512,7 +24512,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24531,7 +24531,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24565,7 +24565,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24584,7 +24584,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24622,7 +24622,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24641,7 +24641,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24679,7 +24679,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24698,7 +24698,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24736,7 +24736,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24755,7 +24755,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24788,7 +24788,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24807,7 +24807,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24840,7 +24840,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24859,7 +24859,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24890,7 +24890,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24909,7 +24909,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24944,7 +24944,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24963,7 +24963,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24996,7 +24996,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -25015,7 +25015,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25046,7 +25046,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -25065,7 +25065,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25097,7 +25097,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -25116,7 +25116,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25152,7 +25152,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -25171,7 +25171,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25200,7 +25200,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -25219,7 +25219,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25250,7 +25250,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -25269,7 +25269,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25302,7 +25302,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -25321,7 +25321,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25357,7 +25357,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -25376,7 +25376,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25411,7 +25411,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -25430,7 +25430,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25460,7 +25460,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -25479,7 +25479,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25538,7 +25538,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25567,7 +25567,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25586,7 +25586,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25619,7 +25619,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25638,7 +25638,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25671,7 +25671,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25690,7 +25690,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25726,7 +25726,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25745,7 +25745,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25781,7 +25781,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25800,7 +25800,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25834,7 +25834,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25853,7 +25853,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25888,7 +25888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25907,7 +25907,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25926,7 +25926,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25945,7 +25945,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25966,7 +25966,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25985,7 +25985,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -26018,7 +26018,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -26037,7 +26037,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -26076,7 +26076,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <f>'Main Sheet'!A68</f>
       </c>
@@ -26105,7 +26105,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="54"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -26124,7 +26124,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="142"/>
       <c r="B69" s="143"/>
       <c r="C69" s="35"/>
@@ -26143,7 +26143,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="144"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="145"/>
       <c r="B70" s="145"/>
       <c r="C70" s="145"/>
@@ -26162,7 +26162,7 @@
       <c r="P70" s="145"/>
       <c r="Q70" s="145"/>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="146" t="s">
         <v>147</v>
@@ -26207,7 +26207,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -26246,7 +26246,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="77" t="s">
         <v>149</v>
@@ -26275,7 +26275,7 @@
       <c r="P73" s="20"/>
       <c r="Q73" s="20"/>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="148" t="s">
         <v>150</v>
@@ -26320,7 +26320,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="151" t="s">
         <v>151</v>
@@ -26365,7 +26365,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -26384,7 +26384,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="144"/>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="142"/>
       <c r="B77" s="156" t="s">
         <v>152</v>
@@ -26431,7 +26431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="161"/>
       <c r="B78" s="162" t="s">
         <v>154</v>
@@ -26476,7 +26476,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -26495,7 +26495,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="164" t="s">
         <v>155</v>
@@ -26518,7 +26518,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="167" t="s">
         <v>157</v>
@@ -26541,7 +26541,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -26564,7 +26564,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -26587,7 +26587,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -26610,7 +26610,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -26633,7 +26633,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -26656,7 +26656,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -26679,7 +26679,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -26702,7 +26702,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -26725,7 +26725,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -26748,7 +26748,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19" t="s">
         <v>167</v>
@@ -26771,7 +26771,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26792,7 +26792,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26813,7 +26813,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26834,7 +26834,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26855,7 +26855,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26876,7 +26876,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26897,7 +26897,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19"/>
       <c r="C98" s="131">
@@ -26918,7 +26918,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -26941,7 +26941,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -26964,7 +26964,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -26987,7 +26987,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -27010,7 +27010,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -27033,7 +27033,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -27056,7 +27056,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19" t="s">
         <v>174</v>
@@ -27079,7 +27079,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -27098,7 +27098,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -27117,7 +27117,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="19"/>
       <c r="C108" s="131"/>
@@ -27136,7 +27136,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="169"/>
       <c r="C109" s="150"/>
@@ -27155,7 +27155,7 @@
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
     </row>
-    <row r="110" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="35"/>
       <c r="B110" s="164" t="s">
         <v>175</v>
@@ -27229,11 +27229,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A2:AC56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>176</v>
       </c>
@@ -27265,7 +27264,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>177</v>
       </c>
@@ -27298,7 +27297,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>178</v>
       </c>
@@ -27331,7 +27330,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>179</v>
       </c>
@@ -27364,7 +27363,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>180</v>
       </c>
@@ -27397,7 +27396,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>181</v>
       </c>
@@ -27430,7 +27429,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>182</v>
       </c>
@@ -27463,7 +27462,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>183</v>
       </c>
@@ -27496,7 +27495,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27527,7 +27526,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27558,7 +27557,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>184</v>
       </c>
@@ -27591,7 +27590,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>185</v>
       </c>
@@ -27624,7 +27623,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>186</v>
       </c>
@@ -27657,7 +27656,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>187</v>
       </c>
@@ -27690,7 +27689,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>188</v>
       </c>
@@ -27723,7 +27722,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>189</v>
       </c>
@@ -27756,7 +27755,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>190</v>
       </c>
@@ -27789,7 +27788,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>191</v>
       </c>
@@ -27822,7 +27821,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>192</v>
       </c>
@@ -27855,7 +27854,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>193</v>
       </c>
@@ -27888,7 +27887,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>194</v>
       </c>
@@ -27921,7 +27920,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>195</v>
       </c>
@@ -27954,7 +27953,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>196</v>
       </c>
@@ -27987,7 +27986,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>197</v>
       </c>
@@ -28020,7 +28019,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>198</v>
       </c>
@@ -28053,7 +28052,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>199</v>
       </c>
@@ -28086,7 +28085,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>200</v>
       </c>
@@ -28118,7 +28117,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>201</v>
       </c>
@@ -28150,7 +28149,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>202</v>
       </c>
@@ -28182,7 +28181,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>203</v>
       </c>
@@ -28214,7 +28213,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>204</v>
       </c>
@@ -28246,7 +28245,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -28276,7 +28275,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -28306,7 +28305,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>205</v>
       </c>
@@ -28338,7 +28337,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>206</v>
       </c>
@@ -28370,7 +28369,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>207</v>
       </c>
@@ -28402,7 +28401,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>208</v>
       </c>
@@ -28434,7 +28433,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>209</v>
       </c>
@@ -28466,7 +28465,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -28496,7 +28495,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>210</v>
       </c>
@@ -28528,7 +28527,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>211</v>
       </c>
@@ -28560,7 +28559,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>212</v>
       </c>
@@ -28592,7 +28591,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>213</v>
       </c>
@@ -28624,7 +28623,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28654,7 +28653,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28684,7 +28683,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28714,7 +28713,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28744,7 +28743,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>214</v>
       </c>
@@ -28776,7 +28775,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>215</v>
       </c>
@@ -28808,7 +28807,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28838,7 +28837,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28868,7 +28867,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28898,7 +28897,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28928,7 +28927,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28958,7 +28957,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -29053,11 +29052,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A2:AC45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>216</v>
       </c>
@@ -29089,7 +29087,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -29120,7 +29118,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -29151,7 +29149,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -29182,7 +29180,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -29213,7 +29211,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -29244,7 +29242,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -29275,7 +29273,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -29306,7 +29304,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -29337,7 +29335,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -29368,7 +29366,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -29399,7 +29397,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -29430,7 +29428,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -29461,7 +29459,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -29492,7 +29490,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29523,7 +29521,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29554,7 +29552,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29585,7 +29583,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29616,7 +29614,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29647,7 +29645,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29678,7 +29676,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29708,7 +29706,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29738,7 +29736,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29768,7 +29766,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29798,7 +29796,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29828,7 +29826,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29858,7 +29856,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29888,7 +29886,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29918,7 +29916,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29948,7 +29946,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29978,7 +29976,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -30008,7 +30006,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -30038,7 +30036,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -30068,7 +30066,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -30098,7 +30096,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -30128,7 +30126,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -30158,7 +30156,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>214</v>
       </c>
@@ -30190,7 +30188,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>215</v>
       </c>
@@ -30222,7 +30220,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -30252,7 +30250,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -30282,7 +30280,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -30312,7 +30310,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -30342,7 +30340,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -30372,7 +30370,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -52115,19 +52113,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -52141,7 +52139,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>223</v>
       </c>
@@ -52153,7 +52151,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>224</v>
       </c>
@@ -52164,7 +52162,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>225</v>
       </c>
@@ -52175,7 +52173,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>226</v>
       </c>
@@ -52186,13 +52184,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -16396,7 +16396,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>97</v>
@@ -18764,30 +18764,74 @@
       <c r="C180" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D180" s="52"/>
-      <c r="E180" s="52"/>
-      <c r="F180" s="52"/>
-      <c r="G180" s="53"/>
-      <c r="H180" s="52"/>
-      <c r="I180" s="52"/>
-      <c r="J180" s="52"/>
-      <c r="K180" s="52"/>
-      <c r="L180" s="52"/>
-      <c r="M180" s="53"/>
+      <c r="D180" s="52">
+        <v>16897.53</v>
+      </c>
+      <c r="E180" s="52">
+        <v>5491.7</v>
+      </c>
+      <c r="F180" s="52">
+        <v>11405.829999999998</v>
+      </c>
+      <c r="G180" s="53">
+        <v>0.6749998372543206</v>
+      </c>
+      <c r="H180" s="52">
+        <v>9226.27</v>
+      </c>
+      <c r="I180" s="52">
+        <v>3702.78</v>
+      </c>
+      <c r="J180" s="52">
+        <v>2977.1100000000006</v>
+      </c>
+      <c r="K180" s="52">
+        <v>2335.9700000000003</v>
+      </c>
+      <c r="L180" s="52">
+        <v>641.1400000000003</v>
+      </c>
+      <c r="M180" s="53">
+        <v>0.2153565034546927</v>
+      </c>
       <c r="N180" s="53"/>
-      <c r="O180" s="52"/>
-      <c r="P180" s="52"/>
-      <c r="Q180" s="52"/>
-      <c r="R180" s="53"/>
-      <c r="S180" s="54"/>
-      <c r="T180" s="54"/>
-      <c r="U180" s="54"/>
-      <c r="V180" s="53"/>
+      <c r="O180" s="52">
+        <v>6249.16</v>
+      </c>
+      <c r="P180" s="52">
+        <v>1366.81</v>
+      </c>
+      <c r="Q180" s="52">
+        <v>4882.35</v>
+      </c>
+      <c r="R180" s="53">
+        <v>0.7812810041669601</v>
+      </c>
+      <c r="S180" s="54">
+        <v>125.17</v>
+      </c>
+      <c r="T180" s="54">
+        <v>23.75</v>
+      </c>
+      <c r="U180" s="54">
+        <v>101.42</v>
+      </c>
+      <c r="V180" s="53">
+        <v>0.8102580490532876</v>
+      </c>
       <c r="W180" s="53"/>
-      <c r="X180" s="55"/>
-      <c r="Y180" s="55"/>
-      <c r="Z180" s="53"/>
-      <c r="AA180" s="56"/>
+      <c r="X180" s="55">
+        <v>75.32294736842105</v>
+      </c>
+      <c r="Y180" s="55">
+        <v>61.286703843093385</v>
+      </c>
+      <c r="Z180" s="53">
+        <v>0.3257</v>
+      </c>
+      <c r="AA180" s="56">
+        <v>0.454</v>
+      </c>
       <c r="AB180" s="57"/>
       <c r="AD180" s="35" t="s">
         <v>95</v>
@@ -21061,30 +21105,74 @@
       <c r="C229" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="D229" s="52"/>
-      <c r="E229" s="52"/>
-      <c r="F229" s="52"/>
-      <c r="G229" s="53"/>
-      <c r="H229" s="52"/>
-      <c r="I229" s="52"/>
-      <c r="J229" s="52"/>
-      <c r="K229" s="52"/>
-      <c r="L229" s="52"/>
-      <c r="M229" s="53"/>
+      <c r="D229" s="52">
+        <v>8795.03</v>
+      </c>
+      <c r="E229" s="52">
+        <v>0</v>
+      </c>
+      <c r="F229" s="52">
+        <v>8795.03</v>
+      </c>
+      <c r="G229" s="53">
+        <v>1</v>
+      </c>
+      <c r="H229" s="52">
+        <v>6369.12</v>
+      </c>
+      <c r="I229" s="52">
+        <v>0</v>
+      </c>
+      <c r="J229" s="52">
+        <v>4527.889999999999</v>
+      </c>
+      <c r="K229" s="52">
+        <v>0</v>
+      </c>
+      <c r="L229" s="52">
+        <v>4527.889999999999</v>
+      </c>
+      <c r="M229" s="53">
+        <v>1</v>
+      </c>
       <c r="N229" s="53"/>
-      <c r="O229" s="52"/>
-      <c r="P229" s="52"/>
-      <c r="Q229" s="52"/>
-      <c r="R229" s="53"/>
-      <c r="S229" s="54"/>
-      <c r="T229" s="54"/>
-      <c r="U229" s="54"/>
-      <c r="V229" s="53"/>
+      <c r="O229" s="52">
+        <v>1841.23</v>
+      </c>
+      <c r="P229" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q229" s="52">
+        <v>1841.23</v>
+      </c>
+      <c r="R229" s="53">
+        <v>1</v>
+      </c>
+      <c r="S229" s="54">
+        <v>36.92</v>
+      </c>
+      <c r="T229" s="54">
+        <v>0</v>
+      </c>
+      <c r="U229" s="54">
+        <v>36.92</v>
+      </c>
+      <c r="V229" s="53">
+        <v>1</v>
+      </c>
       <c r="W229" s="53"/>
-      <c r="X229" s="55"/>
-      <c r="Y229" s="55"/>
-      <c r="Z229" s="53"/>
-      <c r="AA229" s="56"/>
+      <c r="X229" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y229" s="55">
+        <v>65.70711175027087</v>
+      </c>
+      <c r="Z229" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA229" s="56">
+        <v>0.2758</v>
+      </c>
       <c r="AB229" s="57"/>
       <c r="AD229" s="35"/>
       <c r="AE229" s="36"/>
@@ -21803,7 +21891,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:AD71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -21817,7 +21905,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -21839,7 +21927,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>102</v>
       </c>
@@ -21887,7 +21975,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -21905,7 +21993,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -21952,7 +22040,7 @@
         <v>-105.77028571428589</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -21969,7 +22057,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -22019,7 +22107,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -22036,7 +22124,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -22079,7 +22167,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -22096,7 +22184,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -22143,7 +22231,7 @@
         <v>24.375135929463628</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -22160,7 +22248,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -22210,7 +22298,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -22227,7 +22315,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -22274,7 +22362,7 @@
         <v>89.17785714285712</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -22291,7 +22379,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -22336,7 +22424,7 @@
         <v>34.40668587896252</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -22353,7 +22441,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -22403,7 +22491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -22420,7 +22508,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -22459,7 +22547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -22476,7 +22564,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -22517,7 +22605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -22534,7 +22622,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -22573,7 +22661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -22590,7 +22678,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -22635,7 +22723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -22652,7 +22740,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -22695,7 +22783,7 @@
         <v>-6.366734006734025</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -22712,7 +22800,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -22755,7 +22843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -22772,7 +22860,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -22819,7 +22907,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -22836,7 +22924,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -22881,7 +22969,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -22898,7 +22986,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -22941,7 +23029,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -22958,7 +23046,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -22999,7 +23087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -23016,7 +23104,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -23061,7 +23149,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -23078,7 +23166,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -23121,7 +23209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -23138,7 +23226,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -23175,7 +23263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -23192,7 +23280,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -23233,7 +23321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -23250,7 +23338,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -23293,7 +23381,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -23310,7 +23398,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -23352,7 +23440,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -23369,7 +23457,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -23414,7 +23502,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -23431,7 +23519,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -23476,7 +23564,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -23493,7 +23581,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -23538,7 +23626,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -23555,7 +23643,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -23592,7 +23680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -23609,7 +23697,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -23626,7 +23714,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -23643,7 +23731,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -23664,7 +23752,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -23681,7 +23769,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -23722,7 +23810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -23739,7 +23827,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -23784,7 +23872,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="102">
         <f>'Main Sheet'!A68</f>
       </c>
@@ -23819,7 +23907,7 @@
         <f>SUM(M67/(N67+I67))</f>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -23836,7 +23924,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="36"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="35"/>
       <c r="B69" s="35"/>
       <c r="C69" s="36"/>
@@ -23853,7 +23941,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
         <v>122</v>
       </c>
@@ -23888,7 +23976,7 @@
       <c r="N70" s="35"/>
       <c r="O70" s="35"/>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="59"/>
       <c r="B71" s="98" t="s">
         <v>126</v>
@@ -24271,7 +24359,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB110"/>
+  <dimension ref="A1:AD110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -24282,7 +24370,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24303,7 +24391,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>127</v>
@@ -24365,7 +24453,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>143</v>
       </c>
@@ -24423,7 +24511,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -24459,7 +24547,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -24478,7 +24566,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -24512,7 +24600,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -24531,7 +24619,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -24565,7 +24653,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -24584,7 +24672,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -24622,7 +24710,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -24641,7 +24729,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -24679,7 +24767,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -24698,7 +24786,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -24736,7 +24824,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -24755,7 +24843,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -24788,7 +24876,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -24807,7 +24895,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -24840,7 +24928,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -24859,7 +24947,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -24890,7 +24978,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -24909,7 +24997,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -24944,7 +25032,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -24963,7 +25051,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -24996,7 +25084,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -25015,7 +25103,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25046,7 +25134,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -25065,7 +25153,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25097,7 +25185,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -25116,7 +25204,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -25152,7 +25240,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -25171,7 +25259,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -25200,7 +25288,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -25219,7 +25307,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -25250,7 +25338,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -25269,7 +25357,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -25302,7 +25390,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -25321,7 +25409,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -25357,7 +25445,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -25376,7 +25464,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -25411,7 +25499,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -25430,7 +25518,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -25460,7 +25548,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -25479,7 +25567,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -25519,7 +25607,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -25538,7 +25626,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -25567,7 +25655,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -25586,7 +25674,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -25619,7 +25707,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -25638,7 +25726,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -25671,7 +25759,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -25690,7 +25778,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -25726,7 +25814,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -25745,7 +25833,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -25781,7 +25869,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -25800,7 +25888,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -25834,7 +25922,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -25853,7 +25941,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -25888,7 +25976,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -25907,7 +25995,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -25926,7 +26014,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -25945,7 +26033,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -25966,7 +26054,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -25985,7 +26073,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -26018,7 +26106,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -26037,7 +26125,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -26076,7 +26164,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <f>'Main Sheet'!A68</f>
       </c>
@@ -26105,7 +26193,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="54"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -26124,7 +26212,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="142"/>
       <c r="B69" s="143"/>
       <c r="C69" s="35"/>
@@ -26143,7 +26231,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="144"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="145"/>
       <c r="B70" s="145"/>
       <c r="C70" s="145"/>
@@ -26162,7 +26250,7 @@
       <c r="P70" s="145"/>
       <c r="Q70" s="145"/>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="146" t="s">
         <v>147</v>
@@ -26207,7 +26295,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -26246,7 +26334,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="77" t="s">
         <v>149</v>
@@ -26275,7 +26363,7 @@
       <c r="P73" s="20"/>
       <c r="Q73" s="20"/>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="148" t="s">
         <v>150</v>
@@ -26320,7 +26408,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="151" t="s">
         <v>151</v>
@@ -26365,7 +26453,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -26384,7 +26472,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="144"/>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="142"/>
       <c r="B77" s="156" t="s">
         <v>152</v>
@@ -26431,7 +26519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="161"/>
       <c r="B78" s="162" t="s">
         <v>154</v>
@@ -26476,7 +26564,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -26495,7 +26583,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="164" t="s">
         <v>155</v>
@@ -26518,7 +26606,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="167" t="s">
         <v>157</v>
@@ -26541,7 +26629,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="19" t="s">
         <v>158</v>
@@ -26564,7 +26652,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="35"/>
       <c r="B83" s="19" t="s">
         <v>159</v>
@@ -26587,7 +26675,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="19" t="s">
         <v>160</v>
@@ -26610,7 +26698,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85" s="19" t="s">
         <v>161</v>
@@ -26633,7 +26721,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
     </row>
-    <row r="86" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86" s="19" t="s">
         <v>162</v>
@@ -26656,7 +26744,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
     </row>
-    <row r="87" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="35"/>
       <c r="B87" s="19" t="s">
         <v>163</v>
@@ -26679,7 +26767,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
     </row>
-    <row r="88" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="35"/>
       <c r="B88" s="19" t="s">
         <v>164</v>
@@ -26702,7 +26790,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
     </row>
-    <row r="89" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="35"/>
       <c r="B89" s="19" t="s">
         <v>165</v>
@@ -26725,7 +26813,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
     </row>
-    <row r="90" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -26748,7 +26836,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
     </row>
-    <row r="91" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="19" t="s">
         <v>167</v>
@@ -26771,7 +26859,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
     </row>
-    <row r="92" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="19"/>
       <c r="C92" s="131">
@@ -26792,7 +26880,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="19"/>
       <c r="C93" s="131">
@@ -26813,7 +26901,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="19"/>
       <c r="C94" s="131">
@@ -26834,7 +26922,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
     </row>
-    <row r="95" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="19"/>
       <c r="C95" s="131">
@@ -26855,7 +26943,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
     </row>
-    <row r="96" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="19"/>
       <c r="C96" s="131">
@@ -26876,7 +26964,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
     </row>
-    <row r="97" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="19"/>
       <c r="C97" s="131">
@@ -26897,7 +26985,7 @@
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
     </row>
-    <row r="98" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="19"/>
       <c r="C98" s="131">
@@ -26918,7 +27006,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="19" t="s">
         <v>168</v>
@@ -26941,7 +27029,7 @@
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A100" s="35"/>
       <c r="B100" s="19" t="s">
         <v>169</v>
@@ -26964,7 +27052,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A101" s="35"/>
       <c r="B101" s="19" t="s">
         <v>170</v>
@@ -26987,7 +27075,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="35"/>
       <c r="B102" s="19" t="s">
         <v>171</v>
@@ -27010,7 +27098,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="35"/>
       <c r="B103" s="19" t="s">
         <v>172</v>
@@ -27033,7 +27121,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="35"/>
       <c r="B104" s="19" t="s">
         <v>173</v>
@@ -27056,7 +27144,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="35"/>
       <c r="B105" s="19" t="s">
         <v>174</v>
@@ -27079,7 +27167,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="19"/>
       <c r="C106" s="131"/>
@@ -27098,7 +27186,7 @@
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="19"/>
       <c r="C107" s="131"/>
@@ -27117,7 +27205,7 @@
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="19"/>
       <c r="C108" s="131"/>
@@ -27136,7 +27224,7 @@
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="169"/>
       <c r="C109" s="150"/>
@@ -27155,7 +27243,7 @@
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
     </row>
-    <row r="110" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="35"/>
       <c r="B110" s="164" t="s">
         <v>175</v>
@@ -27229,10 +27317,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC56"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>176</v>
       </c>
@@ -27264,7 +27353,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172" t="s">
         <v>177</v>
       </c>
@@ -27297,7 +27386,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>178</v>
       </c>
@@ -27330,7 +27419,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="175" t="s">
         <v>179</v>
       </c>
@@ -27363,7 +27452,7 @@
       <c r="AB5" s="175"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176" t="s">
         <v>180</v>
       </c>
@@ -27396,7 +27485,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="177" t="s">
         <v>181</v>
       </c>
@@ -27429,7 +27518,7 @@
       <c r="AB7" s="177"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176" t="s">
         <v>182</v>
       </c>
@@ -27462,7 +27551,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="178" t="s">
         <v>183</v>
       </c>
@@ -27495,7 +27584,7 @@
       <c r="AB9" s="178"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="179"/>
       <c r="B10" s="179"/>
       <c r="C10" s="179"/>
@@ -27526,7 +27615,7 @@
       <c r="AB10" s="179"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="180"/>
@@ -27557,7 +27646,7 @@
       <c r="AB11" s="180"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="181" t="s">
         <v>184</v>
       </c>
@@ -27590,7 +27679,7 @@
       <c r="AB12" s="181"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="182" t="s">
         <v>185</v>
       </c>
@@ -27623,7 +27712,7 @@
       <c r="AB13" s="182"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="183" t="s">
         <v>186</v>
       </c>
@@ -27656,7 +27745,7 @@
       <c r="AB14" s="183"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="172" t="s">
         <v>187</v>
       </c>
@@ -27689,7 +27778,7 @@
       <c r="AB15" s="172"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>188</v>
       </c>
@@ -27722,7 +27811,7 @@
       <c r="AB16" s="184"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>189</v>
       </c>
@@ -27755,7 +27844,7 @@
       <c r="AB17" s="185"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="186" t="s">
         <v>190</v>
       </c>
@@ -27788,7 +27877,7 @@
       <c r="AB18" s="186"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="178" t="s">
         <v>191</v>
       </c>
@@ -27821,7 +27910,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="187" t="s">
         <v>192</v>
       </c>
@@ -27854,7 +27943,7 @@
       <c r="AB20" s="187"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="188" t="s">
         <v>193</v>
       </c>
@@ -27887,7 +27976,7 @@
       <c r="AB21" s="188"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="188" t="s">
         <v>194</v>
       </c>
@@ -27920,7 +28009,7 @@
       <c r="AB22" s="188"/>
       <c r="AC22" s="173"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="188" t="s">
         <v>195</v>
       </c>
@@ -27953,7 +28042,7 @@
       <c r="AB23" s="188"/>
       <c r="AC23" s="173"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="188" t="s">
         <v>196</v>
       </c>
@@ -27986,7 +28075,7 @@
       <c r="AB24" s="188"/>
       <c r="AC24" s="173"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="189" t="s">
         <v>197</v>
       </c>
@@ -28019,7 +28108,7 @@
       <c r="AB25" s="189"/>
       <c r="AC25" s="173"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="181" t="s">
         <v>198</v>
       </c>
@@ -28052,7 +28141,7 @@
       <c r="AB26" s="181"/>
       <c r="AC26" s="173"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="190" t="s">
         <v>199</v>
       </c>
@@ -28085,7 +28174,7 @@
       <c r="AB27" s="190"/>
       <c r="AC27" s="173"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172" t="s">
         <v>200</v>
       </c>
@@ -28117,7 +28206,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>201</v>
       </c>
@@ -28149,7 +28238,7 @@
       <c r="AA29" s="190"/>
       <c r="AB29" s="190"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="191" t="s">
         <v>202</v>
       </c>
@@ -28181,7 +28270,7 @@
       <c r="AA30" s="191"/>
       <c r="AB30" s="191"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="191" t="s">
         <v>203</v>
       </c>
@@ -28213,7 +28302,7 @@
       <c r="AA31" s="191"/>
       <c r="AB31" s="191"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="191" t="s">
         <v>204</v>
       </c>
@@ -28245,7 +28334,7 @@
       <c r="AA32" s="191"/>
       <c r="AB32" s="191"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="191"/>
       <c r="B33" s="191"/>
       <c r="C33" s="191"/>
@@ -28275,7 +28364,7 @@
       <c r="AA33" s="191"/>
       <c r="AB33" s="191"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="191"/>
       <c r="B34" s="191"/>
       <c r="C34" s="191"/>
@@ -28305,7 +28394,7 @@
       <c r="AA34" s="191"/>
       <c r="AB34" s="191"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="192" t="s">
         <v>205</v>
       </c>
@@ -28337,7 +28426,7 @@
       <c r="AA35" s="192"/>
       <c r="AB35" s="192"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="193" t="s">
         <v>206</v>
       </c>
@@ -28369,7 +28458,7 @@
       <c r="AA36" s="193"/>
       <c r="AB36" s="193"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="194" t="s">
         <v>207</v>
       </c>
@@ -28401,7 +28490,7 @@
       <c r="AA37" s="194"/>
       <c r="AB37" s="194"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="179" t="s">
         <v>208</v>
       </c>
@@ -28433,7 +28522,7 @@
       <c r="AA38" s="179"/>
       <c r="AB38" s="179"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="181" t="s">
         <v>209</v>
       </c>
@@ -28465,7 +28554,7 @@
       <c r="AA39" s="181"/>
       <c r="AB39" s="181"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="195"/>
       <c r="B40" s="195"/>
       <c r="C40" s="195"/>
@@ -28495,7 +28584,7 @@
       <c r="AA40" s="195"/>
       <c r="AB40" s="195"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="172" t="s">
         <v>210</v>
       </c>
@@ -28527,7 +28616,7 @@
       <c r="AA41" s="172"/>
       <c r="AB41" s="172"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="196" t="s">
         <v>211</v>
       </c>
@@ -28559,7 +28648,7 @@
       <c r="AA42" s="196"/>
       <c r="AB42" s="196"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="172" t="s">
         <v>212</v>
       </c>
@@ -28591,7 +28680,7 @@
       <c r="AA43" s="172"/>
       <c r="AB43" s="172"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="197" t="s">
         <v>213</v>
       </c>
@@ -28623,7 +28712,7 @@
       <c r="AA44" s="197"/>
       <c r="AB44" s="197"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="198"/>
       <c r="B45" s="198"/>
       <c r="C45" s="198"/>
@@ -28653,7 +28742,7 @@
       <c r="AA45" s="198"/>
       <c r="AB45" s="198"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="198"/>
       <c r="B46" s="198"/>
       <c r="C46" s="198"/>
@@ -28683,7 +28772,7 @@
       <c r="AA46" s="198"/>
       <c r="AB46" s="198"/>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="198"/>
       <c r="B47" s="198"/>
       <c r="C47" s="198"/>
@@ -28713,7 +28802,7 @@
       <c r="AA47" s="198"/>
       <c r="AB47" s="198"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="199"/>
       <c r="B48" s="199"/>
       <c r="C48" s="199"/>
@@ -28743,7 +28832,7 @@
       <c r="AA48" s="199"/>
       <c r="AB48" s="199"/>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="172" t="s">
         <v>214</v>
       </c>
@@ -28775,7 +28864,7 @@
       <c r="AA49" s="172"/>
       <c r="AB49" s="172"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="200" t="s">
         <v>215</v>
       </c>
@@ -28807,7 +28896,7 @@
       <c r="AA50" s="200"/>
       <c r="AB50" s="200"/>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="201"/>
       <c r="B51" s="201"/>
       <c r="C51" s="201"/>
@@ -28837,7 +28926,7 @@
       <c r="AA51" s="201"/>
       <c r="AB51" s="201"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="176"/>
       <c r="B52" s="176"/>
       <c r="C52" s="176"/>
@@ -28867,7 +28956,7 @@
       <c r="AA52" s="176"/>
       <c r="AB52" s="176"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="198"/>
       <c r="B53" s="198"/>
       <c r="C53" s="198"/>
@@ -28897,7 +28986,7 @@
       <c r="AA53" s="198"/>
       <c r="AB53" s="198"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="198"/>
       <c r="B54" s="198"/>
       <c r="C54" s="198"/>
@@ -28927,7 +29016,7 @@
       <c r="AA54" s="198"/>
       <c r="AB54" s="198"/>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="198"/>
       <c r="B55" s="198"/>
       <c r="C55" s="198"/>
@@ -28957,7 +29046,7 @@
       <c r="AA55" s="198"/>
       <c r="AB55" s="198"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="202"/>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -29052,10 +29141,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AC45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <sheetData>
-    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="171" t="s">
         <v>216</v>
       </c>
@@ -29087,7 +29177,7 @@
       <c r="AA2" s="171"/>
       <c r="AB2" s="171"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="172"/>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -29118,7 +29208,7 @@
       <c r="AB3" s="172"/>
       <c r="AC3" s="173"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="174"/>
       <c r="B4" s="174"/>
       <c r="C4" s="174"/>
@@ -29149,7 +29239,7 @@
       <c r="AB4" s="174"/>
       <c r="AC4" s="173"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="203"/>
       <c r="B5" s="203"/>
       <c r="C5" s="203"/>
@@ -29180,7 +29270,7 @@
       <c r="AB5" s="203"/>
       <c r="AC5" s="173"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="176"/>
       <c r="B6" s="176"/>
       <c r="C6" s="176"/>
@@ -29211,7 +29301,7 @@
       <c r="AB6" s="176"/>
       <c r="AC6" s="173"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="204"/>
       <c r="B7" s="204"/>
       <c r="C7" s="204"/>
@@ -29242,7 +29332,7 @@
       <c r="AB7" s="204"/>
       <c r="AC7" s="173"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="176"/>
       <c r="B8" s="176"/>
       <c r="C8" s="176"/>
@@ -29273,7 +29363,7 @@
       <c r="AB8" s="176"/>
       <c r="AC8" s="173"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="205"/>
       <c r="B9" s="205"/>
       <c r="C9" s="205"/>
@@ -29304,7 +29394,7 @@
       <c r="AB9" s="205"/>
       <c r="AC9" s="173"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="206"/>
       <c r="B10" s="206"/>
       <c r="C10" s="206"/>
@@ -29335,7 +29425,7 @@
       <c r="AB10" s="206"/>
       <c r="AC10" s="173"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="172"/>
       <c r="B11" s="172"/>
       <c r="C11" s="172"/>
@@ -29366,7 +29456,7 @@
       <c r="AB11" s="172"/>
       <c r="AC11" s="173"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="207"/>
       <c r="B12" s="207"/>
       <c r="C12" s="207"/>
@@ -29397,7 +29487,7 @@
       <c r="AB12" s="207"/>
       <c r="AC12" s="173"/>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="172"/>
       <c r="B13" s="172"/>
       <c r="C13" s="172"/>
@@ -29428,7 +29518,7 @@
       <c r="AB13" s="172"/>
       <c r="AC13" s="173"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="184"/>
       <c r="B14" s="184"/>
       <c r="C14" s="184"/>
@@ -29459,7 +29549,7 @@
       <c r="AB14" s="184"/>
       <c r="AC14" s="173"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="208"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
@@ -29490,7 +29580,7 @@
       <c r="AB15" s="208"/>
       <c r="AC15" s="173"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="208"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
@@ -29521,7 +29611,7 @@
       <c r="AB16" s="208"/>
       <c r="AC16" s="173"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="205"/>
       <c r="B17" s="205"/>
       <c r="C17" s="205"/>
@@ -29552,7 +29642,7 @@
       <c r="AB17" s="205"/>
       <c r="AC17" s="173"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="205"/>
       <c r="B18" s="205"/>
       <c r="C18" s="205"/>
@@ -29583,7 +29673,7 @@
       <c r="AB18" s="205"/>
       <c r="AC18" s="173"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="209"/>
       <c r="B19" s="209"/>
       <c r="C19" s="209"/>
@@ -29614,7 +29704,7 @@
       <c r="AB19" s="209"/>
       <c r="AC19" s="173"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="172"/>
       <c r="B20" s="172"/>
       <c r="C20" s="172"/>
@@ -29645,7 +29735,7 @@
       <c r="AB20" s="172"/>
       <c r="AC20" s="173"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -29676,7 +29766,7 @@
       <c r="AB21" s="190"/>
       <c r="AC21" s="173"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="172"/>
       <c r="B22" s="172"/>
       <c r="C22" s="172"/>
@@ -29706,7 +29796,7 @@
       <c r="AA22" s="172"/>
       <c r="AB22" s="172"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="210"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -29736,7 +29826,7 @@
       <c r="AA23" s="210"/>
       <c r="AB23" s="210"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="211"/>
       <c r="B24" s="211"/>
       <c r="C24" s="211"/>
@@ -29766,7 +29856,7 @@
       <c r="AA24" s="211"/>
       <c r="AB24" s="211"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="172"/>
       <c r="B25" s="172"/>
       <c r="C25" s="172"/>
@@ -29796,7 +29886,7 @@
       <c r="AA25" s="172"/>
       <c r="AB25" s="172"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="174"/>
       <c r="B26" s="174"/>
       <c r="C26" s="174"/>
@@ -29826,7 +29916,7 @@
       <c r="AA26" s="174"/>
       <c r="AB26" s="174"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="212"/>
       <c r="B27" s="212"/>
       <c r="C27" s="212"/>
@@ -29856,7 +29946,7 @@
       <c r="AA27" s="212"/>
       <c r="AB27" s="212"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="172"/>
       <c r="B28" s="172"/>
       <c r="C28" s="172"/>
@@ -29886,7 +29976,7 @@
       <c r="AA28" s="172"/>
       <c r="AB28" s="172"/>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="213"/>
       <c r="B29" s="213"/>
       <c r="C29" s="213"/>
@@ -29916,7 +30006,7 @@
       <c r="AA29" s="213"/>
       <c r="AB29" s="213"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="172"/>
       <c r="B30" s="172"/>
       <c r="C30" s="172"/>
@@ -29946,7 +30036,7 @@
       <c r="AA30" s="172"/>
       <c r="AB30" s="172"/>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="213"/>
       <c r="B31" s="213"/>
       <c r="C31" s="213"/>
@@ -29976,7 +30066,7 @@
       <c r="AA31" s="213"/>
       <c r="AB31" s="213"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="172"/>
       <c r="B32" s="172"/>
       <c r="C32" s="172"/>
@@ -30006,7 +30096,7 @@
       <c r="AA32" s="172"/>
       <c r="AB32" s="172"/>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="200"/>
@@ -30036,7 +30126,7 @@
       <c r="AA33" s="200"/>
       <c r="AB33" s="200"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
       <c r="B34" s="198"/>
       <c r="C34" s="198"/>
@@ -30066,7 +30156,7 @@
       <c r="AA34" s="198"/>
       <c r="AB34" s="198"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
       <c r="B35" s="198"/>
       <c r="C35" s="198"/>
@@ -30096,7 +30186,7 @@
       <c r="AA35" s="198"/>
       <c r="AB35" s="198"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
       <c r="B36" s="198"/>
       <c r="C36" s="198"/>
@@ -30126,7 +30216,7 @@
       <c r="AA36" s="198"/>
       <c r="AB36" s="198"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="199"/>
       <c r="B37" s="199"/>
       <c r="C37" s="199"/>
@@ -30156,7 +30246,7 @@
       <c r="AA37" s="199"/>
       <c r="AB37" s="199"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="172" t="s">
         <v>214</v>
       </c>
@@ -30188,7 +30278,7 @@
       <c r="AA38" s="172"/>
       <c r="AB38" s="172"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="200" t="s">
         <v>215</v>
       </c>
@@ -30220,7 +30310,7 @@
       <c r="AA39" s="200"/>
       <c r="AB39" s="200"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="176"/>
       <c r="C40" s="176"/>
@@ -30250,7 +30340,7 @@
       <c r="AA40" s="176"/>
       <c r="AB40" s="176"/>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="176"/>
       <c r="B41" s="176"/>
       <c r="C41" s="176"/>
@@ -30280,7 +30370,7 @@
       <c r="AA41" s="176"/>
       <c r="AB41" s="176"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="198"/>
       <c r="B42" s="198"/>
       <c r="C42" s="198"/>
@@ -30310,7 +30400,7 @@
       <c r="AA42" s="198"/>
       <c r="AB42" s="198"/>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="198"/>
       <c r="B43" s="198"/>
       <c r="C43" s="198"/>
@@ -30340,7 +30430,7 @@
       <c r="AA43" s="198"/>
       <c r="AB43" s="198"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="198"/>
       <c r="B44" s="198"/>
       <c r="C44" s="198"/>
@@ -30370,7 +30460,7 @@
       <c r="AA44" s="198"/>
       <c r="AB44" s="198"/>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="202"/>
       <c r="B45" s="202"/>
       <c r="C45" s="202"/>
@@ -52113,19 +52203,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="10.29" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>340</v>
       </c>
@@ -52139,7 +52229,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>223</v>
       </c>
@@ -52151,7 +52241,7 @@
         <v>0.0882352941176471</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>224</v>
       </c>
@@ -52162,7 +52252,7 @@
         <v>95.35</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
         <v>225</v>
       </c>
@@ -52173,7 +52263,7 @@
         <v>102.69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>226</v>
       </c>
@@ -52184,13 +52274,13 @@
         <v>134.82</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="P8" s="35">
         <v>324.19</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="P9" s="35">
         <v>415</v>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -9864,30 +9864,74 @@
       <c r="C6" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53"/>
+      <c r="D6" s="52">
+        <v>245679.5</v>
+      </c>
+      <c r="E6" s="52">
+        <v>216530.08</v>
+      </c>
+      <c r="F6" s="52">
+        <v>29149.420000000013</v>
+      </c>
+      <c r="G6" s="53">
+        <v>0.11864815745717495</v>
+      </c>
+      <c r="H6" s="52">
+        <v>208360.5</v>
+      </c>
+      <c r="I6" s="52">
+        <v>168361.6</v>
+      </c>
+      <c r="J6" s="52">
+        <v>180366.49</v>
+      </c>
+      <c r="K6" s="52">
+        <v>138438.46000000002</v>
+      </c>
+      <c r="L6" s="52">
+        <v>41928.02999999997</v>
+      </c>
+      <c r="M6" s="53">
+        <v>0.23246019812216767</v>
+      </c>
       <c r="N6" s="53"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="53"/>
+      <c r="O6" s="52">
+        <v>27994.01</v>
+      </c>
+      <c r="P6" s="52">
+        <v>29923.14</v>
+      </c>
+      <c r="Q6" s="52">
+        <v>-1929.130000000001</v>
+      </c>
+      <c r="R6" s="53">
+        <v>-0.06891224229754869</v>
+      </c>
+      <c r="S6" s="54">
+        <v>565.45</v>
+      </c>
+      <c r="T6" s="54">
+        <v>600.25</v>
+      </c>
+      <c r="U6" s="54">
+        <v>-34.799999999999955</v>
+      </c>
+      <c r="V6" s="53">
+        <v>-0.061543903086037584</v>
+      </c>
       <c r="W6" s="53"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="56"/>
+      <c r="X6" s="55">
+        <v>80.24736359850063</v>
+      </c>
+      <c r="Y6" s="55">
+        <v>65.99877634098505</v>
+      </c>
+      <c r="Z6" s="53">
+        <v>0.2225</v>
+      </c>
+      <c r="AA6" s="56">
+        <v>0.1519</v>
+      </c>
       <c r="AB6" s="57"/>
       <c r="AD6" s="35"/>
       <c r="AE6" s="35"/>
@@ -10227,30 +10271,74 @@
       <c r="C13" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="53"/>
+      <c r="D13" s="52">
+        <v>129074.86</v>
+      </c>
+      <c r="E13" s="62">
+        <v>85864.08</v>
+      </c>
+      <c r="F13" s="52">
+        <v>43210.78</v>
+      </c>
+      <c r="G13" s="53">
+        <v>0.3347730146676123</v>
+      </c>
+      <c r="H13" s="52">
+        <v>101420.72</v>
+      </c>
+      <c r="I13" s="52">
+        <v>79791.03</v>
+      </c>
+      <c r="J13" s="52">
+        <v>83645.65</v>
+      </c>
+      <c r="K13" s="52">
+        <v>71604.5</v>
+      </c>
+      <c r="L13" s="52">
+        <v>12041.149999999994</v>
+      </c>
+      <c r="M13" s="53">
+        <v>0.1439542881189876</v>
+      </c>
       <c r="N13" s="53"/>
-      <c r="O13" s="52"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="53"/>
+      <c r="O13" s="52">
+        <v>17775.07</v>
+      </c>
+      <c r="P13" s="52">
+        <v>8186.53</v>
+      </c>
+      <c r="Q13" s="52">
+        <v>9588.54</v>
+      </c>
+      <c r="R13" s="53">
+        <v>0.5394375380800188</v>
+      </c>
+      <c r="S13" s="54">
+        <v>356.07</v>
+      </c>
+      <c r="T13" s="54">
+        <v>168.25</v>
+      </c>
+      <c r="U13" s="54">
+        <v>187.82</v>
+      </c>
+      <c r="V13" s="53">
+        <v>0.5274805515769371</v>
+      </c>
       <c r="W13" s="53"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="55"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="56"/>
+      <c r="X13" s="55">
+        <v>36.09539375928678</v>
+      </c>
+      <c r="Y13" s="55">
+        <v>77.66490997775718</v>
+      </c>
+      <c r="Z13" s="53">
+        <v>0.0707</v>
+      </c>
+      <c r="AA13" s="56">
+        <v>0.2142</v>
+      </c>
       <c r="AB13" s="57"/>
       <c r="AD13" s="35"/>
       <c r="AE13" s="35"/>
@@ -10590,30 +10678,74 @@
       <c r="C20" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="53"/>
+      <c r="D20" s="52">
+        <v>27500.32</v>
+      </c>
+      <c r="E20" s="52">
+        <v>11999.08</v>
+      </c>
+      <c r="F20" s="52">
+        <v>15501.24</v>
+      </c>
+      <c r="G20" s="53">
+        <v>0.5636748954193987</v>
+      </c>
+      <c r="H20" s="52">
+        <v>19565.83</v>
+      </c>
+      <c r="I20" s="52">
+        <v>7921.92</v>
+      </c>
+      <c r="J20" s="52">
+        <v>13767.340000000002</v>
+      </c>
+      <c r="K20" s="52">
+        <v>6211.24</v>
+      </c>
+      <c r="L20" s="52">
+        <v>7556.100000000002</v>
+      </c>
+      <c r="M20" s="53">
+        <v>0.5488424052867149</v>
+      </c>
       <c r="N20" s="53"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="53"/>
+      <c r="O20" s="52">
+        <v>5798.49</v>
+      </c>
+      <c r="P20" s="52">
+        <v>1710.68</v>
+      </c>
+      <c r="Q20" s="52">
+        <v>4087.8099999999995</v>
+      </c>
+      <c r="R20" s="53">
+        <v>0.7049783650571096</v>
+      </c>
+      <c r="S20" s="54">
+        <v>125.39</v>
+      </c>
+      <c r="T20" s="54">
+        <v>34.75</v>
+      </c>
+      <c r="U20" s="54">
+        <v>90.64</v>
+      </c>
+      <c r="V20" s="53">
+        <v>0.7228646622537682</v>
+      </c>
       <c r="W20" s="53"/>
-      <c r="X20" s="55"/>
-      <c r="Y20" s="55"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="56"/>
+      <c r="X20" s="55">
+        <v>117.328345323741</v>
+      </c>
+      <c r="Y20" s="55">
+        <v>63.27846478985563</v>
+      </c>
+      <c r="Z20" s="53">
+        <v>0.3398</v>
+      </c>
+      <c r="AA20" s="56">
+        <v>0.2885</v>
+      </c>
       <c r="AB20" s="57"/>
       <c r="AD20" s="35"/>
       <c r="AE20" s="35"/>
@@ -10955,30 +11087,74 @@
       <c r="C27" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="53"/>
+      <c r="D27" s="55">
+        <v>150850.82</v>
+      </c>
+      <c r="E27" s="55">
+        <v>144370.8</v>
+      </c>
+      <c r="F27" s="52">
+        <v>6480.020000000019</v>
+      </c>
+      <c r="G27" s="53">
+        <v>0.042956478459978</v>
+      </c>
+      <c r="H27" s="52">
+        <v>102178.42</v>
+      </c>
+      <c r="I27" s="52">
+        <v>89222.05</v>
+      </c>
+      <c r="J27" s="52">
+        <v>62464.86</v>
+      </c>
+      <c r="K27" s="52">
+        <v>58984</v>
+      </c>
+      <c r="L27" s="52">
+        <v>3480.8600000000006</v>
+      </c>
+      <c r="M27" s="53">
+        <v>0.05572509087509362</v>
+      </c>
       <c r="N27" s="53"/>
-      <c r="O27" s="52"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="53"/>
+      <c r="O27" s="52">
+        <v>39713.56</v>
+      </c>
+      <c r="P27" s="52">
+        <v>30238.05</v>
+      </c>
+      <c r="Q27" s="52">
+        <v>9475.509999999998</v>
+      </c>
+      <c r="R27" s="53">
+        <v>0.23859633837913294</v>
+      </c>
+      <c r="S27" s="54">
+        <v>795.22</v>
+      </c>
+      <c r="T27" s="54">
+        <v>615</v>
+      </c>
+      <c r="U27" s="54">
+        <v>180.22000000000003</v>
+      </c>
+      <c r="V27" s="53">
+        <v>0.22662910892583188</v>
+      </c>
       <c r="W27" s="53"/>
-      <c r="X27" s="55"/>
-      <c r="Y27" s="55"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="56"/>
+      <c r="X27" s="55">
+        <v>89.67276422764228</v>
+      </c>
+      <c r="Y27" s="55">
+        <v>61.20621468124544</v>
+      </c>
+      <c r="Z27" s="53">
+        <v>0.382</v>
+      </c>
+      <c r="AA27" s="56">
+        <v>0.3227</v>
+      </c>
       <c r="AB27" s="57"/>
       <c r="AD27" s="35"/>
       <c r="AE27" s="35"/>
@@ -11318,30 +11494,74 @@
       <c r="C34" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="53"/>
+      <c r="D34" s="52">
+        <v>396422.03</v>
+      </c>
+      <c r="E34" s="52">
+        <v>259347.71</v>
+      </c>
+      <c r="F34" s="52">
+        <v>137074.32000000004</v>
+      </c>
+      <c r="G34" s="53">
+        <v>0.3457787651205964</v>
+      </c>
+      <c r="H34" s="52">
+        <v>327431.12</v>
+      </c>
+      <c r="I34" s="65">
+        <v>223659.54</v>
+      </c>
+      <c r="J34" s="52">
+        <v>271519.78</v>
+      </c>
+      <c r="K34" s="52">
+        <v>197370.72</v>
+      </c>
+      <c r="L34" s="52">
+        <v>74149.06000000003</v>
+      </c>
+      <c r="M34" s="53">
+        <v>0.27308898084699396</v>
+      </c>
       <c r="N34" s="53"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="52"/>
-      <c r="Q34" s="52"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="54"/>
-      <c r="T34" s="54"/>
-      <c r="U34" s="54"/>
-      <c r="V34" s="53"/>
+      <c r="O34" s="52">
+        <v>55911.34</v>
+      </c>
+      <c r="P34" s="52">
+        <v>26288.82</v>
+      </c>
+      <c r="Q34" s="52">
+        <v>29622.519999999997</v>
+      </c>
+      <c r="R34" s="53">
+        <v>0.5298123779540966</v>
+      </c>
+      <c r="S34" s="54">
+        <v>1120.27</v>
+      </c>
+      <c r="T34" s="54">
+        <v>607.75</v>
+      </c>
+      <c r="U34" s="54">
+        <v>512.52</v>
+      </c>
+      <c r="V34" s="53">
+        <v>0.4574968534371178</v>
+      </c>
       <c r="W34" s="53"/>
-      <c r="X34" s="55"/>
-      <c r="Y34" s="55"/>
-      <c r="Z34" s="53"/>
-      <c r="AA34" s="56"/>
+      <c r="X34" s="55">
+        <v>58.721793500617025</v>
+      </c>
+      <c r="Y34" s="55">
+        <v>61.5841822414239</v>
+      </c>
+      <c r="Z34" s="53">
+        <v>0.1376</v>
+      </c>
+      <c r="AA34" s="56">
+        <v>0.174</v>
+      </c>
       <c r="AB34" s="57"/>
       <c r="AD34" s="35"/>
       <c r="AE34" s="35"/>
@@ -11681,30 +11901,74 @@
       <c r="C41" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="53"/>
+      <c r="D41" s="52">
+        <v>128258.5</v>
+      </c>
+      <c r="E41" s="52">
+        <v>53944.83</v>
+      </c>
+      <c r="F41" s="52">
+        <v>74313.67</v>
+      </c>
+      <c r="G41" s="53">
+        <v>0.5794054195238522</v>
+      </c>
+      <c r="H41" s="52">
+        <v>94098.32</v>
+      </c>
+      <c r="I41" s="52">
+        <v>49261.61</v>
+      </c>
+      <c r="J41" s="52">
+        <v>69042.09000000001</v>
+      </c>
+      <c r="K41" s="52">
+        <v>35683.74</v>
+      </c>
+      <c r="L41" s="52">
+        <v>33358.35000000001</v>
+      </c>
+      <c r="M41" s="53">
+        <v>0.4831596204576079</v>
+      </c>
       <c r="N41" s="53"/>
-      <c r="O41" s="52"/>
-      <c r="P41" s="52"/>
-      <c r="Q41" s="52"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="54"/>
-      <c r="V41" s="53"/>
+      <c r="O41" s="52">
+        <v>25056.23</v>
+      </c>
+      <c r="P41" s="52">
+        <v>13577.87</v>
+      </c>
+      <c r="Q41" s="52">
+        <v>11478.359999999999</v>
+      </c>
+      <c r="R41" s="53">
+        <v>0.45810403241030273</v>
+      </c>
+      <c r="S41" s="54">
+        <v>501.83</v>
+      </c>
+      <c r="T41" s="54">
+        <v>299.5</v>
+      </c>
+      <c r="U41" s="54">
+        <v>202.32999999999998</v>
+      </c>
+      <c r="V41" s="53">
+        <v>0.40318434529621583</v>
+      </c>
       <c r="W41" s="53"/>
-      <c r="X41" s="55"/>
-      <c r="Y41" s="55"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="56"/>
+      <c r="X41" s="55">
+        <v>15.63679465776294</v>
+      </c>
+      <c r="Y41" s="55">
+        <v>68.07122423898531</v>
+      </c>
+      <c r="Z41" s="53">
+        <v>0.0868</v>
+      </c>
+      <c r="AA41" s="56">
+        <v>0.2663</v>
+      </c>
       <c r="AB41" s="57"/>
       <c r="AD41" s="35"/>
       <c r="AE41" s="35"/>
@@ -12046,30 +12310,74 @@
       <c r="C48" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="53"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="53"/>
+      <c r="D48" s="52">
+        <v>65693.36</v>
+      </c>
+      <c r="E48" s="52">
+        <v>33326.49</v>
+      </c>
+      <c r="F48" s="52">
+        <v>32366.870000000003</v>
+      </c>
+      <c r="G48" s="53">
+        <v>0.49269621769993194</v>
+      </c>
+      <c r="H48" s="52">
+        <v>50582.37</v>
+      </c>
+      <c r="I48" s="52">
+        <v>25196.36</v>
+      </c>
+      <c r="J48" s="52">
+        <v>39438.990000000005</v>
+      </c>
+      <c r="K48" s="52">
+        <v>20036.420000000002</v>
+      </c>
+      <c r="L48" s="52">
+        <v>19402.570000000003</v>
+      </c>
+      <c r="M48" s="53">
+        <v>0.49196417048205343</v>
+      </c>
       <c r="N48" s="53"/>
-      <c r="O48" s="52"/>
-      <c r="P48" s="52"/>
-      <c r="Q48" s="52"/>
-      <c r="R48" s="53"/>
-      <c r="S48" s="54"/>
-      <c r="T48" s="54"/>
-      <c r="U48" s="54"/>
-      <c r="V48" s="53"/>
+      <c r="O48" s="52">
+        <v>11143.38</v>
+      </c>
+      <c r="P48" s="52">
+        <v>5159.94</v>
+      </c>
+      <c r="Q48" s="52">
+        <v>5983.44</v>
+      </c>
+      <c r="R48" s="53">
+        <v>0.5369501892603501</v>
+      </c>
+      <c r="S48" s="54">
+        <v>223.22</v>
+      </c>
+      <c r="T48" s="54">
+        <v>113.25</v>
+      </c>
+      <c r="U48" s="54">
+        <v>109.97</v>
+      </c>
+      <c r="V48" s="53">
+        <v>0.49265298808350505</v>
+      </c>
       <c r="W48" s="53"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="53"/>
-      <c r="AA48" s="56"/>
+      <c r="X48" s="55">
+        <v>71.78922737306843</v>
+      </c>
+      <c r="Y48" s="55">
+        <v>67.69550512136009</v>
+      </c>
+      <c r="Z48" s="53">
+        <v>0.244</v>
+      </c>
+      <c r="AA48" s="56">
+        <v>0.23</v>
+      </c>
       <c r="AB48" s="57"/>
       <c r="AD48" s="35"/>
       <c r="AE48" s="35"/>
@@ -12409,30 +12717,74 @@
       <c r="C55" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="53"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="52"/>
-      <c r="K55" s="52"/>
-      <c r="L55" s="52"/>
-      <c r="M55" s="53"/>
+      <c r="D55" s="52">
+        <v>155296.79</v>
+      </c>
+      <c r="E55" s="52">
+        <v>127814.48</v>
+      </c>
+      <c r="F55" s="52">
+        <v>27482.310000000012</v>
+      </c>
+      <c r="G55" s="53">
+        <v>0.176966375158173</v>
+      </c>
+      <c r="H55" s="52">
+        <v>109364.97</v>
+      </c>
+      <c r="I55" s="52">
+        <v>96483.38</v>
+      </c>
+      <c r="J55" s="52">
+        <v>75135.01000000001</v>
+      </c>
+      <c r="K55" s="52">
+        <v>71221.34</v>
+      </c>
+      <c r="L55" s="52">
+        <v>3913.670000000013</v>
+      </c>
+      <c r="M55" s="53">
+        <v>0.05208850042077604</v>
+      </c>
       <c r="N55" s="53"/>
-      <c r="O55" s="52"/>
-      <c r="P55" s="52"/>
-      <c r="Q55" s="52"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="54"/>
-      <c r="T55" s="54"/>
-      <c r="U55" s="54"/>
-      <c r="V55" s="53"/>
+      <c r="O55" s="52">
+        <v>34229.96</v>
+      </c>
+      <c r="P55" s="52">
+        <v>25262.04</v>
+      </c>
+      <c r="Q55" s="52">
+        <v>8967.919999999998</v>
+      </c>
+      <c r="R55" s="53">
+        <v>0.2619903733454552</v>
+      </c>
+      <c r="S55" s="54">
+        <v>685.48</v>
+      </c>
+      <c r="T55" s="54">
+        <v>533.75</v>
+      </c>
+      <c r="U55" s="54">
+        <v>151.73000000000002</v>
+      </c>
+      <c r="V55" s="53">
+        <v>0.22134854408589605</v>
+      </c>
       <c r="W55" s="53"/>
-      <c r="X55" s="55"/>
-      <c r="Y55" s="55"/>
-      <c r="Z55" s="53"/>
-      <c r="AA55" s="56"/>
+      <c r="X55" s="55">
+        <v>58.699953161592504</v>
+      </c>
+      <c r="Y55" s="55">
+        <v>67.00679527854935</v>
+      </c>
+      <c r="Z55" s="53">
+        <v>0.2451</v>
+      </c>
+      <c r="AA55" s="56">
+        <v>0.2958</v>
+      </c>
       <c r="AB55" s="57"/>
       <c r="AD55" s="35"/>
       <c r="AE55" s="35"/>
@@ -12772,30 +13124,74 @@
       <c r="C62" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D62" s="52"/>
-      <c r="E62" s="52"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="52"/>
-      <c r="I62" s="52"/>
-      <c r="J62" s="52"/>
-      <c r="K62" s="52"/>
-      <c r="L62" s="52"/>
-      <c r="M62" s="53"/>
+      <c r="D62" s="52">
+        <v>20420.56</v>
+      </c>
+      <c r="E62" s="52">
+        <v>20420.56</v>
+      </c>
+      <c r="F62" s="52">
+        <v>0</v>
+      </c>
+      <c r="G62" s="53">
+        <v>0</v>
+      </c>
+      <c r="H62" s="52">
+        <v>15859.68</v>
+      </c>
+      <c r="I62" s="52">
+        <v>13435.12</v>
+      </c>
+      <c r="J62" s="52">
+        <v>12689.1</v>
+      </c>
+      <c r="K62" s="52">
+        <v>11478.25</v>
+      </c>
+      <c r="L62" s="52">
+        <v>1210.8500000000004</v>
+      </c>
+      <c r="M62" s="53">
+        <v>0.09542441938356545</v>
+      </c>
       <c r="N62" s="53"/>
-      <c r="O62" s="52"/>
-      <c r="P62" s="52"/>
-      <c r="Q62" s="52"/>
-      <c r="R62" s="53"/>
-      <c r="S62" s="54"/>
-      <c r="T62" s="54"/>
-      <c r="U62" s="54"/>
-      <c r="V62" s="53"/>
+      <c r="O62" s="52">
+        <v>3170.58</v>
+      </c>
+      <c r="P62" s="52">
+        <v>1956.87</v>
+      </c>
+      <c r="Q62" s="52">
+        <v>1213.71</v>
+      </c>
+      <c r="R62" s="53">
+        <v>0.38280377722687964</v>
+      </c>
+      <c r="S62" s="54">
+        <v>63.5</v>
+      </c>
+      <c r="T62" s="54">
+        <v>48.25</v>
+      </c>
+      <c r="U62" s="54">
+        <v>15.25</v>
+      </c>
+      <c r="V62" s="53">
+        <v>0.24015748031496062</v>
+      </c>
       <c r="W62" s="53"/>
-      <c r="X62" s="55"/>
-      <c r="Y62" s="55"/>
-      <c r="Z62" s="53"/>
-      <c r="AA62" s="56"/>
+      <c r="X62" s="55">
+        <v>144.7759585492228</v>
+      </c>
+      <c r="Y62" s="55">
+        <v>71.82495570677168</v>
+      </c>
+      <c r="Z62" s="53">
+        <v>0.3421</v>
+      </c>
+      <c r="AA62" s="56">
+        <v>0.2233</v>
+      </c>
       <c r="AB62" s="57"/>
       <c r="AD62" s="35"/>
       <c r="AE62" s="35"/>
@@ -13129,30 +13525,74 @@
       <c r="C69" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D69" s="52"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="52"/>
-      <c r="I69" s="52"/>
-      <c r="J69" s="52"/>
-      <c r="K69" s="52"/>
-      <c r="L69" s="52"/>
-      <c r="M69" s="53"/>
+      <c r="D69" s="52">
+        <v>47801.68</v>
+      </c>
+      <c r="E69" s="52">
+        <v>10650.43</v>
+      </c>
+      <c r="F69" s="52">
+        <v>37151.25</v>
+      </c>
+      <c r="G69" s="53">
+        <v>0.7771954876899724</v>
+      </c>
+      <c r="H69" s="52">
+        <v>35572.59</v>
+      </c>
+      <c r="I69" s="52">
+        <v>10547.08</v>
+      </c>
+      <c r="J69" s="52">
+        <v>27136.549999999996</v>
+      </c>
+      <c r="K69" s="52">
+        <v>10398.3</v>
+      </c>
+      <c r="L69" s="52">
+        <v>16738.249999999996</v>
+      </c>
+      <c r="M69" s="53">
+        <v>0.6168156969106242</v>
+      </c>
       <c r="N69" s="53"/>
-      <c r="O69" s="52"/>
-      <c r="P69" s="52"/>
-      <c r="Q69" s="52"/>
-      <c r="R69" s="53"/>
-      <c r="S69" s="54"/>
-      <c r="T69" s="54"/>
-      <c r="U69" s="54"/>
-      <c r="V69" s="53"/>
+      <c r="O69" s="52">
+        <v>8436.04</v>
+      </c>
+      <c r="P69" s="52">
+        <v>148.78</v>
+      </c>
+      <c r="Q69" s="52">
+        <v>8287.26</v>
+      </c>
+      <c r="R69" s="53">
+        <v>0.9823637630926358</v>
+      </c>
+      <c r="S69" s="54">
+        <v>169.32</v>
+      </c>
+      <c r="T69" s="54">
+        <v>2.75</v>
+      </c>
+      <c r="U69" s="54">
+        <v>166.57</v>
+      </c>
+      <c r="V69" s="53">
+        <v>0.9837585636664304</v>
+      </c>
       <c r="W69" s="53"/>
-      <c r="X69" s="55"/>
-      <c r="Y69" s="55"/>
-      <c r="Z69" s="53"/>
-      <c r="AA69" s="56"/>
+      <c r="X69" s="55">
+        <v>37.58181818181818</v>
+      </c>
+      <c r="Y69" s="55">
+        <v>72.22475431425701</v>
+      </c>
+      <c r="Z69" s="53">
+        <v>0.0097</v>
+      </c>
+      <c r="AA69" s="56">
+        <v>0.2558</v>
+      </c>
       <c r="AB69" s="57"/>
       <c r="AD69" s="35"/>
       <c r="AE69" s="35"/>
@@ -13482,30 +13922,74 @@
       <c r="C76" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
-      <c r="J76" s="52"/>
-      <c r="K76" s="52"/>
-      <c r="L76" s="52"/>
-      <c r="M76" s="53"/>
+      <c r="D76" s="52">
+        <v>77166.16</v>
+      </c>
+      <c r="E76" s="52">
+        <v>44764.99</v>
+      </c>
+      <c r="F76" s="52">
+        <v>32401.170000000006</v>
+      </c>
+      <c r="G76" s="53">
+        <v>0.41988832928838243</v>
+      </c>
+      <c r="H76" s="52">
+        <v>54302.66</v>
+      </c>
+      <c r="I76" s="52">
+        <v>29696.65</v>
+      </c>
+      <c r="J76" s="52">
+        <v>31383.390000000003</v>
+      </c>
+      <c r="K76" s="52">
+        <v>23592.600000000002</v>
+      </c>
+      <c r="L76" s="52">
+        <v>7790.790000000001</v>
+      </c>
+      <c r="M76" s="53">
+        <v>0.24824564841465502</v>
+      </c>
       <c r="N76" s="53"/>
-      <c r="O76" s="52"/>
-      <c r="P76" s="52"/>
-      <c r="Q76" s="52"/>
-      <c r="R76" s="53"/>
-      <c r="S76" s="54"/>
-      <c r="T76" s="54"/>
-      <c r="U76" s="54"/>
-      <c r="V76" s="53"/>
+      <c r="O76" s="52">
+        <v>22919.27</v>
+      </c>
+      <c r="P76" s="52">
+        <v>6104.05</v>
+      </c>
+      <c r="Q76" s="52">
+        <v>16815.22</v>
+      </c>
+      <c r="R76" s="53">
+        <v>0.7336717094392623</v>
+      </c>
+      <c r="S76" s="54">
+        <v>470.62</v>
+      </c>
+      <c r="T76" s="54">
+        <v>120.25</v>
+      </c>
+      <c r="U76" s="54">
+        <v>350.37</v>
+      </c>
+      <c r="V76" s="53">
+        <v>0.7444859971951894</v>
+      </c>
       <c r="W76" s="53"/>
-      <c r="X76" s="55"/>
-      <c r="Y76" s="55"/>
-      <c r="Z76" s="53"/>
-      <c r="AA76" s="56"/>
+      <c r="X76" s="55">
+        <v>125.30844074844074</v>
+      </c>
+      <c r="Y76" s="55">
+        <v>48.58165977967362</v>
+      </c>
+      <c r="Z76" s="53">
+        <v>0.33659999999999995</v>
+      </c>
+      <c r="AA76" s="56">
+        <v>0.2963</v>
+      </c>
       <c r="AB76" s="57"/>
       <c r="AD76" s="35"/>
       <c r="AE76" s="35"/>
@@ -13841,30 +14325,74 @@
       <c r="C83" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="53"/>
-      <c r="H83" s="52"/>
-      <c r="I83" s="52"/>
-      <c r="J83" s="52"/>
-      <c r="K83" s="52"/>
-      <c r="L83" s="52"/>
-      <c r="M83" s="53"/>
+      <c r="D83" s="52">
+        <v>25467.84</v>
+      </c>
+      <c r="E83" s="52">
+        <v>19598.41</v>
+      </c>
+      <c r="F83" s="52">
+        <v>5869.43</v>
+      </c>
+      <c r="G83" s="53">
+        <v>0.2304643817457625</v>
+      </c>
+      <c r="H83" s="52">
+        <v>16606.83</v>
+      </c>
+      <c r="I83" s="52">
+        <v>12958.24</v>
+      </c>
+      <c r="J83" s="52">
+        <v>9659.990000000002</v>
+      </c>
+      <c r="K83" s="52">
+        <v>5354.12</v>
+      </c>
+      <c r="L83" s="52">
+        <v>4305.870000000002</v>
+      </c>
+      <c r="M83" s="53">
+        <v>0.44574269745620865</v>
+      </c>
       <c r="N83" s="53"/>
-      <c r="O83" s="52"/>
-      <c r="P83" s="52"/>
-      <c r="Q83" s="52"/>
-      <c r="R83" s="53"/>
-      <c r="S83" s="54"/>
-      <c r="T83" s="54"/>
-      <c r="U83" s="54"/>
-      <c r="V83" s="53"/>
+      <c r="O83" s="52">
+        <v>6946.84</v>
+      </c>
+      <c r="P83" s="52">
+        <v>7604.12</v>
+      </c>
+      <c r="Q83" s="52">
+        <v>-657.2799999999997</v>
+      </c>
+      <c r="R83" s="53">
+        <v>-0.09461568137455299</v>
+      </c>
+      <c r="S83" s="54">
+        <v>139.07</v>
+      </c>
+      <c r="T83" s="54">
+        <v>147.75</v>
+      </c>
+      <c r="U83" s="54">
+        <v>-8.680000000000007</v>
+      </c>
+      <c r="V83" s="53">
+        <v>-0.06241461134680382</v>
+      </c>
       <c r="W83" s="53"/>
-      <c r="X83" s="55"/>
-      <c r="Y83" s="55"/>
-      <c r="Z83" s="53"/>
-      <c r="AA83" s="56"/>
+      <c r="X83" s="55">
+        <v>44.94192893401015</v>
+      </c>
+      <c r="Y83" s="55">
+        <v>63.7162162306752</v>
+      </c>
+      <c r="Z83" s="53">
+        <v>0.33880000000000005</v>
+      </c>
+      <c r="AA83" s="56">
+        <v>0.3479</v>
+      </c>
       <c r="AB83" s="57"/>
       <c r="AD83" s="35"/>
       <c r="AE83" s="35"/>
@@ -14204,30 +14732,74 @@
       <c r="C90" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D90" s="67"/>
-      <c r="E90" s="67"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="53"/>
+      <c r="D90" s="67">
+        <v>37083.03</v>
+      </c>
+      <c r="E90" s="67">
+        <v>36381.33</v>
+      </c>
+      <c r="F90" s="52">
+        <v>701.6999999999971</v>
+      </c>
+      <c r="G90" s="53">
+        <v>0.018922401972007064</v>
+      </c>
+      <c r="H90" s="52">
+        <v>27002.93</v>
+      </c>
+      <c r="I90" s="52">
+        <v>25060.53</v>
+      </c>
+      <c r="J90" s="52">
+        <v>15440.32</v>
+      </c>
+      <c r="K90" s="52">
+        <v>13974.73</v>
+      </c>
+      <c r="L90" s="52">
+        <v>1465.5900000000001</v>
+      </c>
+      <c r="M90" s="53">
+        <v>0.09491966487741188</v>
+      </c>
       <c r="N90" s="53"/>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="53"/>
-      <c r="S90" s="68"/>
-      <c r="T90" s="68"/>
-      <c r="U90" s="54"/>
-      <c r="V90" s="53"/>
+      <c r="O90" s="52">
+        <v>11562.61</v>
+      </c>
+      <c r="P90" s="52">
+        <v>11085.8</v>
+      </c>
+      <c r="Q90" s="52">
+        <v>476.8100000000013</v>
+      </c>
+      <c r="R90" s="53">
+        <v>0.041237229310683424</v>
+      </c>
+      <c r="S90" s="68">
+        <v>231.75</v>
+      </c>
+      <c r="T90" s="68">
+        <v>225.5</v>
+      </c>
+      <c r="U90" s="54">
+        <v>6.25</v>
+      </c>
+      <c r="V90" s="53">
+        <v>0.02696871628910464</v>
+      </c>
       <c r="W90" s="53"/>
-      <c r="X90" s="55"/>
-      <c r="Y90" s="55"/>
-      <c r="Z90" s="53"/>
-      <c r="AA90" s="56"/>
+      <c r="X90" s="55">
+        <v>50.20310421286031</v>
+      </c>
+      <c r="Y90" s="55">
+        <v>43.49557070636461</v>
+      </c>
+      <c r="Z90" s="53">
+        <v>0.31120000000000003</v>
+      </c>
+      <c r="AA90" s="56">
+        <v>0.2718</v>
+      </c>
       <c r="AB90" s="57"/>
       <c r="AD90" s="35"/>
       <c r="AE90" s="35"/>
@@ -14567,30 +15139,74 @@
       <c r="C97" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D97" s="52"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="53"/>
-      <c r="H97" s="52"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
-      <c r="L97" s="52"/>
-      <c r="M97" s="53"/>
+      <c r="D97" s="52">
+        <v>26186.14</v>
+      </c>
+      <c r="E97" s="52">
+        <v>5762.27</v>
+      </c>
+      <c r="F97" s="52">
+        <v>20423.87</v>
+      </c>
+      <c r="G97" s="53">
+        <v>0.7799496222047235</v>
+      </c>
+      <c r="H97" s="52">
+        <v>19428.98</v>
+      </c>
+      <c r="I97" s="52">
+        <v>7925.81</v>
+      </c>
+      <c r="J97" s="52">
+        <v>12051.32</v>
+      </c>
+      <c r="K97" s="52">
+        <v>7679.910000000001</v>
+      </c>
+      <c r="L97" s="52">
+        <v>4371.409999999999</v>
+      </c>
+      <c r="M97" s="53">
+        <v>0.36273287905391266</v>
+      </c>
       <c r="N97" s="53"/>
-      <c r="O97" s="52"/>
-      <c r="P97" s="52"/>
-      <c r="Q97" s="52"/>
-      <c r="R97" s="53"/>
-      <c r="S97" s="54"/>
-      <c r="T97" s="54"/>
-      <c r="U97" s="54"/>
-      <c r="V97" s="53"/>
+      <c r="O97" s="52">
+        <v>7377.66</v>
+      </c>
+      <c r="P97" s="52">
+        <v>245.9</v>
+      </c>
+      <c r="Q97" s="52">
+        <v>7131.76</v>
+      </c>
+      <c r="R97" s="53">
+        <v>0.9666696486419813</v>
+      </c>
+      <c r="S97" s="54">
+        <v>147.9</v>
+      </c>
+      <c r="T97" s="54">
+        <v>5</v>
+      </c>
+      <c r="U97" s="54">
+        <v>142.9</v>
+      </c>
+      <c r="V97" s="53">
+        <v>0.9661933739012847</v>
+      </c>
       <c r="W97" s="53"/>
-      <c r="X97" s="55"/>
-      <c r="Y97" s="55"/>
-      <c r="Z97" s="53"/>
-      <c r="AA97" s="56"/>
+      <c r="X97" s="55">
+        <v>-432.70799999999997</v>
+      </c>
+      <c r="Y97" s="55">
+        <v>45.687352144692355</v>
+      </c>
+      <c r="Z97" s="53">
+        <v>-0.37549999999999994</v>
+      </c>
+      <c r="AA97" s="56">
+        <v>0.258</v>
+      </c>
       <c r="AB97" s="57"/>
       <c r="AD97" s="35"/>
       <c r="AE97" s="35"/>
@@ -14930,30 +15546,74 @@
       <c r="C104" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="52"/>
-      <c r="E104" s="69"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="52"/>
-      <c r="I104" s="52"/>
-      <c r="J104" s="52"/>
-      <c r="K104" s="52"/>
-      <c r="L104" s="52"/>
-      <c r="M104" s="53"/>
+      <c r="D104" s="52">
+        <v>32473.02</v>
+      </c>
+      <c r="E104" s="69">
+        <v>33188.03</v>
+      </c>
+      <c r="F104" s="52">
+        <v>-715.0099999999984</v>
+      </c>
+      <c r="G104" s="53">
+        <v>-0.022018586506582952</v>
+      </c>
+      <c r="H104" s="52">
+        <v>23075.07</v>
+      </c>
+      <c r="I104" s="52">
+        <v>30925.21</v>
+      </c>
+      <c r="J104" s="52">
+        <v>12691.21</v>
+      </c>
+      <c r="K104" s="52">
+        <v>15184.269999999999</v>
+      </c>
+      <c r="L104" s="52">
+        <v>-2493.0599999999995</v>
+      </c>
+      <c r="M104" s="53">
+        <v>-0.1964398981657383</v>
+      </c>
       <c r="N104" s="53"/>
-      <c r="O104" s="52"/>
-      <c r="P104" s="52"/>
-      <c r="Q104" s="52"/>
-      <c r="R104" s="53"/>
-      <c r="S104" s="54"/>
-      <c r="T104" s="54"/>
-      <c r="U104" s="54"/>
-      <c r="V104" s="53"/>
+      <c r="O104" s="52">
+        <v>10383.86</v>
+      </c>
+      <c r="P104" s="52">
+        <v>15740.94</v>
+      </c>
+      <c r="Q104" s="52">
+        <v>-5357.08</v>
+      </c>
+      <c r="R104" s="53">
+        <v>-0.5159044902377343</v>
+      </c>
+      <c r="S104" s="54">
+        <v>208.2</v>
+      </c>
+      <c r="T104" s="54">
+        <v>317.25</v>
+      </c>
+      <c r="U104" s="54">
+        <v>-109.05000000000001</v>
+      </c>
+      <c r="V104" s="53">
+        <v>-0.5237752161383286</v>
+      </c>
       <c r="W104" s="53"/>
-      <c r="X104" s="55"/>
-      <c r="Y104" s="55"/>
-      <c r="Z104" s="53"/>
-      <c r="AA104" s="56"/>
+      <c r="X104" s="55">
+        <v>7.132608353033885</v>
+      </c>
+      <c r="Y104" s="55">
+        <v>45.139084580403456</v>
+      </c>
+      <c r="Z104" s="53">
+        <v>0.0682</v>
+      </c>
+      <c r="AA104" s="56">
+        <v>0.2894</v>
+      </c>
       <c r="AB104" s="57"/>
       <c r="AD104" s="35"/>
       <c r="AE104" s="35"/>
@@ -15295,30 +15955,74 @@
       <c r="C111" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D111" s="52"/>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="52"/>
-      <c r="I111" s="52"/>
-      <c r="J111" s="52"/>
-      <c r="K111" s="52"/>
-      <c r="L111" s="52"/>
-      <c r="M111" s="53"/>
+      <c r="D111" s="52">
+        <v>58902.56</v>
+      </c>
+      <c r="E111" s="52">
+        <v>0</v>
+      </c>
+      <c r="F111" s="52">
+        <v>58902.56</v>
+      </c>
+      <c r="G111" s="53">
+        <v>1</v>
+      </c>
+      <c r="H111" s="52">
+        <v>37601.88</v>
+      </c>
+      <c r="I111" s="52">
+        <v>45817.77</v>
+      </c>
+      <c r="J111" s="52">
+        <v>21415.85</v>
+      </c>
+      <c r="K111" s="52">
+        <v>23939.389999999996</v>
+      </c>
+      <c r="L111" s="52">
+        <v>-2523.5399999999972</v>
+      </c>
+      <c r="M111" s="53">
+        <v>-0.11783515480356826</v>
+      </c>
       <c r="N111" s="53"/>
-      <c r="O111" s="52"/>
-      <c r="P111" s="52"/>
-      <c r="Q111" s="52"/>
-      <c r="R111" s="53"/>
-      <c r="S111" s="54"/>
-      <c r="T111" s="54"/>
-      <c r="U111" s="54"/>
-      <c r="V111" s="53"/>
+      <c r="O111" s="52">
+        <v>16186.03</v>
+      </c>
+      <c r="P111" s="52">
+        <v>21878.38</v>
+      </c>
+      <c r="Q111" s="52">
+        <v>-5692.35</v>
+      </c>
+      <c r="R111" s="53">
+        <v>-0.3516829018604315</v>
+      </c>
+      <c r="S111" s="54">
+        <v>324.19</v>
+      </c>
+      <c r="T111" s="54">
+        <v>472.75</v>
+      </c>
+      <c r="U111" s="54">
+        <v>-148.56</v>
+      </c>
+      <c r="V111" s="53">
+        <v>-0.45824979178876585</v>
+      </c>
       <c r="W111" s="53"/>
-      <c r="X111" s="55"/>
-      <c r="Y111" s="55"/>
-      <c r="Z111" s="53"/>
-      <c r="AA111" s="56"/>
+      <c r="X111" s="55">
+        <v>48.973178212585935</v>
+      </c>
+      <c r="Y111" s="55">
+        <v>65.70431400737223</v>
+      </c>
+      <c r="Z111" s="53">
+        <v>0.3357</v>
+      </c>
+      <c r="AA111" s="56">
+        <v>0.3616</v>
+      </c>
       <c r="AB111" s="57"/>
       <c r="AD111" s="35"/>
       <c r="AE111" s="35"/>
@@ -18848,30 +19552,74 @@
       <c r="C181" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D181" s="52"/>
-      <c r="E181" s="52"/>
-      <c r="F181" s="52"/>
-      <c r="G181" s="53"/>
-      <c r="H181" s="52"/>
-      <c r="I181" s="52"/>
-      <c r="J181" s="52"/>
-      <c r="K181" s="52"/>
-      <c r="L181" s="52"/>
-      <c r="M181" s="53"/>
+      <c r="D181" s="52">
+        <v>16897.53</v>
+      </c>
+      <c r="E181" s="52">
+        <v>5491.7</v>
+      </c>
+      <c r="F181" s="52">
+        <v>11405.829999999998</v>
+      </c>
+      <c r="G181" s="53">
+        <v>0.6749998372543206</v>
+      </c>
+      <c r="H181" s="52">
+        <v>9226.27</v>
+      </c>
+      <c r="I181" s="52">
+        <v>3702.78</v>
+      </c>
+      <c r="J181" s="52">
+        <v>2977.1100000000006</v>
+      </c>
+      <c r="K181" s="52">
+        <v>2335.9700000000003</v>
+      </c>
+      <c r="L181" s="52">
+        <v>641.1400000000003</v>
+      </c>
+      <c r="M181" s="53">
+        <v>0.2153565034546927</v>
+      </c>
       <c r="N181" s="53"/>
-      <c r="O181" s="52"/>
-      <c r="P181" s="52"/>
-      <c r="Q181" s="52"/>
-      <c r="R181" s="53"/>
-      <c r="S181" s="54"/>
-      <c r="T181" s="54"/>
-      <c r="U181" s="54"/>
-      <c r="V181" s="53"/>
+      <c r="O181" s="52">
+        <v>6249.16</v>
+      </c>
+      <c r="P181" s="52">
+        <v>1366.81</v>
+      </c>
+      <c r="Q181" s="52">
+        <v>4882.35</v>
+      </c>
+      <c r="R181" s="53">
+        <v>0.7812810041669601</v>
+      </c>
+      <c r="S181" s="54">
+        <v>125.17</v>
+      </c>
+      <c r="T181" s="54">
+        <v>23.75</v>
+      </c>
+      <c r="U181" s="54">
+        <v>101.42</v>
+      </c>
+      <c r="V181" s="53">
+        <v>0.8102580490532876</v>
+      </c>
       <c r="W181" s="53"/>
-      <c r="X181" s="55"/>
-      <c r="Y181" s="55"/>
-      <c r="Z181" s="53"/>
-      <c r="AA181" s="56"/>
+      <c r="X181" s="55">
+        <v>75.32294736842105</v>
+      </c>
+      <c r="Y181" s="55">
+        <v>61.286703843093385</v>
+      </c>
+      <c r="Z181" s="53">
+        <v>0.3257</v>
+      </c>
+      <c r="AA181" s="56">
+        <v>0.454</v>
+      </c>
       <c r="AB181" s="57"/>
       <c r="AD181" s="35"/>
       <c r="AE181" s="35"/>
@@ -21185,30 +21933,74 @@
       <c r="C230" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D230" s="52"/>
-      <c r="E230" s="52"/>
-      <c r="F230" s="52"/>
-      <c r="G230" s="53"/>
-      <c r="H230" s="52"/>
-      <c r="I230" s="52"/>
-      <c r="J230" s="52"/>
-      <c r="K230" s="52"/>
-      <c r="L230" s="52"/>
-      <c r="M230" s="53"/>
+      <c r="D230" s="52">
+        <v>8795.03</v>
+      </c>
+      <c r="E230" s="52">
+        <v>0</v>
+      </c>
+      <c r="F230" s="52">
+        <v>8795.03</v>
+      </c>
+      <c r="G230" s="53">
+        <v>1</v>
+      </c>
+      <c r="H230" s="52">
+        <v>6369.12</v>
+      </c>
+      <c r="I230" s="52">
+        <v>0</v>
+      </c>
+      <c r="J230" s="52">
+        <v>4527.889999999999</v>
+      </c>
+      <c r="K230" s="52">
+        <v>0</v>
+      </c>
+      <c r="L230" s="52">
+        <v>4527.889999999999</v>
+      </c>
+      <c r="M230" s="53">
+        <v>1</v>
+      </c>
       <c r="N230" s="53"/>
-      <c r="O230" s="52"/>
-      <c r="P230" s="52"/>
-      <c r="Q230" s="52"/>
-      <c r="R230" s="53"/>
-      <c r="S230" s="54"/>
-      <c r="T230" s="54"/>
-      <c r="U230" s="54"/>
-      <c r="V230" s="53"/>
+      <c r="O230" s="52">
+        <v>1841.23</v>
+      </c>
+      <c r="P230" s="52">
+        <v>0</v>
+      </c>
+      <c r="Q230" s="52">
+        <v>1841.23</v>
+      </c>
+      <c r="R230" s="53">
+        <v>1</v>
+      </c>
+      <c r="S230" s="54">
+        <v>36.92</v>
+      </c>
+      <c r="T230" s="54">
+        <v>0</v>
+      </c>
+      <c r="U230" s="54">
+        <v>36.92</v>
+      </c>
+      <c r="V230" s="53">
+        <v>1</v>
+      </c>
       <c r="W230" s="53"/>
-      <c r="X230" s="55"/>
-      <c r="Y230" s="55"/>
-      <c r="Z230" s="53"/>
-      <c r="AA230" s="56"/>
+      <c r="X230" s="55">
+        <v>0</v>
+      </c>
+      <c r="Y230" s="55">
+        <v>65.70711175027087</v>
+      </c>
+      <c r="Z230" s="53">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="56">
+        <v>0.2758</v>
+      </c>
       <c r="AB230" s="57"/>
       <c r="AD230" s="35"/>
       <c r="AE230" s="35"/>

--- a/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
+++ b/public/Cassidy_Davies_Electrical_BPMN_Data.xlsx
@@ -17100,7 +17100,7 @@
       <c r="AH132" s="19"/>
       <c r="AI132" s="58"/>
     </row>
-    <row r="133" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B133" s="20"/>
       <c r="C133" s="51" t="s">
         <v>97</v>
@@ -22683,7 +22683,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD71"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11.43" style="35" customWidth="1"/>
@@ -22697,7 +22697,7 @@
     <col min="15" max="15" width="16.86" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
@@ -22719,7 +22719,7 @@
       <c r="Q1" s="79"/>
       <c r="R1" s="79"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>102</v>
       </c>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="P2" s="35"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
@@ -22785,7 +22785,7 @@
       <c r="O3" s="84"/>
       <c r="P3" s="35"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="85">
         <v>7658</v>
       </c>
@@ -22832,7 +22832,7 @@
         <v>-105.77028571428589</v>
       </c>
     </row>
-    <row r="5" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="88"/>
       <c r="B5" s="89"/>
       <c r="C5" s="89"/>
@@ -22849,7 +22849,7 @@
       <c r="N5" s="89"/>
       <c r="O5" s="58"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="85">
         <v>8142</v>
       </c>
@@ -22899,7 +22899,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -22916,7 +22916,7 @@
       <c r="N7" s="91"/>
       <c r="O7" s="58"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="85">
         <v>8824</v>
       </c>
@@ -22959,7 +22959,7 @@
         <v>50.13333333333333</v>
       </c>
     </row>
-    <row r="9" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="90"/>
       <c r="B9" s="91"/>
       <c r="C9" s="91"/>
@@ -22976,7 +22976,7 @@
       <c r="N9" s="91"/>
       <c r="O9" s="58"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="85">
         <v>8127</v>
       </c>
@@ -23023,7 +23023,7 @@
         <v>24.375135929463628</v>
       </c>
     </row>
-    <row r="11" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="90"/>
       <c r="B11" s="91"/>
       <c r="C11" s="91"/>
@@ -23040,7 +23040,7 @@
       <c r="N11" s="91"/>
       <c r="O11" s="58"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="85">
         <v>8183</v>
       </c>
@@ -23090,7 +23090,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="90"/>
       <c r="B13" s="91"/>
       <c r="C13" s="91"/>
@@ -23107,7 +23107,7 @@
       <c r="N13" s="91"/>
       <c r="O13" s="58"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="85">
         <v>8886</v>
       </c>
@@ -23154,7 +23154,7 @@
         <v>89.17785714285712</v>
       </c>
     </row>
-    <row r="15" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="90"/>
       <c r="B15" s="91"/>
       <c r="C15" s="91"/>
@@ -23171,7 +23171,7 @@
       <c r="N15" s="91"/>
       <c r="O15" s="58"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="85">
         <v>8887</v>
       </c>
@@ -23216,7 +23216,7 @@
         <v>34.40668587896252</v>
       </c>
     </row>
-    <row r="17" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="90"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91"/>
@@ -23233,7 +23233,7 @@
       <c r="N17" s="91"/>
       <c r="O17" s="58"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="85">
         <v>8670</v>
       </c>
@@ -23283,7 +23283,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="90"/>
       <c r="B19" s="91"/>
       <c r="C19" s="91"/>
@@ -23300,7 +23300,7 @@
       <c r="N19" s="91"/>
       <c r="O19" s="58"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="85">
         <v>8907</v>
       </c>
@@ -23339,7 +23339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="90"/>
       <c r="B21" s="91"/>
       <c r="C21" s="91"/>
@@ -23356,7 +23356,7 @@
       <c r="N21" s="91"/>
       <c r="O21" s="58"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="85">
         <v>9065</v>
       </c>
@@ -23397,7 +23397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="90"/>
       <c r="B23" s="91"/>
       <c r="C23" s="91"/>
@@ -23414,7 +23414,7 @@
       <c r="N23" s="91"/>
       <c r="O23" s="58"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -23453,7 +23453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="95"/>
       <c r="C25" s="95"/>
@@ -23470,7 +23470,7 @@
       <c r="N25" s="95"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -23515,7 +23515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="91"/>
@@ -23532,7 +23532,7 @@
       <c r="N27" s="91"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -23575,7 +23575,7 @@
         <v>-6.366734006734025</v>
       </c>
     </row>
-    <row r="29" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="90"/>
       <c r="B29" s="91"/>
       <c r="C29" s="91"/>
@@ -23592,7 +23592,7 @@
       <c r="N29" s="91"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -23635,7 +23635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="90"/>
       <c r="B31" s="91"/>
       <c r="C31" s="91"/>
@@ -23652,7 +23652,7 @@
       <c r="N31" s="91"/>
       <c r="O31" s="58"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -23699,7 +23699,7 @@
         <v>10.108588351431392</v>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="90"/>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
@@ -23716,7 +23716,7 @@
       <c r="N33" s="91"/>
       <c r="O33" s="58"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -23761,7 +23761,7 @@
         <v>4.512234432234419</v>
       </c>
     </row>
-    <row r="35" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="90"/>
       <c r="B35" s="91"/>
       <c r="C35" s="91"/>
@@ -23778,7 +23778,7 @@
       <c r="N35" s="91"/>
       <c r="O35" s="58"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -23821,7 +23821,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="37" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="90"/>
       <c r="B37" s="91"/>
       <c r="C37" s="91"/>
@@ -23838,7 +23838,7 @@
       <c r="N37" s="91"/>
       <c r="O37" s="58"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -23879,7 +23879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="90"/>
       <c r="B39" s="91"/>
       <c r="C39" s="91"/>
@@ -23896,7 +23896,7 @@
       <c r="N39" s="91"/>
       <c r="O39" s="58"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -23941,7 +23941,7 @@
         <v>-1063.9049999999997</v>
       </c>
     </row>
-    <row r="41" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="90"/>
       <c r="B41" s="91"/>
       <c r="C41" s="91"/>
@@ -23958,7 +23958,7 @@
       <c r="N41" s="91"/>
       <c r="O41" s="58"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -24001,7 +24001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="90"/>
       <c r="B43" s="91"/>
       <c r="C43" s="91"/>
@@ -24018,7 +24018,7 @@
       <c r="N43" s="91"/>
       <c r="O43" s="58"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -24055,7 +24055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="90"/>
       <c r="B45" s="91"/>
       <c r="C45" s="91"/>
@@ -24072,7 +24072,7 @@
       <c r="N45" s="96"/>
       <c r="O45" s="97"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -24113,7 +24113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="90"/>
       <c r="B47" s="91"/>
       <c r="C47" s="91"/>
@@ -24130,7 +24130,7 @@
       <c r="N47" s="96"/>
       <c r="O47" s="97"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>8337</v>
       </c>
@@ -24173,7 +24173,7 @@
         <v>56.53631284916201</v>
       </c>
     </row>
-    <row r="49" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="90"/>
       <c r="B49" s="91"/>
       <c r="C49" s="91"/>
@@ -24190,7 +24190,7 @@
       <c r="N49" s="96"/>
       <c r="O49" s="97"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>9240</v>
       </c>
@@ -24232,7 +24232,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="90"/>
       <c r="B51" s="91"/>
       <c r="C51" s="91"/>
@@ -24249,7 +24249,7 @@
       <c r="N51" s="96"/>
       <c r="O51" s="97"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="101">
         <v>7428</v>
       </c>
@@ -24294,7 +24294,7 @@
         <v>14.333675527039448</v>
       </c>
     </row>
-    <row r="53" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="90"/>
       <c r="B53" s="91"/>
       <c r="C53" s="91"/>
@@ -24311,7 +24311,7 @@
       <c r="N53" s="96"/>
       <c r="O53" s="97"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>9351</v>
       </c>
@@ -24356,7 +24356,7 @@
         <v>-134.73684210526315</v>
       </c>
     </row>
-    <row r="55" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="90"/>
       <c r="B55" s="91"/>
       <c r="C55" s="91"/>
@@ -24373,7 +24373,7 @@
       <c r="N55" s="96"/>
       <c r="O55" s="97"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="59">
         <v>7429</v>
       </c>
@@ -24418,7 +24418,7 @@
         <v>242.69662921348313</v>
       </c>
     </row>
-    <row r="57" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="90"/>
       <c r="B57" s="91"/>
       <c r="C57" s="91"/>
@@ -24435,7 +24435,7 @@
       <c r="N57" s="96"/>
       <c r="O57" s="97"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="59">
         <v>9508</v>
       </c>
@@ -24472,7 +24472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="90"/>
       <c r="B59" s="91"/>
       <c r="C59" s="91"/>
@@ -24489,7 +24489,7 @@
       <c r="N59" s="96"/>
       <c r="O59" s="97"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="59"/>
       <c r="B60" s="98"/>
       <c r="C60" s="99"/>
@@ -24506,7 +24506,7 @@
       <c r="N60" s="98"/>
       <c r="O60" s="60"/>
     </row>
-    <row r="61" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="90"/>
       <c r="B61" s="91"/>
       <c r="C61" s="91"/>
@@ -24523,7 +24523,7 @@
       <c r="N61" s="96"/>
       <c r="O61" s="97"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="59"/>
       <c r="B62" s="98" t="s">
         <v>60</v>
@@ -24544,7 +24544,7 @@
       <c r="N62" s="98"/>
       <c r="O62" s="60"/>
     </row>
-    <row r="63" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="90"/>
       <c r="B63" s="91"/>
       <c r="C63" s="91"/>
@@ -24561,7 +24561,7 @@
       <c r="N63" s="96"/>
       <c r="O63" s="97"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>8946</v>
       </c>
@@ -24602,7 +24602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="7.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="7.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="90"/>
       <c r="B65" s="91"/>
       <c r="C65" s="91"/>
@@ -24619,7 +24619,7 @@
       <c r="N65" s="96"/>
       <c r="O65" s="97"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="102">
         <v>8308</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>-25.71043082686644</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="102">
         <f>'Main Sheet'!A68</f>
       </c>
@@ -24699,7 +24699,7 @@
         <f>SUM(M67/(N67+I67))</f>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="36"/>
@@ -24716,7 +24716,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="36"/>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="35"/>
       <c r="B69" s="35"/>
       <c r="C69" s="36"/>
@@ -24733,7 +24733,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="35"/>
     </row>
-    <row r="70" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
         <v>122</v>
       </c>
@@ -24768,7 +24768,7 @@
       <c r="N70" s="35"/>
       <c r="O70" s="35"/>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="59"/>
       <c r="B71" s="98" t="s">
         <v>126</v>
@@ -25151,7 +25151,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD110"/>
+  <dimension ref="A1:AB110"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.5390625"/>
   <cols>
     <col min="1" max="1" width="11" style="35" customWidth="1"/>
@@ -25162,7 +25162,7 @@
     <col min="6" max="17" width="11.43" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="46.5" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" ht="46.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25183,7 +25183,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="115"/>
       <c r="B2" s="116" t="s">
         <v>127</v>
@@ -25245,7 +25245,7 @@
       <c r="AA2" s="120"/>
       <c r="AB2" s="121"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="122" t="s">
         <v>143</v>
       </c>
@@ -25303,7 +25303,7 @@
       <c r="AA3" s="129"/>
       <c r="AB3" s="130"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>7658</v>
       </c>
@@ -25339,7 +25339,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
       <c r="C5" s="70"/>
@@ -25358,7 +25358,7 @@
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>8142</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
       <c r="C7" s="70"/>
@@ -25411,7 +25411,7 @@
       <c r="P7" s="70"/>
       <c r="Q7" s="70"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>8824</v>
       </c>
@@ -25445,7 +25445,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
       <c r="C9" s="70"/>
@@ -25464,7 +25464,7 @@
       <c r="P9" s="70"/>
       <c r="Q9" s="70"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>8127</v>
       </c>
@@ -25502,7 +25502,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
       <c r="C11" s="70"/>
@@ -25521,7 +25521,7 @@
       <c r="P11" s="70"/>
       <c r="Q11" s="70"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8183</v>
       </c>
@@ -25559,7 +25559,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -25578,7 +25578,7 @@
       <c r="P13" s="61"/>
       <c r="Q13" s="61"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>8886</v>
       </c>
@@ -25616,7 +25616,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="B15" s="61"/>
       <c r="C15" s="61"/>
@@ -25635,7 +25635,7 @@
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>8887</v>
       </c>
@@ -25668,7 +25668,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="131"/>
     </row>
-    <row r="17" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="132"/>
       <c r="B17" s="132"/>
       <c r="C17" s="132"/>
@@ -25687,7 +25687,7 @@
       <c r="P17" s="132"/>
       <c r="Q17" s="132"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>8670</v>
       </c>
@@ -25720,7 +25720,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="131"/>
     </row>
-    <row r="19" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -25739,7 +25739,7 @@
       <c r="P19" s="61"/>
       <c r="Q19" s="61"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>8907</v>
       </c>
@@ -25770,7 +25770,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="131"/>
     </row>
-    <row r="21" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="61"/>
       <c r="B21" s="61"/>
       <c r="C21" s="61"/>
@@ -25789,7 +25789,7 @@
       <c r="P21" s="61"/>
       <c r="Q21" s="61"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>9065</v>
       </c>
@@ -25824,7 +25824,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="131"/>
     </row>
-    <row r="23" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="133"/>
       <c r="B23" s="134"/>
       <c r="C23" s="134"/>
@@ -25843,7 +25843,7 @@
       <c r="P23" s="134"/>
       <c r="Q23" s="137"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>9259</v>
       </c>
@@ -25876,7 +25876,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="131"/>
     </row>
-    <row r="25" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="66"/>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -25895,7 +25895,7 @@
       <c r="P25" s="66"/>
       <c r="Q25" s="66"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>8352</v>
       </c>
@@ -25926,7 +25926,7 @@
       <c r="P26" s="54"/>
       <c r="Q26" s="131"/>
     </row>
-    <row r="27" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="61"/>
       <c r="B27" s="61"/>
       <c r="C27" s="61"/>
@@ -25945,7 +25945,7 @@
       <c r="P27" s="61"/>
       <c r="Q27" s="61"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>8234</v>
       </c>
@@ -25977,7 +25977,7 @@
       <c r="Q28" s="131"/>
       <c r="S28" s="138"/>
     </row>
-    <row r="29" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="61"/>
       <c r="B29" s="61"/>
       <c r="C29" s="61"/>
@@ -25996,7 +25996,7 @@
       <c r="P29" s="61"/>
       <c r="Q29" s="61"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>8214</v>
       </c>
@@ -26032,7 +26032,7 @@
       <c r="Q30" s="131"/>
       <c r="S30" s="139"/>
     </row>
-    <row r="31" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
       <c r="B31" s="61"/>
       <c r="C31" s="61"/>
@@ -26051,7 +26051,7 @@
       <c r="P31" s="61"/>
       <c r="Q31" s="61"/>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>6792</v>
       </c>
@@ -26080,7 +26080,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="131"/>
     </row>
-    <row r="33" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="61"/>
       <c r="B33" s="61"/>
       <c r="C33" s="61"/>
@@ -26099,7 +26099,7 @@
       <c r="P33" s="61"/>
       <c r="Q33" s="61"/>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>8840</v>
       </c>
@@ -26130,7 +26130,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="131"/>
     </row>
-    <row r="35" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="61"/>
       <c r="B35" s="61"/>
       <c r="C35" s="61"/>
@@ -26149,7 +26149,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>8769</v>
       </c>
@@ -26182,7 +26182,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="131"/>
     </row>
-    <row r="37" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61"/>
@@ -26201,7 +26201,7 @@
       <c r="P37" s="61"/>
       <c r="Q37" s="61"/>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>7901</v>
       </c>
@@ -26237,7 +26237,7 @@
       <c r="Q38" s="131"/>
       <c r="S38" s="139"/>
     </row>
-    <row r="39" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="61"/>
       <c r="B39" s="61"/>
       <c r="C39" s="61"/>
@@ -26256,7 +26256,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>8923</v>
       </c>
@@ -26291,7 +26291,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="131"/>
     </row>
-    <row r="41" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="61"/>
       <c r="B41" s="61"/>
       <c r="C41" s="61"/>
@@ -26310,7 +26310,7 @@
       <c r="P41" s="61"/>
       <c r="Q41" s="61"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>7864</v>
       </c>
@@ -26340,7 +26340,7 @@
       <c r="Q42" s="131"/>
       <c r="S42" s="139"/>
     </row>
-    <row r="43" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="61"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61"/>
@@ -26359,7 +26359,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="19">
         <v>7912</v>
       </c>
@@ -26399,7 +26399,7 @@
       </c>
       <c r="S44" s="139"/>
     </row>
-    <row r="45" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="61"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
@@ -26418,7 +26418,7 @@
       <c r="P45" s="61"/>
       <c r="Q45" s="61"/>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>8360</v>
       </c>
@@ -26447,7 +26447,7 @@
       <c r="P46" s="98"/>
       <c r="Q46" s="140"/>
     </row>
-    <row r="47" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="61"/>
       <c r="B47" s="61"/>
       <c r="C47" s="61"/>
@@ -26466,7 +26466,7 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="19">
         <v>8337</v>
       </c>
@@ -26499,7 +26499,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="131"/>
     </row>
-    <row r="49" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="61"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61"/>
@@ -26518,7 +26518,7 @@
       <c r="P49" s="61"/>
       <c r="Q49" s="61"/>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="19">
         <v>9240</v>
       </c>
@@ -26551,7 +26551,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="131"/>
     </row>
-    <row r="51" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="61"/>
@@ -26570,7 +26570,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="19">
         <v>7428</v>
       </c>
@@ -26606,7 +26606,7 @@
       <c r="Q52" s="131"/>
       <c r="S52" s="139"/>
     </row>
-    <row r="53" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="61"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61"/>
@@ -26625,7 +26625,7 @@
       <c r="P53" s="61"/>
       <c r="Q53" s="61"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="19">
         <v>9351</v>
       </c>
@@ -26661,7 +26661,7 @@
       <c r="Q54" s="131"/>
       <c r="S54" s="138"/>
     </row>
-    <row r="55" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="61"/>
       <c r="B55" s="61"/>
       <c r="C55" s="61"/>
@@ -26680,7 +26680,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="19">
         <v>7429</v>
       </c>
@@ -26714,7 +26714,7 @@
       <c r="Q56" s="131"/>
       <c r="S56" s="139"/>
     </row>
-    <row r="57" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="61"/>
@@ -26733,7 +26733,7 @@
       <c r="P57" s="61"/>
       <c r="Q57" s="61"/>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="19">
         <v>9508</v>
       </c>
@@ -26768,7 +26768,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="61"/>
       <c r="B59" s="61"/>
       <c r="C59" s="61"/>
@@ -26787,7 +26787,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="20"/>
       <c r="C60" s="54"/>
@@ -26806,7 +26806,7 @@
       <c r="P60" s="54"/>
       <c r="Q60" s="131"/>
     </row>
-    <row r="61" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="61"/>
       <c r="B61" s="61"/>
       <c r="C61" s="61"/>
@@ -26825,7 +26825,7 @@
       <c r="P61" s="61"/>
       <c r="Q61" s="61"/>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>60</v>
@@ -26846,7 +26846,7 @@
       <c r="P62" s="54"/>
       <c r="Q62" s="131"/>
     </row>
-    <row r="63" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="61"/>
@@ -26865,7 +26865,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>8946</v>
       </c>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="Q64" s="131"/>
     </row>
-    <row r="65" ht="6" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" ht="6" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="61"/>
       <c r="B65" s="61"/>
       <c r="C65" s="61"/>
@@ -26917,7 +26917,7 @@
       <c r="P65" s="61"/>
       <c r="Q65" s="61"/>
     </row>
-    <row r="66" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <v>8308</v>
       </c>
@@ -26956,7 +26956,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <f>'Main Sheet'!A68</f>
       </c>
@@ -26985,7 +26985,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="54"/>
     </row>
-    <row r="68" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="142"/>
       <c r="B68" s="143"/>
       <c r="C68" s="35"/>
@@ -27004,7 +27004,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="144"/>
     </row>
-    <row r="69" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="142"/>
       <c r="B69" s="143"/>
       <c r="C69" s="35"/>
@@ -27023,7 +27023,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="144"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="145"/>
       <c r="B70" s="145"/>
       <c r="C70" s="145"/>
@@ -27042,7 +27042,7 @@
       <c r="P70" s="145"/>
       <c r="Q70" s="145"/>
     </row>
-    <row r="71" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="142"/>
       <c r="B71" s="146" t="s">
         <v>147</v>
@@ -27087,7 +27087,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="142"/>
       <c r="B72" s="77" t="s">
         <v>148</v>
@@ -27126,7 +27126,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="142"/>
       <c r="B73" s="77" t="s">
         <v>149</v>
@@ -27155,7 +27155,7 @@
       <c r="P73" s="20"/>
       <c r="Q73" s="20"/>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="142"/>
       <c r="B74" s="148" t="s">
         <v>150</v>
@@ -27200,7 +27200,7 @@
         <v>1478.4</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="142"/>
       <c r="B75" s="151" t="s">
         <v>151</v>
@@ -27245,7 +27245,7 @@
         <v>-828.4</v>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="142"/>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -27264,7 +27264,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="144"/>
     </row>
-    <row r="77" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="142"/>
       <c r="B77" s="156" t="s">
         <v>152</v>
@@ -27311,7 +27311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="161"/>
       <c r="B78" s="162" t="s">
         <v>154</v>
@@ -27356,7 +27356,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="35"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -27375,7 +27375,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
     </row>
-    <row r="80" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="35"/>
       <c r="B80" s="164" t="s">
         <v>155</v>
@@ -27398,7 +27398,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
     </row>
-    <row r="81" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="35"/>
       <c r="B81" s="167" t="s">
         <v>157</v>
@@ -27421,7 +27421,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
     </row>
-    <row r="82" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:17"